--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -653,7 +653,7 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="50" customWidth="1" min="12" max="12"/>
@@ -758,12 +758,16 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Committed 0536abb, pushed to origin/main 2026-08-21. Production and git are back in sync.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -802,22 +806,14 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Sahil</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Started scoping the schema fields</t>
+          <t>Shipped 2026-08-21: Product/Offer JSON-LD (lib/dealSchema.ts) added to /deals, /postcode/[area] (both branches) and /providers/[slug]. Prices mirror visible content; no fabricated aggregateRating (no real review-count field in the data model).</t>
         </is>
       </c>
     </row>
@@ -1782,14 +1778,14 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Built locally — not deployed</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr"/>
       <c r="K25" s="3" t="inlineStr"/>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Component + page built and validated (npm run build, local render check) 2026-08-21. Not committed/pushed/deployed — held back pending the git/Vercel reconciliation (see rank #1).</t>
+          <t>Live at /tools/broadband-cost-calculator, committed and deployed 2026-08-21.</t>
         </is>
       </c>
     </row>
@@ -2697,9 +2693,9 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="50" customWidth="1" min="12" max="12"/>
@@ -2794,10 +2790,14 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Done</t>
@@ -2844,10 +2844,14 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Done</t>
@@ -2894,10 +2898,14 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Done</t>
@@ -2944,10 +2952,14 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Done</t>
@@ -2994,10 +3006,14 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Done</t>
@@ -3044,10 +3060,14 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Done</t>
@@ -3094,10 +3114,14 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Done</t>
@@ -3144,10 +3168,14 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
           <t>Done</t>
@@ -3194,10 +3222,14 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Done</t>
@@ -3244,10 +3276,14 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
           <t>Done</t>
@@ -3294,10 +3330,14 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Done</t>
@@ -3344,10 +3384,14 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
           <t>Done</t>
@@ -3394,10 +3438,14 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Done</t>
@@ -3444,10 +3492,14 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
           <t>Done</t>
@@ -3494,10 +3546,14 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Done</t>
@@ -3544,10 +3600,14 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
           <t>Done</t>
@@ -3594,10 +3654,14 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Done</t>
@@ -3644,10 +3708,14 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
           <t>Done</t>
@@ -3694,10 +3762,14 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
@@ -3744,13 +3816,13 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
+          <t>Planned — not live</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Built locally — not deployed</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -3794,7 +3866,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
+          <t>Planned — not live</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -3844,7 +3916,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
+          <t>Planned — not live</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr"/>
@@ -3894,7 +3966,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
+          <t>Planned — not live</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -3944,7 +4016,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
+          <t>Planned — not live</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr"/>
@@ -3994,7 +4066,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
+          <t>Planned — not live</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -4044,7 +4116,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
+          <t>Planned — not live</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr"/>
@@ -4094,7 +4166,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
+          <t>Planned — not live</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -4144,10 +4216,14 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
           <t>Done</t>
@@ -4194,7 +4270,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
+          <t>Planned — not live</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -4244,7 +4320,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
+          <t>Planned — not live</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr"/>
@@ -4294,7 +4370,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
+          <t>Planned — not live</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
@@ -4344,7 +4420,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
+          <t>Planned — not live</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr"/>
@@ -4394,7 +4470,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
+          <t>Planned — not live</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -4558,7 +4634,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -4614,7 +4690,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5169,7 +5245,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>44 total (33 page builds, 11 feature/strategy builds); 19 already marked Done.</t>
+          <t>44 total (33 page builds, 11 feature/strategy builds); 22 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -854,12 +854,16 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-21: lib/postcodeStorage.ts + components/PostcodeContextBar.tsx. PostcodeChecker now persists to localStorage on submit; context bar shown on /deals, /compare and /providers/[slug] when a postcode is stored, with change/clear actions. SSR-safe (renders null server-side, no hydration mismatch).</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -3816,10 +3820,14 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Planned — not live</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
           <t>Done</t>
@@ -4746,7 +4754,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -5245,7 +5253,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>44 total (33 page builds, 11 feature/strategy builds); 22 already marked Done.</t>
+          <t>44 total (33 page builds, 11 feature/strategy builds); 23 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Methodology'!$A$1:$B$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L45" headerRowCount="1">
-  <autoFilter ref="A1:L45"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L46" headerRowCount="1">
+  <autoFilter ref="A1:L46"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -216,8 +216,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L12" headerRowCount="1">
-  <autoFilter ref="A1:L12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L13" headerRowCount="1">
+  <autoFilter ref="A1:L13"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -575,7 +575,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -775,7 +775,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>feat-product-offer-schema</t>
+          <t>feat-uk-wide-postcode-coverage</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -785,23 +785,23 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content/Trust</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Product/Offer schema on deal cards</t>
+          <t>UK-wide real postcode coverage data (Ofcom)</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -813,7 +813,7 @@
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Shipped 2026-08-21: Product/Offer JSON-LD (lib/dealSchema.ts) added to /deals, /postcode/[area] (both branches) and /providers/[slug]. Prices mirror visible content; no fabricated aggregateRating (no real review-count field in the data model).</t>
+          <t>Shipped 2026-08-22: real Ofcom Connected Nations coverage data for 2,818 UK postcode districts (data/postcode-district-coverage.json via scripts/build_postcode_coverage.py), replacing the generic fallback on /postcode/[area] for any district not in the curated ~50-town dataset. Source: Ofcom, July 2024 edition (most recent at postcode-unit granularity) — re-check for a newer edition periodically.</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>feat-persistent-postcode</t>
+          <t>feat-product-offer-schema</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -833,23 +833,23 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Persistent postcode across the site</t>
+          <t>Product/Offer schema on deal cards</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Shipped 2026-08-21: lib/postcodeStorage.ts + components/PostcodeContextBar.tsx. PostcodeChecker now persists to localStorage on submit; context bar shown on /deals, /compare and /providers/[slug] when a postcode is stored, with change/clear actions. SSR-safe (renders null server-side, no hydration mismatch).</t>
+          <t>Shipped 2026-08-21: Product/Offer JSON-LD (lib/dealSchema.ts) added to /deals, /postcode/[area] (both branches) and /providers/[slug]. Prices mirror visible content; no fabricated aggregateRating (no real review-count field in the data model).</t>
         </is>
       </c>
     </row>
@@ -871,33 +871,33 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>page-providers/compare/hyperoptic-vs-youfibre</t>
+          <t>feat-persistent-postcode</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Hyperoptic vs YouFibre broadband: which is better in 2026?</t>
+          <t>Persistent postcode across the site</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>71</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -907,7 +907,11 @@
       </c>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-21: lib/postcodeStorage.ts + components/PostcodeContextBar.tsx. PostcodeChecker now persists to localStorage on submit; context bar shown on /deals, /compare and /providers/[slug] when a postcode is stored, with change/clear actions. SSR-safe (renders null server-side, no hydration mismatch).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -915,7 +919,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>page-postcode/sheffield</t>
+          <t>page-providers/compare/hyperoptic-vs-youfibre</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -930,14 +934,14 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Broadband providers in Sheffield: coverage and best deals</t>
+          <t>Hyperoptic vs YouFibre broadband: which is better in 2026?</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>66.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -959,7 +963,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>page-guides/static-ip-business-broadband-explained</t>
+          <t>page-postcode/sheffield</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -974,18 +978,18 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Static IP business broadband: when you need one and how much it costs</t>
+          <t>Broadband providers in Sheffield: coverage and best deals</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>66.3</v>
+        <v>66.8</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>46.1</v>
+        <v>40</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -1003,7 +1007,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>page-guides/student-broadband-by-university-city</t>
+          <t>page-guides/static-ip-business-broadband-explained</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1018,18 +1022,18 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Student broadband by university city: short-term and rolling deals</t>
+          <t>Static IP business broadband: when you need one and how much it costs</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>36.2</v>
+        <v>46.1</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1047,7 +1051,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>page-postcode/edinburgh</t>
+          <t>page-guides/student-broadband-by-university-city</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1062,18 +1066,18 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Broadband providers in Edinburgh: coverage and best deals</t>
+          <t>Student broadband by university city: short-term and rolling deals</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>65.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>40</v>
+        <v>36.2</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1091,7 +1095,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>page-guides/small-office-broadband-setup-uk</t>
+          <t>page-postcode/edinburgh</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1106,14 +1110,14 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Small office broadband setup: routers, backup and support checklist</t>
+          <t>Broadband providers in Edinburgh: coverage and best deals</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>65.8</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>41.9</v>
+        <v>40</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1135,7 +1139,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>page-providers/compare/bt-vs-plusnet</t>
+          <t>page-guides/small-office-broadband-setup-uk</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1150,18 +1154,18 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>BT vs Plusnet broadband: which is better in 2026?</t>
+          <t>Small office broadband setup: routers, backup and support checklist</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>65.5</v>
+        <v>65.8</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>36.4</v>
+        <v>41.9</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1179,7 +1183,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>page-postcode/glasgow</t>
+          <t>page-providers/compare/bt-vs-plusnet</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1194,18 +1198,18 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Broadband providers in Glasgow: coverage and best deals</t>
+          <t>BT vs Plusnet broadband: which is better in 2026?</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
         <v>65.5</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>40.2</v>
+        <v>36.4</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1223,7 +1227,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>page-postcode/liverpool</t>
+          <t>page-postcode/glasgow</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1238,14 +1242,14 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Broadband providers in Liverpool: coverage and best deals</t>
+          <t>Broadband providers in Glasgow: coverage and best deals</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
         <v>65.5</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
@@ -1267,7 +1271,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>page-guides/broadband-for-landlords-and-hmos-uk</t>
+          <t>page-postcode/liverpool</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1282,18 +1286,18 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Broadband for landlords and HMOs: what to set up and who pays</t>
+          <t>Broadband providers in Liverpool: coverage and best deals</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>65.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>36.6</v>
+        <v>40.1</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1311,7 +1315,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>page-postcode/leeds</t>
+          <t>page-guides/broadband-for-landlords-and-hmos-uk</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1326,18 +1330,18 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Broadband providers in Leeds: coverage and best deals</t>
+          <t>Broadband for landlords and HMOs: what to set up and who pays</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
         <v>65.09999999999999</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>40.3</v>
+        <v>36.6</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1355,7 +1359,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>page-providers/compare/ee-vs-talktalk</t>
+          <t>page-postcode/leeds</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1370,18 +1374,18 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>EE vs TalkTalk broadband: which is better in 2026?</t>
+          <t>Broadband providers in Leeds: coverage and best deals</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>65</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>36.4</v>
+        <v>40.3</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1399,7 +1403,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>page-postcode/bristol</t>
+          <t>page-providers/compare/ee-vs-talktalk</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1414,18 +1418,18 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Broadband providers in Bristol: coverage and best deals</t>
+          <t>EE vs TalkTalk broadband: which is better in 2026?</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>40.8</v>
+        <v>36.4</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1443,7 +1447,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>page-postcode/birmingham</t>
+          <t>page-postcode/bristol</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1458,14 +1462,14 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Broadband providers in Birmingham: coverage and best deals</t>
+          <t>Broadband providers in Bristol: coverage and best deals</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>64.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>41.1</v>
+        <v>40.8</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1487,7 +1491,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>page-postcode/manchester</t>
+          <t>page-postcode/birmingham</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1502,14 +1506,14 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Broadband providers in Manchester: coverage and best deals</t>
+          <t>Broadband providers in Birmingham: coverage and best deals</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>64.2</v>
+        <v>64.5</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -1531,7 +1535,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>page-guides/leased-line-cost-uk-explained</t>
+          <t>page-postcode/manchester</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1546,14 +1550,14 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Leased line cost UK: what small businesses actually pay</t>
+          <t>Broadband providers in Manchester: coverage and best deals</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>63.3</v>
+        <v>64.2</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>58.6</v>
+        <v>41.2</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1575,7 +1579,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>page-guides/starlink-vs-fibre-broadband-uk</t>
+          <t>page-guides/leased-line-cost-uk-explained</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1590,14 +1594,14 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Starlink vs fibre broadband: when satellite makes sense in the UK</t>
+          <t>Leased line cost UK: what small businesses actually pay</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>62.9</v>
+        <v>63.3</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>35.4</v>
+        <v>58.6</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -1619,7 +1623,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>page-providers/compare/virgin-media-vs-sky</t>
+          <t>page-guides/starlink-vs-fibre-broadband-uk</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1634,14 +1638,14 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Virgin Media vs Sky broadband: which is better in 2026?</t>
+          <t>Starlink vs fibre broadband: when satellite makes sense in the UK</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>62.8</v>
+        <v>62.9</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>36.2</v>
+        <v>35.4</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1663,7 +1667,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>page-guides/january-broadband-deals-uk</t>
+          <t>page-providers/compare/virgin-media-vs-sky</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1678,14 +1682,14 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>January broadband deals UK: new-year switching guide</t>
+          <t>Virgin Media vs Sky broadband: which is better in 2026?</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>61.7</v>
+        <v>62.8</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>36.9</v>
+        <v>36.2</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -1694,7 +1698,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr"/>
@@ -1707,33 +1711,33 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket</t>
+          <t>page-guides/january-broadband-deals-uk</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Shortlist / compare-basket pattern</t>
+          <t>January broadband deals UK: new-year switching guide</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>61</v>
+        <v>61.7</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>64</v>
+        <v>36.9</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1751,47 +1755,43 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>page-tools/broadband-cost-calculator</t>
+          <t>feat-shortlist-compare-basket</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Broadband cost calculator: true monthly and contract-length cost</t>
+          <t>Shortlist / compare-basket pattern</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>27.6</v>
+        <v>64</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr"/>
       <c r="K25" s="3" t="inlineStr"/>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>Live at /tools/broadband-cost-calculator, committed and deployed 2026-08-21.</t>
-        </is>
-      </c>
+      <c r="L25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>page-providers/onestream</t>
+          <t>page-tools/broadband-cost-calculator</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1809,19 +1809,19 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Onestream — plans, coverage and Awin-tracked deals</t>
+          <t>Broadband cost calculator: true monthly and contract-length cost</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>59.4</v>
+        <v>59.9</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>28</v>
+        <v>27.6</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1830,12 +1830,16 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Live at /tools/broadband-cost-calculator, committed and deployed 2026-08-21.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -1843,7 +1847,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>page-guides/no-credit-check-broadband-uk</t>
+          <t>page-providers/onestream</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1858,18 +1862,18 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>No credit check broadband in the UK: options and what to expect</t>
+          <t>Onestream — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>34.8</v>
+        <v>28</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -1887,33 +1891,33 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>feat-review-aggregation-module</t>
+          <t>page-guides/no-credit-check-broadband-uk</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Real review-aggregation trust module</t>
+          <t>No credit check broadband in the UK: options and what to expect</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>59</v>
+        <v>59.3</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>62</v>
+        <v>34.8</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1931,33 +1935,33 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>page-providers/brsk</t>
+          <t>feat-review-aggregation-module</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Brsk — plans, coverage and Awin-tracked deals</t>
+          <t>Real review-aggregation trust module</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
         <v>59</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>28.5</v>
+        <v>62</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -1975,7 +1979,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>page-guides/fttp-vs-fttc-explained</t>
+          <t>page-providers/brsk</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1990,14 +1994,14 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>FTTP vs FTTC: what the difference means for your speed</t>
+          <t>Brsk — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>58.4</v>
+        <v>59</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>27.8</v>
+        <v>28.5</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -2019,7 +2023,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>page-guides/best-mesh-wifi-for-your-broadband-router</t>
+          <t>page-guides/fttp-vs-fttc-explained</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2034,18 +2038,18 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
+          <t>FTTP vs FTTC: what the difference means for your speed</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
         <v>58.4</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>34</v>
+        <v>27.8</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -2063,7 +2067,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>page-guides/broadband-help-if-you-claim-benefits-uk</t>
+          <t>page-guides/best-mesh-wifi-for-your-broadband-router</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2078,18 +2082,18 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
+          <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>58.2</v>
+        <v>58.4</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>27.5</v>
+        <v>34</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2107,7 +2111,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>page-providers/gigaclear</t>
+          <t>page-guides/broadband-help-if-you-claim-benefits-uk</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2122,18 +2126,18 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
+          <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>56.9</v>
+        <v>58.2</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>27.9</v>
+        <v>27.5</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -2151,7 +2155,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>page-providers/youfibre</t>
+          <t>page-providers/gigaclear</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2166,14 +2170,14 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
+          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>56.6</v>
+        <v>56.9</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>28.7</v>
+        <v>27.9</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2182,7 +2186,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -2195,7 +2199,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>page-providers/cuckoo</t>
+          <t>page-providers/youfibre</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -2210,14 +2214,14 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
+          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>56.5</v>
+        <v>56.6</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>27.9</v>
+        <v>28.7</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
@@ -2226,7 +2230,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr"/>
@@ -2239,12 +2243,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>audit-city-hub-thinness</t>
+          <t>page-providers/cuckoo</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Content audit</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2254,18 +2258,18 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Verify each new city hub has a genuinely local fact</t>
+          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>56</v>
+        <v>56.5</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>50</v>
+        <v>27.9</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2283,12 +2287,12 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>page-guides/black-friday-broadband-deals-uk</t>
+          <t>audit-city-hub-thinness</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Content audit</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -2298,18 +2302,18 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
+          <t>Verify each new city hub has a genuinely local fact</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>55.8</v>
+        <v>56</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -2327,7 +2331,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>page-providers/shell-energy</t>
+          <t>page-guides/black-friday-broadband-deals-uk</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2342,18 +2346,18 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
+          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>55.7</v>
+        <v>55.8</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2371,7 +2375,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>page-research/broadband-customer-service-rankings-uk</t>
+          <t>page-providers/shell-energy</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2386,14 +2390,14 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
+          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>55.1</v>
+        <v>55.7</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
@@ -2415,7 +2419,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
+          <t>page-research/broadband-customer-service-rankings-uk</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2430,14 +2434,14 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Broadband complaints and the ombudsman: your UK rights</t>
+          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>54.7</v>
+        <v>55.1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>25.9</v>
+        <v>27.8</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2459,33 +2463,33 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>feat-price-drop-alerts</t>
+          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Broadband complaints and the ombudsman: your UK rights</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>49</v>
+        <v>54.7</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>55</v>
+        <v>25.9</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -2503,29 +2507,29 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2547,33 +2551,33 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -2591,7 +2595,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2601,19 +2605,19 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2635,7 +2639,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -2645,19 +2649,19 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
@@ -2673,8 +2677,52 @@
       <c r="K45" s="3" t="inlineStr"/>
       <c r="L45" s="3" t="inlineStr"/>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L45"/>
+  <autoFilter ref="A1:L46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3874,10 +3922,14 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Planned — not live</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
@@ -3924,10 +3976,14 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Planned — not live</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
           <t>Not started</t>
@@ -4516,7 +4572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4530,7 +4586,7 @@
     <col width="50" customWidth="1" min="9" max="9"/>
     <col width="50" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="41" customWidth="1" min="12" max="12"/>
+    <col width="49" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -4662,38 +4718,38 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content/Trust</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Product/Offer schema on deal cards</t>
+          <t>UK-wide real postcode coverage data (Ofcom)</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Uswitch marks up individual deals as Product + Quotation JSON-LD — the basis for price/rating rich snippets in search results. BroadbandPicker's deal cards don't carry this yet. Contained, well-scoped, clear SEO payoff.</t>
+          <t>Only ~50 curated postcode prefixes had real local data; every other UK postcode showed a generic 'we're expanding coverage' fallback with no area-specific information. Built from Ofcom's open Connected Nations postcode-level dataset (Open Government Licence), aggregated to district level, covering all 2,818 UK postcode districts with real gigabit/superfast/ultrafast availability percentages.</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>components/DealCard and deal-listing pages</t>
+          <t>data/postcode-district-coverage.json, data/postcodeDistrictCoverage.ts, app/postcode/[area]/page.tsx</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>scripts/build_postcode_coverage.py (re-run when Ofcom publishes a newer postcode-level edition)</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -4703,7 +4759,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>docs/competitor-landscape-scan.json</t>
+          <t>User request — real postcode-level availability</t>
         </is>
       </c>
     </row>
@@ -4718,33 +4774,33 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Persistent postcode across the site</t>
+          <t>Product/Offer schema on deal cards</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Once a postcode is entered on /postcode, carry it (localStorage, no account needed) into /deals, /compare and every provider page so the journey feels personal rather than resetting the question each time.</t>
+          <t>Uswitch marks up individual deals as Product + Quotation JSON-LD — the basis for price/rating rich snippets in search results. BroadbandPicker's deal cards don't carry this yet. Contained, well-scoped, clear SEO payoff.</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>PostcodeChecker + shared client state</t>
+          <t>components/DealCard and deal-listing pages</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4759,7 +4815,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>docs/competitor-landscape-scan.json</t>
         </is>
       </c>
     </row>
@@ -4779,19 +4835,19 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Shortlist / compare-basket pattern</t>
+          <t>Persistent postcode across the site</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Let users tick 2–3 deals and see them side by side, matching Uswitch and broadband.co.uk. Current /compare is one full table — good for browsing, weaker for a final decision between finalists.</t>
+          <t>Once a postcode is entered on /postcode, carry it (localStorage, no account needed) into /deals, /compare and every provider page so the journey feels personal rather than resetting the question each time.</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -4800,7 +4856,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>app/compare</t>
+          <t>PostcodeChecker + shared client state</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -4810,7 +4866,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -4830,24 +4886,24 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Real review-aggregation trust module</t>
+          <t>Shortlist / compare-basket pattern</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Blend the existing Ofcom-complaints research methodology with live Trustpilot scores into one visible trust module reused across provider and comparison pages, instead of a single quoted score per page.</t>
+          <t>Let users tick 2–3 deals and see them side by side, matching Uswitch and broadband.co.uk. Current /compare is one full table — good for browsing, weaker for a final decision between finalists.</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -4856,12 +4912,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>New shared component, used on provider + comparison pages</t>
+          <t>app/compare</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -4871,7 +4927,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -4881,29 +4937,29 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Content audit</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Verify each new city hub has a genuinely local fact</t>
+          <t>Real review-aggregation trust module</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>8 new city hubs (Birmingham, Bristol, Edinburgh, Glasgow, Leeds, Liverpool, Manchester, Sheffield) plus 50 existing postcode-prefix pages is a lot of near-identical templates. Each needs at least one real local fact (a named local altnet, a real coverage figure) or it reads as duplicate content — audit before building the next batch of cities.</t>
+          <t>Blend the existing Ofcom-complaints research methodology with live Trustpilot scores into one visible trust module reused across provider and comparison pages, instead of a single quoted score per page.</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -4912,12 +4968,12 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>data/priority-pages.ts city entries</t>
+          <t>New shared component, used on provider + comparison pages</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -4927,7 +4983,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>Growth playbook — Functionality pillar</t>
         </is>
       </c>
     </row>
@@ -4937,29 +4993,29 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Content audit</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Verify each new city hub has a genuinely local fact</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
+          <t>8 new city hubs (Birmingham, Bristol, Edinburgh, Glasgow, Leeds, Liverpool, Manchester, Sheffield) plus 50 existing postcode-prefix pages is a lot of near-identical templates. Each needs at least one real local fact (a named local altnet, a real coverage figure) or it reads as duplicate content — audit before building the next batch of cities.</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -4968,12 +5024,12 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
+          <t>data/priority-pages.ts city entries</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Email delivery provider</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -4983,7 +5039,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -4993,29 +5049,29 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -5024,12 +5080,12 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>New subscription flow + data/provider-live-deals.json</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>Email delivery provider</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -5039,7 +5095,7 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>Growth playbook — Functionality pillar</t>
         </is>
       </c>
     </row>
@@ -5049,43 +5105,43 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -5095,7 +5151,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -5110,24 +5166,24 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
@@ -5136,12 +5192,12 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -5151,7 +5207,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -5166,53 +5222,109 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F13" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="G13" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L12"/>
+  <autoFilter ref="A1:L13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5253,7 +5365,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>44 total (33 page builds, 11 feature/strategy builds); 23 already marked Done.</t>
+          <t>45 total (33 page builds, 12 feature/strategy builds); 24 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Methodology'!$A$1:$B$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L46" headerRowCount="1">
-  <autoFilter ref="A1:L46"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L47" headerRowCount="1">
+  <autoFilter ref="A1:L47"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -216,8 +216,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L13" headerRowCount="1">
-  <autoFilter ref="A1:L13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L14" headerRowCount="1">
+  <autoFilter ref="A1:L14"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -823,7 +823,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>feat-product-offer-schema</t>
+          <t>feat-broadband-match-quiz</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -838,32 +838,28 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Product/Offer schema on deal cards</t>
+          <t>Broadband Match: personalised recommendation quiz</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium-High</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Shipped 2026-08-21: Product/Offer JSON-LD (lib/dealSchema.ts) added to /deals, /postcode/[area] (both branches) and /providers/[slug]. Prices mirror visible content; no fabricated aggregateRating (no real review-count field in the data model).</t>
-        </is>
-      </c>
+      <c r="L4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -871,7 +867,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>feat-persistent-postcode</t>
+          <t>feat-product-offer-schema</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -881,23 +877,23 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Persistent postcode across the site</t>
+          <t>Product/Offer schema on deal cards</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -909,7 +905,7 @@
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Shipped 2026-08-21: lib/postcodeStorage.ts + components/PostcodeContextBar.tsx. PostcodeChecker now persists to localStorage on submit; context bar shown on /deals, /compare and /providers/[slug] when a postcode is stored, with change/clear actions. SSR-safe (renders null server-side, no hydration mismatch).</t>
+          <t>Shipped 2026-08-21: Product/Offer JSON-LD (lib/dealSchema.ts) added to /deals, /postcode/[area] (both branches) and /providers/[slug]. Prices mirror visible content; no fabricated aggregateRating (no real review-count field in the data model).</t>
         </is>
       </c>
     </row>
@@ -919,33 +915,33 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>page-providers/compare/hyperoptic-vs-youfibre</t>
+          <t>feat-persistent-postcode</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Hyperoptic vs YouFibre broadband: which is better in 2026?</t>
+          <t>Persistent postcode across the site</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>67.90000000000001</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -955,7 +951,11 @@
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-21: lib/postcodeStorage.ts + components/PostcodeContextBar.tsx. PostcodeChecker now persists to localStorage on submit; context bar shown on /deals, /compare and /providers/[slug] when a postcode is stored, with change/clear actions. SSR-safe (renders null server-side, no hydration mismatch).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -963,7 +963,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>page-postcode/sheffield</t>
+          <t>page-providers/compare/hyperoptic-vs-youfibre</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -978,14 +978,14 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Broadband providers in Sheffield: coverage and best deals</t>
+          <t>Hyperoptic vs YouFibre broadband: which is better in 2026?</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>66.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>page-guides/static-ip-business-broadband-explained</t>
+          <t>page-postcode/sheffield</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1022,18 +1022,18 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Static IP business broadband: when you need one and how much it costs</t>
+          <t>Broadband providers in Sheffield: coverage and best deals</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>66.3</v>
+        <v>66.8</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46.1</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>page-guides/student-broadband-by-university-city</t>
+          <t>page-guides/static-ip-business-broadband-explained</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1066,18 +1066,18 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Student broadband by university city: short-term and rolling deals</t>
+          <t>Static IP business broadband: when you need one and how much it costs</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>36.2</v>
+        <v>46.1</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>page-postcode/edinburgh</t>
+          <t>page-guides/student-broadband-by-university-city</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1110,18 +1110,18 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Broadband providers in Edinburgh: coverage and best deals</t>
+          <t>Student broadband by university city: short-term and rolling deals</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>65.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>40</v>
+        <v>36.2</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>page-guides/small-office-broadband-setup-uk</t>
+          <t>page-postcode/edinburgh</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1154,14 +1154,14 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Small office broadband setup: routers, backup and support checklist</t>
+          <t>Broadband providers in Edinburgh: coverage and best deals</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
         <v>65.8</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>41.9</v>
+        <v>40</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>page-providers/compare/bt-vs-plusnet</t>
+          <t>page-guides/small-office-broadband-setup-uk</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1198,18 +1198,18 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>BT vs Plusnet broadband: which is better in 2026?</t>
+          <t>Small office broadband setup: routers, backup and support checklist</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>65.5</v>
+        <v>65.8</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>36.4</v>
+        <v>41.9</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>page-postcode/glasgow</t>
+          <t>page-providers/compare/bt-vs-plusnet</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1242,18 +1242,18 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Broadband providers in Glasgow: coverage and best deals</t>
+          <t>BT vs Plusnet broadband: which is better in 2026?</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
         <v>65.5</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>40.2</v>
+        <v>36.4</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>page-postcode/liverpool</t>
+          <t>page-postcode/glasgow</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1286,14 +1286,14 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Broadband providers in Liverpool: coverage and best deals</t>
+          <t>Broadband providers in Glasgow: coverage and best deals</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
         <v>65.5</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>page-guides/broadband-for-landlords-and-hmos-uk</t>
+          <t>page-postcode/liverpool</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1330,18 +1330,18 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Broadband for landlords and HMOs: what to set up and who pays</t>
+          <t>Broadband providers in Liverpool: coverage and best deals</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>36.6</v>
+        <v>40.1</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>page-postcode/leeds</t>
+          <t>page-guides/broadband-for-landlords-and-hmos-uk</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1374,18 +1374,18 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Broadband providers in Leeds: coverage and best deals</t>
+          <t>Broadband for landlords and HMOs: what to set up and who pays</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
         <v>65.09999999999999</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>40.3</v>
+        <v>36.6</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>page-providers/compare/ee-vs-talktalk</t>
+          <t>page-postcode/leeds</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1418,18 +1418,18 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>EE vs TalkTalk broadband: which is better in 2026?</t>
+          <t>Broadband providers in Leeds: coverage and best deals</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>65</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>36.4</v>
+        <v>40.3</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>page-postcode/bristol</t>
+          <t>page-providers/compare/ee-vs-talktalk</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1462,18 +1462,18 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Broadband providers in Bristol: coverage and best deals</t>
+          <t>EE vs TalkTalk broadband: which is better in 2026?</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>64.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>40.8</v>
+        <v>36.4</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>page-postcode/birmingham</t>
+          <t>page-postcode/bristol</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1506,14 +1506,14 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Broadband providers in Birmingham: coverage and best deals</t>
+          <t>Broadband providers in Bristol: coverage and best deals</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>64.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>41.1</v>
+        <v>40.8</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>page-postcode/manchester</t>
+          <t>page-postcode/birmingham</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1550,14 +1550,14 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Broadband providers in Manchester: coverage and best deals</t>
+          <t>Broadband providers in Birmingham: coverage and best deals</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>64.2</v>
+        <v>64.5</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>page-guides/leased-line-cost-uk-explained</t>
+          <t>page-postcode/manchester</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1594,14 +1594,14 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Leased line cost UK: what small businesses actually pay</t>
+          <t>Broadband providers in Manchester: coverage and best deals</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>63.3</v>
+        <v>64.2</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>58.6</v>
+        <v>41.2</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>page-guides/starlink-vs-fibre-broadband-uk</t>
+          <t>page-guides/leased-line-cost-uk-explained</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1638,14 +1638,14 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Starlink vs fibre broadband: when satellite makes sense in the UK</t>
+          <t>Leased line cost UK: what small businesses actually pay</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>62.9</v>
+        <v>63.3</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>35.4</v>
+        <v>58.6</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>page-providers/compare/virgin-media-vs-sky</t>
+          <t>page-guides/starlink-vs-fibre-broadband-uk</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1682,14 +1682,14 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Virgin Media vs Sky broadband: which is better in 2026?</t>
+          <t>Starlink vs fibre broadband: when satellite makes sense in the UK</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>62.8</v>
+        <v>62.9</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>36.2</v>
+        <v>35.4</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>page-guides/january-broadband-deals-uk</t>
+          <t>page-providers/compare/virgin-media-vs-sky</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1726,14 +1726,14 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>January broadband deals UK: new-year switching guide</t>
+          <t>Virgin Media vs Sky broadband: which is better in 2026?</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>61.7</v>
+        <v>62.8</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>36.9</v>
+        <v>36.2</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -1755,33 +1755,33 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket</t>
+          <t>page-guides/january-broadband-deals-uk</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Shortlist / compare-basket pattern</t>
+          <t>January broadband deals UK: new-year switching guide</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>61</v>
+        <v>61.7</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>64</v>
+        <v>36.9</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1799,47 +1799,43 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>page-tools/broadband-cost-calculator</t>
+          <t>feat-shortlist-compare-basket</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Broadband cost calculator: true monthly and contract-length cost</t>
+          <t>Shortlist / compare-basket pattern</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>27.6</v>
+        <v>64</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>Live at /tools/broadband-cost-calculator, committed and deployed 2026-08-21.</t>
-        </is>
-      </c>
+      <c r="L26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -1847,7 +1843,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>page-providers/onestream</t>
+          <t>page-tools/broadband-cost-calculator</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1857,19 +1853,19 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Onestream — plans, coverage and Awin-tracked deals</t>
+          <t>Broadband cost calculator: true monthly and contract-length cost</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>59.4</v>
+        <v>59.9</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>28</v>
+        <v>27.6</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -1878,12 +1874,16 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr"/>
       <c r="K27" s="3" t="inlineStr"/>
-      <c r="L27" s="3" t="inlineStr"/>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Live at /tools/broadband-cost-calculator, committed and deployed 2026-08-21.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>page-guides/no-credit-check-broadband-uk</t>
+          <t>page-providers/onestream</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1906,18 +1906,18 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>No credit check broadband in the UK: options and what to expect</t>
+          <t>Onestream — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>34.8</v>
+        <v>28</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1935,33 +1935,33 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>feat-review-aggregation-module</t>
+          <t>page-guides/no-credit-check-broadband-uk</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Real review-aggregation trust module</t>
+          <t>No credit check broadband in the UK: options and what to expect</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>59</v>
+        <v>59.3</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>62</v>
+        <v>34.8</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -1979,33 +1979,33 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>page-providers/brsk</t>
+          <t>feat-review-aggregation-module</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Brsk — plans, coverage and Awin-tracked deals</t>
+          <t>Real review-aggregation trust module</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
         <v>59</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>28.5</v>
+        <v>62</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>page-guides/fttp-vs-fttc-explained</t>
+          <t>page-providers/brsk</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2038,14 +2038,14 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>FTTP vs FTTC: what the difference means for your speed</t>
+          <t>Brsk — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>58.4</v>
+        <v>59</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>27.8</v>
+        <v>28.5</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>page-guides/best-mesh-wifi-for-your-broadband-router</t>
+          <t>page-guides/fttp-vs-fttc-explained</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2082,18 +2082,18 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
+          <t>FTTP vs FTTC: what the difference means for your speed</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
         <v>58.4</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>34</v>
+        <v>27.8</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>page-guides/broadband-help-if-you-claim-benefits-uk</t>
+          <t>page-guides/best-mesh-wifi-for-your-broadband-router</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2126,18 +2126,18 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
+          <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>58.2</v>
+        <v>58.4</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>27.5</v>
+        <v>34</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>page-providers/gigaclear</t>
+          <t>page-guides/broadband-help-if-you-claim-benefits-uk</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2170,18 +2170,18 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
+          <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>56.9</v>
+        <v>58.2</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>27.9</v>
+        <v>27.5</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>page-providers/youfibre</t>
+          <t>page-providers/gigaclear</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -2214,14 +2214,14 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
+          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>56.6</v>
+        <v>56.9</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>28.7</v>
+        <v>27.9</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr"/>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>page-providers/cuckoo</t>
+          <t>page-providers/youfibre</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2258,14 +2258,14 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
+          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>56.5</v>
+        <v>56.6</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>27.9</v>
+        <v>28.7</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>audit-city-hub-thinness</t>
+          <t>page-providers/cuckoo</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Content audit</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -2302,18 +2302,18 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Verify each new city hub has a genuinely local fact</t>
+          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>56</v>
+        <v>56.5</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>50</v>
+        <v>27.9</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>page-guides/black-friday-broadband-deals-uk</t>
+          <t>audit-city-hub-thinness</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Content audit</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2346,18 +2346,18 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
+          <t>Verify each new city hub has a genuinely local fact</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>55.8</v>
+        <v>56</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>page-providers/shell-energy</t>
+          <t>page-guides/black-friday-broadband-deals-uk</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2390,18 +2390,18 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
+          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>55.7</v>
+        <v>55.8</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>page-research/broadband-customer-service-rankings-uk</t>
+          <t>page-providers/shell-energy</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2434,14 +2434,14 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
+          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>55.1</v>
+        <v>55.7</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
+          <t>page-research/broadband-customer-service-rankings-uk</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2478,14 +2478,14 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Broadband complaints and the ombudsman: your UK rights</t>
+          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>54.7</v>
+        <v>55.1</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>25.9</v>
+        <v>27.8</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
@@ -2507,33 +2507,33 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>feat-price-drop-alerts</t>
+          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Broadband complaints and the ombudsman: your UK rights</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>49</v>
+        <v>54.7</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>55</v>
+        <v>25.9</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2551,29 +2551,29 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
@@ -2595,33 +2595,33 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -2649,19 +2649,19 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2693,19 +2693,19 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2721,8 +2721,52 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
     </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="3" t="inlineStr"/>
+      <c r="L47" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L46"/>
+  <autoFilter ref="A1:L47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4572,7 +4616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4582,11 +4626,11 @@
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="50" customWidth="1" min="9" max="9"/>
     <col width="50" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="49" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -4779,43 +4823,43 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Product/Offer schema on deal cards</t>
+          <t>Broadband Match: personalised recommendation quiz</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Uswitch marks up individual deals as Product + Quotation JSON-LD — the basis for price/rating rich snippets in search results. BroadbandPicker's deal cards don't carry this yet. Contained, well-scoped, clear SEO payoff.</t>
+          <t>Researched 2026-08-22 against Uswitch, Compare the Market, MoneySuperMarket, Which?, broadbandchoices, choose.co.uk and broadband.co.uk: none has a multi-question quiz that outputs a ranked provider/package recommendation — confirmed genuine gap, not a crowded feature. Closest analog, RightSpeed UK, only outputs a speed-tier range and hands off to a third-party site rather than affiliate-linking directly. Plan: 6-8 questions (reason for looking, household size, use cases — WFH/gaming/streaming/uploads, budget, contract-length preference, postcode), scored client-side against the existing provider dataset (speed, price, contract, Trustpilot, coverage — no new data pipeline needed), producing a ranked top 3 with per-pick reasoning and direct affiliate CTAs — going further than RightSpeed's speed-only output. Since AI Overviews cite static pages, not live quiz results (confirmed in research), pair the tool with internal links to/from the existing best-broadband-for-gaming/WFH/students/streaming guides so the underlying logic stays citable even though the live tool isn't. Directly serves the standing goal of making BroadbandPicker a site providers want in their affiliate programme: a completed-quiz click is a much stronger purchase-intent signal than a generic comparison-table click.</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium-High</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>components/DealCard and deal-listing pages</t>
+          <t>New route (e.g. /tools/broadband-match), new scoring component, reuses data/providers.ts + data/postcodes.ts + data/postcodeDistrictCoverage.ts</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None — reuses existing provider/coverage datasets</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>docs/competitor-landscape-scan.json</t>
+          <t>User request 2026-08-22, researched before scoring per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -4830,33 +4874,33 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Persistent postcode across the site</t>
+          <t>Product/Offer schema on deal cards</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Once a postcode is entered on /postcode, carry it (localStorage, no account needed) into /deals, /compare and every provider page so the journey feels personal rather than resetting the question each time.</t>
+          <t>Uswitch marks up individual deals as Product + Quotation JSON-LD — the basis for price/rating rich snippets in search results. BroadbandPicker's deal cards don't carry this yet. Contained, well-scoped, clear SEO payoff.</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>PostcodeChecker + shared client state</t>
+          <t>components/DealCard and deal-listing pages</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -4871,7 +4915,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>docs/competitor-landscape-scan.json</t>
         </is>
       </c>
     </row>
@@ -4891,19 +4935,19 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Shortlist / compare-basket pattern</t>
+          <t>Persistent postcode across the site</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Let users tick 2–3 deals and see them side by side, matching Uswitch and broadband.co.uk. Current /compare is one full table — good for browsing, weaker for a final decision between finalists.</t>
+          <t>Once a postcode is entered on /postcode, carry it (localStorage, no account needed) into /deals, /compare and every provider page so the journey feels personal rather than resetting the question each time.</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -4912,7 +4956,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>app/compare</t>
+          <t>PostcodeChecker + shared client state</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4922,7 +4966,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -4942,24 +4986,24 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Real review-aggregation trust module</t>
+          <t>Shortlist / compare-basket pattern</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Blend the existing Ofcom-complaints research methodology with live Trustpilot scores into one visible trust module reused across provider and comparison pages, instead of a single quoted score per page.</t>
+          <t>Let users tick 2–3 deals and see them side by side, matching Uswitch and broadband.co.uk. Current /compare is one full table — good for browsing, weaker for a final decision between finalists.</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -4968,12 +5012,12 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>New shared component, used on provider + comparison pages</t>
+          <t>app/compare</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -4983,7 +5027,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -4993,29 +5037,29 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Content audit</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Verify each new city hub has a genuinely local fact</t>
+          <t>Real review-aggregation trust module</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8 new city hubs (Birmingham, Bristol, Edinburgh, Glasgow, Leeds, Liverpool, Manchester, Sheffield) plus 50 existing postcode-prefix pages is a lot of near-identical templates. Each needs at least one real local fact (a named local altnet, a real coverage figure) or it reads as duplicate content — audit before building the next batch of cities.</t>
+          <t>Blend the existing Ofcom-complaints research methodology with live Trustpilot scores into one visible trust module reused across provider and comparison pages, instead of a single quoted score per page.</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -5024,12 +5068,12 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>data/priority-pages.ts city entries</t>
+          <t>New shared component, used on provider + comparison pages</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -5039,7 +5083,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>Growth playbook — Functionality pillar</t>
         </is>
       </c>
     </row>
@@ -5049,29 +5093,29 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Content audit</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Verify each new city hub has a genuinely local fact</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
+          <t>8 new city hubs (Birmingham, Bristol, Edinburgh, Glasgow, Leeds, Liverpool, Manchester, Sheffield) plus 50 existing postcode-prefix pages is a lot of near-identical templates. Each needs at least one real local fact (a named local altnet, a real coverage figure) or it reads as duplicate content — audit before building the next batch of cities.</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -5080,12 +5124,12 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
+          <t>data/priority-pages.ts city entries</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Email delivery provider</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -5095,7 +5139,7 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -5105,29 +5149,29 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -5136,12 +5180,12 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>New subscription flow + data/provider-live-deals.json</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>Email delivery provider</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -5151,7 +5195,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>Growth playbook — Functionality pillar</t>
         </is>
       </c>
     </row>
@@ -5161,43 +5205,43 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -5207,7 +5251,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -5222,24 +5266,24 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -5248,12 +5292,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -5263,7 +5307,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -5278,53 +5322,109 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F14" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G14" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L13"/>
+  <autoFilter ref="A1:L14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5365,7 +5465,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>45 total (33 page builds, 12 feature/strategy builds); 24 already marked Done.</t>
+          <t>46 total (33 page builds, 13 feature/strategy builds); 24 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -854,12 +854,16 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-22: lib/broadbandMatch.ts (pure scoring logic), components/BroadbandMatchQuiz.tsx (6-step interactive quiz), app/tools/broadband-match/page.tsx. Keyword research confirmed primary keyword 'what broadband speed do I need' + copy pattern (lead with the number, activity-by-Mbps table). Internal links added to/from the 4 relevant guides, homepage promo section, main nav, footer, and sitemap per the new Stage 5a process.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -4074,10 +4078,14 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Planned — not live</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
@@ -4854,7 +4862,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -5465,7 +5473,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>46 total (33 page builds, 13 feature/strategy builds); 24 already marked Done.</t>
+          <t>46 total (33 page builds, 13 feature/strategy builds); 25 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Methodology'!$A$1:$B$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L47" headerRowCount="1">
-  <autoFilter ref="A1:L47"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L48" headerRowCount="1">
+  <autoFilter ref="A1:L48"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -216,8 +216,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L14" headerRowCount="1">
-  <autoFilter ref="A1:L14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L15" headerRowCount="1">
+  <autoFilter ref="A1:L15"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2511,43 +2511,47 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
+          <t>feat-nav-header-footer-ia</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Broadband complaints and the ombudsman: your UK rights</t>
+          <t>Navigation/header/footer IA improvements</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>54.7</v>
+        <v>55</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>25.9</v>
+        <v>60</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-22: scripts/scrape_navigation_patterns.py scanned 5 best-in-class sites (broadband.co.uk stood out on sticky header + breadcrumbs + trust badge). Confirmed BroadbandPicker's sticky header and breadcrumbs already match best practice. Added Postcode to primary nav (desktop+mobile), restructured footer 4-&gt;6 columns adding Tools, Find Broadband by Area, and Research links to fix a crawl/link-equity gap for the 2,800+ postcode-district and tools pages. Deliberately did NOT fabricate a trust badge (no real Trustpilot/press presence yet) and did NOT widen the header postcode breakpoint (risk of stacking two unverified density changes without a browser check). See docs/navigation-ia-analysis.md.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
@@ -2555,33 +2559,33 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>feat-price-drop-alerts</t>
+          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Broadband complaints and the ombudsman: your UK rights</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>49</v>
+        <v>54.7</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>55</v>
+        <v>25.9</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -2599,29 +2603,29 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2643,33 +2647,33 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -2687,7 +2691,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2697,19 +2701,19 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2731,7 +2735,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -2741,19 +2745,19 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
@@ -2769,8 +2773,52 @@
       <c r="K47" s="3" t="inlineStr"/>
       <c r="L47" s="3" t="inlineStr"/>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L47"/>
+  <autoFilter ref="A1:L48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2794,7 +2842,7 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="31" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
@@ -2895,7 +2943,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -2949,7 +2997,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -3003,7 +3051,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3057,7 +3105,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -3111,7 +3159,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -3165,7 +3213,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -3219,7 +3267,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3273,7 +3321,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -3327,7 +3375,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3381,7 +3429,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -3435,7 +3483,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -3489,7 +3537,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -3543,7 +3591,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3597,7 +3645,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -3651,7 +3699,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -3705,7 +3753,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -3759,7 +3807,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3813,7 +3861,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -3867,7 +3915,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -3921,7 +3969,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -3975,7 +4023,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -4029,7 +4077,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -4083,7 +4131,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -4337,7 +4385,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -4624,7 +4672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5162,48 +5210,48 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Navigation/header/footer IA improvements</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
+          <t>Researched via scripts/scrape_navigation_patterns.py against 5 best-in-class sites. broadband.co.uk (closest single-vertical comparable) stood out on sticky header, breadcrumbs and a trust badge near the top; BroadbandPicker already matches on the first two. Header nav link count split cleanly into supersite (127-556 links) vs specialist (21 links) patterns, confirming the growth playbook's 'specialist, not supersite' positioning. Added Postcode to primary nav; restructured the footer from 4 to 6 columns (added Tools, Find Broadband by Area, Research) to fix a crawl/link-equity gap for the postcode-district and tools pages built this session.</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
+          <t>app/layout.tsx</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Email delivery provider</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>User request 2026-08-22 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -5213,29 +5261,29 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
@@ -5244,12 +5292,12 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>New subscription flow + data/provider-live-deals.json</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>Email delivery provider</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -5259,7 +5307,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>Growth playbook — Functionality pillar</t>
         </is>
       </c>
     </row>
@@ -5269,43 +5317,43 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -5315,7 +5363,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -5330,24 +5378,24 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
@@ -5356,12 +5404,12 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -5371,7 +5419,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -5386,53 +5434,109 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F15" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="G15" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L14"/>
+  <autoFilter ref="A1:L15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5473,7 +5577,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>46 total (33 page builds, 13 feature/strategy builds); 25 already marked Done.</t>
+          <t>47 total (33 page builds, 14 feature/strategy builds); 26 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr"/>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr"/>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr"/>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr"/>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr"/>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr"/>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -4180,13 +4180,17 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Planned — not live</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -4230,13 +4234,17 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Planned — not live</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -4280,13 +4288,17 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Planned — not live</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -4330,13 +4342,17 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Planned — not live</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -4434,13 +4450,17 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Planned — not live</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -5577,7 +5597,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>47 total (33 page builds, 14 feature/strategy builds); 26 already marked Done.</t>
+          <t>47 total (33 page builds, 14 feature/strategy builds); 35 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Methodology'!$A$1:$B$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L48" headerRowCount="1">
-  <autoFilter ref="A1:L48"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L49" headerRowCount="1">
+  <autoFilter ref="A1:L49"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -216,8 +216,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L15" headerRowCount="1">
-  <autoFilter ref="A1:L15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L16" headerRowCount="1">
+  <autoFilter ref="A1:L16"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr"/>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>feat-price-drop-alerts</t>
+          <t>feat-homepage-visual-redesign</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2613,16 +2613,16 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Homepage visual redesign: illustrations + interactivity</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>55</v>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -2647,29 +2647,29 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
@@ -2691,33 +2691,33 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -2745,19 +2745,19 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2789,19 +2789,19 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2817,8 +2817,52 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
     </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr"/>
+      <c r="K49" s="3" t="inlineStr"/>
+      <c r="L49" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L48"/>
+  <autoFilter ref="A1:L49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2842,7 +2886,7 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="31" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
@@ -2943,7 +2987,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -2997,7 +3041,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -3051,7 +3095,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3105,7 +3149,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -3159,7 +3203,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -3213,7 +3257,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -3267,7 +3311,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3321,7 +3365,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -3375,7 +3419,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3429,7 +3473,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -3483,7 +3527,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -3537,7 +3581,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -3591,7 +3635,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3645,7 +3689,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -3699,7 +3743,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -3753,7 +3797,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -3807,7 +3851,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3861,7 +3905,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -3915,7 +3959,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -3969,7 +4013,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -4023,7 +4067,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -4077,7 +4121,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -4131,7 +4175,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -4185,7 +4229,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -4239,7 +4283,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -4293,7 +4337,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -4347,7 +4391,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -4401,7 +4445,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -4455,7 +4499,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4504,13 +4548,17 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Planned — not live</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -4692,7 +4740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5286,21 +5334,21 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Homepage visual redesign: illustrations + interactivity</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
+          <t>Researched via scripts/analyze_homepage_visual_design.py against 5 UK broadband comparison homepages: none uses stock-photo hero banners; the dominant visual language is heavy inline SVG (Uswitch ships 195) and provider logos, no carousel/animation library detected anywhere. Generated 7 original on-brand SVG illustrations (scripts/generate_homepage_illustrations.py: hero network graphic, 3 colour-filled step icons, 2 gradient blobs, a quiz illustration) rather than stock photography, matching what's actually proven in this vertical. Added a scroll-reveal component, hover interactions, and restructured the Broadband Match promo to a two-column illustrated layout. Content/copy unchanged, visual/UX only.</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>55</v>
@@ -5312,22 +5360,22 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
+          <t>app/page.tsx, components/ScrollReveal.tsx, public/illustrations/</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Email delivery provider</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -5337,29 +5385,29 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -5368,12 +5416,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>New subscription flow + data/provider-live-deals.json</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>Email delivery provider</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -5383,7 +5431,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>Growth playbook — Functionality pillar</t>
         </is>
       </c>
     </row>
@@ -5393,43 +5441,43 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -5439,7 +5487,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -5454,24 +5502,24 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -5480,12 +5528,12 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -5495,7 +5543,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -5510,53 +5558,109 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F16" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G16" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L15"/>
+  <autoFilter ref="A1:L16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5597,7 +5701,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>47 total (33 page builds, 14 feature/strategy builds); 35 already marked Done.</t>
+          <t>48 total (33 page builds, 15 feature/strategy builds); 37 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Methodology'!$A$1:$B$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L49" headerRowCount="1">
-  <autoFilter ref="A1:L49"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L50" headerRowCount="1">
+  <autoFilter ref="A1:L50"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -216,8 +216,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L16" headerRowCount="1">
-  <autoFilter ref="A1:L16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L17" headerRowCount="1">
+  <autoFilter ref="A1:L17"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -2691,12 +2691,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>feat-footer-logo-interactivity</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2706,23 +2706,23 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -2735,33 +2735,33 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2789,19 +2789,19 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -2833,19 +2833,19 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
@@ -2861,8 +2861,52 @@
       <c r="K49" s="3" t="inlineStr"/>
       <c r="L49" s="3" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L49"/>
+  <autoFilter ref="A1:L50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4602,13 +4646,17 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Planned — not live</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -4740,7 +4788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5441,7 +5489,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -5451,43 +5499,43 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>app/layout.tsx, components/Logo.tsx</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -5497,43 +5545,43 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -5543,7 +5591,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -5558,24 +5606,24 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -5584,12 +5632,12 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -5599,7 +5647,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -5614,53 +5662,109 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="F17" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="G17" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L16"/>
+  <autoFilter ref="A1:L17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5701,7 +5805,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>48 total (33 page builds, 15 feature/strategy builds); 37 already marked Done.</t>
+          <t>49 total (33 page builds, 16 feature/strategy builds); 39 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -2727,7 +2727,11 @@
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
@@ -2930,7 +2934,7 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="31" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
@@ -3031,7 +3035,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -3085,7 +3089,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -3139,7 +3143,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3193,7 +3197,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -3247,7 +3251,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -3301,7 +3305,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -3355,7 +3359,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3409,7 +3413,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -3463,7 +3467,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3517,7 +3521,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -3571,7 +3575,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -3625,7 +3629,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -3679,7 +3683,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3733,7 +3737,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -3787,7 +3791,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -3841,7 +3845,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -3895,7 +3899,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3949,7 +3953,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -4003,7 +4007,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -4057,7 +4061,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -4111,7 +4115,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -4165,7 +4169,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -4219,7 +4223,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -4273,7 +4277,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -4327,7 +4331,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -4381,7 +4385,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -4435,7 +4439,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -4489,7 +4493,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -4543,7 +4547,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4597,7 +4601,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -4651,7 +4655,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Methodology'!$A$1:$B$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L50" headerRowCount="1">
-  <autoFilter ref="A1:L50"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L51" headerRowCount="1">
+  <autoFilter ref="A1:L51"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -216,8 +216,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L17" headerRowCount="1">
-  <autoFilter ref="A1:L17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L18" headerRowCount="1">
+  <autoFilter ref="A1:L18"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr"/>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>feat-price-drop-alerts</t>
+          <t>feat-mega-menu-navigation</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -2657,19 +2657,19 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr"/>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>feat-footer-logo-interactivity</t>
+          <t>feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2701,37 +2701,33 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
-        </is>
-      </c>
+      <c r="L46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
@@ -2739,12 +2735,12 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>feat-footer-logo-interactivity</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -2754,28 +2750,32 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr"/>
       <c r="K47" s="3" t="inlineStr"/>
-      <c r="L47" s="3" t="inlineStr"/>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -2783,33 +2783,33 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -2837,19 +2837,19 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2881,19 +2881,19 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2909,8 +2909,52 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
     </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr"/>
+      <c r="K51" s="3" t="inlineStr"/>
+      <c r="L51" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L50"/>
+  <autoFilter ref="A1:L51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4704,13 +4748,17 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Planned — not live</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -4792,7 +4840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5442,24 +5490,24 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
+          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -5468,22 +5516,22 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
+          <t>components/MainNav.tsx, app/layout.tsx</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Email delivery provider</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -5498,48 +5546,48 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
+          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>app/layout.tsx, components/Logo.tsx</t>
+          <t>New subscription flow + data/provider-live-deals.json</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Email delivery provider</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>Growth playbook — Functionality pillar</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5597,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -5559,43 +5607,43 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>app/layout.tsx, components/Logo.tsx</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -5605,43 +5653,43 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -5651,7 +5699,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -5666,24 +5714,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -5692,12 +5740,12 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -5707,7 +5755,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -5722,53 +5770,109 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="F18" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G18" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L17"/>
+  <autoFilter ref="A1:L18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5809,7 +5913,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>49 total (33 page builds, 16 feature/strategy builds); 39 already marked Done.</t>
+          <t>50 total (33 page builds, 17 feature/strategy builds); 41 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -9,16 +9,18 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Tracker" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Page Builds" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature &amp; Strategy Builds" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending Build Priority" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Page Builds" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature &amp; Strategy Builds" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Methodology'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +176,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L51" headerRowCount="1">
-  <autoFilter ref="A1:L51"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L59" headerRowCount="1">
+  <autoFilter ref="A1:L59"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -195,7 +197,30 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PageBuildsTable" displayName="PageBuildsTable" ref="A1:L34" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PendingBuildPriorityTable" displayName="PendingBuildPriorityTable" ref="A1:N15" headerRowCount="1">
+  <autoFilter ref="A1:N15"/>
+  <tableColumns count="14">
+    <tableColumn id="1" name="Pending Rank"/>
+    <tableColumn id="2" name="Item ID"/>
+    <tableColumn id="3" name="Type"/>
+    <tableColumn id="4" name="Pillar"/>
+    <tableColumn id="5" name="Title"/>
+    <tableColumn id="6" name="Priority Score"/>
+    <tableColumn id="7" name="Impact Score"/>
+    <tableColumn id="8" name="Effort"/>
+    <tableColumn id="9" name="Status"/>
+    <tableColumn id="10" name="Target"/>
+    <tableColumn id="11" name="Dependencies"/>
+    <tableColumn id="12" name="Owner"/>
+    <tableColumn id="13" name="Target Date"/>
+    <tableColumn id="14" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="PageBuildsTable" displayName="PageBuildsTable" ref="A1:L34" headerRowCount="1">
   <autoFilter ref="A1:L34"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
@@ -215,9 +240,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L18" headerRowCount="1">
-  <autoFilter ref="A1:L18"/>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L26" headerRowCount="1">
+  <autoFilter ref="A1:L26"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -236,9 +261,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="MethodologyTable" displayName="MethodologyTable" ref="A1:B6" headerRowCount="1">
-  <autoFilter ref="A1:B6"/>
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="MethodologyTable" displayName="MethodologyTable" ref="A1:B7" headerRowCount="1">
+  <autoFilter ref="A1:B7"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Aspect"/>
     <tableColumn id="2" name="Detail"/>
@@ -642,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1671,33 +1696,33 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>page-guides/starlink-vs-fibre-broadband-uk</t>
+          <t>ops-conversion-reporting-loop</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Starlink vs fibre broadband: when satellite makes sense in the UK</t>
+          <t>Validate conversion events and establish the GSC/analytics reporting loop</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>62.9</v>
+        <v>63</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>35.4</v>
+        <v>72</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1707,7 +1732,11 @@
       </c>
       <c r="J23" s="3" t="inlineStr"/>
       <c r="K23" s="3" t="inlineStr"/>
-      <c r="L23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Shipped to Vercel production 2026-08-23: consent-aware GA4 events for postcode submits, speed-test starts/completions/failures, deal filter/sort use and outbound provider clicks, with session first-touch attribution and no full postcode sent. Measurement contract and weekly GSC/GA4 loop documented in docs/analytics-measurement-plan.md.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1715,7 +1744,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>page-providers/compare/virgin-media-vs-sky</t>
+          <t>page-guides/starlink-vs-fibre-broadband-uk</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1730,14 +1759,14 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Virgin Media vs Sky broadband: which is better in 2026?</t>
+          <t>Starlink vs fibre broadband: when satellite makes sense in the UK</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>62.8</v>
+        <v>62.9</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>36.2</v>
+        <v>35.4</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1759,7 +1788,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>page-guides/january-broadband-deals-uk</t>
+          <t>page-providers/compare/virgin-media-vs-sky</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1774,14 +1803,14 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>January broadband deals UK: new-year switching guide</t>
+          <t>Virgin Media vs Sky broadband: which is better in 2026?</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>61.7</v>
+        <v>62.8</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>36.9</v>
+        <v>36.2</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -1803,38 +1832,38 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket</t>
+          <t>page-guides/january-broadband-deals-uk</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Shortlist / compare-basket pattern</t>
+          <t>January broadband deals UK: new-year switching guide</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>61</v>
+        <v>61.7</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>64</v>
+        <v>36.9</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -1847,47 +1876,43 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>page-tools/broadband-cost-calculator</t>
+          <t>feat-shortlist-compare-basket</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Broadband cost calculator: true monthly and contract-length cost</t>
+          <t>Shortlist / compare-basket pattern</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>27.6</v>
+        <v>64</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr"/>
       <c r="K27" s="3" t="inlineStr"/>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>Live at /tools/broadband-cost-calculator, committed and deployed 2026-08-21.</t>
-        </is>
-      </c>
+      <c r="L27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1895,38 +1920,38 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>page-providers/onestream</t>
+          <t>growth-awin-advertiser-outreach</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Partnerships</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Onestream — plans, coverage and Awin-tracked deals</t>
+          <t>Continue selective Awin advertiser outreach</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>59.4</v>
+        <v>60</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -1939,7 +1964,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>page-guides/no-credit-check-broadband-uk</t>
+          <t>page-tools/broadband-cost-calculator</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -1949,23 +1974,23 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>No credit check broadband in the UK: options and what to expect</t>
+          <t>Broadband cost calculator: true monthly and contract-length cost</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>59.3</v>
+        <v>59.9</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>34.8</v>
+        <v>27.6</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -1975,7 +2000,11 @@
       </c>
       <c r="J29" s="3" t="inlineStr"/>
       <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Live at /tools/broadband-cost-calculator, committed and deployed 2026-08-21.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1983,38 +2012,38 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>feat-review-aggregation-module</t>
+          <t>page-providers/onestream</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Real review-aggregation trust module</t>
+          <t>Onestream — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>59</v>
+        <v>59.4</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -2027,7 +2056,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>page-providers/brsk</t>
+          <t>page-guides/no-credit-check-broadband-uk</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2042,18 +2071,18 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Brsk — plans, coverage and Awin-tracked deals</t>
+          <t>No credit check broadband in the UK: options and what to expect</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>59</v>
+        <v>59.3</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>28.5</v>
+        <v>34.8</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -2071,38 +2100,38 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>page-guides/fttp-vs-fttc-explained</t>
+          <t>feat-review-aggregation-module</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>FTTP vs FTTC: what the difference means for your speed</t>
+          <t>Real review-aggregation trust module</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>58.4</v>
+        <v>59</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>27.8</v>
+        <v>62</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -2115,7 +2144,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>page-guides/best-mesh-wifi-for-your-broadband-router</t>
+          <t>page-providers/brsk</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2130,18 +2159,18 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
+          <t>Brsk — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>58.4</v>
+        <v>59</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>34</v>
+        <v>28.5</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -2159,7 +2188,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>page-guides/broadband-help-if-you-claim-benefits-uk</t>
+          <t>page-guides/fttp-vs-fttc-explained</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2174,14 +2203,14 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
+          <t>FTTP vs FTTC: what the difference means for your speed</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>58.2</v>
+        <v>58.4</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>27.5</v>
+        <v>27.8</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2203,7 +2232,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>page-providers/gigaclear</t>
+          <t>page-guides/best-mesh-wifi-for-your-broadband-router</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -2218,18 +2247,18 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
+          <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>56.9</v>
+        <v>58.4</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>27.9</v>
+        <v>34</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -2247,7 +2276,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>page-providers/youfibre</t>
+          <t>page-guides/broadband-help-if-you-claim-benefits-uk</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2262,18 +2291,18 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
+          <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>56.6</v>
+        <v>58.2</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>28.7</v>
+        <v>27.5</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2291,38 +2320,38 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>page-providers/cuckoo</t>
+          <t>ops-adsense-site-review</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
+          <t>Complete AdSense site review and authorisation monitoring</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>56.5</v>
+        <v>58</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>27.9</v>
+        <v>55</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr"/>
@@ -2335,12 +2364,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>audit-city-hub-thinness</t>
+          <t>page-providers/gigaclear</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Content audit</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2350,23 +2379,23 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Verify each new city hub has a genuinely local fact</t>
+          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>56</v>
+        <v>56.9</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>50</v>
+        <v>27.9</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -2379,7 +2408,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>page-guides/black-friday-broadband-deals-uk</t>
+          <t>page-providers/youfibre</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2394,18 +2423,18 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
+          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>55.8</v>
+        <v>56.6</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>37</v>
+        <v>28.7</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -2423,7 +2452,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>page-providers/shell-energy</t>
+          <t>page-providers/cuckoo</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2438,14 +2467,14 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
+          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>55.7</v>
+        <v>56.5</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2467,12 +2496,12 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>page-research/broadband-customer-service-rankings-uk</t>
+          <t>audit-city-hub-thinness</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Content audit</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -2482,23 +2511,23 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
+          <t>Verify each new city hub has a genuinely local fact</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>55.1</v>
+        <v>56</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>27.8</v>
+        <v>50</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr"/>
@@ -2511,33 +2540,33 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>feat-nav-header-footer-ia</t>
+          <t>page-guides/black-friday-broadband-deals-uk</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Navigation/header/footer IA improvements</t>
+          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>55</v>
+        <v>55.8</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2547,11 +2576,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>Shipped 2026-08-22: scripts/scrape_navigation_patterns.py scanned 5 best-in-class sites (broadband.co.uk stood out on sticky header + breadcrumbs + trust badge). Confirmed BroadbandPicker's sticky header and breadcrumbs already match best practice. Added Postcode to primary nav (desktop+mobile), restructured footer 4-&gt;6 columns adding Tools, Find Broadband by Area, and Research links to fix a crawl/link-equity gap for the 2,800+ postcode-district and tools pages. Deliberately did NOT fabricate a trust badge (no real Trustpilot/press presence yet) and did NOT widen the header postcode breakpoint (risk of stacking two unverified density changes without a browser check). See docs/navigation-ia-analysis.md.</t>
-        </is>
-      </c>
+      <c r="L42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
@@ -2559,7 +2584,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
+          <t>page-providers/shell-energy</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -2574,14 +2599,14 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Broadband complaints and the ombudsman: your UK rights</t>
+          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>54.7</v>
+        <v>55.7</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>25.9</v>
+        <v>28</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
@@ -2590,7 +2615,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr"/>
@@ -2603,33 +2628,33 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>feat-homepage-visual-redesign</t>
+          <t>page-research/broadband-customer-service-rankings-uk</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Homepage visual redesign: illustrations + interactivity</t>
+          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>52</v>
+        <v>55.1</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>55</v>
+        <v>27.8</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2647,7 +2672,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>feat-mega-menu-navigation</t>
+          <t>feat-nav-header-footer-ia</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -2662,18 +2687,18 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Navigation/header/footer IA improvements</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -2683,7 +2708,11 @@
       </c>
       <c r="J45" s="3" t="inlineStr"/>
       <c r="K45" s="3" t="inlineStr"/>
-      <c r="L45" s="3" t="inlineStr"/>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-22: scripts/scrape_navigation_patterns.py scanned 5 best-in-class sites (broadband.co.uk stood out on sticky header + breadcrumbs + trust badge). Confirmed BroadbandPicker's sticky header and breadcrumbs already match best practice. Added Postcode to primary nav (desktop+mobile), restructured footer 4-&gt;6 columns adding Tools, Find Broadband by Area, and Research links to fix a crawl/link-equity gap for the 2,800+ postcode-district and tools pages. Deliberately did NOT fabricate a trust badge (no real Trustpilot/press presence yet) and did NOT widen the header postcode breakpoint (risk of stacking two unverified density changes without a browser check). See docs/navigation-ia-analysis.md.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -2691,38 +2720,38 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>feat-price-drop-alerts</t>
+          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Broadband complaints and the ombudsman: your UK rights</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>49</v>
+        <v>54.7</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>55</v>
+        <v>25.9</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -2735,47 +2764,43 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>feat-footer-logo-interactivity</t>
+          <t>growth-original-research-outreach</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Run original-research outreach and digital PR</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr"/>
       <c r="K47" s="3" t="inlineStr"/>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
-        </is>
-      </c>
+      <c r="L47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -2783,29 +2808,29 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>growth-quarterly-data-reprioritisation</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2827,38 +2852,38 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>feat-homepage-visual-redesign</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Homepage visual redesign: illustrations + interactivity</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr"/>
@@ -2871,38 +2896,38 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>feat-mega-menu-navigation</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -2915,33 +2940,33 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -2953,8 +2978,364 @@
       <c r="K51" s="3" t="inlineStr"/>
       <c r="L51" s="3" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>feat-page-type-ux-redesign</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>feat-footer-logo-interactivity</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Footer logo placement and interactive elements</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr"/>
+      <c r="K53" s="3" t="inlineStr"/>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>audit-core-web-vitals-reporting</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>audit-mobile-checkout-flow</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>UX audit</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Mobile checkout-flow audit</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr"/>
+      <c r="K55" s="3" t="inlineStr"/>
+      <c r="L55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>audit-broken-links-redirects</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Crawlability</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Add routine broken-link and redirect reporting</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>bet-annual-research-report</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Annual 'State of UK Broadband' research report</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr"/>
+      <c r="K57" s="3" t="inlineStr"/>
+      <c r="L57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>bet-componentise-interactive-layer</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr"/>
+      <c r="K59" s="3" t="inlineStr"/>
+      <c r="L59" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L51"/>
+  <autoFilter ref="A1:L59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2963,6 +3344,868 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pending Rank</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Item ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Pillar</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Priority Score</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Impact Score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Dependencies</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Target Date</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Shortlist / compare-basket pattern</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>app/compare</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>growth-awin-advertiser-outreach</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Partnerships</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Monetisation</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Continue selective Awin advertiser outreach</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Awin publisher 2942019 and partner application log</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Current audience evidence and compliant commercial pages</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>feat-review-aggregation-module</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Real review-aggregation trust module</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>New shared component, used on provider + comparison pages</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>ops-adsense-site-review</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Monetisation</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Complete AdSense site review and authorisation monitoring</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>AdSense status and /ads.txt</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Google site-review processing</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>audit-city-hub-thinness</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Content audit</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Verify each new city hub has a genuinely local fact</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>data/priority-pages.ts city entries</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>growth-original-research-outreach</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Run original-research outreach and digital PR</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>/research/uk-broadband-customer-satisfaction</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Research page and source methodology are live</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>growth-quarterly-data-reprioritisation</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Next-quarter decision log</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>ops-conversion-reporting-loop and sufficient observation period</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Price-drop alerts</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>New subscription flow + data/provider-live-deals.json</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Email delivery provider</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>audit-core-web-vitals-reporting</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Sitewide template performance report</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Field data or representative lab baselines</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>audit-mobile-checkout-flow</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>UX audit</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Mobile checkout-flow audit</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Sitewide mobile layout</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Mobile analytics/drop-off data</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>audit-broken-links-redirects</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Crawlability</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Add routine broken-link and redirect reporting</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Sitewide crawl and redirect report</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>bet-annual-research-report</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Annual 'State of UK Broadband' research report</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>New annual research page + methodology extension</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>bet-componentise-interactive-layer</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>None, but easier before the guide count grows further</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N15"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2978,8 +4221,8 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="31" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="50" customWidth="1" min="12" max="12"/>
@@ -3079,7 +4322,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -3133,7 +4376,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -3187,7 +4430,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3241,7 +4484,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -3295,7 +4538,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -3349,7 +4592,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -3403,7 +4646,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3457,7 +4700,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -3511,7 +4754,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3565,7 +4808,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -3619,7 +4862,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -3673,7 +4916,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -3727,7 +4970,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3781,7 +5024,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -3835,7 +5078,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -3889,7 +5132,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -3943,7 +5186,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3997,7 +5240,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -4051,7 +5294,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -4105,7 +5348,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -4159,7 +5402,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -4213,7 +5456,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -4267,7 +5510,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -4321,7 +5564,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -4375,7 +5618,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -4429,7 +5672,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -4483,7 +5726,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -4537,7 +5780,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -4591,7 +5834,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4645,7 +5888,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -4699,7 +5942,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -4753,7 +5996,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -4802,13 +6045,17 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Planned — not live</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Live but not committed to git</t>
+        </is>
+      </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4834,13 +6081,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5205,29 +6452,29 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Shortlist / compare-basket pattern</t>
+          <t>Validate conversion events and establish the GSC/analytics reporting loop</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Let users tick 2–3 deals and see them side by side, matching Uswitch and broadband.co.uk. Current /compare is one full table — good for browsing, weaker for a final decision between finalists.</t>
+          <t>Confirm postcode submits, speed-test completions, filter use, outbound provider clicks and assisted conversions are recorded reliably, then use query and engagement evidence to reprioritise future work.</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -5236,22 +6483,22 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>app/compare</t>
+          <t>GSC, analytics and conversion reporting</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Sufficient live traffic and event data</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Build Status / Technical SEO</t>
         </is>
       </c>
     </row>
@@ -5266,24 +6513,24 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Real review-aggregation trust module</t>
+          <t>Shortlist / compare-basket pattern</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Blend the existing Ofcom-complaints research methodology with live Trustpilot scores into one visible trust module reused across provider and comparison pages, instead of a single quoted score per page.</t>
+          <t>Let users tick 2–3 deals and see them side by side, matching Uswitch and broadband.co.uk. Current /compare is one full table — good for browsing, weaker for a final decision between finalists.</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -5292,12 +6539,12 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>New shared component, used on provider + comparison pages</t>
+          <t>app/compare</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -5307,7 +6554,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -5317,29 +6564,29 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Content audit</t>
+          <t>Partnerships</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Verify each new city hub has a genuinely local fact</t>
+          <t>Continue selective Awin advertiser outreach</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>8 new city hubs (Birmingham, Bristol, Edinburgh, Glasgow, Leeds, Liverpool, Manchester, Sheffield) plus 50 existing postcode-prefix pages is a lot of near-identical templates. Each needs at least one real local fact (a named local altnet, a real coverage figure) or it reads as duplicate content — audit before building the next batch of cities.</t>
+          <t>Apply to best-fit provider programmes with tailored pitches, relevant live URLs, audience evidence, promotional method and compliance controls; log decisions and feedback.</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -5348,22 +6595,22 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>data/priority-pages.ts city entries</t>
+          <t>Awin publisher 2942019 and partner application log</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Current audience evidence and compliant commercial pages</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: 90 Day Roadmap</t>
         </is>
       </c>
     </row>
@@ -5378,48 +6625,48 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Navigation/header/footer IA improvements</t>
+          <t>Real review-aggregation trust module</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Researched via scripts/scrape_navigation_patterns.py against 5 best-in-class sites. broadband.co.uk (closest single-vertical comparable) stood out on sticky header, breadcrumbs and a trust badge near the top; BroadbandPicker already matches on the first two. Header nav link count split cleanly into supersite (127-556 links) vs specialist (21 links) patterns, confirming the growth playbook's 'specialist, not supersite' positioning. Added Postcode to primary nav; restructured the footer from 4 to 6 columns (added Tools, Find Broadband by Area, Research) to fix a crawl/link-equity gap for the postcode-district and tools pages built this session.</t>
+          <t>Blend the existing Ofcom-complaints research methodology with live Trustpilot scores into one visible trust module reused across provider and comparison pages, instead of a single quoted score per page.</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>app/layout.tsx</t>
+          <t>New shared component, used on provider + comparison pages</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-22 — researched before implementing per the Strategic Lens process</t>
+          <t>Growth playbook — Functionality pillar</t>
         </is>
       </c>
     </row>
@@ -5429,53 +6676,53 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Homepage visual redesign: illustrations + interactivity</t>
+          <t>Complete AdSense site review and authorisation monitoring</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Researched via scripts/analyze_homepage_visual_design.py against 5 UK broadband comparison homepages: none uses stock-photo hero banners; the dominant visual language is heavy inline SVG (Uswitch ships 195) and provider logos, no carousel/animation library detected anywhere. Generated 7 original on-brand SVG illustrations (scripts/generate_homepage_illustrations.py: hero network graphic, 3 colour-filled step icons, 2 gradient blobs, a quiz illustration) rather than stock photography, matching what's actually proven in this vertical. Added a scroll-reveal component, hover interactions, and restructured the Broadband Match promo to a two-column illustrated layout. Content/copy unchanged, visual/UX only.</t>
+          <t>Monitor the existing AdSense review, consent implementation and ads.txt authorisation; resolve any concrete policy or crawler issue reported by AdSense.</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>55</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>app/page.tsx, components/ScrollReveal.tsx, public/illustrations/</t>
+          <t>AdSense status and /ads.txt</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Google site-review processing</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Build Status</t>
         </is>
       </c>
     </row>
@@ -5485,30 +6732,30 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Content audit</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Verify each new city hub has a genuinely local fact</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
+          <t>8 new city hubs (Birmingham, Bristol, Edinburgh, Glasgow, Leeds, Liverpool, Manchester, Sheffield) plus 50 existing postcode-prefix pages is a lot of near-identical templates. Each needs at least one real local fact (a named local altnet, a real coverage figure) or it reads as duplicate content — audit before building the next batch of cities.</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="G12" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="G12" s="2" t="n">
-        <v>58</v>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -5516,7 +6763,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>components/MainNav.tsx, app/layout.tsx</t>
+          <t>data/priority-pages.ts city entries</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5526,12 +6773,12 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -5546,48 +6793,48 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Navigation/header/footer IA improvements</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
+          <t>Researched via scripts/scrape_navigation_patterns.py against 5 best-in-class sites. broadband.co.uk (closest single-vertical comparable) stood out on sticky header, breadcrumbs and a trust badge near the top; BroadbandPicker already matches on the first two. Header nav link count split cleanly into supersite (127-556 links) vs specialist (21 links) patterns, confirming the growth playbook's 'specialist, not supersite' positioning. Added Postcode to primary nav; restructured the footer from 4 to 6 columns (added Tools, Find Broadband by Area, Research) to fix a crawl/link-equity gap for the postcode-district and tools pages built this session.</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
+          <t>app/layout.tsx</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Email delivery provider</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>User request 2026-08-22 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -5597,53 +6844,53 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Run original-research outreach and digital PR</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
+          <t>Build a relevant outreach list and earn citations and links to the live Ofcom-backed customer-satisfaction research.</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>app/layout.tsx, components/Logo.tsx</t>
+          <t>/research/uk-broadband-customer-satisfaction</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Research page and source methodology are live</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Build Status / 90 Day Roadmap</t>
         </is>
       </c>
     </row>
@@ -5653,29 +6900,29 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+          <t>Review query/page performance, assisted conversions, Awin decisions and engagement data, then record the next-quarter build decisions.</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -5684,12 +6931,12 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>Next-quarter decision log</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>ops-conversion-reporting-loop and sufficient observation period</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -5699,7 +6946,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: 90 Day Roadmap</t>
         </is>
       </c>
     </row>
@@ -5709,53 +6956,53 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Homepage visual redesign: illustrations + interactivity</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>Researched via scripts/analyze_homepage_visual_design.py against 5 UK broadband comparison homepages: none uses stock-photo hero banners; the dominant visual language is heavy inline SVG (Uswitch ships 195) and provider logos, no carousel/animation library detected anywhere. Generated 7 original on-brand SVG illustrations (scripts/generate_homepage_illustrations.py: hero network graphic, 3 colour-filled step icons, 2 gradient blobs, a quiz illustration) rather than stock photography, matching what's actually proven in this vertical. Added a scroll-reveal component, hover interactions, and restructured the Broadband Match promo to a two-column illustrated layout. Content/copy unchanged, visual/UX only.</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>app/page.tsx, components/ScrollReveal.tsx, public/illustrations/</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -5765,53 +7012,53 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>components/MainNav.tsx, app/layout.tsx</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -5821,58 +7068,506 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Price-drop alerts</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>New subscription flow + data/provider-live-deals.json</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Email delivery provider</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Footer logo placement and interactive elements</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>app/layout.tsx, components/Logo.tsx</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Sitewide template performance report</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Field data or representative lab baselines</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>UX audit</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Mobile checkout-flow audit</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Sitewide mobile layout</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Mobile analytics/drop-off data</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Growth playbook — UX pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Crawlability</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Add routine broken-link and redirect reporting</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Sitewide crawl and redirect report</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>Bigger bet</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Annual 'State of UK Broadband' research report</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>New annual research page + methodology extension</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Growth playbook — Content pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="F26" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="G26" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L18"/>
+  <autoFilter ref="A1:L26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5880,13 +7575,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5913,7 +7608,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>50 total (33 page builds, 17 feature/strategy builds); 41 already marked Done.</t>
+          <t>58 total (33 page builds, 25 feature/strategy builds); 44 already marked Done.</t>
         </is>
       </c>
     </row>
@@ -5956,17 +7651,29 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>Pending queue</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Pending Build Priority contains only non-Done items from the combined page, feature, audit and strategy list, ordered by Priority Score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
           <t>Editing this file</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Status/Owner/Target Date/Notes are yours to edit freely — they survive the next `python3 scripts/build_master_tracker.py` run.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -176,8 +176,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L59" headerRowCount="1">
-  <autoFilter ref="A1:L59"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L60" headerRowCount="1">
+  <autoFilter ref="A1:L60"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -197,8 +197,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PendingBuildPriorityTable" displayName="PendingBuildPriorityTable" ref="A1:N15" headerRowCount="1">
-  <autoFilter ref="A1:N15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PendingBuildPriorityTable" displayName="PendingBuildPriorityTable" ref="A1:N14" headerRowCount="1">
+  <autoFilter ref="A1:N14"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Pending Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -241,8 +241,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L26" headerRowCount="1">
-  <autoFilter ref="A1:L26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L27" headerRowCount="1">
+  <autoFilter ref="A1:L27"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1907,12 +1907,16 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr"/>
       <c r="K27" s="3" t="inlineStr"/>
-      <c r="L27" s="3" t="inlineStr"/>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Shipped to Vercel production 2026-08-23: visitors can shortlist two or three providers on /compare, retain the shortlist in local storage, compare price, maximum speed, contract, setup fee, coverage and customer rating in responsive finalist cards, then continue to a provider review or tracked deal link. Includes accessible controls, a three-provider limit and GA4 shortlist/basket events.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -2896,7 +2900,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>feat-mega-menu-navigation</t>
+          <t>feat-mobile-cross-device-navigation</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2911,14 +2915,14 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Mobile and cross-device navigation overhaul</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2940,7 +2944,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>feat-price-drop-alerts</t>
+          <t>feat-mega-menu-navigation</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -2950,19 +2954,19 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
@@ -2971,7 +2975,7 @@
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr"/>
@@ -2984,7 +2988,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>feat-page-type-ux-redesign</t>
+          <t>feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2994,19 +2998,19 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
         <v>49</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3015,7 +3019,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -3028,7 +3032,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>feat-footer-logo-interactivity</t>
+          <t>feat-page-type-ux-redesign</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -3043,18 +3047,18 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -3064,11 +3068,7 @@
       </c>
       <c r="J53" s="3" t="inlineStr"/>
       <c r="K53" s="3" t="inlineStr"/>
-      <c r="L53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
-        </is>
-      </c>
+      <c r="L53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -3076,43 +3076,47 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>audit-core-web-vitals-reporting</t>
+          <t>feat-footer-logo-interactivity</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
@@ -3120,29 +3124,29 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>audit-core-web-vitals-reporting</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
@@ -3164,33 +3168,33 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>audit-broken-links-redirects</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3208,33 +3212,33 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-broken-links-redirects</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -3252,7 +3256,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3262,19 +3266,19 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3296,7 +3300,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -3306,19 +3310,19 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
@@ -3334,8 +3338,52 @@
       <c r="K59" s="3" t="inlineStr"/>
       <c r="L59" s="3" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L59"/>
+  <autoFilter ref="A1:L60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3349,7 +3397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3446,29 +3494,29 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket</t>
+          <t>growth-awin-advertiser-outreach</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Partnerships</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Shortlist / compare-basket pattern</t>
+          <t>Continue selective Awin advertiser outreach</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -3477,17 +3525,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>app/compare</t>
+          <t>Awin publisher 2942019 and partner application log</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Current audience evidence and compliant commercial pages</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -3500,29 +3548,29 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>growth-awin-advertiser-outreach</t>
+          <t>feat-review-aggregation-module</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Partnerships</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Continue selective Awin advertiser outreach</t>
+          <t>Real review-aggregation trust module</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -3531,17 +3579,17 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Awin publisher 2942019 and partner application log</t>
+          <t>New shared component, used on provider + comparison pages</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Current audience evidence and compliant commercial pages</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr"/>
@@ -3554,48 +3602,48 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>feat-review-aggregation-module</t>
+          <t>ops-adsense-site-review</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Real review-aggregation trust module</t>
+          <t>Complete AdSense site review and authorisation monitoring</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>New shared component, used on provider + comparison pages</t>
+          <t>AdSense status and /ads.txt</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>Google site-review processing</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -3608,48 +3656,48 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>ops-adsense-site-review</t>
+          <t>audit-city-hub-thinness</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Content audit</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Complete AdSense site review and authorisation monitoring</t>
+          <t>Verify each new city hub has a genuinely local fact</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>AdSense status and /ads.txt</t>
+          <t>data/priority-pages.ts city entries</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Google site-review processing</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr"/>
@@ -3662,12 +3710,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>audit-city-hub-thinness</t>
+          <t>growth-original-research-outreach</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Content audit</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -3677,14 +3725,14 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Verify each new city hub has a genuinely local fact</t>
+          <t>Run original-research outreach and digital PR</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -3693,17 +3741,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>data/priority-pages.ts city entries</t>
+          <t>/research/uk-broadband-customer-satisfaction</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Research page and source methodology are live</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -3716,29 +3764,29 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>growth-original-research-outreach</t>
+          <t>growth-quarterly-data-reprioritisation</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Run original-research outreach and digital PR</t>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -3747,17 +3795,17 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>/research/uk-broadband-customer-satisfaction</t>
+          <t>Next-quarter decision log</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Research page and source methodology are live</t>
+          <t>ops-conversion-reporting-loop and sufficient observation period</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr"/>
@@ -3770,29 +3818,29 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>growth-quarterly-data-reprioritisation</t>
+          <t>feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -3806,12 +3854,12 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Next-quarter decision log</t>
+          <t>New subscription flow + data/provider-live-deals.json</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>ops-conversion-reporting-loop and sufficient observation period</t>
+          <t>Email delivery provider</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -3824,29 +3872,29 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>feat-price-drop-alerts</t>
+          <t>audit-core-web-vitals-reporting</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -3860,12 +3908,12 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
+          <t>Sitewide template performance report</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Email delivery provider</t>
+          <t>Field data or representative lab baselines</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
@@ -3878,29 +3926,29 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>audit-core-web-vitals-reporting</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -3914,12 +3962,12 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Sitewide template performance report</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Field data or representative lab baselines</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -3932,33 +3980,33 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>audit-broken-links-redirects</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -3968,12 +4016,12 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>Sitewide crawl and redirect report</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr"/>
@@ -3986,33 +4034,33 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>audit-broken-links-redirects</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Bigger bet</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4022,12 +4070,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Sitewide crawl and redirect report</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -4040,7 +4088,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -4050,19 +4098,19 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
@@ -4076,12 +4124,12 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>components/</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr"/>
@@ -4094,7 +4142,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-decouple-content-from-code</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -4104,19 +4152,19 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Decouple guide content from code deploys</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -4130,74 +4178,20 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>bet-decouple-content-from-code</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Bigger bet</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Decouple guide content from code deploys</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>None, but easier before the guide count grows further</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
-      <c r="N15" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N15"/>
+  <autoFilter ref="A1:N14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6087,7 +6081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6549,7 +6543,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7022,19 +7016,19 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Mobile and cross-device navigation overhaul</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
+          <t>New scripts/analyze_mobile_ux.py scanned Uswitch, broadband.co.uk and choose.co.uk (MoneySavingExpert 403, reported not bypassed) with a mobile Safari user agent for markup/CSS signals: viewport meta and hamburger menu markers were universal but already correct on our own site; tel: click-to-call was absent everywhere (0/4, skipped); sticky bottom CTA (1/4) and apple-touch-icon (2/4) were too weak/incomplete to act on. The real gap was found by direct inspection, not the scan: the mobile nav was a small anchored dropdown of 10 flat links with ~36px touch targets, while the desktop nav beside it was a full mega-menu, and the header postcode checker was desktop-only so phone users had no quick postcode access outside the homepage/deals page. Replaced it with new components/MobileNav.tsx: a full-width slide-down panel reusing the desktop mega-menu's own icon/link data (exported from MainNav.tsx, so the two can't drift apart), every link at a 44px (min-h-11) touch target, and the postcode checker embedded at the top so it's reachable from any page. Added anchor ids to /guides category sections so the new mobile Guides menu jumps to a real target instead of an unread query param.</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -7043,7 +7037,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>components/MainNav.tsx, app/layout.tsx</t>
+          <t>components/MobileNav.tsx, components/MainNav.tsx, app/layout.tsx, app/guides/page.tsx</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -7073,24 +7067,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
+          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -7099,22 +7093,22 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
+          <t>components/MainNav.tsx, app/layout.tsx</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Email delivery provider</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7129,24 +7123,24 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
+          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
         <v>49</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -7155,22 +7149,22 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
+          <t>New subscription flow + data/provider-live-deals.json</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Email delivery provider</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>Growth playbook — Functionality pillar</t>
         </is>
       </c>
     </row>
@@ -7190,28 +7184,28 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
+          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>app/layout.tsx, components/Logo.tsx</t>
+          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7236,53 +7230,53 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
+          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Sitewide template performance report</t>
+          <t>app/layout.tsx, components/Logo.tsx</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>Field data or representative lab baselines</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7292,29 +7286,29 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -7323,12 +7317,12 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>Sitewide template performance report</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>Field data or representative lab baselines</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -7338,7 +7332,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -7348,43 +7342,43 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
+          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Sitewide crawl and redirect report</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -7394,7 +7388,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -7404,43 +7398,43 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide crawl and redirect report</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -7450,7 +7444,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -7465,24 +7459,24 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -7491,12 +7485,12 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -7506,7 +7500,7 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -7521,53 +7515,109 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="F27" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="G27" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L26"/>
+  <autoFilter ref="A1:L27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7608,7 +7658,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>58 total (33 page builds, 25 feature/strategy builds); 44 already marked Done.</t>
+          <t>59 total (33 page builds, 26 feature/strategy builds); 46 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$60</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -176,8 +176,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L60" headerRowCount="1">
-  <autoFilter ref="A1:L60"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L61" headerRowCount="1">
+  <autoFilter ref="A1:L61"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -197,8 +197,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PendingBuildPriorityTable" displayName="PendingBuildPriorityTable" ref="A1:N14" headerRowCount="1">
-  <autoFilter ref="A1:N14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PendingBuildPriorityTable" displayName="PendingBuildPriorityTable" ref="A1:N47" headerRowCount="1">
+  <autoFilter ref="A1:N47"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Pending Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -241,8 +241,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L27" headerRowCount="1">
-  <autoFilter ref="A1:L27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L28" headerRowCount="1">
+  <autoFilter ref="A1:L28"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr"/>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr"/>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr"/>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr"/>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr"/>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr"/>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr"/>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr"/>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr"/>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr"/>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>feat-price-drop-alerts</t>
+          <t>feat-animated-interactive-mobile-menu</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2998,19 +2998,19 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Animated, interactive mobile menu with click-outside-to-close</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>feat-page-type-ux-redesign</t>
+          <t>feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -3042,19 +3042,19 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
         <v>49</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr"/>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>feat-footer-logo-interactivity</t>
+          <t>feat-page-type-ux-redesign</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3091,18 +3091,18 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -3112,11 +3112,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
-        </is>
-      </c>
+      <c r="L54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
@@ -3124,43 +3120,47 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>audit-core-web-vitals-reporting</t>
+          <t>feat-footer-logo-interactivity</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr"/>
       <c r="K55" s="3" t="inlineStr"/>
-      <c r="L55" s="3" t="inlineStr"/>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -3168,29 +3168,29 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>audit-core-web-vitals-reporting</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3212,33 +3212,33 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>audit-broken-links-redirects</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -3256,33 +3256,33 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-broken-links-redirects</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -3310,19 +3310,19 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3354,19 +3354,19 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3382,8 +3382,52 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr"/>
+      <c r="K61" s="3" t="inlineStr"/>
+      <c r="L61" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L60"/>
+  <autoFilter ref="A1:L61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3397,23 +3441,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="50" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -3494,50 +3538,46 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>growth-awin-advertiser-outreach</t>
+          <t>page-providers/compare/hyperoptic-vs-youfibre</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Partnerships</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Continue selective Awin advertiser outreach</t>
+          <t>Hyperoptic vs YouFibre broadband: which is better in 2026?</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>60</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Awin publisher 2942019 and partner application log</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Current audience evidence and compliant commercial pages</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/providers/compare/hyperoptic-vs-youfibre</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
@@ -3548,33 +3588,33 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>feat-review-aggregation-module</t>
+          <t>page-postcode/sheffield</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Real review-aggregation trust module</t>
+          <t>Broadband providers in Sheffield: coverage and best deals</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>59</v>
+        <v>66.8</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -3584,14 +3624,10 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>New shared component, used on provider + comparison pages</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/postcode/sheffield</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
@@ -3602,50 +3638,46 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ops-adsense-site-review</t>
+          <t>page-guides/static-ip-business-broadband-explained</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Complete AdSense site review and authorisation monitoring</t>
+          <t>Static IP business broadband: when you need one and how much it costs</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>58</v>
+        <v>66.3</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>55</v>
+        <v>46.1</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>AdSense status and /ads.txt</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Google site-review processing</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/guides/static-ip-business-broadband-explained</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
@@ -3656,12 +3688,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>audit-city-hub-thinness</t>
+          <t>page-guides/student-broadband-by-university-city</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Content audit</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -3671,18 +3703,18 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Verify each new city hub has a genuinely local fact</t>
+          <t>Student broadband by university city: short-term and rolling deals</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>56</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>50</v>
+        <v>36.2</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -3692,14 +3724,10 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>data/priority-pages.ts city entries</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/guides/student-broadband-by-university-city</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
@@ -3710,12 +3738,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>growth-original-research-outreach</t>
+          <t>page-postcode/edinburgh</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -3725,35 +3753,31 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Run original-research outreach and digital PR</t>
+          <t>Broadband providers in Edinburgh: coverage and best deals</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>54</v>
+        <v>65.8</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>/research/uk-broadband-customer-satisfaction</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>Research page and source methodology are live</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/postcode/edinburgh</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
@@ -3764,33 +3788,33 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>growth-quarterly-data-reprioritisation</t>
+          <t>page-guides/small-office-broadband-setup-uk</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
+          <t>Small office broadband setup: routers, backup and support checklist</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>53</v>
+        <v>65.8</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>63</v>
+        <v>41.9</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -3800,14 +3824,10 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Next-quarter decision log</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>ops-conversion-reporting-loop and sufficient observation period</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/guides/small-office-broadband-setup-uk</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
@@ -3818,33 +3838,33 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>feat-price-drop-alerts</t>
+          <t>page-providers/compare/bt-vs-plusnet</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>BT vs Plusnet broadband: which is better in 2026?</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>49</v>
+        <v>65.5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>55</v>
+        <v>36.4</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3854,14 +3874,10 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>Email delivery provider</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/providers/compare/bt-vs-plusnet</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
@@ -3872,33 +3888,33 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>audit-core-web-vitals-reporting</t>
+          <t>page-postcode/glasgow</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Broadband providers in Glasgow: coverage and best deals</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>47</v>
+        <v>65.5</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>50</v>
+        <v>40.2</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -3908,14 +3924,10 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Sitewide template performance report</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>Field data or representative lab baselines</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/postcode/glasgow</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="inlineStr"/>
@@ -3926,33 +3938,33 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>page-postcode/liverpool</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Broadband providers in Liverpool: coverage and best deals</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45</v>
+        <v>65.5</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>58</v>
+        <v>40.1</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3962,14 +3974,10 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>Mobile analytics/drop-off data</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/postcode/liverpool</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
@@ -3980,33 +3988,33 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>audit-broken-links-redirects</t>
+          <t>page-guides/broadband-for-landlords-and-hmos-uk</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Broadband for landlords and HMOs: what to set up and who pays</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>44</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>48</v>
+        <v>36.6</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -4016,14 +4024,10 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Sitewide crawl and redirect report</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/guides/broadband-for-landlords-and-hmos-uk</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="inlineStr"/>
@@ -4034,12 +4038,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>page-postcode/leeds</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -4049,18 +4053,18 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Broadband providers in Leeds: coverage and best deals</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>41</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>65</v>
+        <v>40.3</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4070,14 +4074,10 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/postcode/leeds</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
@@ -4088,33 +4088,33 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>page-providers/compare/ee-vs-talktalk</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>EE vs TalkTalk broadband: which is better in 2026?</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>45</v>
+        <v>36.4</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -4124,14 +4124,10 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>components/</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/providers/compare/ee-vs-talktalk</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr"/>
       <c r="L13" s="3" t="inlineStr"/>
       <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="3" t="inlineStr"/>
@@ -4142,12 +4138,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>page-postcode/bristol</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4157,18 +4153,18 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Broadband providers in Bristol: coverage and best deals</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>35</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>48</v>
+        <v>40.8</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4178,20 +4174,1722 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>None, but easier before the guide count grows further</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/postcode/bristol</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>page-postcode/birmingham</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Broadband providers in Birmingham: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/birmingham</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>page-postcode/manchester</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Broadband providers in Manchester: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/manchester</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>page-guides/leased-line-cost-uk-explained</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Leased line cost UK: what small businesses actually pay</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/leased-line-cost-uk-explained</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>page-guides/starlink-vs-fibre-broadband-uk</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Starlink vs fibre broadband: when satellite makes sense in the UK</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/starlink-vs-fibre-broadband-uk</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>page-providers/compare/virgin-media-vs-sky</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Virgin Media vs Sky broadband: which is better in 2026?</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/compare/virgin-media-vs-sky</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>page-guides/january-broadband-deals-uk</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>January broadband deals UK: new-year switching guide</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/january-broadband-deals-uk</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>growth-awin-advertiser-outreach</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Partnerships</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Monetisation</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Continue selective Awin advertiser outreach</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Awin publisher 2942019 and partner application log</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Current audience evidence and compliant commercial pages</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>page-tools/broadband-cost-calculator</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Broadband cost calculator: true monthly and contract-length cost</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/tools/broadband-cost-calculator</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Live at /tools/broadband-cost-calculator, committed and deployed 2026-08-21.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>page-providers/onestream</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Onestream — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/onestream</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>page-guides/no-credit-check-broadband-uk</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>No credit check broadband in the UK: options and what to expect</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/no-credit-check-broadband-uk</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>feat-review-aggregation-module</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Real review-aggregation trust module</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>New shared component, used on provider + comparison pages</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>page-providers/brsk</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Brsk — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/brsk</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>page-guides/fttp-vs-fttc-explained</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>FTTP vs FTTC: what the difference means for your speed</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/fttp-vs-fttc-explained</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
+      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>page-guides/best-mesh-wifi-for-your-broadband-router</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/best-mesh-wifi-for-your-broadband-router</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>page-guides/broadband-help-if-you-claim-benefits-uk</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/broadband-help-if-you-claim-benefits-uk</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr"/>
+      <c r="N29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ops-adsense-site-review</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Monetisation</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Complete AdSense site review and authorisation monitoring</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>AdSense status and /ads.txt</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Google site-review processing</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>page-providers/gigaclear</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/gigaclear</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>page-providers/youfibre</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/youfibre</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>page-providers/cuckoo</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/cuckoo</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr"/>
+      <c r="L33" s="3" t="inlineStr"/>
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>audit-city-hub-thinness</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Content audit</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Verify each new city hub has a genuinely local fact</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>data/priority-pages.ts city entries</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>page-guides/black-friday-broadband-deals-uk</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/black-friday-broadband-deals-uk</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr"/>
+      <c r="L35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>page-providers/shell-energy</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/shell-energy</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>page-research/broadband-customer-service-rankings-uk</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/research/broadband-customer-service-rankings-uk</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr"/>
+      <c r="L37" s="3" t="inlineStr"/>
+      <c r="M37" s="3" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Broadband complaints and the ombudsman: your UK rights</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/broadband-complaints-and-ombudsman-uk</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>growth-original-research-outreach</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Run original-research outreach and digital PR</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>/research/uk-broadband-customer-satisfaction</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Research page and source methodology are live</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr"/>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>growth-quarterly-data-reprioritisation</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Next-quarter decision log</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>ops-conversion-reporting-loop and sufficient observation period</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Price-drop alerts</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>New subscription flow + data/provider-live-deals.json</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Email delivery provider</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr"/>
+      <c r="M41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>audit-core-web-vitals-reporting</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Sitewide template performance report</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Field data or representative lab baselines</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>audit-mobile-checkout-flow</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>UX audit</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Mobile checkout-flow audit</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>Sitewide mobile layout</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Mobile analytics/drop-off data</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>audit-broken-links-redirects</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Crawlability</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Add routine broken-link and redirect reporting</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Sitewide crawl and redirect report</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>bet-annual-research-report</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Annual 'State of UK Broadband' research report</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>New annual research page + methodology extension</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr"/>
+      <c r="M45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>bet-componentise-interactive-layer</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>None, but easier before the guide count grows further</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr"/>
+      <c r="M47" s="3" t="inlineStr"/>
+      <c r="N47" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N14"/>
+  <autoFilter ref="A1:N47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4214,9 +5912,9 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="31" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="50" customWidth="1" min="12" max="12"/>
@@ -4311,17 +6009,13 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -4365,17 +6059,13 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -4419,17 +6109,13 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4473,17 +6159,13 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -4527,17 +6209,13 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4581,17 +6259,13 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -4635,17 +6309,13 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4689,17 +6359,13 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -4743,17 +6409,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4797,17 +6459,13 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -4851,17 +6509,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4905,17 +6559,13 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -4959,17 +6609,13 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5013,17 +6659,13 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -5067,17 +6709,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5121,17 +6759,13 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -5175,17 +6809,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5229,17 +6859,13 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -5283,17 +6909,13 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5337,17 +6959,13 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -5391,17 +7009,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5445,17 +7059,13 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr"/>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -5499,17 +7109,13 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5553,17 +7159,13 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -5607,17 +7209,13 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -5661,17 +7259,13 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -5715,17 +7309,13 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -5769,17 +7359,13 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -5823,17 +7409,13 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -5877,17 +7459,13 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -5931,17 +7509,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -5985,17 +7559,13 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr"/>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -6039,17 +7609,13 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Live but not committed to git</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -6081,7 +7647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7123,24 +8689,24 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Animated, interactive mobile menu with click-outside-to-close</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
+          <t>Direct UX/interaction-design request, not a scraping pass. Rewrote components/MobileNav.tsx from a native &lt;details&gt; element (no animation, no click-outside-to-close) to a controlled client component: hamburger icon morphs into an X on open; a blurred backdrop closes the menu on click or Escape; the panel and its sections slide/fade in with a staggered delay reusing the same transition idiom as components/ScrollReveal.tsx; Providers/Postcode/Guides/Tools became single-open accordions using a CSS-only grid-template-rows 0fr-&gt;1fr transition (no JS height measurement); the menu auto-closes on route change via usePathname(); background scroll is locked while open; focus moves into the panel on open and returns to the trigger on Escape. Global prefers-reduced-motion handling already in app/globals.css applies automatically. Not visually verified on a real device — no browser automation tool available this session, validated via build output, generated CSS and server-rendered markup only.</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -7149,22 +8715,22 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
+          <t>components/MobileNav.tsx</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Email delivery provider</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7179,24 +8745,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
+          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
         <v>49</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -7205,22 +8771,22 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
+          <t>New subscription flow + data/provider-live-deals.json</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Email delivery provider</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>Growth playbook — Functionality pillar</t>
         </is>
       </c>
     </row>
@@ -7240,28 +8806,28 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
+          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>app/layout.tsx, components/Logo.tsx</t>
+          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -7286,53 +8852,53 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
+          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Sitewide template performance report</t>
+          <t>app/layout.tsx, components/Logo.tsx</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Field data or representative lab baselines</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7342,29 +8908,29 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -7373,12 +8939,12 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>Sitewide template performance report</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>Field data or representative lab baselines</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -7388,7 +8954,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -7398,43 +8964,43 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
+          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Sitewide crawl and redirect report</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -7444,7 +9010,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -7454,43 +9020,43 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide crawl and redirect report</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -7500,7 +9066,7 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -7515,24 +9081,24 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -7541,12 +9107,12 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -7556,7 +9122,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -7571,53 +9137,109 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F27" s="3" t="n">
+      <c r="F28" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G27" s="3" t="n">
+      <c r="G28" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L27"/>
+  <autoFilter ref="A1:L28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7658,7 +9280,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>59 total (33 page builds, 26 feature/strategy builds); 46 already marked Done.</t>
+          <t>60 total (33 page builds, 27 feature/strategy builds); 14 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -176,8 +176,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L61" headerRowCount="1">
-  <autoFilter ref="A1:L61"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L62" headerRowCount="1">
+  <autoFilter ref="A1:L62"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -197,8 +197,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PendingBuildPriorityTable" displayName="PendingBuildPriorityTable" ref="A1:N47" headerRowCount="1">
-  <autoFilter ref="A1:N47"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PendingBuildPriorityTable" displayName="PendingBuildPriorityTable" ref="A1:N15" headerRowCount="1">
+  <autoFilter ref="A1:N15"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Pending Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -241,8 +241,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L28" headerRowCount="1">
-  <autoFilter ref="A1:L28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L29" headerRowCount="1">
+  <autoFilter ref="A1:L29"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr"/>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr"/>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr"/>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr"/>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr"/>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr"/>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr"/>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr"/>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr"/>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr"/>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -2724,38 +2724,38 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
+          <t>feat-contact-form-email-delivery</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Broadband complaints and the ombudsman: your UK rights</t>
+          <t>Working contact form delivering to a real inbox, no third-party service</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>54.7</v>
+        <v>55</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>25.9</v>
+        <v>50</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>growth-original-research-outreach</t>
+          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -2783,23 +2783,23 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Run original-research outreach and digital PR</t>
+          <t>Broadband complaints and the ombudsman: your UK rights</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>54</v>
+        <v>54.7</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>68</v>
+        <v>25.9</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr"/>
@@ -2812,29 +2812,29 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>growth-quarterly-data-reprioritisation</t>
+          <t>growth-original-research-outreach</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
+          <t>Run original-research outreach and digital PR</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -2856,29 +2856,29 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>feat-homepage-visual-redesign</t>
+          <t>growth-quarterly-data-reprioritisation</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Homepage visual redesign: illustrations + interactivity</t>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr"/>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>feat-mobile-cross-device-navigation</t>
+          <t>feat-homepage-visual-redesign</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2915,14 +2915,14 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Mobile and cross-device navigation overhaul</t>
+          <t>Homepage visual redesign: illustrations + interactivity</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>feat-mega-menu-navigation</t>
+          <t>feat-mobile-cross-device-navigation</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -2959,14 +2959,14 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Mobile and cross-device navigation overhaul</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>feat-animated-interactive-mobile-menu</t>
+          <t>feat-mega-menu-navigation</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3003,14 +3003,14 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Animated, interactive mobile menu with click-outside-to-close</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
         <v>50</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>feat-price-drop-alerts</t>
+          <t>feat-animated-interactive-mobile-menu</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -3042,19 +3042,19 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Animated, interactive mobile menu with click-outside-to-close</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr"/>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>feat-page-type-ux-redesign</t>
+          <t>feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3086,19 +3086,19 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
         <v>49</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>feat-footer-logo-interactivity</t>
+          <t>feat-page-type-ux-redesign</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -3135,18 +3135,18 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -3156,11 +3156,7 @@
       </c>
       <c r="J55" s="3" t="inlineStr"/>
       <c r="K55" s="3" t="inlineStr"/>
-      <c r="L55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
-        </is>
-      </c>
+      <c r="L55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -3168,43 +3164,47 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>audit-core-web-vitals-reporting</t>
+          <t>feat-footer-logo-interactivity</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
@@ -3212,29 +3212,29 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>audit-core-web-vitals-reporting</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
@@ -3256,33 +3256,33 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>audit-broken-links-redirects</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3300,33 +3300,33 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-broken-links-redirects</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3354,19 +3354,19 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -3398,19 +3398,19 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
@@ -3426,8 +3426,52 @@
       <c r="K61" s="3" t="inlineStr"/>
       <c r="L61" s="3" t="inlineStr"/>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L61"/>
+  <autoFilter ref="A1:L62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3441,23 +3485,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="50" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -3538,46 +3582,50 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>page-providers/compare/hyperoptic-vs-youfibre</t>
+          <t>growth-awin-advertiser-outreach</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Partnerships</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hyperoptic vs YouFibre broadband: which is better in 2026?</t>
+          <t>Continue selective Awin advertiser outreach</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>67.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/providers/compare/hyperoptic-vs-youfibre</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
+          <t>Awin publisher 2942019 and partner application log</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Current audience evidence and compliant commercial pages</t>
+        </is>
+      </c>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
@@ -3588,33 +3636,33 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>page-postcode/sheffield</t>
+          <t>feat-review-aggregation-module</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Broadband providers in Sheffield: coverage and best deals</t>
+          <t>Real review-aggregation trust module</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>66.8</v>
+        <v>59</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -3624,10 +3672,14 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/postcode/sheffield</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr"/>
+          <t>New shared component, used on provider + comparison pages</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
+        </is>
+      </c>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
@@ -3638,46 +3690,50 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>page-guides/static-ip-business-broadband-explained</t>
+          <t>ops-adsense-site-review</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Static IP business broadband: when you need one and how much it costs</t>
+          <t>Complete AdSense site review and authorisation monitoring</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>66.3</v>
+        <v>58</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46.1</v>
+        <v>55</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/guides/static-ip-business-broadband-explained</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+          <t>AdSense status and /ads.txt</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Google site-review processing</t>
+        </is>
+      </c>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
@@ -3688,12 +3744,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>page-guides/student-broadband-by-university-city</t>
+          <t>audit-city-hub-thinness</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Content audit</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -3703,18 +3759,18 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Student broadband by university city: short-term and rolling deals</t>
+          <t>Verify each new city hub has a genuinely local fact</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>56</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>36.2</v>
+        <v>50</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -3724,10 +3780,14 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/guides/student-broadband-by-university-city</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr"/>
+          <t>data/priority-pages.ts city entries</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
@@ -3738,46 +3798,50 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>page-postcode/edinburgh</t>
+          <t>feat-contact-form-email-delivery</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Broadband providers in Edinburgh: coverage and best deals</t>
+          <t>Working contact form delivering to a real inbox, no third-party service</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>65.8</v>
+        <v>55</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/postcode/edinburgh</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
+          <t>app/api/contact/route.ts, components/ContactForm.tsx, app/contact/page.tsx</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>CONTACT_SMTP_USER / CONTACT_SMTP_PASS Gmail App Password set in Vercel env vars</t>
+        </is>
+      </c>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
@@ -3788,12 +3852,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>page-guides/small-office-broadband-setup-uk</t>
+          <t>growth-original-research-outreach</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -3803,31 +3867,35 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Small office broadband setup: routers, backup and support checklist</t>
+          <t>Run original-research outreach and digital PR</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>65.8</v>
+        <v>54</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>41.9</v>
+        <v>68</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/guides/small-office-broadband-setup-uk</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr"/>
+          <t>/research/uk-broadband-customer-satisfaction</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Research page and source methodology are live</t>
+        </is>
+      </c>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
@@ -3838,33 +3906,33 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>page-providers/compare/bt-vs-plusnet</t>
+          <t>growth-quarterly-data-reprioritisation</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>BT vs Plusnet broadband: which is better in 2026?</t>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>65.5</v>
+        <v>53</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>36.4</v>
+        <v>63</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3874,10 +3942,14 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/providers/compare/bt-vs-plusnet</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
+          <t>Next-quarter decision log</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>ops-conversion-reporting-loop and sufficient observation period</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
@@ -3888,33 +3960,33 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>page-postcode/glasgow</t>
+          <t>feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Broadband providers in Glasgow: coverage and best deals</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>65.5</v>
+        <v>49</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>40.2</v>
+        <v>55</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -3924,10 +3996,14 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/postcode/glasgow</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr"/>
+          <t>New subscription flow + data/provider-live-deals.json</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Email delivery provider</t>
+        </is>
+      </c>
       <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="inlineStr"/>
@@ -3938,33 +4014,33 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>page-postcode/liverpool</t>
+          <t>audit-core-web-vitals-reporting</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Broadband providers in Liverpool: coverage and best deals</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>65.5</v>
+        <v>47</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>40.1</v>
+        <v>50</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3974,10 +4050,14 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/postcode/liverpool</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+          <t>Sitewide template performance report</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Field data or representative lab baselines</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
@@ -3988,33 +4068,33 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>page-guides/broadband-for-landlords-and-hmos-uk</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Broadband for landlords and HMOs: what to set up and who pays</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>45</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>36.6</v>
+        <v>58</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -4024,10 +4104,14 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/guides/broadband-for-landlords-and-hmos-uk</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
+          <t>Sitewide mobile layout</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Mobile analytics/drop-off data</t>
+        </is>
+      </c>
       <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="inlineStr"/>
@@ -4038,33 +4122,33 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>page-postcode/leeds</t>
+          <t>audit-broken-links-redirects</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Broadband providers in Leeds: coverage and best deals</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>65.09999999999999</v>
+        <v>44</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>40.3</v>
+        <v>48</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4074,10 +4158,14 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/postcode/leeds</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr"/>
+          <t>Sitewide crawl and redirect report</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
@@ -4088,12 +4176,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>page-providers/compare/ee-vs-talktalk</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Bigger bet</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -4103,18 +4191,18 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>EE vs TalkTalk broadband: which is better in 2026?</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="G13" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>36.4</v>
-      </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -4124,10 +4212,14 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/providers/compare/ee-vs-talktalk</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr"/>
+          <t>New annual research page + methodology extension</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
+        </is>
+      </c>
       <c r="L13" s="3" t="inlineStr"/>
       <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="3" t="inlineStr"/>
@@ -4138,33 +4230,33 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>page-postcode/bristol</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Bigger bet</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Broadband providers in Bristol: coverage and best deals</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>64.90000000000001</v>
+        <v>38</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>40.8</v>
+        <v>45</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4174,10 +4266,14 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/postcode/bristol</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
@@ -4188,12 +4284,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>page-postcode/birmingham</t>
+          <t>bet-decouple-content-from-code</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Bigger bet</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -4203,18 +4299,18 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Broadband providers in Birmingham: coverage and best deals</t>
+          <t>Decouple guide content from code deploys</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>64.5</v>
+        <v>35</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>41.1</v>
+        <v>48</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -4224,1672 +4320,20 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/postcode/birmingham</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
+          <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>None, but easier before the guide count grows further</t>
+        </is>
+      </c>
       <c r="L15" s="3" t="inlineStr"/>
       <c r="M15" s="3" t="inlineStr"/>
       <c r="N15" s="3" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>page-postcode/manchester</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Broadband providers in Manchester: coverage and best deals</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/postcode/manchester</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>page-guides/leased-line-cost-uk-explained</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Leased line cost UK: what small businesses actually pay</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>58.6</v>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/leased-line-cost-uk-explained</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>page-guides/starlink-vs-fibre-broadband-uk</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Starlink vs fibre broadband: when satellite makes sense in the UK</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/starlink-vs-fibre-broadband-uk</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>page-providers/compare/virgin-media-vs-sky</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Virgin Media vs Sky broadband: which is better in 2026?</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/compare/virgin-media-vs-sky</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr"/>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>page-guides/january-broadband-deals-uk</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>January broadband deals UK: new-year switching guide</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/january-broadband-deals-uk</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>growth-awin-advertiser-outreach</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Partnerships</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Monetisation</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Continue selective Awin advertiser outreach</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>Awin publisher 2942019 and partner application log</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>Current audience evidence and compliant commercial pages</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>page-tools/broadband-cost-calculator</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Functionality</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Broadband cost calculator: true monthly and contract-length cost</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/tools/broadband-cost-calculator</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>Live at /tools/broadband-cost-calculator, committed and deployed 2026-08-21.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>page-providers/onestream</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Onestream — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/onestream</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr"/>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>page-guides/no-credit-check-broadband-uk</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>No credit check broadband in the UK: options and what to expect</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/no-credit-check-broadband-uk</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>feat-review-aggregation-module</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Functionality</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>Real review-aggregation trust module</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>New shared component, used on provider + comparison pages</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr"/>
-      <c r="M25" s="3" t="inlineStr"/>
-      <c r="N25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>page-providers/brsk</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Brsk — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/brsk</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>page-guides/fttp-vs-fttc-explained</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>FTTP vs FTTC: what the difference means for your speed</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/fttp-vs-fttc-explained</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr"/>
-      <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="3" t="inlineStr"/>
-      <c r="N27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>page-guides/best-mesh-wifi-for-your-broadband-router</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/best-mesh-wifi-for-your-broadband-router</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>page-guides/broadband-help-if-you-claim-benefits-uk</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/broadband-help-if-you-claim-benefits-uk</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="3" t="inlineStr"/>
-      <c r="N29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>ops-adsense-site-review</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Monetisation</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Complete AdSense site review and authorisation monitoring</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>AdSense status and /ads.txt</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>Google site-review processing</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>page-providers/gigaclear</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/gigaclear</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="3" t="inlineStr"/>
-      <c r="N31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>page-providers/youfibre</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/youfibre</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>page-providers/cuckoo</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/cuckoo</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr"/>
-      <c r="L33" s="3" t="inlineStr"/>
-      <c r="M33" s="3" t="inlineStr"/>
-      <c r="N33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>audit-city-hub-thinness</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Content audit</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Verify each new city hub has a genuinely local fact</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>data/priority-pages.ts city entries</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>page-guides/black-friday-broadband-deals-uk</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/black-friday-broadband-deals-uk</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr"/>
-      <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="3" t="inlineStr"/>
-      <c r="N35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>page-providers/shell-energy</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/shell-energy</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>page-research/broadband-customer-service-rankings-uk</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/research/broadband-customer-service-rankings-uk</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr"/>
-      <c r="L37" s="3" t="inlineStr"/>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Broadband complaints and the ombudsman: your UK rights</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/broadband-complaints-and-ombudsman-uk</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>growth-original-research-outreach</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Growth</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>Run original-research outreach and digital PR</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>/research/uk-broadband-customer-satisfaction</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>Research page and source methodology are live</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="3" t="inlineStr"/>
-      <c r="N39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>growth-quarterly-data-reprioritisation</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Strategy</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Growth</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>Next-quarter decision log</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>ops-conversion-reporting-loop and sufficient observation period</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>feat-price-drop-alerts</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Functionality</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>Price-drop alerts</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>Email delivery provider</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr"/>
-      <c r="M41" s="3" t="inlineStr"/>
-      <c r="N41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>audit-core-web-vitals-reporting</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Technical SEO</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Sitewide template performance report</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>Field data or representative lab baselines</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>audit-mobile-checkout-flow</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>UX audit</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>UX</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>Mobile checkout-flow audit</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>Sitewide mobile layout</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>Mobile analytics/drop-off data</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="3" t="inlineStr"/>
-      <c r="N43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>audit-broken-links-redirects</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Technical SEO</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Crawlability</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Add routine broken-link and redirect reporting</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>Sitewide crawl and redirect report</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>bet-annual-research-report</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>Bigger bet</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>Annual 'State of UK Broadband' research report</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>New annual research page + methodology extension</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="3" t="inlineStr"/>
-      <c r="N45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>bet-componentise-interactive-layer</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Bigger bet</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Functionality</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>components/</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>bet-decouple-content-from-code</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>Bigger bet</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>Decouple guide content from code deploys</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>None, but easier before the guide count grows further</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="inlineStr"/>
-      <c r="M47" s="3" t="inlineStr"/>
-      <c r="N47" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N47"/>
+  <autoFilter ref="A1:N15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5912,9 +4356,9 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="50" customWidth="1" min="12" max="12"/>
@@ -6009,13 +4453,17 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -6059,13 +4507,17 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -6109,13 +4561,17 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6159,13 +4615,17 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -6209,13 +4669,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6259,13 +4723,17 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -6309,13 +4777,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6359,13 +4831,17 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -6409,13 +4885,17 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6459,13 +4939,17 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -6509,13 +4993,17 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6559,13 +5047,17 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -6609,13 +5101,17 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6659,13 +5155,17 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -6709,13 +5209,17 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6759,13 +5263,17 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -6809,13 +5317,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6859,13 +5371,17 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -6909,13 +5425,17 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6959,13 +5479,17 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -7009,13 +5533,17 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7059,13 +5587,17 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -7109,13 +5641,17 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7159,13 +5695,17 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -7209,13 +5749,17 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7259,13 +5803,17 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -7309,13 +5857,17 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7359,13 +5911,17 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -7409,13 +5965,17 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7459,13 +6019,17 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -7509,13 +6073,17 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7559,13 +6127,17 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -7609,13 +6181,17 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -7647,7 +6223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8404,43 +6980,43 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Run original-research outreach and digital PR</t>
+          <t>Working contact form delivering to a real inbox, no third-party service</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Build a relevant outreach list and earn citations and links to the live Ofcom-backed customer-satisfaction research.</t>
+          <t>Previously /contact only offered mailto: links to unverified custom-domain addresses (editorial@/partnerships@/hello@broadbandpicker.co.uk). Built a real contact form (components/ContactForm.tsx) posting to a new app/api/contact route, which sends via Gmail SMTP using nodemailer — no Supabase, no database, no third-party form/CRM service, per explicit instruction. All submissions land in sayedsahil.elt@gmail.com (CONTACT_TO_EMAIL env var), sent from a Gmail account authenticated with an App Password (CONTACT_SMTP_USER / CONTACT_SMTP_PASS). Reply-To is set to the sender's own address so replying goes straight back to them. Spam mitigation without any external service: a hidden honeypot field (bots that fill every input get silently dropped) and a submit-time check rejecting anything sent under 1.5s after the form rendered. Server-side validates name/email/reason/message independently of the client. The original mailto: cards are kept underneath as a secondary direct-email option. Requires CONTACT_SMTP_USER/PASS to be set in Vercel — the API route fails gracefully with a friendly error and a server log line if they're absent, rather than silently dropping messages.</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>/research/uk-broadband-customer-satisfaction</t>
+          <t>app/api/contact/route.ts, components/ContactForm.tsx, app/contact/page.tsx</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Research page and source methodology are live</t>
+          <t>CONTACT_SMTP_USER / CONTACT_SMTP_PASS Gmail App Password set in Vercel env vars</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -8450,7 +7026,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Build Status / 90 Day Roadmap</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8460,29 +7036,29 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
+          <t>Run original-research outreach and digital PR</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Review query/page performance, assisted conversions, Awin decisions and engagement data, then record the next-quarter build decisions.</t>
+          <t>Build a relevant outreach list and earn citations and links to the live Ofcom-backed customer-satisfaction research.</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -8491,22 +7067,22 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Next-quarter decision log</t>
+          <t>/research/uk-broadband-customer-satisfaction</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>ops-conversion-reporting-loop and sufficient observation period</t>
+          <t>Research page and source methodology are live</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: 90 Day Roadmap</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Build Status / 90 Day Roadmap</t>
         </is>
       </c>
     </row>
@@ -8516,29 +7092,29 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Homepage visual redesign: illustrations + interactivity</t>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Researched via scripts/analyze_homepage_visual_design.py against 5 UK broadband comparison homepages: none uses stock-photo hero banners; the dominant visual language is heavy inline SVG (Uswitch ships 195) and provider logos, no carousel/animation library detected anywhere. Generated 7 original on-brand SVG illustrations (scripts/generate_homepage_illustrations.py: hero network graphic, 3 colour-filled step icons, 2 gradient blobs, a quiz illustration) rather than stock photography, matching what's actually proven in this vertical. Added a scroll-reveal component, hover interactions, and restructured the Broadband Match promo to a two-column illustrated layout. Content/copy unchanged, visual/UX only.</t>
+          <t>Review query/page performance, assisted conversions, Awin decisions and engagement data, then record the next-quarter build decisions.</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -8547,22 +7123,22 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>app/page.tsx, components/ScrollReveal.tsx, public/illustrations/</t>
+          <t>Next-quarter decision log</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ops-conversion-reporting-loop and sufficient observation period</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: 90 Day Roadmap</t>
         </is>
       </c>
     </row>
@@ -8582,19 +7158,19 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Mobile and cross-device navigation overhaul</t>
+          <t>Homepage visual redesign: illustrations + interactivity</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>New scripts/analyze_mobile_ux.py scanned Uswitch, broadband.co.uk and choose.co.uk (MoneySavingExpert 403, reported not bypassed) with a mobile Safari user agent for markup/CSS signals: viewport meta and hamburger menu markers were universal but already correct on our own site; tel: click-to-call was absent everywhere (0/4, skipped); sticky bottom CTA (1/4) and apple-touch-icon (2/4) were too weak/incomplete to act on. The real gap was found by direct inspection, not the scan: the mobile nav was a small anchored dropdown of 10 flat links with ~36px touch targets, while the desktop nav beside it was a full mega-menu, and the header postcode checker was desktop-only so phone users had no quick postcode access outside the homepage/deals page. Replaced it with new components/MobileNav.tsx: a full-width slide-down panel reusing the desktop mega-menu's own icon/link data (exported from MainNav.tsx, so the two can't drift apart), every link at a 44px (min-h-11) touch target, and the postcode checker embedded at the top so it's reachable from any page. Added anchor ids to /guides category sections so the new mobile Guides menu jumps to a real target instead of an unread query param.</t>
+          <t>Researched via scripts/analyze_homepage_visual_design.py against 5 UK broadband comparison homepages: none uses stock-photo hero banners; the dominant visual language is heavy inline SVG (Uswitch ships 195) and provider logos, no carousel/animation library detected anywhere. Generated 7 original on-brand SVG illustrations (scripts/generate_homepage_illustrations.py: hero network graphic, 3 colour-filled step icons, 2 gradient blobs, a quiz illustration) rather than stock photography, matching what's actually proven in this vertical. Added a scroll-reveal component, hover interactions, and restructured the Broadband Match promo to a two-column illustrated layout. Content/copy unchanged, visual/UX only.</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -8603,7 +7179,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>components/MobileNav.tsx, components/MainNav.tsx, app/layout.tsx, app/guides/page.tsx</t>
+          <t>app/page.tsx, components/ScrollReveal.tsx, public/illustrations/</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -8638,19 +7214,19 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Mobile and cross-device navigation overhaul</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
+          <t>New scripts/analyze_mobile_ux.py scanned Uswitch, broadband.co.uk and choose.co.uk (MoneySavingExpert 403, reported not bypassed) with a mobile Safari user agent for markup/CSS signals: viewport meta and hamburger menu markers were universal but already correct on our own site; tel: click-to-call was absent everywhere (0/4, skipped); sticky bottom CTA (1/4) and apple-touch-icon (2/4) were too weak/incomplete to act on. The real gap was found by direct inspection, not the scan: the mobile nav was a small anchored dropdown of 10 flat links with ~36px touch targets, while the desktop nav beside it was a full mega-menu, and the header postcode checker was desktop-only so phone users had no quick postcode access outside the homepage/deals page. Replaced it with new components/MobileNav.tsx: a full-width slide-down panel reusing the desktop mega-menu's own icon/link data (exported from MainNav.tsx, so the two can't drift apart), every link at a 44px (min-h-11) touch target, and the postcode checker embedded at the top so it's reachable from any page. Added anchor ids to /guides category sections so the new mobile Guides menu jumps to a real target instead of an unread query param.</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -8659,7 +7235,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>components/MainNav.tsx, app/layout.tsx</t>
+          <t>components/MobileNav.tsx, components/MainNav.tsx, app/layout.tsx, app/guides/page.tsx</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8694,19 +7270,19 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Animated, interactive mobile menu with click-outside-to-close</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Direct UX/interaction-design request, not a scraping pass. Rewrote components/MobileNav.tsx from a native &lt;details&gt; element (no animation, no click-outside-to-close) to a controlled client component: hamburger icon morphs into an X on open; a blurred backdrop closes the menu on click or Escape; the panel and its sections slide/fade in with a staggered delay reusing the same transition idiom as components/ScrollReveal.tsx; Providers/Postcode/Guides/Tools became single-open accordions using a CSS-only grid-template-rows 0fr-&gt;1fr transition (no JS height measurement); the menu auto-closes on route change via usePathname(); background scroll is locked while open; focus moves into the panel on open and returns to the trigger on Escape. Global prefers-reduced-motion handling already in app/globals.css applies automatically. Not visually verified on a real device — no browser automation tool available this session, validated via build output, generated CSS and server-rendered markup only.</t>
+          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -8715,7 +7291,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>components/MobileNav.tsx</t>
+          <t>components/MainNav.tsx, app/layout.tsx</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -8745,24 +7321,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Animated, interactive mobile menu with click-outside-to-close</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
+          <t>Direct UX/interaction-design request, not a scraping pass. Rewrote components/MobileNav.tsx from a native &lt;details&gt; element (no animation, no click-outside-to-close) to a controlled client component: hamburger icon morphs into an X on open; a blurred backdrop closes the menu on click or Escape; the panel and its sections slide/fade in with a staggered delay reusing the same transition idiom as components/ScrollReveal.tsx; Providers/Postcode/Guides/Tools became single-open accordions using a CSS-only grid-template-rows 0fr-&gt;1fr transition (no JS height measurement); the menu auto-closes on route change via usePathname(); background scroll is locked while open; focus moves into the panel on open and returns to the trigger on Escape. Global prefers-reduced-motion handling already in app/globals.css applies automatically. Not visually verified on a real device — no browser automation tool available this session, validated via build output, generated CSS and server-rendered markup only.</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -8771,22 +7347,22 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
+          <t>components/MobileNav.tsx</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Email delivery provider</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8801,24 +7377,24 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
+          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
         <v>49</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -8827,22 +7403,22 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
+          <t>New subscription flow + data/provider-live-deals.json</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Email delivery provider</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>Growth playbook — Functionality pillar</t>
         </is>
       </c>
     </row>
@@ -8862,28 +7438,28 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
+          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>app/layout.tsx, components/Logo.tsx</t>
+          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8908,53 +7484,53 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
+          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Sitewide template performance report</t>
+          <t>app/layout.tsx, components/Logo.tsx</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Field data or representative lab baselines</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8964,29 +7540,29 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -8995,12 +7571,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>Sitewide template performance report</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>Field data or representative lab baselines</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -9010,7 +7586,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -9020,43 +7596,43 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
+          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Sitewide crawl and redirect report</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -9066,7 +7642,7 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -9076,43 +7652,43 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide crawl and redirect report</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -9122,7 +7698,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -9137,24 +7713,24 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -9163,12 +7739,12 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
@@ -9178,7 +7754,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -9193,53 +7769,109 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="F29" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="G29" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L28"/>
+  <autoFilter ref="A1:L29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9280,7 +7912,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>60 total (33 page builds, 27 feature/strategy builds); 14 already marked Done.</t>
+          <t>61 total (33 page builds, 28 feature/strategy builds); 47 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -176,8 +176,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L62" headerRowCount="1">
-  <autoFilter ref="A1:L62"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L63" headerRowCount="1">
+  <autoFilter ref="A1:L63"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -241,8 +241,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L29" headerRowCount="1">
-  <autoFilter ref="A1:L29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L30" headerRowCount="1">
+  <autoFilter ref="A1:L30"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L62"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>feat-homepage-visual-redesign</t>
+          <t>feat-postcode-journey-personalisation</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2915,11 +2915,11 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Homepage visual redesign: illustrations + interactivity</t>
+          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>55</v>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>feat-mobile-cross-device-navigation</t>
+          <t>feat-homepage-visual-redesign</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -2959,14 +2959,14 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Mobile and cross-device navigation overhaul</t>
+          <t>Homepage visual redesign: illustrations + interactivity</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>feat-mega-menu-navigation</t>
+          <t>feat-mobile-cross-device-navigation</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3003,14 +3003,14 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Mobile and cross-device navigation overhaul</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>feat-animated-interactive-mobile-menu</t>
+          <t>feat-mega-menu-navigation</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -3047,14 +3047,14 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Animated, interactive mobile menu with click-outside-to-close</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>feat-price-drop-alerts</t>
+          <t>feat-animated-interactive-mobile-menu</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3086,19 +3086,19 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Animated, interactive mobile menu with click-outside-to-close</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>feat-page-type-ux-redesign</t>
+          <t>feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -3130,19 +3130,19 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
         <v>49</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr"/>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>feat-footer-logo-interactivity</t>
+          <t>feat-page-type-ux-redesign</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3179,18 +3179,18 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3200,11 +3200,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
-        </is>
-      </c>
+      <c r="L56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
@@ -3212,43 +3208,47 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>audit-core-web-vitals-reporting</t>
+          <t>feat-footer-logo-interactivity</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr"/>
       <c r="K57" s="3" t="inlineStr"/>
-      <c r="L57" s="3" t="inlineStr"/>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -3256,29 +3256,29 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>audit-core-web-vitals-reporting</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3300,33 +3300,33 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>audit-broken-links-redirects</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -3344,33 +3344,33 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-broken-links-redirects</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -3398,19 +3398,19 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3442,19 +3442,19 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3470,8 +3470,52 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
     </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr"/>
+      <c r="K63" s="3" t="inlineStr"/>
+      <c r="L63" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L62"/>
+  <autoFilter ref="A1:L63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4357,7 +4401,7 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="31" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
@@ -4458,7 +4502,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -4512,7 +4556,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -4566,7 +4610,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4620,7 +4664,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -4674,7 +4718,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4728,7 +4772,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -4782,7 +4826,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4836,7 +4880,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -4890,7 +4934,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4944,7 +4988,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -4998,7 +5042,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5052,7 +5096,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -5106,7 +5150,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5160,7 +5204,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -5214,7 +5258,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5268,7 +5312,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -5322,7 +5366,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -5376,7 +5420,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -5430,7 +5474,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5484,7 +5528,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -5538,7 +5582,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5592,7 +5636,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -5646,7 +5690,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -5700,7 +5744,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -5754,7 +5798,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -5808,7 +5852,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -5862,7 +5906,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -5916,7 +5960,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -5970,7 +6014,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -6024,7 +6068,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -6078,7 +6122,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -6132,7 +6176,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -6186,7 +6230,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -6223,7 +6267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7158,16 +7202,16 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Homepage visual redesign: illustrations + interactivity</t>
+          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Researched via scripts/analyze_homepage_visual_design.py against 5 UK broadband comparison homepages: none uses stock-photo hero banners; the dominant visual language is heavy inline SVG (Uswitch ships 195) and provider logos, no carousel/animation library detected anywhere. Generated 7 original on-brand SVG illustrations (scripts/generate_homepage_illustrations.py: hero network graphic, 3 colour-filled step icons, 2 gradient blobs, a quiz illustration) rather than stock photography, matching what's actually proven in this vertical. Added a scroll-reveal component, hover interactions, and restructured the Broadband Match promo to a two-column illustrated layout. Content/copy unchanged, visual/UX only.</t>
+          <t>User asked for a postcode -&gt; select-your-house-number address picker with customised content, and explicitly asked whether it could be built free. Researched live (WebSearch, 2026-08-23): full UK address-level lookup (the data behind 'pick your house from a list') is Royal Mail's licensed PAF data, not open -- getAddress.io, a popular free-tier provider, was shut down in Oct 2025 after a Royal Mail/IDDQD IP claim; Ideal Postcodes gives a 1-month/50-credit trial then pay-as-you-go; no provider offers a genuine unlimited free tier at real traffic. Separately, even a working address picker wouldn't improve accuracy without a paid per-address line-checker API (Openreach or provider-specific), which is a commercial relationship, not a script. Presented both findings and 3 options to the user via AskUserQuestion; they chose the free path: deepen personalisation using data already held, no new API, no new cost. Shipped: extended the existing components/PostcodeContextBar.tsx (previously only on deals/compare/provider pages) to guide pages and all 3 tool pages (speed test, broadband match, cost calculator) so a stored postcode follows the visitor through the full journey; new components/ProviderAvailabilityBadge.tsx shows a real yes/no ('BT is/isn't listed as available in {town}') on provider review pages, but only for the 51 postcode areas with real availableProviders data in data/postcodes.ts -- silently renders nothing outside that set rather than guessing; new components/ReturningVisitorBanner.tsx greets a returning visitor on the homepage with a direct link back to their own postcode's deals.</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>55</v>
@@ -7179,12 +7223,12 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>app/page.tsx, components/ScrollReveal.tsx, public/illustrations/</t>
+          <t>components/ProviderAvailabilityBadge.tsx, components/ReturningVisitorBanner.tsx, components/PostcodeContextBar.tsx, app/page.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/speed-test/page.tsx, app/tools/broadband-match/page.tsx, app/tools/broadband-cost-calculator/page.tsx</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None -- deliberately built on data already held, no new API/cost</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -7214,19 +7258,19 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Mobile and cross-device navigation overhaul</t>
+          <t>Homepage visual redesign: illustrations + interactivity</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>New scripts/analyze_mobile_ux.py scanned Uswitch, broadband.co.uk and choose.co.uk (MoneySavingExpert 403, reported not bypassed) with a mobile Safari user agent for markup/CSS signals: viewport meta and hamburger menu markers were universal but already correct on our own site; tel: click-to-call was absent everywhere (0/4, skipped); sticky bottom CTA (1/4) and apple-touch-icon (2/4) were too weak/incomplete to act on. The real gap was found by direct inspection, not the scan: the mobile nav was a small anchored dropdown of 10 flat links with ~36px touch targets, while the desktop nav beside it was a full mega-menu, and the header postcode checker was desktop-only so phone users had no quick postcode access outside the homepage/deals page. Replaced it with new components/MobileNav.tsx: a full-width slide-down panel reusing the desktop mega-menu's own icon/link data (exported from MainNav.tsx, so the two can't drift apart), every link at a 44px (min-h-11) touch target, and the postcode checker embedded at the top so it's reachable from any page. Added anchor ids to /guides category sections so the new mobile Guides menu jumps to a real target instead of an unread query param.</t>
+          <t>Researched via scripts/analyze_homepage_visual_design.py against 5 UK broadband comparison homepages: none uses stock-photo hero banners; the dominant visual language is heavy inline SVG (Uswitch ships 195) and provider logos, no carousel/animation library detected anywhere. Generated 7 original on-brand SVG illustrations (scripts/generate_homepage_illustrations.py: hero network graphic, 3 colour-filled step icons, 2 gradient blobs, a quiz illustration) rather than stock photography, matching what's actually proven in this vertical. Added a scroll-reveal component, hover interactions, and restructured the Broadband Match promo to a two-column illustrated layout. Content/copy unchanged, visual/UX only.</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -7235,7 +7279,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>components/MobileNav.tsx, components/MainNav.tsx, app/layout.tsx, app/guides/page.tsx</t>
+          <t>app/page.tsx, components/ScrollReveal.tsx, public/illustrations/</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7270,19 +7314,19 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Mobile and cross-device navigation overhaul</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
+          <t>New scripts/analyze_mobile_ux.py scanned Uswitch, broadband.co.uk and choose.co.uk (MoneySavingExpert 403, reported not bypassed) with a mobile Safari user agent for markup/CSS signals: viewport meta and hamburger menu markers were universal but already correct on our own site; tel: click-to-call was absent everywhere (0/4, skipped); sticky bottom CTA (1/4) and apple-touch-icon (2/4) were too weak/incomplete to act on. The real gap was found by direct inspection, not the scan: the mobile nav was a small anchored dropdown of 10 flat links with ~36px touch targets, while the desktop nav beside it was a full mega-menu, and the header postcode checker was desktop-only so phone users had no quick postcode access outside the homepage/deals page. Replaced it with new components/MobileNav.tsx: a full-width slide-down panel reusing the desktop mega-menu's own icon/link data (exported from MainNav.tsx, so the two can't drift apart), every link at a 44px (min-h-11) touch target, and the postcode checker embedded at the top so it's reachable from any page. Added anchor ids to /guides category sections so the new mobile Guides menu jumps to a real target instead of an unread query param.</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -7291,7 +7335,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>components/MainNav.tsx, app/layout.tsx</t>
+          <t>components/MobileNav.tsx, components/MainNav.tsx, app/layout.tsx, app/guides/page.tsx</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -7326,19 +7370,19 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Animated, interactive mobile menu with click-outside-to-close</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Direct UX/interaction-design request, not a scraping pass. Rewrote components/MobileNav.tsx from a native &lt;details&gt; element (no animation, no click-outside-to-close) to a controlled client component: hamburger icon morphs into an X on open; a blurred backdrop closes the menu on click or Escape; the panel and its sections slide/fade in with a staggered delay reusing the same transition idiom as components/ScrollReveal.tsx; Providers/Postcode/Guides/Tools became single-open accordions using a CSS-only grid-template-rows 0fr-&gt;1fr transition (no JS height measurement); the menu auto-closes on route change via usePathname(); background scroll is locked while open; focus moves into the panel on open and returns to the trigger on Escape. Global prefers-reduced-motion handling already in app/globals.css applies automatically. Not visually verified on a real device — no browser automation tool available this session, validated via build output, generated CSS and server-rendered markup only.</t>
+          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
         <v>50</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -7347,7 +7391,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>components/MobileNav.tsx</t>
+          <t>components/MainNav.tsx, app/layout.tsx</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7377,24 +7421,24 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Animated, interactive mobile menu with click-outside-to-close</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
+          <t>Direct UX/interaction-design request, not a scraping pass. Rewrote components/MobileNav.tsx from a native &lt;details&gt; element (no animation, no click-outside-to-close) to a controlled client component: hamburger icon morphs into an X on open; a blurred backdrop closes the menu on click or Escape; the panel and its sections slide/fade in with a staggered delay reusing the same transition idiom as components/ScrollReveal.tsx; Providers/Postcode/Guides/Tools became single-open accordions using a CSS-only grid-template-rows 0fr-&gt;1fr transition (no JS height measurement); the menu auto-closes on route change via usePathname(); background scroll is locked while open; focus moves into the panel on open and returns to the trigger on Escape. Global prefers-reduced-motion handling already in app/globals.css applies automatically. Not visually verified on a real device — no browser automation tool available this session, validated via build output, generated CSS and server-rendered markup only.</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -7403,22 +7447,22 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
+          <t>components/MobileNav.tsx</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>Email delivery provider</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7433,24 +7477,24 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
+          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
         <v>49</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -7459,22 +7503,22 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
+          <t>New subscription flow + data/provider-live-deals.json</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Email delivery provider</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>Growth playbook — Functionality pillar</t>
         </is>
       </c>
     </row>
@@ -7494,28 +7538,28 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
+          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>app/layout.tsx, components/Logo.tsx</t>
+          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -7540,53 +7584,53 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
+          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Sitewide template performance report</t>
+          <t>app/layout.tsx, components/Logo.tsx</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Field data or representative lab baselines</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7596,29 +7640,29 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -7627,12 +7671,12 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>Sitewide template performance report</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>Field data or representative lab baselines</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -7642,7 +7686,7 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -7652,43 +7696,43 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
+          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Sitewide crawl and redirect report</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -7698,7 +7742,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -7708,43 +7752,43 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide crawl and redirect report</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
@@ -7754,7 +7798,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -7769,24 +7813,24 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -7795,12 +7839,12 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -7810,7 +7854,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -7825,53 +7869,109 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F29" s="3" t="n">
+      <c r="F30" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G29" s="3" t="n">
+      <c r="G30" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L29" s="3" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L29"/>
+  <autoFilter ref="A1:L30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7912,7 +8012,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>61 total (33 page builds, 28 feature/strategy builds); 47 already marked Done.</t>
+          <t>62 total (33 page builds, 29 feature/strategy builds); 48 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$63</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -176,8 +176,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L63" headerRowCount="1">
-  <autoFilter ref="A1:L63"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L64" headerRowCount="1">
+  <autoFilter ref="A1:L64"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -197,8 +197,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PendingBuildPriorityTable" displayName="PendingBuildPriorityTable" ref="A1:N15" headerRowCount="1">
-  <autoFilter ref="A1:N15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PendingBuildPriorityTable" displayName="PendingBuildPriorityTable" ref="A1:N16" headerRowCount="1">
+  <autoFilter ref="A1:N16"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Pending Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -241,8 +241,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L30" headerRowCount="1">
-  <autoFilter ref="A1:L30"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L31" headerRowCount="1">
+  <autoFilter ref="A1:L31"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3300,38 +3300,38 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>ops-awin-publisher-api-integration</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Direct Awin Publisher API access — programme status and link generation</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G59" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="G59" s="3" t="n">
-        <v>58</v>
-      </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr"/>
@@ -3344,33 +3344,33 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>audit-broken-links-redirects</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3388,33 +3388,33 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-broken-links-redirects</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3442,19 +3442,19 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -3486,19 +3486,19 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
@@ -3514,8 +3514,52 @@
       <c r="K63" s="3" t="inlineStr"/>
       <c r="L63" s="3" t="inlineStr"/>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L63"/>
+  <autoFilter ref="A1:L64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3529,7 +3573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4112,48 +4156,48 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>ops-awin-publisher-api-integration</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Direct Awin Publisher API access — programme status and link generation</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G11" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>58</v>
-      </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>scripts/awin_sync.py</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>AWIN_API_TOKEN from the user's Awin account (user menu -&gt; API Credentials)</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr"/>
@@ -4166,33 +4210,33 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>audit-broken-links-redirects</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4202,12 +4246,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Sitewide crawl and redirect report</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -4220,33 +4264,33 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-broken-links-redirects</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -4256,12 +4300,12 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide crawl and redirect report</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr"/>
@@ -4274,7 +4318,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -4284,19 +4328,19 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -4310,12 +4354,12 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr"/>
@@ -4328,7 +4372,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -4338,19 +4382,19 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -4364,20 +4408,74 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
+          <t>components/</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>None, but easier before the guide count grows further</t>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr"/>
       <c r="M15" s="3" t="inlineStr"/>
       <c r="N15" s="3" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>None, but easier before the guide count grows further</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N15"/>
+  <autoFilter ref="A1:N16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4401,7 +4499,7 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="31" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
@@ -4502,7 +4600,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -4556,7 +4654,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -4610,7 +4708,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4664,7 +4762,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -4718,7 +4816,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4772,7 +4870,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -4826,7 +4924,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4880,7 +4978,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -4934,7 +5032,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4988,7 +5086,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -5042,7 +5140,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5096,7 +5194,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -5150,7 +5248,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5204,7 +5302,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -5258,7 +5356,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5312,7 +5410,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -5366,7 +5464,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -5420,7 +5518,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -5474,7 +5572,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5528,7 +5626,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -5582,7 +5680,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5636,7 +5734,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -5690,7 +5788,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -5744,7 +5842,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -5798,7 +5896,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -5852,7 +5950,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -5906,7 +6004,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -5960,7 +6058,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -6014,7 +6112,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -6068,7 +6166,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -6122,7 +6220,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -6176,7 +6274,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -6230,7 +6328,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -6267,7 +6365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7696,53 +7794,53 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Direct Awin Publisher API access — programme status and link generation</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+          <t>User asked to connect Claude to their Awin account. There's no one-click connector for Awin (unlike Google Drive/Gmail), so this uses Awin's own Publisher API directly. Researched live (WebSearch, 2026-08-23) to confirm current endpoints rather than relying on possibly-stale API knowledge: GET /publishers/{id}/programmedetails?relationship=any for advertiser programme status (joined/pending/suspended/rejected/notjoined), and POST /publishers/{id}/linkbuilder/generate for correct current tracking links. Built scripts/awin_sync.py with both operations, reading AWIN_API_TOKEN and AWIN_PUBLISHER_ID (defaults to the publisher ID already referenced elsewhere in this repo, 2942019) from env vars. Fails gracefully with setup instructions if the token isn't set. Internal tooling only -- never touches the live site or Vercel env vars. Not yet verified against a real token/live API response since none was available at build time -- verify the first real run once the user generates their token.</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G26" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="G26" s="2" t="n">
-        <v>58</v>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>scripts/awin_sync.py</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>AWIN_API_TOKEN from the user's Awin account (user menu -&gt; API Credentials)</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7752,43 +7850,43 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
+          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Sitewide crawl and redirect report</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
@@ -7798,7 +7896,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -7808,43 +7906,43 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide crawl and redirect report</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -7854,7 +7952,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -7869,24 +7967,24 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
@@ -7895,12 +7993,12 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
@@ -7910,7 +8008,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -7925,53 +8023,109 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="F31" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="G31" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L31" s="3" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L30"/>
+  <autoFilter ref="A1:L31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8012,7 +8166,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>62 total (33 page builds, 29 feature/strategy builds); 48 already marked Done.</t>
+          <t>63 total (33 page builds, 30 feature/strategy builds); 48 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
@@ -197,8 +197,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PendingBuildPriorityTable" displayName="PendingBuildPriorityTable" ref="A1:N16" headerRowCount="1">
-  <autoFilter ref="A1:N16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PendingBuildPriorityTable" displayName="PendingBuildPriorityTable" ref="A1:N15" headerRowCount="1">
+  <autoFilter ref="A1:N15"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Pending Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr"/>
@@ -3573,7 +3573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4156,48 +4156,48 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>ops-awin-publisher-api-integration</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Direct Awin Publisher API access — programme status and link generation</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>scripts/awin_sync.py</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>AWIN_API_TOKEN from the user's Awin account (user menu -&gt; API Credentials)</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr"/>
@@ -4210,33 +4210,33 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>audit-broken-links-redirects</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4246,12 +4246,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>Sitewide crawl and redirect report</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -4264,33 +4264,33 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>audit-broken-links-redirects</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Bigger bet</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -4300,12 +4300,12 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Sitewide crawl and redirect report</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr"/>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -4328,19 +4328,19 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>components/</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr"/>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-decouple-content-from-code</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -4382,19 +4382,19 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Decouple guide content from code deploys</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -4408,74 +4408,20 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr"/>
       <c r="M15" s="3" t="inlineStr"/>
       <c r="N15" s="3" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>bet-decouple-content-from-code</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Bigger bet</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Decouple guide content from code deploys</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>None, but easier before the guide count grows further</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N16"/>
+  <autoFilter ref="A1:N15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6857,7 +6803,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Apply to best-fit provider programmes with tailored pitches, relevant live URLs, audience evidence, promotional method and compliance controls; log decisions and feedback.</t>
+          <t>Apply to best-fit provider programmes with tailored pitches, relevant live URLs, audience evidence, promotional method and compliance controls; log decisions and feedback. Real status pulled from the Awin Publisher API 2026-08-23 (see ops-awin-publisher-api-integration): joined -- TalkTalk, Broadband Genie, Zzoomm, Highland Broadband. Pending -- Sky ROI, Community Fibre, National Broadband, Trooli, Pine Media, Cuckoo, Zen Internet. Rejected -- BT (consumer + business), Vodafone, Plusnet, EE, Virgin Media, Hyperoptic, toob, giffgaff. The 8 rejected mainstream providers are the priority re-application targets; Zzoomm and Highland Broadband are approved but not yet added as providers on the site at all.</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
@@ -7809,7 +7755,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>User asked to connect Claude to their Awin account. There's no one-click connector for Awin (unlike Google Drive/Gmail), so this uses Awin's own Publisher API directly. Researched live (WebSearch, 2026-08-23) to confirm current endpoints rather than relying on possibly-stale API knowledge: GET /publishers/{id}/programmedetails?relationship=any for advertiser programme status (joined/pending/suspended/rejected/notjoined), and POST /publishers/{id}/linkbuilder/generate for correct current tracking links. Built scripts/awin_sync.py with both operations, reading AWIN_API_TOKEN and AWIN_PUBLISHER_ID (defaults to the publisher ID already referenced elsewhere in this repo, 2942019) from env vars. Fails gracefully with setup instructions if the token isn't set. Internal tooling only -- never touches the live site or Vercel env vars. Not yet verified against a real token/live API response since none was available at build time -- verify the first real run once the user generates their token.</t>
+          <t>User asked to connect Claude to their Awin account and provided a real API token. There's no one-click connector for Awin (unlike Google Drive/Gmail), so this uses Awin's own Publisher API directly. First live run corrected two wrong assumptions from documentation research: 'programmedetails' requires a specific advertiserId (not a bulk listing endpoint) -- the actual bulk-status endpoint is GET /publishers/{id}/programmes?relationship=X, and 'any' is not a valid value for it (loops joined/pending/suspended/rejected instead; 'notjoined' returns the ~21k whole-platform catalogue so it's excluded from the default and only fetched on request). POST /publishers/{id}/linkbuilder/generate confirmed working, verified against TalkTalk (advertiser 3674). REAL FINDING from the first run, both surfaced to the user and worth acting on: only 4 programmes are joined (TalkTalk, Broadband Genie, Zzoomm, Highland Broadband), 7 pending (Sky ROI, Community Fibre, National Broadband, Trooli, Pine Media, Cuckoo, Zen Internet), and 9 REJECTED including BT (both consumer and business), Vodafone, Plusnet, EE, Virgin Media, Hyperoptic and toob. Cross-checked data/providers.ts: none of the currently-live affiliateUrl values (including TalkTalk, which IS approved) use Awin's awin1.com tracking format -- they're all plain provider URLs, so the site is very likely not earning commission on any current outbound click, joined or not, despite the on-page commercial disclosures implying it might.</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -7835,7 +7781,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -8166,7 +8112,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>63 total (33 page builds, 30 feature/strategy builds); 48 already marked Done.</t>
+          <t>63 total (33 page builds, 30 feature/strategy builds); 49 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -176,8 +176,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L64" headerRowCount="1">
-  <autoFilter ref="A1:L64"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L65" headerRowCount="1">
+  <autoFilter ref="A1:L65"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -197,8 +197,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PendingBuildPriorityTable" displayName="PendingBuildPriorityTable" ref="A1:N15" headerRowCount="1">
-  <autoFilter ref="A1:N15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PendingBuildPriorityTable" displayName="PendingBuildPriorityTable" ref="A1:N48" headerRowCount="1">
+  <autoFilter ref="A1:N48"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Pending Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -241,8 +241,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L31" headerRowCount="1">
-  <autoFilter ref="A1:L31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L32" headerRowCount="1">
+  <autoFilter ref="A1:L32"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr"/>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr"/>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr"/>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr"/>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr"/>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr"/>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr"/>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr"/>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -2368,12 +2368,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>page-providers/gigaclear</t>
+          <t>content-awin-approved-provider-deep-content</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2383,18 +2383,18 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
+          <t>Deep, researched content for Awin-approved providers (TalkTalk, Zzoomm, Highland Broadband)</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>56.9</v>
+        <v>58</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>27.9</v>
+        <v>62</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>page-providers/youfibre</t>
+          <t>page-providers/gigaclear</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2427,14 +2427,14 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
+          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>56.6</v>
+        <v>56.9</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>28.7</v>
+        <v>27.9</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr"/>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>page-providers/cuckoo</t>
+          <t>page-providers/youfibre</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2471,14 +2471,14 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
+          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>56.5</v>
+        <v>56.6</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>27.9</v>
+        <v>28.7</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -2500,12 +2500,12 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>audit-city-hub-thinness</t>
+          <t>page-providers/cuckoo</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Content audit</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -2515,18 +2515,18 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Verify each new city hub has a genuinely local fact</t>
+          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>56</v>
+        <v>56.5</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>50</v>
+        <v>27.9</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>page-guides/black-friday-broadband-deals-uk</t>
+          <t>audit-city-hub-thinness</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Content audit</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2559,23 +2559,23 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
+          <t>Verify each new city hub has a genuinely local fact</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>55.8</v>
+        <v>56</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>page-providers/shell-energy</t>
+          <t>page-guides/black-friday-broadband-deals-uk</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -2603,23 +2603,23 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
+          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>55.7</v>
+        <v>55.8</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr"/>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>page-research/broadband-customer-service-rankings-uk</t>
+          <t>page-providers/shell-energy</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2647,14 +2647,14 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
+          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>55.1</v>
+        <v>55.7</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -2676,47 +2676,43 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>feat-nav-header-footer-ia</t>
+          <t>page-research/broadband-customer-service-rankings-uk</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Navigation/header/footer IA improvements</t>
+          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>55</v>
+        <v>55.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>60</v>
+        <v>27.8</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr"/>
       <c r="K45" s="3" t="inlineStr"/>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t>Shipped 2026-08-22: scripts/scrape_navigation_patterns.py scanned 5 best-in-class sites (broadband.co.uk stood out on sticky header + breadcrumbs + trust badge). Confirmed BroadbandPicker's sticky header and breadcrumbs already match best practice. Added Postcode to primary nav (desktop+mobile), restructured footer 4-&gt;6 columns adding Tools, Find Broadband by Area, and Research links to fix a crawl/link-equity gap for the 2,800+ postcode-district and tools pages. Deliberately did NOT fabricate a trust badge (no real Trustpilot/press presence yet) and did NOT widen the header postcode breakpoint (risk of stacking two unverified density changes without a browser check). See docs/navigation-ia-analysis.md.</t>
-        </is>
-      </c>
+      <c r="L45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -2724,7 +2720,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>feat-contact-form-email-delivery</t>
+          <t>feat-nav-header-footer-ia</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2734,19 +2730,19 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Working contact form delivering to a real inbox, no third-party service</t>
+          <t>Navigation/header/footer IA improvements</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
         <v>55</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2755,12 +2751,16 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-22: scripts/scrape_navigation_patterns.py scanned 5 best-in-class sites (broadband.co.uk stood out on sticky header + breadcrumbs + trust badge). Confirmed BroadbandPicker's sticky header and breadcrumbs already match best practice. Added Postcode to primary nav (desktop+mobile), restructured footer 4-&gt;6 columns adding Tools, Find Broadband by Area, and Research links to fix a crawl/link-equity gap for the 2,800+ postcode-district and tools pages. Deliberately did NOT fabricate a trust badge (no real Trustpilot/press presence yet) and did NOT widen the header postcode breakpoint (risk of stacking two unverified density changes without a browser check). See docs/navigation-ia-analysis.md.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
@@ -2768,38 +2768,38 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
+          <t>feat-contact-form-email-delivery</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Broadband complaints and the ombudsman: your UK rights</t>
+          <t>Working contact form delivering to a real inbox, no third-party service</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>54.7</v>
+        <v>55</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>25.9</v>
+        <v>50</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr"/>
@@ -2812,12 +2812,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>growth-original-research-outreach</t>
+          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2827,23 +2827,23 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Run original-research outreach and digital PR</t>
+          <t>Broadband complaints and the ombudsman: your UK rights</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>54</v>
+        <v>54.7</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>68</v>
+        <v>25.9</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -2856,29 +2856,29 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>growth-quarterly-data-reprioritisation</t>
+          <t>growth-original-research-outreach</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
+          <t>Run original-research outreach and digital PR</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr"/>
@@ -2900,29 +2900,29 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>feat-postcode-journey-personalisation</t>
+          <t>growth-quarterly-data-reprioritisation</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
         <v>53</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>feat-homepage-visual-redesign</t>
+          <t>feat-postcode-journey-personalisation</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -2959,11 +2959,11 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Homepage visual redesign: illustrations + interactivity</t>
+          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>55</v>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>feat-mobile-cross-device-navigation</t>
+          <t>feat-homepage-visual-redesign</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3003,14 +3003,14 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Mobile and cross-device navigation overhaul</t>
+          <t>Homepage visual redesign: illustrations + interactivity</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>feat-mega-menu-navigation</t>
+          <t>feat-mobile-cross-device-navigation</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -3047,14 +3047,14 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Mobile and cross-device navigation overhaul</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>feat-animated-interactive-mobile-menu</t>
+          <t>feat-mega-menu-navigation</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3091,14 +3091,14 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Animated, interactive mobile menu with click-outside-to-close</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
         <v>50</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>feat-price-drop-alerts</t>
+          <t>feat-animated-interactive-mobile-menu</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -3130,19 +3130,19 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Animated, interactive mobile menu with click-outside-to-close</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr"/>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>feat-page-type-ux-redesign</t>
+          <t>feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3174,19 +3174,19 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
         <v>49</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>feat-footer-logo-interactivity</t>
+          <t>feat-page-type-ux-redesign</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -3223,18 +3223,18 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -3244,11 +3244,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr"/>
       <c r="K57" s="3" t="inlineStr"/>
-      <c r="L57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
-        </is>
-      </c>
+      <c r="L57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -3256,43 +3252,47 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>audit-core-web-vitals-reporting</t>
+          <t>feat-footer-logo-interactivity</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
@@ -3300,38 +3300,38 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>ops-awin-publisher-api-integration</t>
+          <t>audit-core-web-vitals-reporting</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Direct Awin Publisher API access — programme status and link generation</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
         <v>47</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr"/>
@@ -3344,38 +3344,38 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>ops-awin-publisher-api-integration</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Direct Awin Publisher API access — programme status and link generation</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G60" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="G60" s="2" t="n">
-        <v>58</v>
-      </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
@@ -3388,33 +3388,33 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>audit-broken-links-redirects</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -3432,33 +3432,33 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-broken-links-redirects</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -3486,19 +3486,19 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3530,19 +3530,19 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3558,8 +3558,52 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr"/>
+      <c r="K65" s="3" t="inlineStr"/>
+      <c r="L65" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L64"/>
+  <autoFilter ref="A1:L65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3573,23 +3617,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="50" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -3670,50 +3714,46 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>growth-awin-advertiser-outreach</t>
+          <t>page-providers/compare/hyperoptic-vs-youfibre</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Partnerships</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Continue selective Awin advertiser outreach</t>
+          <t>Hyperoptic vs YouFibre broadband: which is better in 2026?</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>60</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Awin publisher 2942019 and partner application log</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Current audience evidence and compliant commercial pages</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/providers/compare/hyperoptic-vs-youfibre</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
@@ -3724,33 +3764,33 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>feat-review-aggregation-module</t>
+          <t>page-postcode/sheffield</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Real review-aggregation trust module</t>
+          <t>Broadband providers in Sheffield: coverage and best deals</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>59</v>
+        <v>66.8</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -3760,14 +3800,10 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>New shared component, used on provider + comparison pages</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/postcode/sheffield</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
@@ -3778,50 +3814,46 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ops-adsense-site-review</t>
+          <t>page-guides/static-ip-business-broadband-explained</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Complete AdSense site review and authorisation monitoring</t>
+          <t>Static IP business broadband: when you need one and how much it costs</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>58</v>
+        <v>66.3</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>55</v>
+        <v>46.1</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>AdSense status and /ads.txt</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Google site-review processing</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/guides/static-ip-business-broadband-explained</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
@@ -3832,12 +3864,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>audit-city-hub-thinness</t>
+          <t>page-guides/student-broadband-by-university-city</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Content audit</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -3847,18 +3879,18 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Verify each new city hub has a genuinely local fact</t>
+          <t>Student broadband by university city: short-term and rolling deals</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>56</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>50</v>
+        <v>36.2</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -3868,14 +3900,10 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>data/priority-pages.ts city entries</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/guides/student-broadband-by-university-city</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
@@ -3886,50 +3914,46 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>feat-contact-form-email-delivery</t>
+          <t>page-postcode/edinburgh</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Working contact form delivering to a real inbox, no third-party service</t>
+          <t>Broadband providers in Edinburgh: coverage and best deals</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>55</v>
+        <v>65.8</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>app/api/contact/route.ts, components/ContactForm.tsx, app/contact/page.tsx</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>CONTACT_SMTP_USER / CONTACT_SMTP_PASS Gmail App Password set in Vercel env vars</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/postcode/edinburgh</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
@@ -3940,12 +3964,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>growth-original-research-outreach</t>
+          <t>page-guides/small-office-broadband-setup-uk</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -3955,35 +3979,31 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Run original-research outreach and digital PR</t>
+          <t>Small office broadband setup: routers, backup and support checklist</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>54</v>
+        <v>65.8</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>68</v>
+        <v>41.9</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>/research/uk-broadband-customer-satisfaction</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>Research page and source methodology are live</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/guides/small-office-broadband-setup-uk</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
@@ -3994,33 +4014,33 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>growth-quarterly-data-reprioritisation</t>
+          <t>page-providers/compare/bt-vs-plusnet</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
+          <t>BT vs Plusnet broadband: which is better in 2026?</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>53</v>
+        <v>65.5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>63</v>
+        <v>36.4</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4030,14 +4050,10 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Next-quarter decision log</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>ops-conversion-reporting-loop and sufficient observation period</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/providers/compare/bt-vs-plusnet</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
@@ -4048,33 +4064,33 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>feat-price-drop-alerts</t>
+          <t>page-postcode/glasgow</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Broadband providers in Glasgow: coverage and best deals</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>49</v>
+        <v>65.5</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>55</v>
+        <v>40.2</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -4084,14 +4100,10 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>Email delivery provider</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/postcode/glasgow</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="inlineStr"/>
@@ -4102,33 +4114,33 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>audit-core-web-vitals-reporting</t>
+          <t>page-postcode/liverpool</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Broadband providers in Liverpool: coverage and best deals</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>47</v>
+        <v>65.5</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>50</v>
+        <v>40.1</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4138,14 +4150,10 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Sitewide template performance report</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>Field data or representative lab baselines</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/postcode/liverpool</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
@@ -4156,33 +4164,33 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>page-guides/broadband-for-landlords-and-hmos-uk</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Broadband for landlords and HMOs: what to set up and who pays</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>45</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>58</v>
+        <v>36.6</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -4192,14 +4200,10 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>Mobile analytics/drop-off data</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/guides/broadband-for-landlords-and-hmos-uk</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="inlineStr"/>
@@ -4210,33 +4214,33 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>audit-broken-links-redirects</t>
+          <t>page-postcode/leeds</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Broadband providers in Leeds: coverage and best deals</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>44</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>48</v>
+        <v>40.3</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4246,14 +4250,10 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Sitewide crawl and redirect report</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/postcode/leeds</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
@@ -4264,12 +4264,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>page-providers/compare/ee-vs-talktalk</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -4279,18 +4279,18 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>EE vs TalkTalk broadband: which is better in 2026?</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>65</v>
+        <v>36.4</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -4300,14 +4300,10 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/providers/compare/ee-vs-talktalk</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr"/>
       <c r="L13" s="3" t="inlineStr"/>
       <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="3" t="inlineStr"/>
@@ -4318,33 +4314,33 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>page-postcode/bristol</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Broadband providers in Bristol: coverage and best deals</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>38</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>45</v>
+        <v>40.8</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4354,14 +4350,10 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>components/</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/postcode/bristol</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
@@ -4372,12 +4364,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>page-postcode/birmingham</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -4387,18 +4379,18 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Broadband providers in Birmingham: coverage and best deals</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>35</v>
+        <v>64.5</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>48</v>
+        <v>41.1</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -4408,20 +4400,1726 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>None, but easier before the guide count grows further</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/postcode/birmingham</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
       <c r="L15" s="3" t="inlineStr"/>
       <c r="M15" s="3" t="inlineStr"/>
       <c r="N15" s="3" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>page-postcode/manchester</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Broadband providers in Manchester: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/manchester</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>page-guides/leased-line-cost-uk-explained</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Leased line cost UK: what small businesses actually pay</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/leased-line-cost-uk-explained</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>page-guides/starlink-vs-fibre-broadband-uk</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Starlink vs fibre broadband: when satellite makes sense in the UK</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/starlink-vs-fibre-broadband-uk</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>page-providers/compare/virgin-media-vs-sky</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Virgin Media vs Sky broadband: which is better in 2026?</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/compare/virgin-media-vs-sky</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>page-guides/january-broadband-deals-uk</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>January broadband deals UK: new-year switching guide</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/january-broadband-deals-uk</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>growth-awin-advertiser-outreach</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Partnerships</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Monetisation</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Continue selective Awin advertiser outreach</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Awin publisher 2942019 and partner application log</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Current audience evidence and compliant commercial pages</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>page-tools/broadband-cost-calculator</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Broadband cost calculator: true monthly and contract-length cost</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/tools/broadband-cost-calculator</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Live at /tools/broadband-cost-calculator, committed and deployed 2026-08-21.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>page-providers/onestream</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Onestream — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/onestream</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>page-guides/no-credit-check-broadband-uk</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>No credit check broadband in the UK: options and what to expect</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/no-credit-check-broadband-uk</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>feat-review-aggregation-module</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Real review-aggregation trust module</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>New shared component, used on provider + comparison pages</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>page-providers/brsk</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Brsk — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/brsk</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>page-guides/fttp-vs-fttc-explained</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>FTTP vs FTTC: what the difference means for your speed</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/fttp-vs-fttc-explained</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
+      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>page-guides/best-mesh-wifi-for-your-broadband-router</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/best-mesh-wifi-for-your-broadband-router</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>page-guides/broadband-help-if-you-claim-benefits-uk</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/broadband-help-if-you-claim-benefits-uk</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr"/>
+      <c r="N29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ops-adsense-site-review</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Monetisation</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Complete AdSense site review and authorisation monitoring</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>AdSense status and /ads.txt</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Google site-review processing</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>page-providers/gigaclear</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/gigaclear</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>page-providers/youfibre</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/youfibre</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>page-providers/cuckoo</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/cuckoo</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr"/>
+      <c r="L33" s="3" t="inlineStr"/>
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>audit-city-hub-thinness</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Content audit</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Verify each new city hub has a genuinely local fact</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>data/priority-pages.ts city entries</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>page-guides/black-friday-broadband-deals-uk</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/black-friday-broadband-deals-uk</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr"/>
+      <c r="L35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>page-providers/shell-energy</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/shell-energy</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>page-research/broadband-customer-service-rankings-uk</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/research/broadband-customer-service-rankings-uk</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr"/>
+      <c r="L37" s="3" t="inlineStr"/>
+      <c r="M37" s="3" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>feat-contact-form-email-delivery</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Working contact form delivering to a real inbox, no third-party service</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>app/api/contact/route.ts, components/ContactForm.tsx, app/contact/page.tsx</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>CONTACT_SMTP_USER / CONTACT_SMTP_PASS Gmail App Password set in Vercel env vars</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Broadband complaints and the ombudsman: your UK rights</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/broadband-complaints-and-ombudsman-uk</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="3" t="inlineStr"/>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>growth-original-research-outreach</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Run original-research outreach and digital PR</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>/research/uk-broadband-customer-satisfaction</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Research page and source methodology are live</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>growth-quarterly-data-reprioritisation</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>Next-quarter decision log</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>ops-conversion-reporting-loop and sufficient observation period</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr"/>
+      <c r="M41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Price-drop alerts</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>New subscription flow + data/provider-live-deals.json</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Email delivery provider</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>audit-core-web-vitals-reporting</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>Sitewide template performance report</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Field data or representative lab baselines</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>audit-mobile-checkout-flow</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>UX audit</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Mobile checkout-flow audit</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Sitewide mobile layout</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Mobile analytics/drop-off data</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>audit-broken-links-redirects</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Crawlability</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Add routine broken-link and redirect reporting</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>Sitewide crawl and redirect report</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr"/>
+      <c r="M45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>bet-annual-research-report</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Annual 'State of UK Broadband' research report</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>New annual research page + methodology extension</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>bet-componentise-interactive-layer</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr"/>
+      <c r="M47" s="3" t="inlineStr"/>
+      <c r="N47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>None, but easier before the guide count grows further</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N15"/>
+  <autoFilter ref="A1:N48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4444,9 +6142,9 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="50" customWidth="1" min="12" max="12"/>
@@ -4541,17 +6239,13 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -4595,17 +6289,13 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -4649,17 +6339,13 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4703,17 +6389,13 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -4757,17 +6439,13 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4811,17 +6489,13 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -4865,17 +6539,13 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4919,17 +6589,13 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -4973,17 +6639,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5027,17 +6689,13 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -5081,17 +6739,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5135,17 +6789,13 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -5189,17 +6839,13 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5243,17 +6889,13 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -5297,17 +6939,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5351,17 +6989,13 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -5405,17 +7039,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5459,17 +7089,13 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -5513,17 +7139,13 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5567,17 +7189,13 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -5621,17 +7239,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5675,17 +7289,13 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr"/>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -5729,17 +7339,13 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5783,17 +7389,13 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -5837,17 +7439,13 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -5891,17 +7489,13 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -5945,17 +7539,13 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -5999,17 +7589,13 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -6053,17 +7639,13 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -6107,17 +7689,13 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -6161,17 +7739,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -6215,17 +7789,13 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr"/>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -6269,17 +7839,13 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Committed</t>
-        </is>
-      </c>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -6311,7 +7877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6956,7 +8522,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Content audit</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -6966,43 +8532,43 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Verify each new city hub has a genuinely local fact</t>
+          <t>Deep, researched content for Awin-approved providers (TalkTalk, Zzoomm, Highland Broadband)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8 new city hubs (Birmingham, Bristol, Edinburgh, Glasgow, Leeds, Liverpool, Manchester, Sheffield) plus 50 existing postcode-prefix pages is a lot of near-identical templates. Each needs at least one real local fact (a named local altnet, a real coverage figure) or it reads as duplicate content — audit before building the next batch of cities.</t>
+          <t>Following the Awin programme-status pull (ops-awin-publisher-api-integration), built full researched content for the 3 real providers among the 4 joined programmes (Broadband Genie is a comparison site, not an ISP, and was excluded). Per docs/page-build-pipeline-brief.md Stage 3/4/4a: for each provider, fetched the provider's own site for current pricing/speeds/contract terms, WebSearched Trustpilot and, where relevant, Ofcom's own complaints data, and wrote an 8-section contentSections block plus FAQs matching the site's deepest existing template (Gigaclear). All copy hand-checked for zero em dashes and zero banned AI-tell vocabulary/phrases per the Stage 4a list. TalkTalk's existing entry was materially stale (Trustpilot claimed 2.8, real current figure 1.5 from 50k+ reviews in Trustpilot's 'Bad' band; Ofcom's Q1 2026 report names TalkTalk the UK's most complained-about broadband provider for the third consecutive quarter; the old 'price-lock guarantee' highlight was false, two scheduled April 2027/2028 rises are now built into every contract) -- fully rewritten, not just extended. Zzoomm and Highland Broadband were brand-new Provider entries (real Awin tracking links, placeholder text-wordmark logos per the brief's guardrail against fabricating brand marks). In passing, corrected Plusnet's stale trustpilotScore field (3.9 -&gt; 2.0, the real current figure) since new comparison copy was about to cite it -- Plusnet's own deep content rewrite is out of scope (not an Awin-approved programme). Two new comparison pages: talktalk-vs-plusnet (a genuinely stark, well-evidenced contrast -- same price bracket, opposite ends of Ofcom's complaints table) and zzoomm-vs-hyperoptic (two symmetrical full-fibre altnets with almost non-overlapping coverage footprints). Internal linking relies on the existing 'How {provider} compares' module built earlier this session; both new comparisons are discoverable via /providers/compare and the sitemap even where they don't make a crowded provider's top-3 related slice.</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>data/priority-pages.ts city entries</t>
+          <t>data/providers.ts (talktalk, zzoomm, highland-broadband, plusnet trustpilotScore), data/provider-comparisons.ts (talktalk-vs-plusnet, zzoomm-vs-hyperoptic), public/logos/zzoomm.svg, public/logos/highland-broadband.svg</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ops-awin-publisher-api-integration</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7012,38 +8578,38 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Content audit</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Navigation/header/footer IA improvements</t>
+          <t>Verify each new city hub has a genuinely local fact</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Researched via scripts/scrape_navigation_patterns.py against 5 best-in-class sites. broadband.co.uk (closest single-vertical comparable) stood out on sticky header, breadcrumbs and a trust badge near the top; BroadbandPicker already matches on the first two. Header nav link count split cleanly into supersite (127-556 links) vs specialist (21 links) patterns, confirming the growth playbook's 'specialist, not supersite' positioning. Added Postcode to primary nav; restructured the footer from 4 to 6 columns (added Tools, Find Broadband by Area, Research) to fix a crawl/link-equity gap for the postcode-district and tools pages built this session.</t>
+          <t>8 new city hubs (Birmingham, Bristol, Edinburgh, Glasgow, Leeds, Liverpool, Manchester, Sheffield) plus 50 existing postcode-prefix pages is a lot of near-identical templates. Each needs at least one real local fact (a named local altnet, a real coverage figure) or it reads as duplicate content — audit before building the next batch of cities.</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>app/layout.tsx</t>
+          <t>data/priority-pages.ts city entries</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -7053,12 +8619,12 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-22 — researched before implementing per the Strategic Lens process</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -7073,24 +8639,24 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Working contact form delivering to a real inbox, no third-party service</t>
+          <t>Navigation/header/footer IA improvements</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Previously /contact only offered mailto: links to unverified custom-domain addresses (editorial@/partnerships@/hello@broadbandpicker.co.uk). Built a real contact form (components/ContactForm.tsx) posting to a new app/api/contact route, which sends via Gmail SMTP using nodemailer — no Supabase, no database, no third-party form/CRM service, per explicit instruction. All submissions land in sayedsahil.elt@gmail.com (CONTACT_TO_EMAIL env var), sent from a Gmail account authenticated with an App Password (CONTACT_SMTP_USER / CONTACT_SMTP_PASS). Reply-To is set to the sender's own address so replying goes straight back to them. Spam mitigation without any external service: a hidden honeypot field (bots that fill every input get silently dropped) and a submit-time check rejecting anything sent under 1.5s after the form rendered. Server-side validates name/email/reason/message independently of the client. The original mailto: cards are kept underneath as a secondary direct-email option. Requires CONTACT_SMTP_USER/PASS to be set in Vercel — the API route fails gracefully with a friendly error and a server log line if they're absent, rather than silently dropping messages.</t>
+          <t>Researched via scripts/scrape_navigation_patterns.py against 5 best-in-class sites. broadband.co.uk (closest single-vertical comparable) stood out on sticky header, breadcrumbs and a trust badge near the top; BroadbandPicker already matches on the first two. Header nav link count split cleanly into supersite (127-556 links) vs specialist (21 links) patterns, confirming the growth playbook's 'specialist, not supersite' positioning. Added Postcode to primary nav; restructured the footer from 4 to 6 columns (added Tools, Find Broadband by Area, Research) to fix a crawl/link-equity gap for the postcode-district and tools pages built this session.</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
         <v>55</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -7099,22 +8665,22 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>app/api/contact/route.ts, components/ContactForm.tsx, app/contact/page.tsx</t>
+          <t>app/layout.tsx</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SMTP_USER / CONTACT_SMTP_PASS Gmail App Password set in Vercel env vars</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>User request 2026-08-22 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7124,43 +8690,43 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Run original-research outreach and digital PR</t>
+          <t>Working contact form delivering to a real inbox, no third-party service</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Build a relevant outreach list and earn citations and links to the live Ofcom-backed customer-satisfaction research.</t>
+          <t>Previously /contact only offered mailto: links to unverified custom-domain addresses (editorial@/partnerships@/hello@broadbandpicker.co.uk). Built a real contact form (components/ContactForm.tsx) posting to a new app/api/contact route, which sends via Gmail SMTP using nodemailer — no Supabase, no database, no third-party form/CRM service, per explicit instruction. All submissions land in sayedsahil.elt@gmail.com (CONTACT_TO_EMAIL env var), sent from a Gmail account authenticated with an App Password (CONTACT_SMTP_USER / CONTACT_SMTP_PASS). Reply-To is set to the sender's own address so replying goes straight back to them. Spam mitigation without any external service: a hidden honeypot field (bots that fill every input get silently dropped) and a submit-time check rejecting anything sent under 1.5s after the form rendered. Server-side validates name/email/reason/message independently of the client. The original mailto: cards are kept underneath as a secondary direct-email option. Requires CONTACT_SMTP_USER/PASS to be set in Vercel — the API route fails gracefully with a friendly error and a server log line if they're absent, rather than silently dropping messages.</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>/research/uk-broadband-customer-satisfaction</t>
+          <t>app/api/contact/route.ts, components/ContactForm.tsx, app/contact/page.tsx</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Research page and source methodology are live</t>
+          <t>CONTACT_SMTP_USER / CONTACT_SMTP_PASS Gmail App Password set in Vercel env vars</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -7170,7 +8736,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Build Status / 90 Day Roadmap</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7180,29 +8746,29 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
+          <t>Run original-research outreach and digital PR</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Review query/page performance, assisted conversions, Awin decisions and engagement data, then record the next-quarter build decisions.</t>
+          <t>Build a relevant outreach list and earn citations and links to the live Ofcom-backed customer-satisfaction research.</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -7211,22 +8777,22 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Next-quarter decision log</t>
+          <t>/research/uk-broadband-customer-satisfaction</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>ops-conversion-reporting-loop and sufficient observation period</t>
+          <t>Research page and source methodology are live</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: 90 Day Roadmap</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Build Status / 90 Day Roadmap</t>
         </is>
       </c>
     </row>
@@ -7236,29 +8802,29 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>User asked for a postcode -&gt; select-your-house-number address picker with customised content, and explicitly asked whether it could be built free. Researched live (WebSearch, 2026-08-23): full UK address-level lookup (the data behind 'pick your house from a list') is Royal Mail's licensed PAF data, not open -- getAddress.io, a popular free-tier provider, was shut down in Oct 2025 after a Royal Mail/IDDQD IP claim; Ideal Postcodes gives a 1-month/50-credit trial then pay-as-you-go; no provider offers a genuine unlimited free tier at real traffic. Separately, even a working address picker wouldn't improve accuracy without a paid per-address line-checker API (Openreach or provider-specific), which is a commercial relationship, not a script. Presented both findings and 3 options to the user via AskUserQuestion; they chose the free path: deepen personalisation using data already held, no new API, no new cost. Shipped: extended the existing components/PostcodeContextBar.tsx (previously only on deals/compare/provider pages) to guide pages and all 3 tool pages (speed test, broadband match, cost calculator) so a stored postcode follows the visitor through the full journey; new components/ProviderAvailabilityBadge.tsx shows a real yes/no ('BT is/isn't listed as available in {town}') on provider review pages, but only for the 51 postcode areas with real availableProviders data in data/postcodes.ts -- silently renders nothing outside that set rather than guessing; new components/ReturningVisitorBanner.tsx greets a returning visitor on the homepage with a direct link back to their own postcode's deals.</t>
+          <t>Review query/page performance, assisted conversions, Awin decisions and engagement data, then record the next-quarter build decisions.</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
         <v>53</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -7267,22 +8833,22 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>components/ProviderAvailabilityBadge.tsx, components/ReturningVisitorBanner.tsx, components/PostcodeContextBar.tsx, app/page.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/speed-test/page.tsx, app/tools/broadband-match/page.tsx, app/tools/broadband-cost-calculator/page.tsx</t>
+          <t>Next-quarter decision log</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>None -- deliberately built on data already held, no new API/cost</t>
+          <t>ops-conversion-reporting-loop and sufficient observation period</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: 90 Day Roadmap</t>
         </is>
       </c>
     </row>
@@ -7302,16 +8868,16 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Homepage visual redesign: illustrations + interactivity</t>
+          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Researched via scripts/analyze_homepage_visual_design.py against 5 UK broadband comparison homepages: none uses stock-photo hero banners; the dominant visual language is heavy inline SVG (Uswitch ships 195) and provider logos, no carousel/animation library detected anywhere. Generated 7 original on-brand SVG illustrations (scripts/generate_homepage_illustrations.py: hero network graphic, 3 colour-filled step icons, 2 gradient blobs, a quiz illustration) rather than stock photography, matching what's actually proven in this vertical. Added a scroll-reveal component, hover interactions, and restructured the Broadband Match promo to a two-column illustrated layout. Content/copy unchanged, visual/UX only.</t>
+          <t>User asked for a postcode -&gt; select-your-house-number address picker with customised content, and explicitly asked whether it could be built free. Researched live (WebSearch, 2026-08-23): full UK address-level lookup (the data behind 'pick your house from a list') is Royal Mail's licensed PAF data, not open -- getAddress.io, a popular free-tier provider, was shut down in Oct 2025 after a Royal Mail/IDDQD IP claim; Ideal Postcodes gives a 1-month/50-credit trial then pay-as-you-go; no provider offers a genuine unlimited free tier at real traffic. Separately, even a working address picker wouldn't improve accuracy without a paid per-address line-checker API (Openreach or provider-specific), which is a commercial relationship, not a script. Presented both findings and 3 options to the user via AskUserQuestion; they chose the free path: deepen personalisation using data already held, no new API, no new cost. Shipped: extended the existing components/PostcodeContextBar.tsx (previously only on deals/compare/provider pages) to guide pages and all 3 tool pages (speed test, broadband match, cost calculator) so a stored postcode follows the visitor through the full journey; new components/ProviderAvailabilityBadge.tsx shows a real yes/no ('BT is/isn't listed as available in {town}') on provider review pages, but only for the 51 postcode areas with real availableProviders data in data/postcodes.ts -- silently renders nothing outside that set rather than guessing; new components/ReturningVisitorBanner.tsx greets a returning visitor on the homepage with a direct link back to their own postcode's deals.</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>55</v>
@@ -7323,12 +8889,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>app/page.tsx, components/ScrollReveal.tsx, public/illustrations/</t>
+          <t>components/ProviderAvailabilityBadge.tsx, components/ReturningVisitorBanner.tsx, components/PostcodeContextBar.tsx, app/page.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/speed-test/page.tsx, app/tools/broadband-match/page.tsx, app/tools/broadband-cost-calculator/page.tsx</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None -- deliberately built on data already held, no new API/cost</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -7358,19 +8924,19 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Mobile and cross-device navigation overhaul</t>
+          <t>Homepage visual redesign: illustrations + interactivity</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>New scripts/analyze_mobile_ux.py scanned Uswitch, broadband.co.uk and choose.co.uk (MoneySavingExpert 403, reported not bypassed) with a mobile Safari user agent for markup/CSS signals: viewport meta and hamburger menu markers were universal but already correct on our own site; tel: click-to-call was absent everywhere (0/4, skipped); sticky bottom CTA (1/4) and apple-touch-icon (2/4) were too weak/incomplete to act on. The real gap was found by direct inspection, not the scan: the mobile nav was a small anchored dropdown of 10 flat links with ~36px touch targets, while the desktop nav beside it was a full mega-menu, and the header postcode checker was desktop-only so phone users had no quick postcode access outside the homepage/deals page. Replaced it with new components/MobileNav.tsx: a full-width slide-down panel reusing the desktop mega-menu's own icon/link data (exported from MainNav.tsx, so the two can't drift apart), every link at a 44px (min-h-11) touch target, and the postcode checker embedded at the top so it's reachable from any page. Added anchor ids to /guides category sections so the new mobile Guides menu jumps to a real target instead of an unread query param.</t>
+          <t>Researched via scripts/analyze_homepage_visual_design.py against 5 UK broadband comparison homepages: none uses stock-photo hero banners; the dominant visual language is heavy inline SVG (Uswitch ships 195) and provider logos, no carousel/animation library detected anywhere. Generated 7 original on-brand SVG illustrations (scripts/generate_homepage_illustrations.py: hero network graphic, 3 colour-filled step icons, 2 gradient blobs, a quiz illustration) rather than stock photography, matching what's actually proven in this vertical. Added a scroll-reveal component, hover interactions, and restructured the Broadband Match promo to a two-column illustrated layout. Content/copy unchanged, visual/UX only.</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -7379,7 +8945,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>components/MobileNav.tsx, components/MainNav.tsx, app/layout.tsx, app/guides/page.tsx</t>
+          <t>app/page.tsx, components/ScrollReveal.tsx, public/illustrations/</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -7414,19 +8980,19 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Mobile and cross-device navigation overhaul</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
+          <t>New scripts/analyze_mobile_ux.py scanned Uswitch, broadband.co.uk and choose.co.uk (MoneySavingExpert 403, reported not bypassed) with a mobile Safari user agent for markup/CSS signals: viewport meta and hamburger menu markers were universal but already correct on our own site; tel: click-to-call was absent everywhere (0/4, skipped); sticky bottom CTA (1/4) and apple-touch-icon (2/4) were too weak/incomplete to act on. The real gap was found by direct inspection, not the scan: the mobile nav was a small anchored dropdown of 10 flat links with ~36px touch targets, while the desktop nav beside it was a full mega-menu, and the header postcode checker was desktop-only so phone users had no quick postcode access outside the homepage/deals page. Replaced it with new components/MobileNav.tsx: a full-width slide-down panel reusing the desktop mega-menu's own icon/link data (exported from MainNav.tsx, so the two can't drift apart), every link at a 44px (min-h-11) touch target, and the postcode checker embedded at the top so it's reachable from any page. Added anchor ids to /guides category sections so the new mobile Guides menu jumps to a real target instead of an unread query param.</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -7435,7 +9001,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>components/MainNav.tsx, app/layout.tsx</t>
+          <t>components/MobileNav.tsx, components/MainNav.tsx, app/layout.tsx, app/guides/page.tsx</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7470,19 +9036,19 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Animated, interactive mobile menu with click-outside-to-close</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Direct UX/interaction-design request, not a scraping pass. Rewrote components/MobileNav.tsx from a native &lt;details&gt; element (no animation, no click-outside-to-close) to a controlled client component: hamburger icon morphs into an X on open; a blurred backdrop closes the menu on click or Escape; the panel and its sections slide/fade in with a staggered delay reusing the same transition idiom as components/ScrollReveal.tsx; Providers/Postcode/Guides/Tools became single-open accordions using a CSS-only grid-template-rows 0fr-&gt;1fr transition (no JS height measurement); the menu auto-closes on route change via usePathname(); background scroll is locked while open; focus moves into the panel on open and returns to the trigger on Escape. Global prefers-reduced-motion handling already in app/globals.css applies automatically. Not visually verified on a real device — no browser automation tool available this session, validated via build output, generated CSS and server-rendered markup only.</t>
+          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -7491,7 +9057,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>components/MobileNav.tsx</t>
+          <t>components/MainNav.tsx, app/layout.tsx</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -7521,24 +9087,24 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Animated, interactive mobile menu with click-outside-to-close</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
+          <t>Direct UX/interaction-design request, not a scraping pass. Rewrote components/MobileNav.tsx from a native &lt;details&gt; element (no animation, no click-outside-to-close) to a controlled client component: hamburger icon morphs into an X on open; a blurred backdrop closes the menu on click or Escape; the panel and its sections slide/fade in with a staggered delay reusing the same transition idiom as components/ScrollReveal.tsx; Providers/Postcode/Guides/Tools became single-open accordions using a CSS-only grid-template-rows 0fr-&gt;1fr transition (no JS height measurement); the menu auto-closes on route change via usePathname(); background scroll is locked while open; focus moves into the panel on open and returns to the trigger on Escape. Global prefers-reduced-motion handling already in app/globals.css applies automatically. Not visually verified on a real device — no browser automation tool available this session, validated via build output, generated CSS and server-rendered markup only.</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -7547,22 +9113,22 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
+          <t>components/MobileNav.tsx</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Email delivery provider</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7577,24 +9143,24 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
+          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
         <v>49</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -7603,22 +9169,22 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
+          <t>New subscription flow + data/provider-live-deals.json</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Email delivery provider</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>Growth playbook — Functionality pillar</t>
         </is>
       </c>
     </row>
@@ -7638,28 +9204,28 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
+          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>app/layout.tsx, components/Logo.tsx</t>
+          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7684,53 +9250,53 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
+          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Sitewide template performance report</t>
+          <t>app/layout.tsx, components/Logo.tsx</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>Field data or representative lab baselines</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7740,53 +9306,53 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Direct Awin Publisher API access — programme status and link generation</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>User asked to connect Claude to their Awin account and provided a real API token. There's no one-click connector for Awin (unlike Google Drive/Gmail), so this uses Awin's own Publisher API directly. First live run corrected two wrong assumptions from documentation research: 'programmedetails' requires a specific advertiserId (not a bulk listing endpoint) -- the actual bulk-status endpoint is GET /publishers/{id}/programmes?relationship=X, and 'any' is not a valid value for it (loops joined/pending/suspended/rejected instead; 'notjoined' returns the ~21k whole-platform catalogue so it's excluded from the default and only fetched on request). POST /publishers/{id}/linkbuilder/generate confirmed working, verified against TalkTalk (advertiser 3674). REAL FINDING from the first run, both surfaced to the user and worth acting on: only 4 programmes are joined (TalkTalk, Broadband Genie, Zzoomm, Highland Broadband), 7 pending (Sky ROI, Community Fibre, National Broadband, Trooli, Pine Media, Cuckoo, Zen Internet), and 9 REJECTED including BT (both consumer and business), Vodafone, Plusnet, EE, Virgin Media, Hyperoptic and toob. Cross-checked data/providers.ts: none of the currently-live affiliateUrl values (including TalkTalk, which IS approved) use Awin's awin1.com tracking format -- they're all plain provider URLs, so the site is very likely not earning commission on any current outbound click, joined or not, despite the on-page commercial disclosures implying it might.</t>
+          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
         <v>47</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>scripts/awin_sync.py</t>
+          <t>Sitewide template performance report</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>AWIN_API_TOKEN from the user's Awin account (user menu -&gt; API Credentials)</t>
+          <t>Field data or representative lab baselines</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -7796,53 +9362,53 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Direct Awin Publisher API access — programme status and link generation</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+          <t>User asked to connect Claude to their Awin account and provided a real API token. There's no one-click connector for Awin (unlike Google Drive/Gmail), so this uses Awin's own Publisher API directly. First live run corrected two wrong assumptions from documentation research: 'programmedetails' requires a specific advertiserId (not a bulk listing endpoint) -- the actual bulk-status endpoint is GET /publishers/{id}/programmes?relationship=X, and 'any' is not a valid value for it (loops joined/pending/suspended/rejected instead; 'notjoined' returns the ~21k whole-platform catalogue so it's excluded from the default and only fetched on request). POST /publishers/{id}/linkbuilder/generate confirmed working, verified against TalkTalk (advertiser 3674). REAL FINDING from the first run, both surfaced to the user and worth acting on: only 4 programmes are joined (TalkTalk, Broadband Genie, Zzoomm, Highland Broadband), 7 pending (Sky ROI, Community Fibre, National Broadband, Trooli, Pine Media, Cuckoo, Zen Internet), and 9 REJECTED including BT (both consumer and business), Vodafone, Plusnet, EE, Virgin Media, Hyperoptic and toob. Cross-checked data/providers.ts: none of the currently-live affiliateUrl values (including TalkTalk, which IS approved) use Awin's awin1.com tracking format -- they're all plain provider URLs, so the site is very likely not earning commission on any current outbound click, joined or not, despite the on-page commercial disclosures implying it might.</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G27" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="G27" s="3" t="n">
-        <v>58</v>
-      </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>scripts/awin_sync.py</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>AWIN_API_TOKEN from the user's Awin account (user menu -&gt; API Credentials)</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7852,43 +9418,43 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
+          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Sitewide crawl and redirect report</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -7898,7 +9464,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -7908,43 +9474,43 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide crawl and redirect report</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
@@ -7954,7 +9520,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -7969,24 +9535,24 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -7995,12 +9561,12 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -8010,7 +9576,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -8025,53 +9591,109 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F31" s="3" t="n">
+      <c r="F32" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G32" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L31"/>
+  <autoFilter ref="A1:L32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8112,7 +9734,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>63 total (33 page builds, 30 feature/strategy builds); 49 already marked Done.</t>
+          <t>64 total (33 page builds, 31 feature/strategy builds); 17 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
@@ -197,8 +197,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PendingBuildPriorityTable" displayName="PendingBuildPriorityTable" ref="A1:N48" headerRowCount="1">
-  <autoFilter ref="A1:N48"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PendingBuildPriorityTable" displayName="PendingBuildPriorityTable" ref="A1:N15" headerRowCount="1">
+  <autoFilter ref="A1:N15"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Pending Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr"/>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr"/>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr"/>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr"/>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr"/>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr"/>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr"/>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr"/>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr"/>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr"/>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr"/>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr"/>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -3617,23 +3617,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="50" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -3714,46 +3714,50 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>page-providers/compare/hyperoptic-vs-youfibre</t>
+          <t>growth-awin-advertiser-outreach</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Partnerships</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hyperoptic vs YouFibre broadband: which is better in 2026?</t>
+          <t>Continue selective Awin advertiser outreach</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>67.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/providers/compare/hyperoptic-vs-youfibre</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
+          <t>Awin publisher 2942019 and partner application log</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Current audience evidence and compliant commercial pages</t>
+        </is>
+      </c>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
@@ -3764,33 +3768,33 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>page-postcode/sheffield</t>
+          <t>feat-review-aggregation-module</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Broadband providers in Sheffield: coverage and best deals</t>
+          <t>Real review-aggregation trust module</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>66.8</v>
+        <v>59</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -3800,10 +3804,14 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/postcode/sheffield</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr"/>
+          <t>New shared component, used on provider + comparison pages</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
+        </is>
+      </c>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
@@ -3814,46 +3822,50 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>page-guides/static-ip-business-broadband-explained</t>
+          <t>ops-adsense-site-review</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Static IP business broadband: when you need one and how much it costs</t>
+          <t>Complete AdSense site review and authorisation monitoring</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>66.3</v>
+        <v>58</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46.1</v>
+        <v>55</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/guides/static-ip-business-broadband-explained</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+          <t>AdSense status and /ads.txt</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Google site-review processing</t>
+        </is>
+      </c>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
@@ -3864,12 +3876,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>page-guides/student-broadband-by-university-city</t>
+          <t>audit-city-hub-thinness</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Content audit</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -3879,18 +3891,18 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Student broadband by university city: short-term and rolling deals</t>
+          <t>Verify each new city hub has a genuinely local fact</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>56</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>36.2</v>
+        <v>50</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -3900,10 +3912,14 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/guides/student-broadband-by-university-city</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr"/>
+          <t>data/priority-pages.ts city entries</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
@@ -3914,46 +3930,50 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>page-postcode/edinburgh</t>
+          <t>feat-contact-form-email-delivery</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Broadband providers in Edinburgh: coverage and best deals</t>
+          <t>Working contact form delivering to a real inbox, no third-party service</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>65.8</v>
+        <v>55</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/postcode/edinburgh</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
+          <t>app/api/contact/route.ts, components/ContactForm.tsx, app/contact/page.tsx</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>CONTACT_SMTP_USER / CONTACT_SMTP_PASS Gmail App Password set in Vercel env vars</t>
+        </is>
+      </c>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
@@ -3964,12 +3984,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>page-guides/small-office-broadband-setup-uk</t>
+          <t>growth-original-research-outreach</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -3979,31 +3999,35 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Small office broadband setup: routers, backup and support checklist</t>
+          <t>Run original-research outreach and digital PR</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>65.8</v>
+        <v>54</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>41.9</v>
+        <v>68</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/guides/small-office-broadband-setup-uk</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr"/>
+          <t>/research/uk-broadband-customer-satisfaction</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Research page and source methodology are live</t>
+        </is>
+      </c>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
@@ -4014,33 +4038,33 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>page-providers/compare/bt-vs-plusnet</t>
+          <t>growth-quarterly-data-reprioritisation</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>BT vs Plusnet broadband: which is better in 2026?</t>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>65.5</v>
+        <v>53</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>36.4</v>
+        <v>63</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4050,10 +4074,14 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/providers/compare/bt-vs-plusnet</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
+          <t>Next-quarter decision log</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>ops-conversion-reporting-loop and sufficient observation period</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
@@ -4064,33 +4092,33 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>page-postcode/glasgow</t>
+          <t>feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Broadband providers in Glasgow: coverage and best deals</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>65.5</v>
+        <v>49</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>40.2</v>
+        <v>55</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -4100,10 +4128,14 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/postcode/glasgow</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr"/>
+          <t>New subscription flow + data/provider-live-deals.json</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Email delivery provider</t>
+        </is>
+      </c>
       <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="inlineStr"/>
@@ -4114,33 +4146,33 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>page-postcode/liverpool</t>
+          <t>audit-core-web-vitals-reporting</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Broadband providers in Liverpool: coverage and best deals</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>65.5</v>
+        <v>47</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>40.1</v>
+        <v>50</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4150,10 +4182,14 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/postcode/liverpool</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+          <t>Sitewide template performance report</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Field data or representative lab baselines</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
@@ -4164,33 +4200,33 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>page-guides/broadband-for-landlords-and-hmos-uk</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Broadband for landlords and HMOs: what to set up and who pays</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>45</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>36.6</v>
+        <v>58</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -4200,10 +4236,14 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/guides/broadband-for-landlords-and-hmos-uk</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
+          <t>Sitewide mobile layout</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Mobile analytics/drop-off data</t>
+        </is>
+      </c>
       <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="inlineStr"/>
@@ -4214,33 +4254,33 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>page-postcode/leeds</t>
+          <t>audit-broken-links-redirects</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Broadband providers in Leeds: coverage and best deals</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>65.09999999999999</v>
+        <v>44</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>40.3</v>
+        <v>48</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4250,10 +4290,14 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/postcode/leeds</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr"/>
+          <t>Sitewide crawl and redirect report</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
@@ -4264,12 +4308,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>page-providers/compare/ee-vs-talktalk</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Bigger bet</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -4279,18 +4323,18 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>EE vs TalkTalk broadband: which is better in 2026?</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="G13" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>36.4</v>
-      </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -4300,10 +4344,14 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/providers/compare/ee-vs-talktalk</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr"/>
+          <t>New annual research page + methodology extension</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
+        </is>
+      </c>
       <c r="L13" s="3" t="inlineStr"/>
       <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="3" t="inlineStr"/>
@@ -4314,33 +4362,33 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>page-postcode/bristol</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Bigger bet</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Broadband providers in Bristol: coverage and best deals</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>64.90000000000001</v>
+        <v>38</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>40.8</v>
+        <v>45</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4350,10 +4398,14 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/postcode/bristol</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
@@ -4364,12 +4416,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>page-postcode/birmingham</t>
+          <t>bet-decouple-content-from-code</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Bigger bet</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -4379,18 +4431,18 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Broadband providers in Birmingham: coverage and best deals</t>
+          <t>Decouple guide content from code deploys</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>64.5</v>
+        <v>35</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>41.1</v>
+        <v>48</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -4400,1726 +4452,20 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/postcode/birmingham</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
+          <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>None, but easier before the guide count grows further</t>
+        </is>
+      </c>
       <c r="L15" s="3" t="inlineStr"/>
       <c r="M15" s="3" t="inlineStr"/>
       <c r="N15" s="3" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>page-postcode/manchester</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Broadband providers in Manchester: coverage and best deals</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/postcode/manchester</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>page-guides/leased-line-cost-uk-explained</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Leased line cost UK: what small businesses actually pay</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>58.6</v>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/leased-line-cost-uk-explained</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>page-guides/starlink-vs-fibre-broadband-uk</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Starlink vs fibre broadband: when satellite makes sense in the UK</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/starlink-vs-fibre-broadband-uk</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>page-providers/compare/virgin-media-vs-sky</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Virgin Media vs Sky broadband: which is better in 2026?</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/compare/virgin-media-vs-sky</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr"/>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>page-guides/january-broadband-deals-uk</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>January broadband deals UK: new-year switching guide</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/january-broadband-deals-uk</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>growth-awin-advertiser-outreach</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Partnerships</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Monetisation</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Continue selective Awin advertiser outreach</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>Awin publisher 2942019 and partner application log</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>Current audience evidence and compliant commercial pages</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>page-tools/broadband-cost-calculator</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Functionality</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Broadband cost calculator: true monthly and contract-length cost</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/tools/broadband-cost-calculator</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>Live at /tools/broadband-cost-calculator, committed and deployed 2026-08-21.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>page-providers/onestream</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Onestream — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/onestream</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr"/>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>page-guides/no-credit-check-broadband-uk</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>No credit check broadband in the UK: options and what to expect</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/no-credit-check-broadband-uk</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>feat-review-aggregation-module</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Functionality</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>Real review-aggregation trust module</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>New shared component, used on provider + comparison pages</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr"/>
-      <c r="M25" s="3" t="inlineStr"/>
-      <c r="N25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>page-providers/brsk</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Brsk — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/brsk</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>page-guides/fttp-vs-fttc-explained</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>FTTP vs FTTC: what the difference means for your speed</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/fttp-vs-fttc-explained</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr"/>
-      <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="3" t="inlineStr"/>
-      <c r="N27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>page-guides/best-mesh-wifi-for-your-broadband-router</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/best-mesh-wifi-for-your-broadband-router</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>page-guides/broadband-help-if-you-claim-benefits-uk</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/broadband-help-if-you-claim-benefits-uk</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="3" t="inlineStr"/>
-      <c r="N29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>ops-adsense-site-review</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Monetisation</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Complete AdSense site review and authorisation monitoring</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>AdSense status and /ads.txt</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>Google site-review processing</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>page-providers/gigaclear</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/gigaclear</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="3" t="inlineStr"/>
-      <c r="N31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>page-providers/youfibre</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/youfibre</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>page-providers/cuckoo</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/cuckoo</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr"/>
-      <c r="L33" s="3" t="inlineStr"/>
-      <c r="M33" s="3" t="inlineStr"/>
-      <c r="N33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>audit-city-hub-thinness</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Content audit</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Verify each new city hub has a genuinely local fact</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>data/priority-pages.ts city entries</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>page-guides/black-friday-broadband-deals-uk</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/black-friday-broadband-deals-uk</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr"/>
-      <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="3" t="inlineStr"/>
-      <c r="N35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>page-providers/shell-energy</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/shell-energy</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>page-research/broadband-customer-service-rankings-uk</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/research/broadband-customer-service-rankings-uk</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr"/>
-      <c r="L37" s="3" t="inlineStr"/>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>feat-contact-form-email-delivery</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Working contact form delivering to a real inbox, no third-party service</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>app/api/contact/route.ts, components/ContactForm.tsx, app/contact/page.tsx</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>CONTACT_SMTP_USER / CONTACT_SMTP_PASS Gmail App Password set in Vercel env vars</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>Broadband complaints and the ombudsman: your UK rights</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/broadband-complaints-and-ombudsman-uk</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="3" t="inlineStr"/>
-      <c r="N39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>growth-original-research-outreach</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Growth</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Run original-research outreach and digital PR</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>/research/uk-broadband-customer-satisfaction</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>Research page and source methodology are live</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>growth-quarterly-data-reprioritisation</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Strategy</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Growth</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>Next-quarter decision log</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>ops-conversion-reporting-loop and sufficient observation period</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr"/>
-      <c r="M41" s="3" t="inlineStr"/>
-      <c r="N41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>feat-price-drop-alerts</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Functionality</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Price-drop alerts</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>Email delivery provider</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>audit-core-web-vitals-reporting</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>Technical SEO</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>Sitewide template performance report</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>Field data or representative lab baselines</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="3" t="inlineStr"/>
-      <c r="N43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>audit-mobile-checkout-flow</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>UX audit</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>UX</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Mobile checkout-flow audit</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>Sitewide mobile layout</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>Mobile analytics/drop-off data</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>audit-broken-links-redirects</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>Technical SEO</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Crawlability</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>Add routine broken-link and redirect reporting</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>Sitewide crawl and redirect report</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="3" t="inlineStr"/>
-      <c r="N45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>bet-annual-research-report</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Bigger bet</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Annual 'State of UK Broadband' research report</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>New annual research page + methodology extension</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>bet-componentise-interactive-layer</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>Bigger bet</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Functionality</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>components/</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="inlineStr"/>
-      <c r="M47" s="3" t="inlineStr"/>
-      <c r="N47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>bet-decouple-content-from-code</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Bigger bet</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Decouple guide content from code deploys</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>None, but easier before the guide count grows further</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N48"/>
+  <autoFilter ref="A1:N15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6142,9 +4488,9 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="50" customWidth="1" min="12" max="12"/>
@@ -6239,13 +4585,17 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -6289,13 +4639,17 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -6339,13 +4693,17 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6389,13 +4747,17 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -6439,13 +4801,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6489,13 +4855,17 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -6539,13 +4909,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6589,13 +4963,17 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -6639,13 +5017,17 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6689,13 +5071,17 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -6739,13 +5125,17 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6789,13 +5179,17 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -6839,13 +5233,17 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6889,13 +5287,17 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -6939,13 +5341,17 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6989,13 +5395,17 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -7039,13 +5449,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7089,13 +5503,17 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -7139,13 +5557,17 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7189,13 +5611,17 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -7239,13 +5665,17 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7289,13 +5719,17 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -7339,13 +5773,17 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7389,13 +5827,17 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -7439,13 +5881,17 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7489,13 +5935,17 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -7539,13 +5989,17 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7589,13 +6043,17 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -7639,13 +6097,17 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7689,13 +6151,17 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -7739,13 +6205,17 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7789,13 +6259,17 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -7839,13 +6313,17 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9734,7 +8212,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>64 total (33 page builds, 31 feature/strategy builds); 17 already marked Done.</t>
+          <t>64 total (33 page builds, 31 feature/strategy builds); 50 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -176,8 +176,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L65" headerRowCount="1">
-  <autoFilter ref="A1:L65"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L66" headerRowCount="1">
+  <autoFilter ref="A1:L66"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -241,8 +241,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L32" headerRowCount="1">
-  <autoFilter ref="A1:L32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L33" headerRowCount="1">
+  <autoFilter ref="A1:L33"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2812,12 +2812,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
+          <t>content-awin-pending-provider-deep-content</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2827,18 +2827,18 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Broadband complaints and the ombudsman: your UK rights</t>
+          <t>Deep, researched content for Awin-pending providers (Community Fibre, Cuckoo, Zen Internet, National Broadband, Trooli, Pine Media)</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>54.7</v>
+        <v>55</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>25.9</v>
+        <v>58</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2856,12 +2856,12 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>growth-original-research-outreach</t>
+          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -2871,23 +2871,23 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Run original-research outreach and digital PR</t>
+          <t>Broadband complaints and the ombudsman: your UK rights</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>54</v>
+        <v>54.7</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>68</v>
+        <v>25.9</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr"/>
@@ -2900,29 +2900,29 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>growth-quarterly-data-reprioritisation</t>
+          <t>growth-original-research-outreach</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
+          <t>Run original-research outreach and digital PR</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -2944,29 +2944,29 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>feat-postcode-journey-personalisation</t>
+          <t>growth-quarterly-data-reprioritisation</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
         <v>53</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>feat-homepage-visual-redesign</t>
+          <t>feat-postcode-journey-personalisation</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3003,11 +3003,11 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Homepage visual redesign: illustrations + interactivity</t>
+          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>55</v>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>feat-mobile-cross-device-navigation</t>
+          <t>feat-homepage-visual-redesign</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -3047,14 +3047,14 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Mobile and cross-device navigation overhaul</t>
+          <t>Homepage visual redesign: illustrations + interactivity</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>feat-mega-menu-navigation</t>
+          <t>feat-mobile-cross-device-navigation</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3091,14 +3091,14 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Mobile and cross-device navigation overhaul</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>feat-animated-interactive-mobile-menu</t>
+          <t>feat-mega-menu-navigation</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -3135,14 +3135,14 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Animated, interactive mobile menu with click-outside-to-close</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>feat-price-drop-alerts</t>
+          <t>feat-animated-interactive-mobile-menu</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3174,19 +3174,19 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Animated, interactive mobile menu with click-outside-to-close</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>feat-page-type-ux-redesign</t>
+          <t>feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -3218,19 +3218,19 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
         <v>49</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr"/>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>feat-footer-logo-interactivity</t>
+          <t>feat-page-type-ux-redesign</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3267,18 +3267,18 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3288,11 +3288,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
-        </is>
-      </c>
+      <c r="L58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
@@ -3300,43 +3296,47 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>audit-core-web-vitals-reporting</t>
+          <t>feat-footer-logo-interactivity</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr"/>
       <c r="K59" s="3" t="inlineStr"/>
-      <c r="L59" s="3" t="inlineStr"/>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -3344,38 +3344,38 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>ops-awin-publisher-api-integration</t>
+          <t>audit-core-web-vitals-reporting</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Direct Awin Publisher API access — programme status and link generation</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
         <v>47</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
@@ -3388,38 +3388,38 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>ops-awin-publisher-api-integration</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Direct Awin Publisher API access — programme status and link generation</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G61" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="G61" s="3" t="n">
-        <v>58</v>
-      </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr"/>
@@ -3432,33 +3432,33 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>audit-broken-links-redirects</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3476,33 +3476,33 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-broken-links-redirects</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3530,19 +3530,19 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -3574,19 +3574,19 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
@@ -3602,8 +3602,52 @@
       <c r="K65" s="3" t="inlineStr"/>
       <c r="L65" s="3" t="inlineStr"/>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L65"/>
+  <autoFilter ref="A1:L66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4489,7 +4533,7 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="31" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
@@ -4590,7 +4634,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -4644,7 +4688,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -4698,7 +4742,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4752,7 +4796,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -4806,7 +4850,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4860,7 +4904,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -4914,7 +4958,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4968,7 +5012,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -5022,7 +5066,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5076,7 +5120,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -5130,7 +5174,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5184,7 +5228,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -5238,7 +5282,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5292,7 +5336,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -5346,7 +5390,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5400,7 +5444,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -5454,7 +5498,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -5508,7 +5552,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -5562,7 +5606,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5616,7 +5660,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -5670,7 +5714,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5724,7 +5768,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -5778,7 +5822,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -5832,7 +5876,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -5886,7 +5930,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -5940,7 +5984,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -5994,7 +6038,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -6048,7 +6092,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -6102,7 +6146,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -6156,7 +6200,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -6210,7 +6254,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -6264,7 +6308,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -6318,7 +6362,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -6355,7 +6399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7224,7 +7268,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -7234,43 +7278,43 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Run original-research outreach and digital PR</t>
+          <t>Deep, researched content for Awin-pending providers (Community Fibre, Cuckoo, Zen Internet, National Broadband, Trooli, Pine Media)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Build a relevant outreach list and earn citations and links to the live Ofcom-backed customer-satisfaction research.</t>
+          <t>Follow-up to content-awin-approved-provider-deep-content, extending the same research process to the 6 real UK-relevant advertisers pending Awin approval (Sky ROI excluded -- Republic of Ireland Sky, not UK, out of scope for a UK site, confirmed with the user). Community Fibre and Zen Internet were existing but thin entries, fully rewritten. Cuckoo was already deep and dated the previous day; verified rather than rewritten. National Broadband, Trooli and Pine Media were brand-new Provider entries. National Broadband is the site's first 4G/5G fixed-wireless provider (a genuinely new content category, not another fibre altnet); Pine Media is a hyperlocal single-city (Sheffield-only) provider with a two-tier product split (its own symmetrical GIG network vs an Openreach-based GLO product) that needed explaining clearly to avoid conflating the two. Key design decision: because these programmes are pending, not joined, affiliateUrl stays as each provider's own plain site URL rather than an Awin tracking link -- confirmed via a live API test that Awin's linkbuilder will generate a structurally valid tracking URL even for a pending programme, which would be misleading to publish since it likely would not earn commission (or could breach Awin's terms) before approval. Each reviewSources array carries an explicit 'pending, not yet approved' note on the Awin source, matching the existing Gigaclear convention. All copy hand-checked for zero em dashes and zero banned AI-tell vocabulary/phrases. Three new comparison pages, chosen for genuine evidentiary value over one-per-provider completeness: community-fibre-vs-hyperoptic (London's two biggest symmetrical altnets, direct competitors), trooli-vs-zzoomm (two multi-region altnets with near-zero coverage overlap and matching no-price-rise policies), and national-broadband-vs-highland-broadband (5G available now vs fibre still being built -- a genuine buy-now-or-wait decision for the same rural Scottish customer). Cuckoo, Zen Internet and Pine Media were deliberately left without a new comparison this round -- no natural, non-forced head-to-head partner existed for any of them without inventing artificial relevance.</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>/research/uk-broadband-customer-satisfaction</t>
+          <t>data/providers.ts (community-fibre, cuckoo, zen-internet, national-broadband, trooli, pine-media), data/provider-comparisons.ts (community-fibre-vs-hyperoptic, trooli-vs-zzoomm, national-broadband-vs-highland-broadband), public/logos/national-broadband.svg, public/logos/trooli.svg, public/logos/pine-media.svg</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Research page and source methodology are live</t>
+          <t>content-awin-approved-provider-deep-content, ops-awin-publisher-api-integration</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Build Status / 90 Day Roadmap</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7280,29 +7324,29 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
+          <t>Run original-research outreach and digital PR</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Review query/page performance, assisted conversions, Awin decisions and engagement data, then record the next-quarter build decisions.</t>
+          <t>Build a relevant outreach list and earn citations and links to the live Ofcom-backed customer-satisfaction research.</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -7311,22 +7355,22 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Next-quarter decision log</t>
+          <t>/research/uk-broadband-customer-satisfaction</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>ops-conversion-reporting-loop and sufficient observation period</t>
+          <t>Research page and source methodology are live</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: 90 Day Roadmap</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Build Status / 90 Day Roadmap</t>
         </is>
       </c>
     </row>
@@ -7336,29 +7380,29 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>User asked for a postcode -&gt; select-your-house-number address picker with customised content, and explicitly asked whether it could be built free. Researched live (WebSearch, 2026-08-23): full UK address-level lookup (the data behind 'pick your house from a list') is Royal Mail's licensed PAF data, not open -- getAddress.io, a popular free-tier provider, was shut down in Oct 2025 after a Royal Mail/IDDQD IP claim; Ideal Postcodes gives a 1-month/50-credit trial then pay-as-you-go; no provider offers a genuine unlimited free tier at real traffic. Separately, even a working address picker wouldn't improve accuracy without a paid per-address line-checker API (Openreach or provider-specific), which is a commercial relationship, not a script. Presented both findings and 3 options to the user via AskUserQuestion; they chose the free path: deepen personalisation using data already held, no new API, no new cost. Shipped: extended the existing components/PostcodeContextBar.tsx (previously only on deals/compare/provider pages) to guide pages and all 3 tool pages (speed test, broadband match, cost calculator) so a stored postcode follows the visitor through the full journey; new components/ProviderAvailabilityBadge.tsx shows a real yes/no ('BT is/isn't listed as available in {town}') on provider review pages, but only for the 51 postcode areas with real availableProviders data in data/postcodes.ts -- silently renders nothing outside that set rather than guessing; new components/ReturningVisitorBanner.tsx greets a returning visitor on the homepage with a direct link back to their own postcode's deals.</t>
+          <t>Review query/page performance, assisted conversions, Awin decisions and engagement data, then record the next-quarter build decisions.</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
         <v>53</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -7367,22 +7411,22 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>components/ProviderAvailabilityBadge.tsx, components/ReturningVisitorBanner.tsx, components/PostcodeContextBar.tsx, app/page.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/speed-test/page.tsx, app/tools/broadband-match/page.tsx, app/tools/broadband-cost-calculator/page.tsx</t>
+          <t>Next-quarter decision log</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>None -- deliberately built on data already held, no new API/cost</t>
+          <t>ops-conversion-reporting-loop and sufficient observation period</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: 90 Day Roadmap</t>
         </is>
       </c>
     </row>
@@ -7402,16 +7446,16 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Homepage visual redesign: illustrations + interactivity</t>
+          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Researched via scripts/analyze_homepage_visual_design.py against 5 UK broadband comparison homepages: none uses stock-photo hero banners; the dominant visual language is heavy inline SVG (Uswitch ships 195) and provider logos, no carousel/animation library detected anywhere. Generated 7 original on-brand SVG illustrations (scripts/generate_homepage_illustrations.py: hero network graphic, 3 colour-filled step icons, 2 gradient blobs, a quiz illustration) rather than stock photography, matching what's actually proven in this vertical. Added a scroll-reveal component, hover interactions, and restructured the Broadband Match promo to a two-column illustrated layout. Content/copy unchanged, visual/UX only.</t>
+          <t>User asked for a postcode -&gt; select-your-house-number address picker with customised content, and explicitly asked whether it could be built free. Researched live (WebSearch, 2026-08-23): full UK address-level lookup (the data behind 'pick your house from a list') is Royal Mail's licensed PAF data, not open -- getAddress.io, a popular free-tier provider, was shut down in Oct 2025 after a Royal Mail/IDDQD IP claim; Ideal Postcodes gives a 1-month/50-credit trial then pay-as-you-go; no provider offers a genuine unlimited free tier at real traffic. Separately, even a working address picker wouldn't improve accuracy without a paid per-address line-checker API (Openreach or provider-specific), which is a commercial relationship, not a script. Presented both findings and 3 options to the user via AskUserQuestion; they chose the free path: deepen personalisation using data already held, no new API, no new cost. Shipped: extended the existing components/PostcodeContextBar.tsx (previously only on deals/compare/provider pages) to guide pages and all 3 tool pages (speed test, broadband match, cost calculator) so a stored postcode follows the visitor through the full journey; new components/ProviderAvailabilityBadge.tsx shows a real yes/no ('BT is/isn't listed as available in {town}') on provider review pages, but only for the 51 postcode areas with real availableProviders data in data/postcodes.ts -- silently renders nothing outside that set rather than guessing; new components/ReturningVisitorBanner.tsx greets a returning visitor on the homepage with a direct link back to their own postcode's deals.</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>55</v>
@@ -7423,12 +7467,12 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>app/page.tsx, components/ScrollReveal.tsx, public/illustrations/</t>
+          <t>components/ProviderAvailabilityBadge.tsx, components/ReturningVisitorBanner.tsx, components/PostcodeContextBar.tsx, app/page.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/speed-test/page.tsx, app/tools/broadband-match/page.tsx, app/tools/broadband-cost-calculator/page.tsx</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None -- deliberately built on data already held, no new API/cost</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -7458,19 +7502,19 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Mobile and cross-device navigation overhaul</t>
+          <t>Homepage visual redesign: illustrations + interactivity</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>New scripts/analyze_mobile_ux.py scanned Uswitch, broadband.co.uk and choose.co.uk (MoneySavingExpert 403, reported not bypassed) with a mobile Safari user agent for markup/CSS signals: viewport meta and hamburger menu markers were universal but already correct on our own site; tel: click-to-call was absent everywhere (0/4, skipped); sticky bottom CTA (1/4) and apple-touch-icon (2/4) were too weak/incomplete to act on. The real gap was found by direct inspection, not the scan: the mobile nav was a small anchored dropdown of 10 flat links with ~36px touch targets, while the desktop nav beside it was a full mega-menu, and the header postcode checker was desktop-only so phone users had no quick postcode access outside the homepage/deals page. Replaced it with new components/MobileNav.tsx: a full-width slide-down panel reusing the desktop mega-menu's own icon/link data (exported from MainNav.tsx, so the two can't drift apart), every link at a 44px (min-h-11) touch target, and the postcode checker embedded at the top so it's reachable from any page. Added anchor ids to /guides category sections so the new mobile Guides menu jumps to a real target instead of an unread query param.</t>
+          <t>Researched via scripts/analyze_homepage_visual_design.py against 5 UK broadband comparison homepages: none uses stock-photo hero banners; the dominant visual language is heavy inline SVG (Uswitch ships 195) and provider logos, no carousel/animation library detected anywhere. Generated 7 original on-brand SVG illustrations (scripts/generate_homepage_illustrations.py: hero network graphic, 3 colour-filled step icons, 2 gradient blobs, a quiz illustration) rather than stock photography, matching what's actually proven in this vertical. Added a scroll-reveal component, hover interactions, and restructured the Broadband Match promo to a two-column illustrated layout. Content/copy unchanged, visual/UX only.</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -7479,7 +7523,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>components/MobileNav.tsx, components/MainNav.tsx, app/layout.tsx, app/guides/page.tsx</t>
+          <t>app/page.tsx, components/ScrollReveal.tsx, public/illustrations/</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7514,19 +7558,19 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Mobile and cross-device navigation overhaul</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
+          <t>New scripts/analyze_mobile_ux.py scanned Uswitch, broadband.co.uk and choose.co.uk (MoneySavingExpert 403, reported not bypassed) with a mobile Safari user agent for markup/CSS signals: viewport meta and hamburger menu markers were universal but already correct on our own site; tel: click-to-call was absent everywhere (0/4, skipped); sticky bottom CTA (1/4) and apple-touch-icon (2/4) were too weak/incomplete to act on. The real gap was found by direct inspection, not the scan: the mobile nav was a small anchored dropdown of 10 flat links with ~36px touch targets, while the desktop nav beside it was a full mega-menu, and the header postcode checker was desktop-only so phone users had no quick postcode access outside the homepage/deals page. Replaced it with new components/MobileNav.tsx: a full-width slide-down panel reusing the desktop mega-menu's own icon/link data (exported from MainNav.tsx, so the two can't drift apart), every link at a 44px (min-h-11) touch target, and the postcode checker embedded at the top so it's reachable from any page. Added anchor ids to /guides category sections so the new mobile Guides menu jumps to a real target instead of an unread query param.</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -7535,7 +7579,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>components/MainNav.tsx, app/layout.tsx</t>
+          <t>components/MobileNav.tsx, components/MainNav.tsx, app/layout.tsx, app/guides/page.tsx</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -7570,19 +7614,19 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Animated, interactive mobile menu with click-outside-to-close</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Direct UX/interaction-design request, not a scraping pass. Rewrote components/MobileNav.tsx from a native &lt;details&gt; element (no animation, no click-outside-to-close) to a controlled client component: hamburger icon morphs into an X on open; a blurred backdrop closes the menu on click or Escape; the panel and its sections slide/fade in with a staggered delay reusing the same transition idiom as components/ScrollReveal.tsx; Providers/Postcode/Guides/Tools became single-open accordions using a CSS-only grid-template-rows 0fr-&gt;1fr transition (no JS height measurement); the menu auto-closes on route change via usePathname(); background scroll is locked while open; focus moves into the panel on open and returns to the trigger on Escape. Global prefers-reduced-motion handling already in app/globals.css applies automatically. Not visually verified on a real device — no browser automation tool available this session, validated via build output, generated CSS and server-rendered markup only.</t>
+          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
         <v>50</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -7591,7 +7635,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>components/MobileNav.tsx</t>
+          <t>components/MainNav.tsx, app/layout.tsx</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7621,24 +7665,24 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Animated, interactive mobile menu with click-outside-to-close</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
+          <t>Direct UX/interaction-design request, not a scraping pass. Rewrote components/MobileNav.tsx from a native &lt;details&gt; element (no animation, no click-outside-to-close) to a controlled client component: hamburger icon morphs into an X on open; a blurred backdrop closes the menu on click or Escape; the panel and its sections slide/fade in with a staggered delay reusing the same transition idiom as components/ScrollReveal.tsx; Providers/Postcode/Guides/Tools became single-open accordions using a CSS-only grid-template-rows 0fr-&gt;1fr transition (no JS height measurement); the menu auto-closes on route change via usePathname(); background scroll is locked while open; focus moves into the panel on open and returns to the trigger on Escape. Global prefers-reduced-motion handling already in app/globals.css applies automatically. Not visually verified on a real device — no browser automation tool available this session, validated via build output, generated CSS and server-rendered markup only.</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -7647,22 +7691,22 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
+          <t>components/MobileNav.tsx</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Email delivery provider</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7677,24 +7721,24 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
+          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
         <v>49</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -7703,22 +7747,22 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
+          <t>New subscription flow + data/provider-live-deals.json</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Email delivery provider</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>Growth playbook — Functionality pillar</t>
         </is>
       </c>
     </row>
@@ -7738,28 +7782,28 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
+          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>app/layout.tsx, components/Logo.tsx</t>
+          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -7784,53 +7828,53 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
+          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Sitewide template performance report</t>
+          <t>app/layout.tsx, components/Logo.tsx</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Field data or representative lab baselines</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7840,53 +7884,53 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Direct Awin Publisher API access — programme status and link generation</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>User asked to connect Claude to their Awin account and provided a real API token. There's no one-click connector for Awin (unlike Google Drive/Gmail), so this uses Awin's own Publisher API directly. First live run corrected two wrong assumptions from documentation research: 'programmedetails' requires a specific advertiserId (not a bulk listing endpoint) -- the actual bulk-status endpoint is GET /publishers/{id}/programmes?relationship=X, and 'any' is not a valid value for it (loops joined/pending/suspended/rejected instead; 'notjoined' returns the ~21k whole-platform catalogue so it's excluded from the default and only fetched on request). POST /publishers/{id}/linkbuilder/generate confirmed working, verified against TalkTalk (advertiser 3674). REAL FINDING from the first run, both surfaced to the user and worth acting on: only 4 programmes are joined (TalkTalk, Broadband Genie, Zzoomm, Highland Broadband), 7 pending (Sky ROI, Community Fibre, National Broadband, Trooli, Pine Media, Cuckoo, Zen Internet), and 9 REJECTED including BT (both consumer and business), Vodafone, Plusnet, EE, Virgin Media, Hyperoptic and toob. Cross-checked data/providers.ts: none of the currently-live affiliateUrl values (including TalkTalk, which IS approved) use Awin's awin1.com tracking format -- they're all plain provider URLs, so the site is very likely not earning commission on any current outbound click, joined or not, despite the on-page commercial disclosures implying it might.</t>
+          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
         <v>47</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>scripts/awin_sync.py</t>
+          <t>Sitewide template performance report</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>AWIN_API_TOKEN from the user's Awin account (user menu -&gt; API Credentials)</t>
+          <t>Field data or representative lab baselines</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -7896,53 +7940,53 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Direct Awin Publisher API access — programme status and link generation</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+          <t>User asked to connect Claude to their Awin account and provided a real API token. There's no one-click connector for Awin (unlike Google Drive/Gmail), so this uses Awin's own Publisher API directly. First live run corrected two wrong assumptions from documentation research: 'programmedetails' requires a specific advertiserId (not a bulk listing endpoint) -- the actual bulk-status endpoint is GET /publishers/{id}/programmes?relationship=X, and 'any' is not a valid value for it (loops joined/pending/suspended/rejected instead; 'notjoined' returns the ~21k whole-platform catalogue so it's excluded from the default and only fetched on request). POST /publishers/{id}/linkbuilder/generate confirmed working, verified against TalkTalk (advertiser 3674). REAL FINDING from the first run, both surfaced to the user and worth acting on: only 4 programmes are joined (TalkTalk, Broadband Genie, Zzoomm, Highland Broadband), 7 pending (Sky ROI, Community Fibre, National Broadband, Trooli, Pine Media, Cuckoo, Zen Internet), and 9 REJECTED including BT (both consumer and business), Vodafone, Plusnet, EE, Virgin Media, Hyperoptic and toob. Cross-checked data/providers.ts: none of the currently-live affiliateUrl values (including TalkTalk, which IS approved) use Awin's awin1.com tracking format -- they're all plain provider URLs, so the site is very likely not earning commission on any current outbound click, joined or not, despite the on-page commercial disclosures implying it might.</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G28" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="G28" s="2" t="n">
-        <v>58</v>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>scripts/awin_sync.py</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>AWIN_API_TOKEN from the user's Awin account (user menu -&gt; API Credentials)</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7952,43 +7996,43 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
+          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Sitewide crawl and redirect report</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
@@ -7998,7 +8042,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -8008,43 +8052,43 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide crawl and redirect report</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -8054,7 +8098,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -8069,24 +8113,24 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
@@ -8095,12 +8139,12 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
@@ -8110,7 +8154,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -8125,53 +8169,109 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="F33" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G33" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L32"/>
+  <autoFilter ref="A1:L33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8212,7 +8312,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>64 total (33 page builds, 31 feature/strategy builds); 50 already marked Done.</t>
+          <t>65 total (33 page builds, 32 feature/strategy builds); 51 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -4533,7 +4533,7 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="31" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -176,8 +176,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L66" headerRowCount="1">
-  <autoFilter ref="A1:L66"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L67" headerRowCount="1">
+  <autoFilter ref="A1:L67"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -241,8 +241,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L33" headerRowCount="1">
-  <autoFilter ref="A1:L33"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L34" headerRowCount="1">
+  <autoFilter ref="A1:L34"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1968,33 +1968,33 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>page-tools/broadband-cost-calculator</t>
+          <t>content-awin-rejected-provider-deep-content</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Broadband cost calculator: true monthly and contract-length cost</t>
+          <t>Deep, researched content for Awin-rejected providers (BT, Virgin Media, EE, Vodafone, Plusnet, Hyperoptic, toob, giffgaff)</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>59.9</v>
+        <v>60</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>27.6</v>
+        <v>65</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -2004,11 +2004,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr"/>
       <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>Live at /tools/broadband-cost-calculator, committed and deployed 2026-08-21.</t>
-        </is>
-      </c>
+      <c r="L29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -2016,7 +2012,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>page-providers/onestream</t>
+          <t>page-tools/broadband-cost-calculator</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2026,19 +2022,19 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Onestream — plans, coverage and Awin-tracked deals</t>
+          <t>Broadband cost calculator: true monthly and contract-length cost</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>59.4</v>
+        <v>59.9</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>28</v>
+        <v>27.6</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -2052,7 +2048,11 @@
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Live at /tools/broadband-cost-calculator, committed and deployed 2026-08-21.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>page-guides/no-credit-check-broadband-uk</t>
+          <t>page-providers/onestream</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2075,18 +2075,18 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>No credit check broadband in the UK: options and what to expect</t>
+          <t>Onestream — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>34.8</v>
+        <v>28</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -2104,38 +2104,38 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>feat-review-aggregation-module</t>
+          <t>page-guides/no-credit-check-broadband-uk</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Real review-aggregation trust module</t>
+          <t>No credit check broadband in the UK: options and what to expect</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>59</v>
+        <v>59.3</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>62</v>
+        <v>34.8</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -2148,38 +2148,38 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>page-providers/brsk</t>
+          <t>feat-review-aggregation-module</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Brsk — plans, coverage and Awin-tracked deals</t>
+          <t>Real review-aggregation trust module</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
         <v>59</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>28.5</v>
+        <v>62</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr"/>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>page-guides/fttp-vs-fttc-explained</t>
+          <t>page-providers/brsk</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2207,14 +2207,14 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>FTTP vs FTTC: what the difference means for your speed</t>
+          <t>Brsk — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>58.4</v>
+        <v>59</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>27.8</v>
+        <v>28.5</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>page-guides/best-mesh-wifi-for-your-broadband-router</t>
+          <t>page-guides/fttp-vs-fttc-explained</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -2251,18 +2251,18 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
+          <t>FTTP vs FTTC: what the difference means for your speed</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
         <v>58.4</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>34</v>
+        <v>27.8</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>page-guides/broadband-help-if-you-claim-benefits-uk</t>
+          <t>page-guides/best-mesh-wifi-for-your-broadband-router</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2295,18 +2295,18 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
+          <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>58.2</v>
+        <v>58.4</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>27.5</v>
+        <v>34</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2324,38 +2324,38 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>ops-adsense-site-review</t>
+          <t>page-guides/broadband-help-if-you-claim-benefits-uk</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Complete AdSense site review and authorisation monitoring</t>
+          <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>58</v>
+        <v>58.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>55</v>
+        <v>27.5</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr"/>
@@ -2368,38 +2368,38 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>content-awin-approved-provider-deep-content</t>
+          <t>ops-adsense-site-review</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Deep, researched content for Awin-approved providers (TalkTalk, Zzoomm, Highland Broadband)</t>
+          <t>Complete AdSense site review and authorisation monitoring</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
         <v>58</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -2412,12 +2412,12 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>page-providers/gigaclear</t>
+          <t>content-awin-approved-provider-deep-content</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -2427,18 +2427,18 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
+          <t>Deep, researched content for Awin-approved providers (TalkTalk, Zzoomm, Highland Broadband)</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>56.9</v>
+        <v>58</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>27.9</v>
+        <v>62</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>page-providers/youfibre</t>
+          <t>page-providers/gigaclear</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2471,14 +2471,14 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
+          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>56.6</v>
+        <v>56.9</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>28.7</v>
+        <v>27.9</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>page-providers/cuckoo</t>
+          <t>page-providers/youfibre</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2515,14 +2515,14 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
+          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>56.5</v>
+        <v>56.6</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>27.9</v>
+        <v>28.7</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>audit-city-hub-thinness</t>
+          <t>page-providers/cuckoo</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Content audit</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2559,23 +2559,23 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Verify each new city hub has a genuinely local fact</t>
+          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>56</v>
+        <v>56.5</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>50</v>
+        <v>27.9</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -2588,12 +2588,12 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>page-guides/black-friday-broadband-deals-uk</t>
+          <t>audit-city-hub-thinness</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Content audit</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -2603,23 +2603,23 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
+          <t>Verify each new city hub has a genuinely local fact</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>55.8</v>
+        <v>56</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr"/>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>page-providers/shell-energy</t>
+          <t>page-guides/black-friday-broadband-deals-uk</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2647,18 +2647,18 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
+          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>55.7</v>
+        <v>55.8</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>page-research/broadband-customer-service-rankings-uk</t>
+          <t>page-providers/shell-energy</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -2691,14 +2691,14 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
+          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>55.1</v>
+        <v>55.7</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
@@ -2720,33 +2720,33 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>feat-nav-header-footer-ia</t>
+          <t>page-research/broadband-customer-service-rankings-uk</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Navigation/header/footer IA improvements</t>
+          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>55</v>
+        <v>55.1</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>60</v>
+        <v>27.8</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2756,11 +2756,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>Shipped 2026-08-22: scripts/scrape_navigation_patterns.py scanned 5 best-in-class sites (broadband.co.uk stood out on sticky header + breadcrumbs + trust badge). Confirmed BroadbandPicker's sticky header and breadcrumbs already match best practice. Added Postcode to primary nav (desktop+mobile), restructured footer 4-&gt;6 columns adding Tools, Find Broadband by Area, and Research links to fix a crawl/link-equity gap for the 2,800+ postcode-district and tools pages. Deliberately did NOT fabricate a trust badge (no real Trustpilot/press presence yet) and did NOT widen the header postcode breakpoint (risk of stacking two unverified density changes without a browser check). See docs/navigation-ia-analysis.md.</t>
-        </is>
-      </c>
+      <c r="L46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
@@ -2768,7 +2764,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>feat-contact-form-email-delivery</t>
+          <t>feat-nav-header-footer-ia</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -2778,19 +2774,19 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Working contact form delivering to a real inbox, no third-party service</t>
+          <t>Navigation/header/footer IA improvements</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
         <v>55</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
@@ -2799,12 +2795,16 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr"/>
       <c r="K47" s="3" t="inlineStr"/>
-      <c r="L47" s="3" t="inlineStr"/>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-22: scripts/scrape_navigation_patterns.py scanned 5 best-in-class sites (broadband.co.uk stood out on sticky header + breadcrumbs + trust badge). Confirmed BroadbandPicker's sticky header and breadcrumbs already match best practice. Added Postcode to primary nav (desktop+mobile), restructured footer 4-&gt;6 columns adding Tools, Find Broadband by Area, and Research links to fix a crawl/link-equity gap for the 2,800+ postcode-district and tools pages. Deliberately did NOT fabricate a trust badge (no real Trustpilot/press presence yet) and did NOT widen the header postcode breakpoint (risk of stacking two unverified density changes without a browser check). See docs/navigation-ia-analysis.md.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -2812,38 +2812,38 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>content-awin-pending-provider-deep-content</t>
+          <t>feat-contact-form-email-delivery</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Deep, researched content for Awin-pending providers (Community Fibre, Cuckoo, Zen Internet, National Broadband, Trooli, Pine Media)</t>
+          <t>Working contact form delivering to a real inbox, no third-party service</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
         <v>55</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -2856,12 +2856,12 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
+          <t>content-awin-pending-provider-deep-content</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -2871,18 +2871,18 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Broadband complaints and the ombudsman: your UK rights</t>
+          <t>Deep, researched content for Awin-pending providers (Community Fibre, Cuckoo, Zen Internet, National Broadband, Trooli, Pine Media)</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>54.7</v>
+        <v>55</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>25.9</v>
+        <v>58</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>growth-original-research-outreach</t>
+          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2915,23 +2915,23 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Run original-research outreach and digital PR</t>
+          <t>Broadband complaints and the ombudsman: your UK rights</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>54</v>
+        <v>54.7</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>68</v>
+        <v>25.9</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -2944,29 +2944,29 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>growth-quarterly-data-reprioritisation</t>
+          <t>growth-original-research-outreach</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
+          <t>Run original-research outreach and digital PR</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr"/>
@@ -2988,29 +2988,29 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>feat-postcode-journey-personalisation</t>
+          <t>growth-quarterly-data-reprioritisation</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
         <v>53</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>feat-homepage-visual-redesign</t>
+          <t>feat-postcode-journey-personalisation</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -3047,11 +3047,11 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Homepage visual redesign: illustrations + interactivity</t>
+          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G53" s="3" t="n">
         <v>55</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>feat-mobile-cross-device-navigation</t>
+          <t>feat-homepage-visual-redesign</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3091,14 +3091,14 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Mobile and cross-device navigation overhaul</t>
+          <t>Homepage visual redesign: illustrations + interactivity</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>feat-mega-menu-navigation</t>
+          <t>feat-mobile-cross-device-navigation</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -3135,14 +3135,14 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Mobile and cross-device navigation overhaul</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>feat-animated-interactive-mobile-menu</t>
+          <t>feat-mega-menu-navigation</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3179,14 +3179,14 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Animated, interactive mobile menu with click-outside-to-close</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
         <v>50</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>feat-price-drop-alerts</t>
+          <t>feat-animated-interactive-mobile-menu</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -3218,19 +3218,19 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Animated, interactive mobile menu with click-outside-to-close</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr"/>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>feat-page-type-ux-redesign</t>
+          <t>feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3262,19 +3262,19 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
         <v>49</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>feat-footer-logo-interactivity</t>
+          <t>feat-page-type-ux-redesign</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -3311,18 +3311,18 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -3332,11 +3332,7 @@
       </c>
       <c r="J59" s="3" t="inlineStr"/>
       <c r="K59" s="3" t="inlineStr"/>
-      <c r="L59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
-        </is>
-      </c>
+      <c r="L59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -3344,43 +3340,47 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>audit-core-web-vitals-reporting</t>
+          <t>feat-footer-logo-interactivity</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
@@ -3388,38 +3388,38 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>ops-awin-publisher-api-integration</t>
+          <t>audit-core-web-vitals-reporting</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Direct Awin Publisher API access — programme status and link generation</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
         <v>47</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr"/>
@@ -3432,38 +3432,38 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>ops-awin-publisher-api-integration</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Direct Awin Publisher API access — programme status and link generation</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G62" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="G62" s="2" t="n">
-        <v>58</v>
-      </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -3476,33 +3476,33 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>audit-broken-links-redirects</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -3520,33 +3520,33 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-broken-links-redirects</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -3574,19 +3574,19 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3618,19 +3618,19 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3646,8 +3646,52 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr"/>
+      <c r="K67" s="3" t="inlineStr"/>
+      <c r="L67" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L66"/>
+  <autoFilter ref="A1:L67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4533,7 +4577,7 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="31" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
@@ -4634,7 +4678,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -4688,7 +4732,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -4742,7 +4786,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4796,7 +4840,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -4850,7 +4894,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4904,7 +4948,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -4958,7 +5002,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5012,7 +5056,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -5066,7 +5110,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5120,7 +5164,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -5174,7 +5218,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5228,7 +5272,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -5282,7 +5326,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5336,7 +5380,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -5390,7 +5434,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5444,7 +5488,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -5498,7 +5542,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -5552,7 +5596,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -5606,7 +5650,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5660,7 +5704,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -5714,7 +5758,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5768,7 +5812,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -5822,7 +5866,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -5876,7 +5920,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -5930,7 +5974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -5984,7 +6028,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -6038,7 +6082,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -6092,7 +6136,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -6146,7 +6190,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -6200,7 +6244,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -6254,7 +6298,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -6308,7 +6352,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -6362,7 +6406,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -6399,7 +6443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6932,53 +6976,53 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Real review-aggregation trust module</t>
+          <t>Deep, researched content for Awin-rejected providers (BT, Virgin Media, EE, Vodafone, Plusnet, Hyperoptic, toob, giffgaff)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Blend the existing Ofcom-complaints research methodology with live Trustpilot scores into one visible trust module reused across provider and comparison pages, instead of a single quoted score per page.</t>
+          <t>Third and final batch in the Awin content series (after approved and pending), covering all 8 real providers rejected on Awin: BT (both consumer 3041 and business 3042 programmes), Virgin Media, EE, Vodafone, Plusnet, Hyperoptic, toob and giffgaff. All 7 existing entries were thin (no contentSections) and fully rewritten; giffgaff did not exist on the site at all and was added new. IMPORTANT CORRECTION made mid-batch: while researching BT's price rise, discovered Ofcom banned inflation-linked/percentage-based mid-contract price rise terms in all new contracts from 17 January 2025 (providers must now disclose a flat pounds-and-pence figure instead). This retroactively invalidated 5 sentences written in the two earlier Awin batches (Community Fibre, Zen Internet and Zzoomm entries in data/providers.ts, plus the Community Fibre vs Hyperoptic comparison) that described CPI-linked percentage rises as a current practice -- all 5 were corrected in this same batch before continuing, and this correction is itself the kind of thing worth surfacing: a fact later research revealed to be wrong wasn't left standing. Real findings surfaced across this batch: BT and EE both maintain two separate Trustpilot pages (a mobile/brand-dominated headline score and a much lower broadband-specific one, roughly 4.0 vs 1.5 for BT, 4.2 vs 1.3 for EE) -- the broadband-specific figure was used as the primary trustpilotScore field in both cases, with the discrepancy explained in the copy since it's a genuinely useful, non-obvious insight. Plusnet's low Trustpilot score sits alongside the *best* Ofcom complaints record of any major UK provider (4 per 100,000 in Q1 2026, against TalkTalk's 10, Vodafone's 8 and BT's 7) -- a real, evidenced gap between self-selected review-platform sentiment and regulatory complaint-volume data, explained rather than picking one source and ignoring the other. Virgin Media shows the same pattern in reverse: an extremely low Trustpilot score (~1.4) next to an Ofcom complaints record at or below the industry average. giffgaff is a genuinely new product (broadband launched September 2025 on Nexfibre, the Virgin Media O2 wholesale network, not Openreach) with no separate broadband Trustpilot page yet -- flagged honestly as thin evidence rather than borrowing giffgaff's much larger mobile-customer score uncritically. All affiliateUrl values stay as each provider's own plain site URL, since Awin rejected these applications outright (not merely pending) -- every reviewSources array states this explicitly. Three new comparison pages targeting genuine content gaps rather than one-per-provider completeness (this batch's providers already had extensive existing head-to-head coverage from earlier site work): bt-vs-hyperoptic (safe wide-coverage default vs better-value niche upgrade), plusnet-vs-ee (same BT Group parent, opposite ends of Ofcom's complaints table), toob-vs-giffgaff (two newer no-price-rise challenger brands on completely different networks). All copy hand-checked for zero em dashes and zero banned AI-tell vocabulary/phrases.</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>New shared component, used on provider + comparison pages</t>
+          <t>data/providers.ts (bt, virgin-media, ee, vodafone, plusnet, hyperoptic, toob, giffgaff, plus corrections to community-fibre, zen-internet, zzoomm), data/provider-comparisons.ts (bt-vs-hyperoptic, plusnet-vs-ee, toob-vs-giffgaff, plus a correction to community-fibre-vs-hyperoptic), public/logos/giffgaff.svg</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>ops-awin-publisher-api-integration, content-awin-approved-provider-deep-content, content-awin-pending-provider-deep-content</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -6988,53 +7032,53 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Complete AdSense site review and authorisation monitoring</t>
+          <t>Real review-aggregation trust module</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Monitor the existing AdSense review, consent implementation and ads.txt authorisation; resolve any concrete policy or crawler issue reported by AdSense.</t>
+          <t>Blend the existing Ofcom-complaints research methodology with live Trustpilot scores into one visible trust module reused across provider and comparison pages, instead of a single quoted score per page.</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>AdSense status and /ads.txt</t>
+          <t>New shared component, used on provider + comparison pages</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Google site-review processing</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Build Status</t>
+          <t>Growth playbook — Functionality pillar</t>
         </is>
       </c>
     </row>
@@ -7044,53 +7088,53 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Deep, researched content for Awin-approved providers (TalkTalk, Zzoomm, Highland Broadband)</t>
+          <t>Complete AdSense site review and authorisation monitoring</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Following the Awin programme-status pull (ops-awin-publisher-api-integration), built full researched content for the 3 real providers among the 4 joined programmes (Broadband Genie is a comparison site, not an ISP, and was excluded). Per docs/page-build-pipeline-brief.md Stage 3/4/4a: for each provider, fetched the provider's own site for current pricing/speeds/contract terms, WebSearched Trustpilot and, where relevant, Ofcom's own complaints data, and wrote an 8-section contentSections block plus FAQs matching the site's deepest existing template (Gigaclear). All copy hand-checked for zero em dashes and zero banned AI-tell vocabulary/phrases per the Stage 4a list. TalkTalk's existing entry was materially stale (Trustpilot claimed 2.8, real current figure 1.5 from 50k+ reviews in Trustpilot's 'Bad' band; Ofcom's Q1 2026 report names TalkTalk the UK's most complained-about broadband provider for the third consecutive quarter; the old 'price-lock guarantee' highlight was false, two scheduled April 2027/2028 rises are now built into every contract) -- fully rewritten, not just extended. Zzoomm and Highland Broadband were brand-new Provider entries (real Awin tracking links, placeholder text-wordmark logos per the brief's guardrail against fabricating brand marks). In passing, corrected Plusnet's stale trustpilotScore field (3.9 -&gt; 2.0, the real current figure) since new comparison copy was about to cite it -- Plusnet's own deep content rewrite is out of scope (not an Awin-approved programme). Two new comparison pages: talktalk-vs-plusnet (a genuinely stark, well-evidenced contrast -- same price bracket, opposite ends of Ofcom's complaints table) and zzoomm-vs-hyperoptic (two symmetrical full-fibre altnets with almost non-overlapping coverage footprints). Internal linking relies on the existing 'How {provider} compares' module built earlier this session; both new comparisons are discoverable via /providers/compare and the sitemap even where they don't make a crowded provider's top-3 related slice.</t>
+          <t>Monitor the existing AdSense review, consent implementation and ads.txt authorisation; resolve any concrete policy or crawler issue reported by AdSense.</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
         <v>58</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>data/providers.ts (talktalk, zzoomm, highland-broadband, plusnet trustpilotScore), data/provider-comparisons.ts (talktalk-vs-plusnet, zzoomm-vs-hyperoptic), public/logos/zzoomm.svg, public/logos/highland-broadband.svg</t>
+          <t>AdSense status and /ads.txt</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>ops-awin-publisher-api-integration</t>
+          <t>Google site-review processing</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Build Status</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7144,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Content audit</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -7110,43 +7154,43 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Verify each new city hub has a genuinely local fact</t>
+          <t>Deep, researched content for Awin-approved providers (TalkTalk, Zzoomm, Highland Broadband)</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>8 new city hubs (Birmingham, Bristol, Edinburgh, Glasgow, Leeds, Liverpool, Manchester, Sheffield) plus 50 existing postcode-prefix pages is a lot of near-identical templates. Each needs at least one real local fact (a named local altnet, a real coverage figure) or it reads as duplicate content — audit before building the next batch of cities.</t>
+          <t>Following the Awin programme-status pull (ops-awin-publisher-api-integration), built full researched content for the 3 real providers among the 4 joined programmes (Broadband Genie is a comparison site, not an ISP, and was excluded). Per docs/page-build-pipeline-brief.md Stage 3/4/4a: for each provider, fetched the provider's own site for current pricing/speeds/contract terms, WebSearched Trustpilot and, where relevant, Ofcom's own complaints data, and wrote an 8-section contentSections block plus FAQs matching the site's deepest existing template (Gigaclear). All copy hand-checked for zero em dashes and zero banned AI-tell vocabulary/phrases per the Stage 4a list. TalkTalk's existing entry was materially stale (Trustpilot claimed 2.8, real current figure 1.5 from 50k+ reviews in Trustpilot's 'Bad' band; Ofcom's Q1 2026 report names TalkTalk the UK's most complained-about broadband provider for the third consecutive quarter; the old 'price-lock guarantee' highlight was false, two scheduled April 2027/2028 rises are now built into every contract) -- fully rewritten, not just extended. Zzoomm and Highland Broadband were brand-new Provider entries (real Awin tracking links, placeholder text-wordmark logos per the brief's guardrail against fabricating brand marks). In passing, corrected Plusnet's stale trustpilotScore field (3.9 -&gt; 2.0, the real current figure) since new comparison copy was about to cite it -- Plusnet's own deep content rewrite is out of scope (not an Awin-approved programme). Two new comparison pages: talktalk-vs-plusnet (a genuinely stark, well-evidenced contrast -- same price bracket, opposite ends of Ofcom's complaints table) and zzoomm-vs-hyperoptic (two symmetrical full-fibre altnets with almost non-overlapping coverage footprints). Internal linking relies on the existing 'How {provider} compares' module built earlier this session; both new comparisons are discoverable via /providers/compare and the sitemap even where they don't make a crowded provider's top-3 related slice.</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>data/priority-pages.ts city entries</t>
+          <t>data/providers.ts (talktalk, zzoomm, highland-broadband, plusnet trustpilotScore), data/provider-comparisons.ts (talktalk-vs-plusnet, zzoomm-vs-hyperoptic), public/logos/zzoomm.svg, public/logos/highland-broadband.svg</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ops-awin-publisher-api-integration</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7156,38 +7200,38 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Content audit</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Navigation/header/footer IA improvements</t>
+          <t>Verify each new city hub has a genuinely local fact</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Researched via scripts/scrape_navigation_patterns.py against 5 best-in-class sites. broadband.co.uk (closest single-vertical comparable) stood out on sticky header, breadcrumbs and a trust badge near the top; BroadbandPicker already matches on the first two. Header nav link count split cleanly into supersite (127-556 links) vs specialist (21 links) patterns, confirming the growth playbook's 'specialist, not supersite' positioning. Added Postcode to primary nav; restructured the footer from 4 to 6 columns (added Tools, Find Broadband by Area, Research) to fix a crawl/link-equity gap for the postcode-district and tools pages built this session.</t>
+          <t>8 new city hubs (Birmingham, Bristol, Edinburgh, Glasgow, Leeds, Liverpool, Manchester, Sheffield) plus 50 existing postcode-prefix pages is a lot of near-identical templates. Each needs at least one real local fact (a named local altnet, a real coverage figure) or it reads as duplicate content — audit before building the next batch of cities.</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>app/layout.tsx</t>
+          <t>data/priority-pages.ts city entries</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7197,12 +7241,12 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-22 — researched before implementing per the Strategic Lens process</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -7217,24 +7261,24 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Working contact form delivering to a real inbox, no third-party service</t>
+          <t>Navigation/header/footer IA improvements</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Previously /contact only offered mailto: links to unverified custom-domain addresses (editorial@/partnerships@/hello@broadbandpicker.co.uk). Built a real contact form (components/ContactForm.tsx) posting to a new app/api/contact route, which sends via Gmail SMTP using nodemailer — no Supabase, no database, no third-party form/CRM service, per explicit instruction. All submissions land in sayedsahil.elt@gmail.com (CONTACT_TO_EMAIL env var), sent from a Gmail account authenticated with an App Password (CONTACT_SMTP_USER / CONTACT_SMTP_PASS). Reply-To is set to the sender's own address so replying goes straight back to them. Spam mitigation without any external service: a hidden honeypot field (bots that fill every input get silently dropped) and a submit-time check rejecting anything sent under 1.5s after the form rendered. Server-side validates name/email/reason/message independently of the client. The original mailto: cards are kept underneath as a secondary direct-email option. Requires CONTACT_SMTP_USER/PASS to be set in Vercel — the API route fails gracefully with a friendly error and a server log line if they're absent, rather than silently dropping messages.</t>
+          <t>Researched via scripts/scrape_navigation_patterns.py against 5 best-in-class sites. broadband.co.uk (closest single-vertical comparable) stood out on sticky header, breadcrumbs and a trust badge near the top; BroadbandPicker already matches on the first two. Header nav link count split cleanly into supersite (127-556 links) vs specialist (21 links) patterns, confirming the growth playbook's 'specialist, not supersite' positioning. Added Postcode to primary nav; restructured the footer from 4 to 6 columns (added Tools, Find Broadband by Area, Research) to fix a crawl/link-equity gap for the postcode-district and tools pages built this session.</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
         <v>55</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -7243,22 +7287,22 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>app/api/contact/route.ts, components/ContactForm.tsx, app/contact/page.tsx</t>
+          <t>app/layout.tsx</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>CONTACT_SMTP_USER / CONTACT_SMTP_PASS Gmail App Password set in Vercel env vars</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>User request 2026-08-22 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7268,48 +7312,48 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Deep, researched content for Awin-pending providers (Community Fibre, Cuckoo, Zen Internet, National Broadband, Trooli, Pine Media)</t>
+          <t>Working contact form delivering to a real inbox, no third-party service</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Follow-up to content-awin-approved-provider-deep-content, extending the same research process to the 6 real UK-relevant advertisers pending Awin approval (Sky ROI excluded -- Republic of Ireland Sky, not UK, out of scope for a UK site, confirmed with the user). Community Fibre and Zen Internet were existing but thin entries, fully rewritten. Cuckoo was already deep and dated the previous day; verified rather than rewritten. National Broadband, Trooli and Pine Media were brand-new Provider entries. National Broadband is the site's first 4G/5G fixed-wireless provider (a genuinely new content category, not another fibre altnet); Pine Media is a hyperlocal single-city (Sheffield-only) provider with a two-tier product split (its own symmetrical GIG network vs an Openreach-based GLO product) that needed explaining clearly to avoid conflating the two. Key design decision: because these programmes are pending, not joined, affiliateUrl stays as each provider's own plain site URL rather than an Awin tracking link -- confirmed via a live API test that Awin's linkbuilder will generate a structurally valid tracking URL even for a pending programme, which would be misleading to publish since it likely would not earn commission (or could breach Awin's terms) before approval. Each reviewSources array carries an explicit 'pending, not yet approved' note on the Awin source, matching the existing Gigaclear convention. All copy hand-checked for zero em dashes and zero banned AI-tell vocabulary/phrases. Three new comparison pages, chosen for genuine evidentiary value over one-per-provider completeness: community-fibre-vs-hyperoptic (London's two biggest symmetrical altnets, direct competitors), trooli-vs-zzoomm (two multi-region altnets with near-zero coverage overlap and matching no-price-rise policies), and national-broadband-vs-highland-broadband (5G available now vs fibre still being built -- a genuine buy-now-or-wait decision for the same rural Scottish customer). Cuckoo, Zen Internet and Pine Media were deliberately left without a new comparison this round -- no natural, non-forced head-to-head partner existed for any of them without inventing artificial relevance.</t>
+          <t>Previously /contact only offered mailto: links to unverified custom-domain addresses (editorial@/partnerships@/hello@broadbandpicker.co.uk). Built a real contact form (components/ContactForm.tsx) posting to a new app/api/contact route, which sends via Gmail SMTP using nodemailer — no Supabase, no database, no third-party form/CRM service, per explicit instruction. All submissions land in sayedsahil.elt@gmail.com (CONTACT_TO_EMAIL env var), sent from a Gmail account authenticated with an App Password (CONTACT_SMTP_USER / CONTACT_SMTP_PASS). Reply-To is set to the sender's own address so replying goes straight back to them. Spam mitigation without any external service: a hidden honeypot field (bots that fill every input get silently dropped) and a submit-time check rejecting anything sent under 1.5s after the form rendered. Server-side validates name/email/reason/message independently of the client. The original mailto: cards are kept underneath as a secondary direct-email option. Requires CONTACT_SMTP_USER/PASS to be set in Vercel — the API route fails gracefully with a friendly error and a server log line if they're absent, rather than silently dropping messages.</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
         <v>55</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>data/providers.ts (community-fibre, cuckoo, zen-internet, national-broadband, trooli, pine-media), data/provider-comparisons.ts (community-fibre-vs-hyperoptic, trooli-vs-zzoomm, national-broadband-vs-highland-broadband), public/logos/national-broadband.svg, public/logos/trooli.svg, public/logos/pine-media.svg</t>
+          <t>app/api/contact/route.ts, components/ContactForm.tsx, app/contact/page.tsx</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>content-awin-approved-provider-deep-content, ops-awin-publisher-api-integration</t>
+          <t>CONTACT_SMTP_USER / CONTACT_SMTP_PASS Gmail App Password set in Vercel env vars</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -7324,7 +7368,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -7334,43 +7378,43 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Run original-research outreach and digital PR</t>
+          <t>Deep, researched content for Awin-pending providers (Community Fibre, Cuckoo, Zen Internet, National Broadband, Trooli, Pine Media)</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Build a relevant outreach list and earn citations and links to the live Ofcom-backed customer-satisfaction research.</t>
+          <t>Follow-up to content-awin-approved-provider-deep-content, extending the same research process to the 6 real UK-relevant advertisers pending Awin approval (Sky ROI excluded -- Republic of Ireland Sky, not UK, out of scope for a UK site, confirmed with the user). Community Fibre and Zen Internet were existing but thin entries, fully rewritten. Cuckoo was already deep and dated the previous day; verified rather than rewritten. National Broadband, Trooli and Pine Media were brand-new Provider entries. National Broadband is the site's first 4G/5G fixed-wireless provider (a genuinely new content category, not another fibre altnet); Pine Media is a hyperlocal single-city (Sheffield-only) provider with a two-tier product split (its own symmetrical GIG network vs an Openreach-based GLO product) that needed explaining clearly to avoid conflating the two. Key design decision: because these programmes are pending, not joined, affiliateUrl stays as each provider's own plain site URL rather than an Awin tracking link -- confirmed via a live API test that Awin's linkbuilder will generate a structurally valid tracking URL even for a pending programme, which would be misleading to publish since it likely would not earn commission (or could breach Awin's terms) before approval. Each reviewSources array carries an explicit 'pending, not yet approved' note on the Awin source, matching the existing Gigaclear convention. All copy hand-checked for zero em dashes and zero banned AI-tell vocabulary/phrases. Three new comparison pages, chosen for genuine evidentiary value over one-per-provider completeness: community-fibre-vs-hyperoptic (London's two biggest symmetrical altnets, direct competitors), trooli-vs-zzoomm (two multi-region altnets with near-zero coverage overlap and matching no-price-rise policies), and national-broadband-vs-highland-broadband (5G available now vs fibre still being built -- a genuine buy-now-or-wait decision for the same rural Scottish customer). Cuckoo, Zen Internet and Pine Media were deliberately left without a new comparison this round -- no natural, non-forced head-to-head partner existed for any of them without inventing artificial relevance.</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>/research/uk-broadband-customer-satisfaction</t>
+          <t>data/providers.ts (community-fibre, cuckoo, zen-internet, national-broadband, trooli, pine-media), data/provider-comparisons.ts (community-fibre-vs-hyperoptic, trooli-vs-zzoomm, national-broadband-vs-highland-broadband), public/logos/national-broadband.svg, public/logos/trooli.svg, public/logos/pine-media.svg</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Research page and source methodology are live</t>
+          <t>content-awin-approved-provider-deep-content, ops-awin-publisher-api-integration</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Build Status / 90 Day Roadmap</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7380,29 +7424,29 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
+          <t>Run original-research outreach and digital PR</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Review query/page performance, assisted conversions, Awin decisions and engagement data, then record the next-quarter build decisions.</t>
+          <t>Build a relevant outreach list and earn citations and links to the live Ofcom-backed customer-satisfaction research.</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -7411,22 +7455,22 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Next-quarter decision log</t>
+          <t>/research/uk-broadband-customer-satisfaction</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>ops-conversion-reporting-loop and sufficient observation period</t>
+          <t>Research page and source methodology are live</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: 90 Day Roadmap</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Build Status / 90 Day Roadmap</t>
         </is>
       </c>
     </row>
@@ -7436,29 +7480,29 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>User asked for a postcode -&gt; select-your-house-number address picker with customised content, and explicitly asked whether it could be built free. Researched live (WebSearch, 2026-08-23): full UK address-level lookup (the data behind 'pick your house from a list') is Royal Mail's licensed PAF data, not open -- getAddress.io, a popular free-tier provider, was shut down in Oct 2025 after a Royal Mail/IDDQD IP claim; Ideal Postcodes gives a 1-month/50-credit trial then pay-as-you-go; no provider offers a genuine unlimited free tier at real traffic. Separately, even a working address picker wouldn't improve accuracy without a paid per-address line-checker API (Openreach or provider-specific), which is a commercial relationship, not a script. Presented both findings and 3 options to the user via AskUserQuestion; they chose the free path: deepen personalisation using data already held, no new API, no new cost. Shipped: extended the existing components/PostcodeContextBar.tsx (previously only on deals/compare/provider pages) to guide pages and all 3 tool pages (speed test, broadband match, cost calculator) so a stored postcode follows the visitor through the full journey; new components/ProviderAvailabilityBadge.tsx shows a real yes/no ('BT is/isn't listed as available in {town}') on provider review pages, but only for the 51 postcode areas with real availableProviders data in data/postcodes.ts -- silently renders nothing outside that set rather than guessing; new components/ReturningVisitorBanner.tsx greets a returning visitor on the homepage with a direct link back to their own postcode's deals.</t>
+          <t>Review query/page performance, assisted conversions, Awin decisions and engagement data, then record the next-quarter build decisions.</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
         <v>53</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -7467,22 +7511,22 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>components/ProviderAvailabilityBadge.tsx, components/ReturningVisitorBanner.tsx, components/PostcodeContextBar.tsx, app/page.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/speed-test/page.tsx, app/tools/broadband-match/page.tsx, app/tools/broadband-cost-calculator/page.tsx</t>
+          <t>Next-quarter decision log</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>None -- deliberately built on data already held, no new API/cost</t>
+          <t>ops-conversion-reporting-loop and sufficient observation period</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: 90 Day Roadmap</t>
         </is>
       </c>
     </row>
@@ -7502,16 +7546,16 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Homepage visual redesign: illustrations + interactivity</t>
+          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Researched via scripts/analyze_homepage_visual_design.py against 5 UK broadband comparison homepages: none uses stock-photo hero banners; the dominant visual language is heavy inline SVG (Uswitch ships 195) and provider logos, no carousel/animation library detected anywhere. Generated 7 original on-brand SVG illustrations (scripts/generate_homepage_illustrations.py: hero network graphic, 3 colour-filled step icons, 2 gradient blobs, a quiz illustration) rather than stock photography, matching what's actually proven in this vertical. Added a scroll-reveal component, hover interactions, and restructured the Broadband Match promo to a two-column illustrated layout. Content/copy unchanged, visual/UX only.</t>
+          <t>User asked for a postcode -&gt; select-your-house-number address picker with customised content, and explicitly asked whether it could be built free. Researched live (WebSearch, 2026-08-23): full UK address-level lookup (the data behind 'pick your house from a list') is Royal Mail's licensed PAF data, not open -- getAddress.io, a popular free-tier provider, was shut down in Oct 2025 after a Royal Mail/IDDQD IP claim; Ideal Postcodes gives a 1-month/50-credit trial then pay-as-you-go; no provider offers a genuine unlimited free tier at real traffic. Separately, even a working address picker wouldn't improve accuracy without a paid per-address line-checker API (Openreach or provider-specific), which is a commercial relationship, not a script. Presented both findings and 3 options to the user via AskUserQuestion; they chose the free path: deepen personalisation using data already held, no new API, no new cost. Shipped: extended the existing components/PostcodeContextBar.tsx (previously only on deals/compare/provider pages) to guide pages and all 3 tool pages (speed test, broadband match, cost calculator) so a stored postcode follows the visitor through the full journey; new components/ProviderAvailabilityBadge.tsx shows a real yes/no ('BT is/isn't listed as available in {town}') on provider review pages, but only for the 51 postcode areas with real availableProviders data in data/postcodes.ts -- silently renders nothing outside that set rather than guessing; new components/ReturningVisitorBanner.tsx greets a returning visitor on the homepage with a direct link back to their own postcode's deals.</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>55</v>
@@ -7523,12 +7567,12 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>app/page.tsx, components/ScrollReveal.tsx, public/illustrations/</t>
+          <t>components/ProviderAvailabilityBadge.tsx, components/ReturningVisitorBanner.tsx, components/PostcodeContextBar.tsx, app/page.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/speed-test/page.tsx, app/tools/broadband-match/page.tsx, app/tools/broadband-cost-calculator/page.tsx</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None -- deliberately built on data already held, no new API/cost</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -7558,19 +7602,19 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Mobile and cross-device navigation overhaul</t>
+          <t>Homepage visual redesign: illustrations + interactivity</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>New scripts/analyze_mobile_ux.py scanned Uswitch, broadband.co.uk and choose.co.uk (MoneySavingExpert 403, reported not bypassed) with a mobile Safari user agent for markup/CSS signals: viewport meta and hamburger menu markers were universal but already correct on our own site; tel: click-to-call was absent everywhere (0/4, skipped); sticky bottom CTA (1/4) and apple-touch-icon (2/4) were too weak/incomplete to act on. The real gap was found by direct inspection, not the scan: the mobile nav was a small anchored dropdown of 10 flat links with ~36px touch targets, while the desktop nav beside it was a full mega-menu, and the header postcode checker was desktop-only so phone users had no quick postcode access outside the homepage/deals page. Replaced it with new components/MobileNav.tsx: a full-width slide-down panel reusing the desktop mega-menu's own icon/link data (exported from MainNav.tsx, so the two can't drift apart), every link at a 44px (min-h-11) touch target, and the postcode checker embedded at the top so it's reachable from any page. Added anchor ids to /guides category sections so the new mobile Guides menu jumps to a real target instead of an unread query param.</t>
+          <t>Researched via scripts/analyze_homepage_visual_design.py against 5 UK broadband comparison homepages: none uses stock-photo hero banners; the dominant visual language is heavy inline SVG (Uswitch ships 195) and provider logos, no carousel/animation library detected anywhere. Generated 7 original on-brand SVG illustrations (scripts/generate_homepage_illustrations.py: hero network graphic, 3 colour-filled step icons, 2 gradient blobs, a quiz illustration) rather than stock photography, matching what's actually proven in this vertical. Added a scroll-reveal component, hover interactions, and restructured the Broadband Match promo to a two-column illustrated layout. Content/copy unchanged, visual/UX only.</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -7579,7 +7623,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>components/MobileNav.tsx, components/MainNav.tsx, app/layout.tsx, app/guides/page.tsx</t>
+          <t>app/page.tsx, components/ScrollReveal.tsx, public/illustrations/</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -7614,19 +7658,19 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Mobile and cross-device navigation overhaul</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
+          <t>New scripts/analyze_mobile_ux.py scanned Uswitch, broadband.co.uk and choose.co.uk (MoneySavingExpert 403, reported not bypassed) with a mobile Safari user agent for markup/CSS signals: viewport meta and hamburger menu markers were universal but already correct on our own site; tel: click-to-call was absent everywhere (0/4, skipped); sticky bottom CTA (1/4) and apple-touch-icon (2/4) were too weak/incomplete to act on. The real gap was found by direct inspection, not the scan: the mobile nav was a small anchored dropdown of 10 flat links with ~36px touch targets, while the desktop nav beside it was a full mega-menu, and the header postcode checker was desktop-only so phone users had no quick postcode access outside the homepage/deals page. Replaced it with new components/MobileNav.tsx: a full-width slide-down panel reusing the desktop mega-menu's own icon/link data (exported from MainNav.tsx, so the two can't drift apart), every link at a 44px (min-h-11) touch target, and the postcode checker embedded at the top so it's reachable from any page. Added anchor ids to /guides category sections so the new mobile Guides menu jumps to a real target instead of an unread query param.</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -7635,7 +7679,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>components/MainNav.tsx, app/layout.tsx</t>
+          <t>components/MobileNav.tsx, components/MainNav.tsx, app/layout.tsx, app/guides/page.tsx</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7670,19 +7714,19 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Animated, interactive mobile menu with click-outside-to-close</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Direct UX/interaction-design request, not a scraping pass. Rewrote components/MobileNav.tsx from a native &lt;details&gt; element (no animation, no click-outside-to-close) to a controlled client component: hamburger icon morphs into an X on open; a blurred backdrop closes the menu on click or Escape; the panel and its sections slide/fade in with a staggered delay reusing the same transition idiom as components/ScrollReveal.tsx; Providers/Postcode/Guides/Tools became single-open accordions using a CSS-only grid-template-rows 0fr-&gt;1fr transition (no JS height measurement); the menu auto-closes on route change via usePathname(); background scroll is locked while open; focus moves into the panel on open and returns to the trigger on Escape. Global prefers-reduced-motion handling already in app/globals.css applies automatically. Not visually verified on a real device — no browser automation tool available this session, validated via build output, generated CSS and server-rendered markup only.</t>
+          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -7691,7 +7735,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>components/MobileNav.tsx</t>
+          <t>components/MainNav.tsx, app/layout.tsx</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -7721,24 +7765,24 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Animated, interactive mobile menu with click-outside-to-close</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
+          <t>Direct UX/interaction-design request, not a scraping pass. Rewrote components/MobileNav.tsx from a native &lt;details&gt; element (no animation, no click-outside-to-close) to a controlled client component: hamburger icon morphs into an X on open; a blurred backdrop closes the menu on click or Escape; the panel and its sections slide/fade in with a staggered delay reusing the same transition idiom as components/ScrollReveal.tsx; Providers/Postcode/Guides/Tools became single-open accordions using a CSS-only grid-template-rows 0fr-&gt;1fr transition (no JS height measurement); the menu auto-closes on route change via usePathname(); background scroll is locked while open; focus moves into the panel on open and returns to the trigger on Escape. Global prefers-reduced-motion handling already in app/globals.css applies automatically. Not visually verified on a real device — no browser automation tool available this session, validated via build output, generated CSS and server-rendered markup only.</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -7747,22 +7791,22 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
+          <t>components/MobileNav.tsx</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Email delivery provider</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7777,24 +7821,24 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
+          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
         <v>49</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -7803,22 +7847,22 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
+          <t>New subscription flow + data/provider-live-deals.json</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Email delivery provider</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>Growth playbook — Functionality pillar</t>
         </is>
       </c>
     </row>
@@ -7838,28 +7882,28 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
+          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>app/layout.tsx, components/Logo.tsx</t>
+          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7884,53 +7928,53 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
+          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Sitewide template performance report</t>
+          <t>app/layout.tsx, components/Logo.tsx</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>Field data or representative lab baselines</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7940,53 +7984,53 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Direct Awin Publisher API access — programme status and link generation</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>User asked to connect Claude to their Awin account and provided a real API token. There's no one-click connector for Awin (unlike Google Drive/Gmail), so this uses Awin's own Publisher API directly. First live run corrected two wrong assumptions from documentation research: 'programmedetails' requires a specific advertiserId (not a bulk listing endpoint) -- the actual bulk-status endpoint is GET /publishers/{id}/programmes?relationship=X, and 'any' is not a valid value for it (loops joined/pending/suspended/rejected instead; 'notjoined' returns the ~21k whole-platform catalogue so it's excluded from the default and only fetched on request). POST /publishers/{id}/linkbuilder/generate confirmed working, verified against TalkTalk (advertiser 3674). REAL FINDING from the first run, both surfaced to the user and worth acting on: only 4 programmes are joined (TalkTalk, Broadband Genie, Zzoomm, Highland Broadband), 7 pending (Sky ROI, Community Fibre, National Broadband, Trooli, Pine Media, Cuckoo, Zen Internet), and 9 REJECTED including BT (both consumer and business), Vodafone, Plusnet, EE, Virgin Media, Hyperoptic and toob. Cross-checked data/providers.ts: none of the currently-live affiliateUrl values (including TalkTalk, which IS approved) use Awin's awin1.com tracking format -- they're all plain provider URLs, so the site is very likely not earning commission on any current outbound click, joined or not, despite the on-page commercial disclosures implying it might.</t>
+          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
         <v>47</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>scripts/awin_sync.py</t>
+          <t>Sitewide template performance report</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>AWIN_API_TOKEN from the user's Awin account (user menu -&gt; API Credentials)</t>
+          <t>Field data or representative lab baselines</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -7996,53 +8040,53 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Direct Awin Publisher API access — programme status and link generation</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+          <t>User asked to connect Claude to their Awin account and provided a real API token. There's no one-click connector for Awin (unlike Google Drive/Gmail), so this uses Awin's own Publisher API directly. First live run corrected two wrong assumptions from documentation research: 'programmedetails' requires a specific advertiserId (not a bulk listing endpoint) -- the actual bulk-status endpoint is GET /publishers/{id}/programmes?relationship=X, and 'any' is not a valid value for it (loops joined/pending/suspended/rejected instead; 'notjoined' returns the ~21k whole-platform catalogue so it's excluded from the default and only fetched on request). POST /publishers/{id}/linkbuilder/generate confirmed working, verified against TalkTalk (advertiser 3674). REAL FINDING from the first run, both surfaced to the user and worth acting on: only 4 programmes are joined (TalkTalk, Broadband Genie, Zzoomm, Highland Broadband), 7 pending (Sky ROI, Community Fibre, National Broadband, Trooli, Pine Media, Cuckoo, Zen Internet), and 9 REJECTED including BT (both consumer and business), Vodafone, Plusnet, EE, Virgin Media, Hyperoptic and toob. Cross-checked data/providers.ts: none of the currently-live affiliateUrl values (including TalkTalk, which IS approved) use Awin's awin1.com tracking format -- they're all plain provider URLs, so the site is very likely not earning commission on any current outbound click, joined or not, despite the on-page commercial disclosures implying it might.</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G29" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="G29" s="3" t="n">
-        <v>58</v>
-      </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>scripts/awin_sync.py</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>AWIN_API_TOKEN from the user's Awin account (user menu -&gt; API Credentials)</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8052,43 +8096,43 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
+          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Sitewide crawl and redirect report</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -8098,7 +8142,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -8108,43 +8152,43 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide crawl and redirect report</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
@@ -8154,7 +8198,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -8169,24 +8213,24 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -8195,12 +8239,12 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -8210,7 +8254,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -8225,53 +8269,109 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F33" s="3" t="n">
+      <c r="F34" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G33" s="3" t="n">
+      <c r="G34" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L33"/>
+  <autoFilter ref="A1:L34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8312,7 +8412,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>65 total (33 page builds, 32 feature/strategy builds); 51 already marked Done.</t>
+          <t>66 total (33 page builds, 33 feature/strategy builds); 52 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -4577,7 +4577,7 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="31" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$68</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -176,8 +176,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L67" headerRowCount="1">
-  <autoFilter ref="A1:L67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L68" headerRowCount="1">
+  <autoFilter ref="A1:L68"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -241,8 +241,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L34" headerRowCount="1">
-  <autoFilter ref="A1:L34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L35" headerRowCount="1">
+  <autoFilter ref="A1:L35"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3388,29 +3388,29 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>audit-core-web-vitals-reporting</t>
+          <t>content-refresh-best-broadband-tv-deals-guide</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Research-led editorial refresh: Best Broadband and TV Deals guide</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr"/>
@@ -3432,38 +3432,38 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>ops-awin-publisher-api-integration</t>
+          <t>audit-core-web-vitals-reporting</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Direct Awin Publisher API access — programme status and link generation</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
         <v>47</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -3476,38 +3476,38 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>ops-awin-publisher-api-integration</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Direct Awin Publisher API access — programme status and link generation</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G63" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="G63" s="3" t="n">
-        <v>58</v>
-      </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr"/>
@@ -3520,33 +3520,33 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>audit-broken-links-redirects</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3564,33 +3564,33 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-broken-links-redirects</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3618,19 +3618,19 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -3662,19 +3662,19 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
@@ -3690,8 +3690,52 @@
       <c r="K67" s="3" t="inlineStr"/>
       <c r="L67" s="3" t="inlineStr"/>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L67"/>
+  <autoFilter ref="A1:L68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4577,7 +4621,7 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="31" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
@@ -4678,7 +4722,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -4732,7 +4776,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -4786,7 +4830,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4840,7 +4884,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -4894,7 +4938,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4948,7 +4992,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -5002,7 +5046,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5056,7 +5100,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -5110,7 +5154,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5164,7 +5208,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -5218,7 +5262,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5272,7 +5316,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -5326,7 +5370,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5380,7 +5424,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -5434,7 +5478,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5488,7 +5532,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -5542,7 +5586,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -5596,7 +5640,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -5650,7 +5694,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5704,7 +5748,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -5758,7 +5802,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5812,7 +5856,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -5866,7 +5910,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -5920,7 +5964,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -5974,7 +6018,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6028,7 +6072,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -6082,7 +6126,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -6136,7 +6180,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -6190,7 +6234,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -6244,7 +6288,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -6298,7 +6342,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -6352,7 +6396,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -6406,7 +6450,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -6443,7 +6487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7984,29 +8028,29 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Research-led editorial refresh: Best Broadband and TV Deals guide</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
+          <t>User-requested application of the same Stage 3/4/4a research process from the Awin content batches to a single existing guide page, /guides/best-broadband-and-tv-deals. Unlike the thin provider stubs rewritten in the Awin batches, this guide was already well-built (tables, methodology, 7 FAQs, real Ofcom citations, last checked 29 July 2026) -- not a stub needing a ground-up rewrite, so this was a verify-and-deepen pass grounded in fresh research rather than a full replacement. Scraped 2 top-ranking competitors (MoneySuperMarket, Uswitch) per Stage 3.0: found MoneySupermarket runs a 15-question FAQ (ours had 7) and leads with an expert-quoted bundling-savings statistic. Traced that claim to its actual primary source rather than citing the secondary restatement: Ofcom's own February 2026 research, savings of £26-£48/month from bundling and pay-TV averaging £12/month within a bundle (23% real-terms fall) -- a stronger, more current, primary-sourced figure than the competitor's 2023-dated stat, added as a new section. Also found and added two genuinely new, specific facts the page didn't have: Virgin Media's Max Volt bundle (real current pricing including its two scheduled rises to April 2028) as a concrete worked example, and Virgin Media's 'Most Reliable Broadband Provider' win at the 2026 Uswitch Telecoms Awards (Opensignal-verified, a genuine third-party measurement). Named the specific Sky bundle example (Sky Stream, Sky TV, Netflix + Full Fibre 300, £35/month) that the existing copy referenced only vaguely. Added 2 new FAQs tied to the new content. Fixed 2 pre-existing em dashes found during the pass (a legitimate en-dash numeric range, '50-100Mbps', was left alone -- not an AI-tell, different typographic use). Updated the page's stated fact-check date and guides.ts updatedDate to 2026-08-24.</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -8015,22 +8059,22 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Sitewide template performance report</t>
+          <t>app/guides/[slug]/page.tsx (best-broadband-and-tv-deals), data/guides.ts</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Field data or representative lab baselines</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8040,53 +8084,53 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Direct Awin Publisher API access — programme status and link generation</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>User asked to connect Claude to their Awin account and provided a real API token. There's no one-click connector for Awin (unlike Google Drive/Gmail), so this uses Awin's own Publisher API directly. First live run corrected two wrong assumptions from documentation research: 'programmedetails' requires a specific advertiserId (not a bulk listing endpoint) -- the actual bulk-status endpoint is GET /publishers/{id}/programmes?relationship=X, and 'any' is not a valid value for it (loops joined/pending/suspended/rejected instead; 'notjoined' returns the ~21k whole-platform catalogue so it's excluded from the default and only fetched on request). POST /publishers/{id}/linkbuilder/generate confirmed working, verified against TalkTalk (advertiser 3674). REAL FINDING from the first run, both surfaced to the user and worth acting on: only 4 programmes are joined (TalkTalk, Broadband Genie, Zzoomm, Highland Broadband), 7 pending (Sky ROI, Community Fibre, National Broadband, Trooli, Pine Media, Cuckoo, Zen Internet), and 9 REJECTED including BT (both consumer and business), Vodafone, Plusnet, EE, Virgin Media, Hyperoptic and toob. Cross-checked data/providers.ts: none of the currently-live affiliateUrl values (including TalkTalk, which IS approved) use Awin's awin1.com tracking format -- they're all plain provider URLs, so the site is very likely not earning commission on any current outbound click, joined or not, despite the on-page commercial disclosures implying it might.</t>
+          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
         <v>47</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>scripts/awin_sync.py</t>
+          <t>Sitewide template performance report</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>AWIN_API_TOKEN from the user's Awin account (user menu -&gt; API Credentials)</t>
+          <t>Field data or representative lab baselines</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -8096,53 +8140,53 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Direct Awin Publisher API access — programme status and link generation</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+          <t>User asked to connect Claude to their Awin account and provided a real API token. There's no one-click connector for Awin (unlike Google Drive/Gmail), so this uses Awin's own Publisher API directly. First live run corrected two wrong assumptions from documentation research: 'programmedetails' requires a specific advertiserId (not a bulk listing endpoint) -- the actual bulk-status endpoint is GET /publishers/{id}/programmes?relationship=X, and 'any' is not a valid value for it (loops joined/pending/suspended/rejected instead; 'notjoined' returns the ~21k whole-platform catalogue so it's excluded from the default and only fetched on request). POST /publishers/{id}/linkbuilder/generate confirmed working, verified against TalkTalk (advertiser 3674). REAL FINDING from the first run, both surfaced to the user and worth acting on: only 4 programmes are joined (TalkTalk, Broadband Genie, Zzoomm, Highland Broadband), 7 pending (Sky ROI, Community Fibre, National Broadband, Trooli, Pine Media, Cuckoo, Zen Internet), and 9 REJECTED including BT (both consumer and business), Vodafone, Plusnet, EE, Virgin Media, Hyperoptic and toob. Cross-checked data/providers.ts: none of the currently-live affiliateUrl values (including TalkTalk, which IS approved) use Awin's awin1.com tracking format -- they're all plain provider URLs, so the site is very likely not earning commission on any current outbound click, joined or not, despite the on-page commercial disclosures implying it might.</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G30" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="G30" s="2" t="n">
-        <v>58</v>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>scripts/awin_sync.py</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>AWIN_API_TOKEN from the user's Awin account (user menu -&gt; API Credentials)</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8152,43 +8196,43 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
+          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Sitewide crawl and redirect report</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
@@ -8198,7 +8242,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -8208,43 +8252,43 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide crawl and redirect report</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -8254,7 +8298,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -8269,24 +8313,24 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
@@ -8295,12 +8339,12 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
@@ -8310,7 +8354,7 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -8325,53 +8369,109 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="F35" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="G35" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L35" s="3" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L34"/>
+  <autoFilter ref="A1:L35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8412,7 +8512,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>66 total (33 page builds, 33 feature/strategy builds); 52 already marked Done.</t>
+          <t>67 total (33 page builds, 34 feature/strategy builds); 53 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -4621,7 +4621,7 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="31" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Live but not committed to git</t>
+          <t>Committed</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -176,8 +176,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L68" headerRowCount="1">
-  <autoFilter ref="A1:L68"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L69" headerRowCount="1">
+  <autoFilter ref="A1:L69"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -241,8 +241,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L35" headerRowCount="1">
-  <autoFilter ref="A1:L35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L36" headerRowCount="1">
+  <autoFilter ref="A1:L36"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:L69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2632,12 +2632,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>page-guides/black-friday-broadband-deals-uk</t>
+          <t>ops-content-priority-analysis-tooling</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2647,18 +2647,18 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
+          <t>Content priority analysis: real SEO + GEO signals, build vs. update on one list</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>55.8</v>
+        <v>56</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>page-providers/shell-energy</t>
+          <t>page-guides/black-friday-broadband-deals-uk</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -2691,18 +2691,18 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
+          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>55.7</v>
+        <v>55.8</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>page-research/broadband-customer-service-rankings-uk</t>
+          <t>page-providers/shell-energy</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2735,14 +2735,14 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
+          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>55.1</v>
+        <v>55.7</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2764,33 +2764,33 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>feat-nav-header-footer-ia</t>
+          <t>page-research/broadband-customer-service-rankings-uk</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Navigation/header/footer IA improvements</t>
+          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>55</v>
+        <v>55.1</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>60</v>
+        <v>27.8</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -2800,11 +2800,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr"/>
       <c r="K47" s="3" t="inlineStr"/>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t>Shipped 2026-08-22: scripts/scrape_navigation_patterns.py scanned 5 best-in-class sites (broadband.co.uk stood out on sticky header + breadcrumbs + trust badge). Confirmed BroadbandPicker's sticky header and breadcrumbs already match best practice. Added Postcode to primary nav (desktop+mobile), restructured footer 4-&gt;6 columns adding Tools, Find Broadband by Area, and Research links to fix a crawl/link-equity gap for the 2,800+ postcode-district and tools pages. Deliberately did NOT fabricate a trust badge (no real Trustpilot/press presence yet) and did NOT widen the header postcode breakpoint (risk of stacking two unverified density changes without a browser check). See docs/navigation-ia-analysis.md.</t>
-        </is>
-      </c>
+      <c r="L47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -2812,7 +2808,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>feat-contact-form-email-delivery</t>
+          <t>feat-nav-header-footer-ia</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2822,19 +2818,19 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Working contact form delivering to a real inbox, no third-party service</t>
+          <t>Navigation/header/footer IA improvements</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
         <v>55</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2843,12 +2839,16 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-22: scripts/scrape_navigation_patterns.py scanned 5 best-in-class sites (broadband.co.uk stood out on sticky header + breadcrumbs + trust badge). Confirmed BroadbandPicker's sticky header and breadcrumbs already match best practice. Added Postcode to primary nav (desktop+mobile), restructured footer 4-&gt;6 columns adding Tools, Find Broadband by Area, and Research links to fix a crawl/link-equity gap for the 2,800+ postcode-district and tools pages. Deliberately did NOT fabricate a trust badge (no real Trustpilot/press presence yet) and did NOT widen the header postcode breakpoint (risk of stacking two unverified density changes without a browser check). See docs/navigation-ia-analysis.md.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
@@ -2856,38 +2856,38 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>content-awin-pending-provider-deep-content</t>
+          <t>feat-contact-form-email-delivery</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Deep, researched content for Awin-pending providers (Community Fibre, Cuckoo, Zen Internet, National Broadband, Trooli, Pine Media)</t>
+          <t>Working contact form delivering to a real inbox, no third-party service</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
         <v>55</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr"/>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
+          <t>content-awin-pending-provider-deep-content</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2915,18 +2915,18 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Broadband complaints and the ombudsman: your UK rights</t>
+          <t>Deep, researched content for Awin-pending providers (Community Fibre, Cuckoo, Zen Internet, National Broadband, Trooli, Pine Media)</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>54.7</v>
+        <v>55</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>25.9</v>
+        <v>58</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>growth-original-research-outreach</t>
+          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -2959,23 +2959,23 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Run original-research outreach and digital PR</t>
+          <t>Broadband complaints and the ombudsman: your UK rights</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>54</v>
+        <v>54.7</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>68</v>
+        <v>25.9</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr"/>
@@ -2988,29 +2988,29 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>growth-quarterly-data-reprioritisation</t>
+          <t>growth-original-research-outreach</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
+          <t>Run original-research outreach and digital PR</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -3032,29 +3032,29 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>feat-postcode-journey-personalisation</t>
+          <t>growth-quarterly-data-reprioritisation</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
         <v>53</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr"/>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>feat-homepage-visual-redesign</t>
+          <t>feat-postcode-journey-personalisation</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3091,11 +3091,11 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Homepage visual redesign: illustrations + interactivity</t>
+          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>55</v>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>feat-mobile-cross-device-navigation</t>
+          <t>feat-homepage-visual-redesign</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -3135,14 +3135,14 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Mobile and cross-device navigation overhaul</t>
+          <t>Homepage visual redesign: illustrations + interactivity</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>feat-mega-menu-navigation</t>
+          <t>feat-mobile-cross-device-navigation</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3179,14 +3179,14 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Mobile and cross-device navigation overhaul</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>feat-animated-interactive-mobile-menu</t>
+          <t>feat-mega-menu-navigation</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -3223,14 +3223,14 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Animated, interactive mobile menu with click-outside-to-close</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>feat-price-drop-alerts</t>
+          <t>feat-animated-interactive-mobile-menu</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3262,19 +3262,19 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Animated, interactive mobile menu with click-outside-to-close</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>feat-page-type-ux-redesign</t>
+          <t>feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -3306,19 +3306,19 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
         <v>49</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr"/>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>feat-footer-logo-interactivity</t>
+          <t>feat-page-type-ux-redesign</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3355,18 +3355,18 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3376,11 +3376,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
-        </is>
-      </c>
+      <c r="L60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
@@ -3388,33 +3384,33 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>content-refresh-best-broadband-tv-deals-guide</t>
+          <t>feat-footer-logo-interactivity</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Research-led editorial refresh: Best Broadband and TV Deals guide</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
         <v>48</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -3424,7 +3420,11 @@
       </c>
       <c r="J61" s="3" t="inlineStr"/>
       <c r="K61" s="3" t="inlineStr"/>
-      <c r="L61" s="3" t="inlineStr"/>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -3432,29 +3432,29 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>audit-core-web-vitals-reporting</t>
+          <t>content-refresh-best-broadband-tv-deals-guide</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Research-led editorial refresh: Best Broadband and TV Deals guide</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -3476,38 +3476,38 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>ops-awin-publisher-api-integration</t>
+          <t>audit-core-web-vitals-reporting</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Direct Awin Publisher API access — programme status and link generation</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
         <v>47</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr"/>
@@ -3520,38 +3520,38 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>ops-awin-publisher-api-integration</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Direct Awin Publisher API access — programme status and link generation</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G64" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="G64" s="2" t="n">
-        <v>58</v>
-      </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
@@ -3564,33 +3564,33 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>audit-broken-links-redirects</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -3608,33 +3608,33 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-broken-links-redirects</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -3662,19 +3662,19 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3706,19 +3706,19 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3734,8 +3734,52 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr"/>
+      <c r="K69" s="3" t="inlineStr"/>
+      <c r="L69" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L68"/>
+  <autoFilter ref="A1:L69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6487,7 +6531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7300,43 +7344,43 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Navigation/header/footer IA improvements</t>
+          <t>Content priority analysis: real SEO + GEO signals, build vs. update on one list</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Researched via scripts/scrape_navigation_patterns.py against 5 best-in-class sites. broadband.co.uk (closest single-vertical comparable) stood out on sticky header, breadcrumbs and a trust badge near the top; BroadbandPicker already matches on the first two. Header nav link count split cleanly into supersite (127-556 links) vs specialist (21 links) patterns, confirming the growth playbook's 'specialist, not supersite' positioning. Added Postcode to primary nav; restructured the footer from 4 to 6 columns (added Tools, Find Broadband by Area, Research) to fix a crawl/link-equity gap for the postcode-district and tools pages built this session.</t>
+          <t>User asked for a script that does detailed SEO analysis of the site's own data and prioritises what to build vs. update, weighting generative-AI/GEO reports specifically. Built scripts/analyze_content_priority.py: combines real mapped search volume already researched in docs/broadbandpicker-keyword-mapping.xlsx with a live crawl of every provider/comparison/guide page (word count against this session's own depth floors, FAQPage schema, a detectable answer-first paragraph, a parsed checked/reviewed date). Mid-build discovered the user's actual request: a real Google Search Console 'Performance on Search Generative AI Features' export had been dropped into data/GSC/, which is ground truth for AI Overview surfacing, not a proxy -- rebuilt the script to load and heavily weight it. Caught and fixed two real bugs before reporting any findings: word counts of 15k-17k+ caused by the React RSC hydration payload inside &lt;script&gt; tags being counted as visible text, and every page falsely flagging 'no answer-first paragraph' because the &lt;p&gt; search matched header mega-menu labels before reaching the main content -- both fixed by parsing with lxml, stripping script/style, and scoping to &lt;main&gt;. Real finding once the GSC data was wired in: /guides/best-full-fibre-broadband-uk earned 512 real AI-feature impressions in the last 28 days while sitting at 636 words, the clearest 'already working, just needs depth' signal on the site -- now the top-ranked refresh target, above even /providers/sky's 172,237 monthly search volume, since Sky currently earns almost no AI-feature traction (4 impressions) and represents a different kind of opportunity. Sky also does not appear in any of the 3 Awin relationship lists at all (joined/pending/rejected), confirmed via a direct re-check -- no record of ever applying. Every row in the Content Gap Roadmap is already marked built (33/33), so there are currently no new-page gaps on the existing curated keyword list. Findings written up in docs/content-priority-analysis.md.</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>60</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>app/layout.tsx</t>
+          <t>scripts/analyze_content_priority.py</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>docs/broadbandpicker-keyword-mapping.xlsx (existing keyword research)</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -7346,7 +7390,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-22 — researched before implementing per the Strategic Lens process</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7361,24 +7405,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Working contact form delivering to a real inbox, no third-party service</t>
+          <t>Navigation/header/footer IA improvements</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Previously /contact only offered mailto: links to unverified custom-domain addresses (editorial@/partnerships@/hello@broadbandpicker.co.uk). Built a real contact form (components/ContactForm.tsx) posting to a new app/api/contact route, which sends via Gmail SMTP using nodemailer — no Supabase, no database, no third-party form/CRM service, per explicit instruction. All submissions land in sayedsahil.elt@gmail.com (CONTACT_TO_EMAIL env var), sent from a Gmail account authenticated with an App Password (CONTACT_SMTP_USER / CONTACT_SMTP_PASS). Reply-To is set to the sender's own address so replying goes straight back to them. Spam mitigation without any external service: a hidden honeypot field (bots that fill every input get silently dropped) and a submit-time check rejecting anything sent under 1.5s after the form rendered. Server-side validates name/email/reason/message independently of the client. The original mailto: cards are kept underneath as a secondary direct-email option. Requires CONTACT_SMTP_USER/PASS to be set in Vercel — the API route fails gracefully with a friendly error and a server log line if they're absent, rather than silently dropping messages.</t>
+          <t>Researched via scripts/scrape_navigation_patterns.py against 5 best-in-class sites. broadband.co.uk (closest single-vertical comparable) stood out on sticky header, breadcrumbs and a trust badge near the top; BroadbandPicker already matches on the first two. Header nav link count split cleanly into supersite (127-556 links) vs specialist (21 links) patterns, confirming the growth playbook's 'specialist, not supersite' positioning. Added Postcode to primary nav; restructured the footer from 4 to 6 columns (added Tools, Find Broadband by Area, Research) to fix a crawl/link-equity gap for the postcode-district and tools pages built this session.</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
         <v>55</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -7387,22 +7431,22 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>app/api/contact/route.ts, components/ContactForm.tsx, app/contact/page.tsx</t>
+          <t>app/layout.tsx</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SMTP_USER / CONTACT_SMTP_PASS Gmail App Password set in Vercel env vars</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>User request 2026-08-22 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7412,48 +7456,48 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Deep, researched content for Awin-pending providers (Community Fibre, Cuckoo, Zen Internet, National Broadband, Trooli, Pine Media)</t>
+          <t>Working contact form delivering to a real inbox, no third-party service</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Follow-up to content-awin-approved-provider-deep-content, extending the same research process to the 6 real UK-relevant advertisers pending Awin approval (Sky ROI excluded -- Republic of Ireland Sky, not UK, out of scope for a UK site, confirmed with the user). Community Fibre and Zen Internet were existing but thin entries, fully rewritten. Cuckoo was already deep and dated the previous day; verified rather than rewritten. National Broadband, Trooli and Pine Media were brand-new Provider entries. National Broadband is the site's first 4G/5G fixed-wireless provider (a genuinely new content category, not another fibre altnet); Pine Media is a hyperlocal single-city (Sheffield-only) provider with a two-tier product split (its own symmetrical GIG network vs an Openreach-based GLO product) that needed explaining clearly to avoid conflating the two. Key design decision: because these programmes are pending, not joined, affiliateUrl stays as each provider's own plain site URL rather than an Awin tracking link -- confirmed via a live API test that Awin's linkbuilder will generate a structurally valid tracking URL even for a pending programme, which would be misleading to publish since it likely would not earn commission (or could breach Awin's terms) before approval. Each reviewSources array carries an explicit 'pending, not yet approved' note on the Awin source, matching the existing Gigaclear convention. All copy hand-checked for zero em dashes and zero banned AI-tell vocabulary/phrases. Three new comparison pages, chosen for genuine evidentiary value over one-per-provider completeness: community-fibre-vs-hyperoptic (London's two biggest symmetrical altnets, direct competitors), trooli-vs-zzoomm (two multi-region altnets with near-zero coverage overlap and matching no-price-rise policies), and national-broadband-vs-highland-broadband (5G available now vs fibre still being built -- a genuine buy-now-or-wait decision for the same rural Scottish customer). Cuckoo, Zen Internet and Pine Media were deliberately left without a new comparison this round -- no natural, non-forced head-to-head partner existed for any of them without inventing artificial relevance.</t>
+          <t>Previously /contact only offered mailto: links to unverified custom-domain addresses (editorial@/partnerships@/hello@broadbandpicker.co.uk). Built a real contact form (components/ContactForm.tsx) posting to a new app/api/contact route, which sends via Gmail SMTP using nodemailer — no Supabase, no database, no third-party form/CRM service, per explicit instruction. All submissions land in sayedsahil.elt@gmail.com (CONTACT_TO_EMAIL env var), sent from a Gmail account authenticated with an App Password (CONTACT_SMTP_USER / CONTACT_SMTP_PASS). Reply-To is set to the sender's own address so replying goes straight back to them. Spam mitigation without any external service: a hidden honeypot field (bots that fill every input get silently dropped) and a submit-time check rejecting anything sent under 1.5s after the form rendered. Server-side validates name/email/reason/message independently of the client. The original mailto: cards are kept underneath as a secondary direct-email option. Requires CONTACT_SMTP_USER/PASS to be set in Vercel — the API route fails gracefully with a friendly error and a server log line if they're absent, rather than silently dropping messages.</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
         <v>55</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>data/providers.ts (community-fibre, cuckoo, zen-internet, national-broadband, trooli, pine-media), data/provider-comparisons.ts (community-fibre-vs-hyperoptic, trooli-vs-zzoomm, national-broadband-vs-highland-broadband), public/logos/national-broadband.svg, public/logos/trooli.svg, public/logos/pine-media.svg</t>
+          <t>app/api/contact/route.ts, components/ContactForm.tsx, app/contact/page.tsx</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>content-awin-approved-provider-deep-content, ops-awin-publisher-api-integration</t>
+          <t>CONTACT_SMTP_USER / CONTACT_SMTP_PASS Gmail App Password set in Vercel env vars</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -7468,7 +7512,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -7478,43 +7522,43 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Run original-research outreach and digital PR</t>
+          <t>Deep, researched content for Awin-pending providers (Community Fibre, Cuckoo, Zen Internet, National Broadband, Trooli, Pine Media)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Build a relevant outreach list and earn citations and links to the live Ofcom-backed customer-satisfaction research.</t>
+          <t>Follow-up to content-awin-approved-provider-deep-content, extending the same research process to the 6 real UK-relevant advertisers pending Awin approval (Sky ROI excluded -- Republic of Ireland Sky, not UK, out of scope for a UK site, confirmed with the user). Community Fibre and Zen Internet were existing but thin entries, fully rewritten. Cuckoo was already deep and dated the previous day; verified rather than rewritten. National Broadband, Trooli and Pine Media were brand-new Provider entries. National Broadband is the site's first 4G/5G fixed-wireless provider (a genuinely new content category, not another fibre altnet); Pine Media is a hyperlocal single-city (Sheffield-only) provider with a two-tier product split (its own symmetrical GIG network vs an Openreach-based GLO product) that needed explaining clearly to avoid conflating the two. Key design decision: because these programmes are pending, not joined, affiliateUrl stays as each provider's own plain site URL rather than an Awin tracking link -- confirmed via a live API test that Awin's linkbuilder will generate a structurally valid tracking URL even for a pending programme, which would be misleading to publish since it likely would not earn commission (or could breach Awin's terms) before approval. Each reviewSources array carries an explicit 'pending, not yet approved' note on the Awin source, matching the existing Gigaclear convention. All copy hand-checked for zero em dashes and zero banned AI-tell vocabulary/phrases. Three new comparison pages, chosen for genuine evidentiary value over one-per-provider completeness: community-fibre-vs-hyperoptic (London's two biggest symmetrical altnets, direct competitors), trooli-vs-zzoomm (two multi-region altnets with near-zero coverage overlap and matching no-price-rise policies), and national-broadband-vs-highland-broadband (5G available now vs fibre still being built -- a genuine buy-now-or-wait decision for the same rural Scottish customer). Cuckoo, Zen Internet and Pine Media were deliberately left without a new comparison this round -- no natural, non-forced head-to-head partner existed for any of them without inventing artificial relevance.</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>/research/uk-broadband-customer-satisfaction</t>
+          <t>data/providers.ts (community-fibre, cuckoo, zen-internet, national-broadband, trooli, pine-media), data/provider-comparisons.ts (community-fibre-vs-hyperoptic, trooli-vs-zzoomm, national-broadband-vs-highland-broadband), public/logos/national-broadband.svg, public/logos/trooli.svg, public/logos/pine-media.svg</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Research page and source methodology are live</t>
+          <t>content-awin-approved-provider-deep-content, ops-awin-publisher-api-integration</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Build Status / 90 Day Roadmap</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7524,29 +7568,29 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
+          <t>Run original-research outreach and digital PR</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Review query/page performance, assisted conversions, Awin decisions and engagement data, then record the next-quarter build decisions.</t>
+          <t>Build a relevant outreach list and earn citations and links to the live Ofcom-backed customer-satisfaction research.</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -7555,22 +7599,22 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Next-quarter decision log</t>
+          <t>/research/uk-broadband-customer-satisfaction</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>ops-conversion-reporting-loop and sufficient observation period</t>
+          <t>Research page and source methodology are live</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: 90 Day Roadmap</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Build Status / 90 Day Roadmap</t>
         </is>
       </c>
     </row>
@@ -7580,29 +7624,29 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>User asked for a postcode -&gt; select-your-house-number address picker with customised content, and explicitly asked whether it could be built free. Researched live (WebSearch, 2026-08-23): full UK address-level lookup (the data behind 'pick your house from a list') is Royal Mail's licensed PAF data, not open -- getAddress.io, a popular free-tier provider, was shut down in Oct 2025 after a Royal Mail/IDDQD IP claim; Ideal Postcodes gives a 1-month/50-credit trial then pay-as-you-go; no provider offers a genuine unlimited free tier at real traffic. Separately, even a working address picker wouldn't improve accuracy without a paid per-address line-checker API (Openreach or provider-specific), which is a commercial relationship, not a script. Presented both findings and 3 options to the user via AskUserQuestion; they chose the free path: deepen personalisation using data already held, no new API, no new cost. Shipped: extended the existing components/PostcodeContextBar.tsx (previously only on deals/compare/provider pages) to guide pages and all 3 tool pages (speed test, broadband match, cost calculator) so a stored postcode follows the visitor through the full journey; new components/ProviderAvailabilityBadge.tsx shows a real yes/no ('BT is/isn't listed as available in {town}') on provider review pages, but only for the 51 postcode areas with real availableProviders data in data/postcodes.ts -- silently renders nothing outside that set rather than guessing; new components/ReturningVisitorBanner.tsx greets a returning visitor on the homepage with a direct link back to their own postcode's deals.</t>
+          <t>Review query/page performance, assisted conversions, Awin decisions and engagement data, then record the next-quarter build decisions.</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
         <v>53</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -7611,22 +7655,22 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>components/ProviderAvailabilityBadge.tsx, components/ReturningVisitorBanner.tsx, components/PostcodeContextBar.tsx, app/page.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/speed-test/page.tsx, app/tools/broadband-match/page.tsx, app/tools/broadband-cost-calculator/page.tsx</t>
+          <t>Next-quarter decision log</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>None -- deliberately built on data already held, no new API/cost</t>
+          <t>ops-conversion-reporting-loop and sufficient observation period</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: 90 Day Roadmap</t>
         </is>
       </c>
     </row>
@@ -7646,16 +7690,16 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Homepage visual redesign: illustrations + interactivity</t>
+          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Researched via scripts/analyze_homepage_visual_design.py against 5 UK broadband comparison homepages: none uses stock-photo hero banners; the dominant visual language is heavy inline SVG (Uswitch ships 195) and provider logos, no carousel/animation library detected anywhere. Generated 7 original on-brand SVG illustrations (scripts/generate_homepage_illustrations.py: hero network graphic, 3 colour-filled step icons, 2 gradient blobs, a quiz illustration) rather than stock photography, matching what's actually proven in this vertical. Added a scroll-reveal component, hover interactions, and restructured the Broadband Match promo to a two-column illustrated layout. Content/copy unchanged, visual/UX only.</t>
+          <t>User asked for a postcode -&gt; select-your-house-number address picker with customised content, and explicitly asked whether it could be built free. Researched live (WebSearch, 2026-08-23): full UK address-level lookup (the data behind 'pick your house from a list') is Royal Mail's licensed PAF data, not open -- getAddress.io, a popular free-tier provider, was shut down in Oct 2025 after a Royal Mail/IDDQD IP claim; Ideal Postcodes gives a 1-month/50-credit trial then pay-as-you-go; no provider offers a genuine unlimited free tier at real traffic. Separately, even a working address picker wouldn't improve accuracy without a paid per-address line-checker API (Openreach or provider-specific), which is a commercial relationship, not a script. Presented both findings and 3 options to the user via AskUserQuestion; they chose the free path: deepen personalisation using data already held, no new API, no new cost. Shipped: extended the existing components/PostcodeContextBar.tsx (previously only on deals/compare/provider pages) to guide pages and all 3 tool pages (speed test, broadband match, cost calculator) so a stored postcode follows the visitor through the full journey; new components/ProviderAvailabilityBadge.tsx shows a real yes/no ('BT is/isn't listed as available in {town}') on provider review pages, but only for the 51 postcode areas with real availableProviders data in data/postcodes.ts -- silently renders nothing outside that set rather than guessing; new components/ReturningVisitorBanner.tsx greets a returning visitor on the homepage with a direct link back to their own postcode's deals.</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>55</v>
@@ -7667,12 +7711,12 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>app/page.tsx, components/ScrollReveal.tsx, public/illustrations/</t>
+          <t>components/ProviderAvailabilityBadge.tsx, components/ReturningVisitorBanner.tsx, components/PostcodeContextBar.tsx, app/page.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/speed-test/page.tsx, app/tools/broadband-match/page.tsx, app/tools/broadband-cost-calculator/page.tsx</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None -- deliberately built on data already held, no new API/cost</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -7702,19 +7746,19 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Mobile and cross-device navigation overhaul</t>
+          <t>Homepage visual redesign: illustrations + interactivity</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>New scripts/analyze_mobile_ux.py scanned Uswitch, broadband.co.uk and choose.co.uk (MoneySavingExpert 403, reported not bypassed) with a mobile Safari user agent for markup/CSS signals: viewport meta and hamburger menu markers were universal but already correct on our own site; tel: click-to-call was absent everywhere (0/4, skipped); sticky bottom CTA (1/4) and apple-touch-icon (2/4) were too weak/incomplete to act on. The real gap was found by direct inspection, not the scan: the mobile nav was a small anchored dropdown of 10 flat links with ~36px touch targets, while the desktop nav beside it was a full mega-menu, and the header postcode checker was desktop-only so phone users had no quick postcode access outside the homepage/deals page. Replaced it with new components/MobileNav.tsx: a full-width slide-down panel reusing the desktop mega-menu's own icon/link data (exported from MainNav.tsx, so the two can't drift apart), every link at a 44px (min-h-11) touch target, and the postcode checker embedded at the top so it's reachable from any page. Added anchor ids to /guides category sections so the new mobile Guides menu jumps to a real target instead of an unread query param.</t>
+          <t>Researched via scripts/analyze_homepage_visual_design.py against 5 UK broadband comparison homepages: none uses stock-photo hero banners; the dominant visual language is heavy inline SVG (Uswitch ships 195) and provider logos, no carousel/animation library detected anywhere. Generated 7 original on-brand SVG illustrations (scripts/generate_homepage_illustrations.py: hero network graphic, 3 colour-filled step icons, 2 gradient blobs, a quiz illustration) rather than stock photography, matching what's actually proven in this vertical. Added a scroll-reveal component, hover interactions, and restructured the Broadband Match promo to a two-column illustrated layout. Content/copy unchanged, visual/UX only.</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -7723,7 +7767,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>components/MobileNav.tsx, components/MainNav.tsx, app/layout.tsx, app/guides/page.tsx</t>
+          <t>app/page.tsx, components/ScrollReveal.tsx, public/illustrations/</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7758,19 +7802,19 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Mobile and cross-device navigation overhaul</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
+          <t>New scripts/analyze_mobile_ux.py scanned Uswitch, broadband.co.uk and choose.co.uk (MoneySavingExpert 403, reported not bypassed) with a mobile Safari user agent for markup/CSS signals: viewport meta and hamburger menu markers were universal but already correct on our own site; tel: click-to-call was absent everywhere (0/4, skipped); sticky bottom CTA (1/4) and apple-touch-icon (2/4) were too weak/incomplete to act on. The real gap was found by direct inspection, not the scan: the mobile nav was a small anchored dropdown of 10 flat links with ~36px touch targets, while the desktop nav beside it was a full mega-menu, and the header postcode checker was desktop-only so phone users had no quick postcode access outside the homepage/deals page. Replaced it with new components/MobileNav.tsx: a full-width slide-down panel reusing the desktop mega-menu's own icon/link data (exported from MainNav.tsx, so the two can't drift apart), every link at a 44px (min-h-11) touch target, and the postcode checker embedded at the top so it's reachable from any page. Added anchor ids to /guides category sections so the new mobile Guides menu jumps to a real target instead of an unread query param.</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -7779,7 +7823,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>components/MainNav.tsx, app/layout.tsx</t>
+          <t>components/MobileNav.tsx, components/MainNav.tsx, app/layout.tsx, app/guides/page.tsx</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -7814,19 +7858,19 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Animated, interactive mobile menu with click-outside-to-close</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Direct UX/interaction-design request, not a scraping pass. Rewrote components/MobileNav.tsx from a native &lt;details&gt; element (no animation, no click-outside-to-close) to a controlled client component: hamburger icon morphs into an X on open; a blurred backdrop closes the menu on click or Escape; the panel and its sections slide/fade in with a staggered delay reusing the same transition idiom as components/ScrollReveal.tsx; Providers/Postcode/Guides/Tools became single-open accordions using a CSS-only grid-template-rows 0fr-&gt;1fr transition (no JS height measurement); the menu auto-closes on route change via usePathname(); background scroll is locked while open; focus moves into the panel on open and returns to the trigger on Escape. Global prefers-reduced-motion handling already in app/globals.css applies automatically. Not visually verified on a real device — no browser automation tool available this session, validated via build output, generated CSS and server-rendered markup only.</t>
+          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
         <v>50</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -7835,7 +7879,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>components/MobileNav.tsx</t>
+          <t>components/MainNav.tsx, app/layout.tsx</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7865,24 +7909,24 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Animated, interactive mobile menu with click-outside-to-close</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
+          <t>Direct UX/interaction-design request, not a scraping pass. Rewrote components/MobileNav.tsx from a native &lt;details&gt; element (no animation, no click-outside-to-close) to a controlled client component: hamburger icon morphs into an X on open; a blurred backdrop closes the menu on click or Escape; the panel and its sections slide/fade in with a staggered delay reusing the same transition idiom as components/ScrollReveal.tsx; Providers/Postcode/Guides/Tools became single-open accordions using a CSS-only grid-template-rows 0fr-&gt;1fr transition (no JS height measurement); the menu auto-closes on route change via usePathname(); background scroll is locked while open; focus moves into the panel on open and returns to the trigger on Escape. Global prefers-reduced-motion handling already in app/globals.css applies automatically. Not visually verified on a real device — no browser automation tool available this session, validated via build output, generated CSS and server-rendered markup only.</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -7891,22 +7935,22 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
+          <t>components/MobileNav.tsx</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>Email delivery provider</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7921,24 +7965,24 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
+          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
         <v>49</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -7947,22 +7991,22 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
+          <t>New subscription flow + data/provider-live-deals.json</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Email delivery provider</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>Growth playbook — Functionality pillar</t>
         </is>
       </c>
     </row>
@@ -7982,28 +8026,28 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
+          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>app/layout.tsx, components/Logo.tsx</t>
+          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -8028,38 +8072,38 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Research-led editorial refresh: Best Broadband and TV Deals guide</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>User-requested application of the same Stage 3/4/4a research process from the Awin content batches to a single existing guide page, /guides/best-broadband-and-tv-deals. Unlike the thin provider stubs rewritten in the Awin batches, this guide was already well-built (tables, methodology, 7 FAQs, real Ofcom citations, last checked 29 July 2026) -- not a stub needing a ground-up rewrite, so this was a verify-and-deepen pass grounded in fresh research rather than a full replacement. Scraped 2 top-ranking competitors (MoneySuperMarket, Uswitch) per Stage 3.0: found MoneySupermarket runs a 15-question FAQ (ours had 7) and leads with an expert-quoted bundling-savings statistic. Traced that claim to its actual primary source rather than citing the secondary restatement: Ofcom's own February 2026 research, savings of £26-£48/month from bundling and pay-TV averaging £12/month within a bundle (23% real-terms fall) -- a stronger, more current, primary-sourced figure than the competitor's 2023-dated stat, added as a new section. Also found and added two genuinely new, specific facts the page didn't have: Virgin Media's Max Volt bundle (real current pricing including its two scheduled rises to April 2028) as a concrete worked example, and Virgin Media's 'Most Reliable Broadband Provider' win at the 2026 Uswitch Telecoms Awards (Opensignal-verified, a genuine third-party measurement). Named the specific Sky bundle example (Sky Stream, Sky TV, Netflix + Full Fibre 300, £35/month) that the existing copy referenced only vaguely. Added 2 new FAQs tied to the new content. Fixed 2 pre-existing em dashes found during the pass (a legitimate en-dash numeric range, '50-100Mbps', was left alone -- not an AI-tell, different typographic use). Updated the page's stated fact-check date and guides.ts updatedDate to 2026-08-24.</t>
+          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
         <v>48</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>app/guides/[slug]/page.tsx (best-broadband-and-tv-deals), data/guides.ts</t>
+          <t>app/layout.tsx, components/Logo.tsx</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8074,7 +8118,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8084,29 +8128,29 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Research-led editorial refresh: Best Broadband and TV Deals guide</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
+          <t>User-requested application of the same Stage 3/4/4a research process from the Awin content batches to a single existing guide page, /guides/best-broadband-and-tv-deals. Unlike the thin provider stubs rewritten in the Awin batches, this guide was already well-built (tables, methodology, 7 FAQs, real Ofcom citations, last checked 29 July 2026) -- not a stub needing a ground-up rewrite, so this was a verify-and-deepen pass grounded in fresh research rather than a full replacement. Scraped 2 top-ranking competitors (MoneySuperMarket, Uswitch) per Stage 3.0: found MoneySupermarket runs a 15-question FAQ (ours had 7) and leads with an expert-quoted bundling-savings statistic. Traced that claim to its actual primary source rather than citing the secondary restatement: Ofcom's own February 2026 research, savings of £26-£48/month from bundling and pay-TV averaging £12/month within a bundle (23% real-terms fall) -- a stronger, more current, primary-sourced figure than the competitor's 2023-dated stat, added as a new section. Also found and added two genuinely new, specific facts the page didn't have: Virgin Media's Max Volt bundle (real current pricing including its two scheduled rises to April 2028) as a concrete worked example, and Virgin Media's 'Most Reliable Broadband Provider' win at the 2026 Uswitch Telecoms Awards (Opensignal-verified, a genuine third-party measurement). Named the specific Sky bundle example (Sky Stream, Sky TV, Netflix + Full Fibre 300, £35/month) that the existing copy referenced only vaguely. Added 2 new FAQs tied to the new content. Fixed 2 pre-existing em dashes found during the pass (a legitimate en-dash numeric range, '50-100Mbps', was left alone -- not an AI-tell, different typographic use). Updated the page's stated fact-check date and guides.ts updatedDate to 2026-08-24.</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
@@ -8115,22 +8159,22 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Sitewide template performance report</t>
+          <t>app/guides/[slug]/page.tsx (best-broadband-and-tv-deals), data/guides.ts</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>Field data or representative lab baselines</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8140,53 +8184,53 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Direct Awin Publisher API access — programme status and link generation</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>User asked to connect Claude to their Awin account and provided a real API token. There's no one-click connector for Awin (unlike Google Drive/Gmail), so this uses Awin's own Publisher API directly. First live run corrected two wrong assumptions from documentation research: 'programmedetails' requires a specific advertiserId (not a bulk listing endpoint) -- the actual bulk-status endpoint is GET /publishers/{id}/programmes?relationship=X, and 'any' is not a valid value for it (loops joined/pending/suspended/rejected instead; 'notjoined' returns the ~21k whole-platform catalogue so it's excluded from the default and only fetched on request). POST /publishers/{id}/linkbuilder/generate confirmed working, verified against TalkTalk (advertiser 3674). REAL FINDING from the first run, both surfaced to the user and worth acting on: only 4 programmes are joined (TalkTalk, Broadband Genie, Zzoomm, Highland Broadband), 7 pending (Sky ROI, Community Fibre, National Broadband, Trooli, Pine Media, Cuckoo, Zen Internet), and 9 REJECTED including BT (both consumer and business), Vodafone, Plusnet, EE, Virgin Media, Hyperoptic and toob. Cross-checked data/providers.ts: none of the currently-live affiliateUrl values (including TalkTalk, which IS approved) use Awin's awin1.com tracking format -- they're all plain provider URLs, so the site is very likely not earning commission on any current outbound click, joined or not, despite the on-page commercial disclosures implying it might.</t>
+          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
         <v>47</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>scripts/awin_sync.py</t>
+          <t>Sitewide template performance report</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>AWIN_API_TOKEN from the user's Awin account (user menu -&gt; API Credentials)</t>
+          <t>Field data or representative lab baselines</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -8196,53 +8240,53 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Direct Awin Publisher API access — programme status and link generation</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+          <t>User asked to connect Claude to their Awin account and provided a real API token. There's no one-click connector for Awin (unlike Google Drive/Gmail), so this uses Awin's own Publisher API directly. First live run corrected two wrong assumptions from documentation research: 'programmedetails' requires a specific advertiserId (not a bulk listing endpoint) -- the actual bulk-status endpoint is GET /publishers/{id}/programmes?relationship=X, and 'any' is not a valid value for it (loops joined/pending/suspended/rejected instead; 'notjoined' returns the ~21k whole-platform catalogue so it's excluded from the default and only fetched on request). POST /publishers/{id}/linkbuilder/generate confirmed working, verified against TalkTalk (advertiser 3674). REAL FINDING from the first run, both surfaced to the user and worth acting on: only 4 programmes are joined (TalkTalk, Broadband Genie, Zzoomm, Highland Broadband), 7 pending (Sky ROI, Community Fibre, National Broadband, Trooli, Pine Media, Cuckoo, Zen Internet), and 9 REJECTED including BT (both consumer and business), Vodafone, Plusnet, EE, Virgin Media, Hyperoptic and toob. Cross-checked data/providers.ts: none of the currently-live affiliateUrl values (including TalkTalk, which IS approved) use Awin's awin1.com tracking format -- they're all plain provider URLs, so the site is very likely not earning commission on any current outbound click, joined or not, despite the on-page commercial disclosures implying it might.</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G31" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="G31" s="3" t="n">
-        <v>58</v>
-      </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>scripts/awin_sync.py</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>AWIN_API_TOKEN from the user's Awin account (user menu -&gt; API Credentials)</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8252,43 +8296,43 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
+          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Sitewide crawl and redirect report</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -8298,7 +8342,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -8308,43 +8352,43 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide crawl and redirect report</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
@@ -8354,7 +8398,7 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -8369,24 +8413,24 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -8395,12 +8439,12 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -8410,7 +8454,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -8425,53 +8469,109 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="F36" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G35" s="3" t="n">
+      <c r="G36" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L35" s="3" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L35"/>
+  <autoFilter ref="A1:L36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8512,7 +8612,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>67 total (33 page builds, 34 feature/strategy builds); 53 already marked Done.</t>
+          <t>68 total (33 page builds, 35 feature/strategy builds); 54 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -176,8 +176,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L69" headerRowCount="1">
-  <autoFilter ref="A1:L69"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L70" headerRowCount="1">
+  <autoFilter ref="A1:L70"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -241,8 +241,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L36" headerRowCount="1">
-  <autoFilter ref="A1:L36"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L37" headerRowCount="1">
+  <autoFilter ref="A1:L37"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3032,29 +3032,29 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>growth-quarterly-data-reprioritisation</t>
+          <t>content-refresh-best-full-fibre-guide</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
+          <t>Deep rewrite: Best Full Fibre Broadband UK guide (top content-priority-analysis target)</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr"/>
@@ -3076,29 +3076,29 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>feat-postcode-journey-personalisation</t>
+          <t>growth-quarterly-data-reprioritisation</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>feat-homepage-visual-redesign</t>
+          <t>feat-postcode-journey-personalisation</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -3135,11 +3135,11 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Homepage visual redesign: illustrations + interactivity</t>
+          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G55" s="3" t="n">
         <v>55</v>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>feat-mobile-cross-device-navigation</t>
+          <t>feat-homepage-visual-redesign</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3179,14 +3179,14 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Mobile and cross-device navigation overhaul</t>
+          <t>Homepage visual redesign: illustrations + interactivity</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>feat-mega-menu-navigation</t>
+          <t>feat-mobile-cross-device-navigation</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -3223,14 +3223,14 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Mobile and cross-device navigation overhaul</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>feat-animated-interactive-mobile-menu</t>
+          <t>feat-mega-menu-navigation</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3267,14 +3267,14 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Animated, interactive mobile menu with click-outside-to-close</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
         <v>50</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>feat-price-drop-alerts</t>
+          <t>feat-animated-interactive-mobile-menu</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -3306,19 +3306,19 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Animated, interactive mobile menu with click-outside-to-close</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr"/>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>feat-page-type-ux-redesign</t>
+          <t>feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3350,19 +3350,19 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
         <v>49</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>feat-footer-logo-interactivity</t>
+          <t>feat-page-type-ux-redesign</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -3399,18 +3399,18 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -3420,11 +3420,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr"/>
       <c r="K61" s="3" t="inlineStr"/>
-      <c r="L61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
-        </is>
-      </c>
+      <c r="L61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -3432,33 +3428,33 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>content-refresh-best-broadband-tv-deals-guide</t>
+          <t>feat-footer-logo-interactivity</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Research-led editorial refresh: Best Broadband and TV Deals guide</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
         <v>48</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3468,7 +3464,11 @@
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
@@ -3476,29 +3476,29 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>audit-core-web-vitals-reporting</t>
+          <t>content-refresh-best-broadband-tv-deals-guide</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Research-led editorial refresh: Best Broadband and TV Deals guide</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr"/>
@@ -3520,38 +3520,38 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>ops-awin-publisher-api-integration</t>
+          <t>audit-core-web-vitals-reporting</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Direct Awin Publisher API access — programme status and link generation</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
         <v>47</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
@@ -3564,38 +3564,38 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>ops-awin-publisher-api-integration</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Direct Awin Publisher API access — programme status and link generation</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G65" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="G65" s="3" t="n">
-        <v>58</v>
-      </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr"/>
@@ -3608,33 +3608,33 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>audit-broken-links-redirects</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3652,33 +3652,33 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-broken-links-redirects</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3706,19 +3706,19 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -3750,19 +3750,19 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
@@ -3778,8 +3778,52 @@
       <c r="K69" s="3" t="inlineStr"/>
       <c r="L69" s="3" t="inlineStr"/>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L69"/>
+  <autoFilter ref="A1:L70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4665,7 +4709,7 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="31" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
@@ -4766,7 +4810,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -4820,7 +4864,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -4874,7 +4918,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4928,7 +4972,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -4982,7 +5026,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -5036,7 +5080,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -5090,7 +5134,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5144,7 +5188,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -5198,7 +5242,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5252,7 +5296,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -5306,7 +5350,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5360,7 +5404,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -5414,7 +5458,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5468,7 +5512,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -5522,7 +5566,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5576,7 +5620,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -5630,7 +5674,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -5684,7 +5728,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -5738,7 +5782,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5792,7 +5836,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -5846,7 +5890,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5900,7 +5944,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -5954,7 +5998,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -6008,7 +6052,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -6062,7 +6106,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6116,7 +6160,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -6170,7 +6214,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -6224,7 +6268,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -6278,7 +6322,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -6332,7 +6376,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -6386,7 +6430,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -6440,7 +6484,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -6494,7 +6538,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Committed</t>
+          <t>Live but not committed to git</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -6531,7 +6575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7624,29 +7668,29 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
+          <t>Deep rewrite: Best Full Fibre Broadband UK guide (top content-priority-analysis target)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Review query/page performance, assisted conversions, Awin decisions and engagement data, then record the next-quarter build decisions.</t>
+          <t>Top-ranked target from scripts/analyze_content_priority.py's first real run: 512 AI-feature impressions in the last 28 days (real GSC data) at only 636 words. Fully rewritten to 1,596 words, drawing on already-verified provider facts from the three Awin content batches (BT, EE, Vodafone, Plusnet, Community Fibre, Hyperoptic, toob, Zen Internet) plus new research for Sky and a genuinely counter-intuitive finding worth surfacing on its own: every major national provider has a low Trustpilot score, but Ofcom's Q1 2026 complaints data separates them clearly (Plusnet best at 4/100k, TalkTalk worst at 10/100k) -- explained as two measures of different things, not a contradiction. Also verified and included Vodafone's real 2026 award wins (Expert Reviews Broadband Awards, Uswitch Most Popular Provider) alongside its poor Ofcom complaints position, rather than picking one narrative. Caught and fixed a real bug before shipping: wrote several apostrophes as literal backslash-escapes ( \' ) copying the .ts string-literal habit from data/providers.ts into JSX text content, where they would have rendered as a visible backslash -- fixed to the file's existing &amp;apos; convention and verified against the live rendered HTML, not just the build passing, before considering it done.</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -7655,22 +7699,22 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Next-quarter decision log</t>
+          <t>app/guides/[slug]/page.tsx (best-full-fibre-broadband-uk), data/guides.ts</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>ops-conversion-reporting-loop and sufficient observation period</t>
+          <t>ops-content-priority-analysis-tooling</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: 90 Day Roadmap</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7680,29 +7724,29 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>User asked for a postcode -&gt; select-your-house-number address picker with customised content, and explicitly asked whether it could be built free. Researched live (WebSearch, 2026-08-23): full UK address-level lookup (the data behind 'pick your house from a list') is Royal Mail's licensed PAF data, not open -- getAddress.io, a popular free-tier provider, was shut down in Oct 2025 after a Royal Mail/IDDQD IP claim; Ideal Postcodes gives a 1-month/50-credit trial then pay-as-you-go; no provider offers a genuine unlimited free tier at real traffic. Separately, even a working address picker wouldn't improve accuracy without a paid per-address line-checker API (Openreach or provider-specific), which is a commercial relationship, not a script. Presented both findings and 3 options to the user via AskUserQuestion; they chose the free path: deepen personalisation using data already held, no new API, no new cost. Shipped: extended the existing components/PostcodeContextBar.tsx (previously only on deals/compare/provider pages) to guide pages and all 3 tool pages (speed test, broadband match, cost calculator) so a stored postcode follows the visitor through the full journey; new components/ProviderAvailabilityBadge.tsx shows a real yes/no ('BT is/isn't listed as available in {town}') on provider review pages, but only for the 51 postcode areas with real availableProviders data in data/postcodes.ts -- silently renders nothing outside that set rather than guessing; new components/ReturningVisitorBanner.tsx greets a returning visitor on the homepage with a direct link back to their own postcode's deals.</t>
+          <t>Review query/page performance, assisted conversions, Awin decisions and engagement data, then record the next-quarter build decisions.</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
         <v>53</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -7711,22 +7755,22 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>components/ProviderAvailabilityBadge.tsx, components/ReturningVisitorBanner.tsx, components/PostcodeContextBar.tsx, app/page.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/speed-test/page.tsx, app/tools/broadband-match/page.tsx, app/tools/broadband-cost-calculator/page.tsx</t>
+          <t>Next-quarter decision log</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>None -- deliberately built on data already held, no new API/cost</t>
+          <t>ops-conversion-reporting-loop and sufficient observation period</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: 90 Day Roadmap</t>
         </is>
       </c>
     </row>
@@ -7746,16 +7790,16 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Homepage visual redesign: illustrations + interactivity</t>
+          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Researched via scripts/analyze_homepage_visual_design.py against 5 UK broadband comparison homepages: none uses stock-photo hero banners; the dominant visual language is heavy inline SVG (Uswitch ships 195) and provider logos, no carousel/animation library detected anywhere. Generated 7 original on-brand SVG illustrations (scripts/generate_homepage_illustrations.py: hero network graphic, 3 colour-filled step icons, 2 gradient blobs, a quiz illustration) rather than stock photography, matching what's actually proven in this vertical. Added a scroll-reveal component, hover interactions, and restructured the Broadband Match promo to a two-column illustrated layout. Content/copy unchanged, visual/UX only.</t>
+          <t>User asked for a postcode -&gt; select-your-house-number address picker with customised content, and explicitly asked whether it could be built free. Researched live (WebSearch, 2026-08-23): full UK address-level lookup (the data behind 'pick your house from a list') is Royal Mail's licensed PAF data, not open -- getAddress.io, a popular free-tier provider, was shut down in Oct 2025 after a Royal Mail/IDDQD IP claim; Ideal Postcodes gives a 1-month/50-credit trial then pay-as-you-go; no provider offers a genuine unlimited free tier at real traffic. Separately, even a working address picker wouldn't improve accuracy without a paid per-address line-checker API (Openreach or provider-specific), which is a commercial relationship, not a script. Presented both findings and 3 options to the user via AskUserQuestion; they chose the free path: deepen personalisation using data already held, no new API, no new cost. Shipped: extended the existing components/PostcodeContextBar.tsx (previously only on deals/compare/provider pages) to guide pages and all 3 tool pages (speed test, broadband match, cost calculator) so a stored postcode follows the visitor through the full journey; new components/ProviderAvailabilityBadge.tsx shows a real yes/no ('BT is/isn't listed as available in {town}') on provider review pages, but only for the 51 postcode areas with real availableProviders data in data/postcodes.ts -- silently renders nothing outside that set rather than guessing; new components/ReturningVisitorBanner.tsx greets a returning visitor on the homepage with a direct link back to their own postcode's deals.</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>55</v>
@@ -7767,12 +7811,12 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>app/page.tsx, components/ScrollReveal.tsx, public/illustrations/</t>
+          <t>components/ProviderAvailabilityBadge.tsx, components/ReturningVisitorBanner.tsx, components/PostcodeContextBar.tsx, app/page.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/speed-test/page.tsx, app/tools/broadband-match/page.tsx, app/tools/broadband-cost-calculator/page.tsx</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None -- deliberately built on data already held, no new API/cost</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -7802,19 +7846,19 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Mobile and cross-device navigation overhaul</t>
+          <t>Homepage visual redesign: illustrations + interactivity</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>New scripts/analyze_mobile_ux.py scanned Uswitch, broadband.co.uk and choose.co.uk (MoneySavingExpert 403, reported not bypassed) with a mobile Safari user agent for markup/CSS signals: viewport meta and hamburger menu markers were universal but already correct on our own site; tel: click-to-call was absent everywhere (0/4, skipped); sticky bottom CTA (1/4) and apple-touch-icon (2/4) were too weak/incomplete to act on. The real gap was found by direct inspection, not the scan: the mobile nav was a small anchored dropdown of 10 flat links with ~36px touch targets, while the desktop nav beside it was a full mega-menu, and the header postcode checker was desktop-only so phone users had no quick postcode access outside the homepage/deals page. Replaced it with new components/MobileNav.tsx: a full-width slide-down panel reusing the desktop mega-menu's own icon/link data (exported from MainNav.tsx, so the two can't drift apart), every link at a 44px (min-h-11) touch target, and the postcode checker embedded at the top so it's reachable from any page. Added anchor ids to /guides category sections so the new mobile Guides menu jumps to a real target instead of an unread query param.</t>
+          <t>Researched via scripts/analyze_homepage_visual_design.py against 5 UK broadband comparison homepages: none uses stock-photo hero banners; the dominant visual language is heavy inline SVG (Uswitch ships 195) and provider logos, no carousel/animation library detected anywhere. Generated 7 original on-brand SVG illustrations (scripts/generate_homepage_illustrations.py: hero network graphic, 3 colour-filled step icons, 2 gradient blobs, a quiz illustration) rather than stock photography, matching what's actually proven in this vertical. Added a scroll-reveal component, hover interactions, and restructured the Broadband Match promo to a two-column illustrated layout. Content/copy unchanged, visual/UX only.</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -7823,7 +7867,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>components/MobileNav.tsx, components/MainNav.tsx, app/layout.tsx, app/guides/page.tsx</t>
+          <t>app/page.tsx, components/ScrollReveal.tsx, public/illustrations/</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -7858,19 +7902,19 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Mobile and cross-device navigation overhaul</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
+          <t>New scripts/analyze_mobile_ux.py scanned Uswitch, broadband.co.uk and choose.co.uk (MoneySavingExpert 403, reported not bypassed) with a mobile Safari user agent for markup/CSS signals: viewport meta and hamburger menu markers were universal but already correct on our own site; tel: click-to-call was absent everywhere (0/4, skipped); sticky bottom CTA (1/4) and apple-touch-icon (2/4) were too weak/incomplete to act on. The real gap was found by direct inspection, not the scan: the mobile nav was a small anchored dropdown of 10 flat links with ~36px touch targets, while the desktop nav beside it was a full mega-menu, and the header postcode checker was desktop-only so phone users had no quick postcode access outside the homepage/deals page. Replaced it with new components/MobileNav.tsx: a full-width slide-down panel reusing the desktop mega-menu's own icon/link data (exported from MainNav.tsx, so the two can't drift apart), every link at a 44px (min-h-11) touch target, and the postcode checker embedded at the top so it's reachable from any page. Added anchor ids to /guides category sections so the new mobile Guides menu jumps to a real target instead of an unread query param.</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -7879,7 +7923,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>components/MainNav.tsx, app/layout.tsx</t>
+          <t>components/MobileNav.tsx, components/MainNav.tsx, app/layout.tsx, app/guides/page.tsx</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7914,19 +7958,19 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Animated, interactive mobile menu with click-outside-to-close</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Direct UX/interaction-design request, not a scraping pass. Rewrote components/MobileNav.tsx from a native &lt;details&gt; element (no animation, no click-outside-to-close) to a controlled client component: hamburger icon morphs into an X on open; a blurred backdrop closes the menu on click or Escape; the panel and its sections slide/fade in with a staggered delay reusing the same transition idiom as components/ScrollReveal.tsx; Providers/Postcode/Guides/Tools became single-open accordions using a CSS-only grid-template-rows 0fr-&gt;1fr transition (no JS height measurement); the menu auto-closes on route change via usePathname(); background scroll is locked while open; focus moves into the panel on open and returns to the trigger on Escape. Global prefers-reduced-motion handling already in app/globals.css applies automatically. Not visually verified on a real device — no browser automation tool available this session, validated via build output, generated CSS and server-rendered markup only.</t>
+          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -7935,7 +7979,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>components/MobileNav.tsx</t>
+          <t>components/MainNav.tsx, app/layout.tsx</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -7965,24 +8009,24 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Animated, interactive mobile menu with click-outside-to-close</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
+          <t>Direct UX/interaction-design request, not a scraping pass. Rewrote components/MobileNav.tsx from a native &lt;details&gt; element (no animation, no click-outside-to-close) to a controlled client component: hamburger icon morphs into an X on open; a blurred backdrop closes the menu on click or Escape; the panel and its sections slide/fade in with a staggered delay reusing the same transition idiom as components/ScrollReveal.tsx; Providers/Postcode/Guides/Tools became single-open accordions using a CSS-only grid-template-rows 0fr-&gt;1fr transition (no JS height measurement); the menu auto-closes on route change via usePathname(); background scroll is locked while open; focus moves into the panel on open and returns to the trigger on Escape. Global prefers-reduced-motion handling already in app/globals.css applies automatically. Not visually verified on a real device — no browser automation tool available this session, validated via build output, generated CSS and server-rendered markup only.</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -7991,22 +8035,22 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
+          <t>components/MobileNav.tsx</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Email delivery provider</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8021,24 +8065,24 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
+          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
         <v>49</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -8047,22 +8091,22 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
+          <t>New subscription flow + data/provider-live-deals.json</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Email delivery provider</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>Growth playbook — Functionality pillar</t>
         </is>
       </c>
     </row>
@@ -8082,28 +8126,28 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
+          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>app/layout.tsx, components/Logo.tsx</t>
+          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8128,38 +8172,38 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Research-led editorial refresh: Best Broadband and TV Deals guide</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>User-requested application of the same Stage 3/4/4a research process from the Awin content batches to a single existing guide page, /guides/best-broadband-and-tv-deals. Unlike the thin provider stubs rewritten in the Awin batches, this guide was already well-built (tables, methodology, 7 FAQs, real Ofcom citations, last checked 29 July 2026) -- not a stub needing a ground-up rewrite, so this was a verify-and-deepen pass grounded in fresh research rather than a full replacement. Scraped 2 top-ranking competitors (MoneySuperMarket, Uswitch) per Stage 3.0: found MoneySupermarket runs a 15-question FAQ (ours had 7) and leads with an expert-quoted bundling-savings statistic. Traced that claim to its actual primary source rather than citing the secondary restatement: Ofcom's own February 2026 research, savings of £26-£48/month from bundling and pay-TV averaging £12/month within a bundle (23% real-terms fall) -- a stronger, more current, primary-sourced figure than the competitor's 2023-dated stat, added as a new section. Also found and added two genuinely new, specific facts the page didn't have: Virgin Media's Max Volt bundle (real current pricing including its two scheduled rises to April 2028) as a concrete worked example, and Virgin Media's 'Most Reliable Broadband Provider' win at the 2026 Uswitch Telecoms Awards (Opensignal-verified, a genuine third-party measurement). Named the specific Sky bundle example (Sky Stream, Sky TV, Netflix + Full Fibre 300, £35/month) that the existing copy referenced only vaguely. Added 2 new FAQs tied to the new content. Fixed 2 pre-existing em dashes found during the pass (a legitimate en-dash numeric range, '50-100Mbps', was left alone -- not an AI-tell, different typographic use). Updated the page's stated fact-check date and guides.ts updatedDate to 2026-08-24.</t>
+          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
         <v>48</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>app/guides/[slug]/page.tsx (best-broadband-and-tv-deals), data/guides.ts</t>
+          <t>app/layout.tsx, components/Logo.tsx</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -8174,7 +8218,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8184,29 +8228,29 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Research-led editorial refresh: Best Broadband and TV Deals guide</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
+          <t>User-requested application of the same Stage 3/4/4a research process from the Awin content batches to a single existing guide page, /guides/best-broadband-and-tv-deals. Unlike the thin provider stubs rewritten in the Awin batches, this guide was already well-built (tables, methodology, 7 FAQs, real Ofcom citations, last checked 29 July 2026) -- not a stub needing a ground-up rewrite, so this was a verify-and-deepen pass grounded in fresh research rather than a full replacement. Scraped 2 top-ranking competitors (MoneySuperMarket, Uswitch) per Stage 3.0: found MoneySupermarket runs a 15-question FAQ (ours had 7) and leads with an expert-quoted bundling-savings statistic. Traced that claim to its actual primary source rather than citing the secondary restatement: Ofcom's own February 2026 research, savings of £26-£48/month from bundling and pay-TV averaging £12/month within a bundle (23% real-terms fall) -- a stronger, more current, primary-sourced figure than the competitor's 2023-dated stat, added as a new section. Also found and added two genuinely new, specific facts the page didn't have: Virgin Media's Max Volt bundle (real current pricing including its two scheduled rises to April 2028) as a concrete worked example, and Virgin Media's 'Most Reliable Broadband Provider' win at the 2026 Uswitch Telecoms Awards (Opensignal-verified, a genuine third-party measurement). Named the specific Sky bundle example (Sky Stream, Sky TV, Netflix + Full Fibre 300, £35/month) that the existing copy referenced only vaguely. Added 2 new FAQs tied to the new content. Fixed 2 pre-existing em dashes found during the pass (a legitimate en-dash numeric range, '50-100Mbps', was left alone -- not an AI-tell, different typographic use). Updated the page's stated fact-check date and guides.ts updatedDate to 2026-08-24.</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -8215,22 +8259,22 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Sitewide template performance report</t>
+          <t>app/guides/[slug]/page.tsx (best-broadband-and-tv-deals), data/guides.ts</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Field data or representative lab baselines</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8240,53 +8284,53 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Direct Awin Publisher API access — programme status and link generation</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>User asked to connect Claude to their Awin account and provided a real API token. There's no one-click connector for Awin (unlike Google Drive/Gmail), so this uses Awin's own Publisher API directly. First live run corrected two wrong assumptions from documentation research: 'programmedetails' requires a specific advertiserId (not a bulk listing endpoint) -- the actual bulk-status endpoint is GET /publishers/{id}/programmes?relationship=X, and 'any' is not a valid value for it (loops joined/pending/suspended/rejected instead; 'notjoined' returns the ~21k whole-platform catalogue so it's excluded from the default and only fetched on request). POST /publishers/{id}/linkbuilder/generate confirmed working, verified against TalkTalk (advertiser 3674). REAL FINDING from the first run, both surfaced to the user and worth acting on: only 4 programmes are joined (TalkTalk, Broadband Genie, Zzoomm, Highland Broadband), 7 pending (Sky ROI, Community Fibre, National Broadband, Trooli, Pine Media, Cuckoo, Zen Internet), and 9 REJECTED including BT (both consumer and business), Vodafone, Plusnet, EE, Virgin Media, Hyperoptic and toob. Cross-checked data/providers.ts: none of the currently-live affiliateUrl values (including TalkTalk, which IS approved) use Awin's awin1.com tracking format -- they're all plain provider URLs, so the site is very likely not earning commission on any current outbound click, joined or not, despite the on-page commercial disclosures implying it might.</t>
+          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
         <v>47</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>scripts/awin_sync.py</t>
+          <t>Sitewide template performance report</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>AWIN_API_TOKEN from the user's Awin account (user menu -&gt; API Credentials)</t>
+          <t>Field data or representative lab baselines</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -8296,53 +8340,53 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Direct Awin Publisher API access — programme status and link generation</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+          <t>User asked to connect Claude to their Awin account and provided a real API token. There's no one-click connector for Awin (unlike Google Drive/Gmail), so this uses Awin's own Publisher API directly. First live run corrected two wrong assumptions from documentation research: 'programmedetails' requires a specific advertiserId (not a bulk listing endpoint) -- the actual bulk-status endpoint is GET /publishers/{id}/programmes?relationship=X, and 'any' is not a valid value for it (loops joined/pending/suspended/rejected instead; 'notjoined' returns the ~21k whole-platform catalogue so it's excluded from the default and only fetched on request). POST /publishers/{id}/linkbuilder/generate confirmed working, verified against TalkTalk (advertiser 3674). REAL FINDING from the first run, both surfaced to the user and worth acting on: only 4 programmes are joined (TalkTalk, Broadband Genie, Zzoomm, Highland Broadband), 7 pending (Sky ROI, Community Fibre, National Broadband, Trooli, Pine Media, Cuckoo, Zen Internet), and 9 REJECTED including BT (both consumer and business), Vodafone, Plusnet, EE, Virgin Media, Hyperoptic and toob. Cross-checked data/providers.ts: none of the currently-live affiliateUrl values (including TalkTalk, which IS approved) use Awin's awin1.com tracking format -- they're all plain provider URLs, so the site is very likely not earning commission on any current outbound click, joined or not, despite the on-page commercial disclosures implying it might.</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G32" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="G32" s="2" t="n">
-        <v>58</v>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>scripts/awin_sync.py</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>AWIN_API_TOKEN from the user's Awin account (user menu -&gt; API Credentials)</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8352,43 +8396,43 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
+          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Sitewide crawl and redirect report</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
@@ -8398,7 +8442,7 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -8408,43 +8452,43 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide crawl and redirect report</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -8454,7 +8498,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -8469,24 +8513,24 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
@@ -8495,12 +8539,12 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
@@ -8510,7 +8554,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -8525,53 +8569,109 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="F37" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G37" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K37" s="3" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="L37" s="3" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L36"/>
+  <autoFilter ref="A1:L37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8612,7 +8712,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>68 total (33 page builds, 35 feature/strategy builds); 54 already marked Done.</t>
+          <t>69 total (33 page builds, 36 feature/strategy builds); 55 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -176,8 +176,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L70" headerRowCount="1">
-  <autoFilter ref="A1:L70"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L71" headerRowCount="1">
+  <autoFilter ref="A1:L71"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -241,8 +241,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L37" headerRowCount="1">
-  <autoFilter ref="A1:L37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L38" headerRowCount="1">
+  <autoFilter ref="A1:L38"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3208,29 +3208,29 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>feat-mobile-cross-device-navigation</t>
+          <t>content-refresh-cheapest-broadband-guide</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Mobile and cross-device navigation overhaul</t>
+          <t>Deep rewrite: Cheapest Broadband Deals UK guide (2nd content-priority-analysis target)</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>feat-mega-menu-navigation</t>
+          <t>feat-mobile-cross-device-navigation</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3267,14 +3267,14 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Mobile and cross-device navigation overhaul</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>feat-animated-interactive-mobile-menu</t>
+          <t>feat-mega-menu-navigation</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -3311,14 +3311,14 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Animated, interactive mobile menu with click-outside-to-close</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>feat-price-drop-alerts</t>
+          <t>feat-animated-interactive-mobile-menu</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3350,19 +3350,19 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Animated, interactive mobile menu with click-outside-to-close</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>feat-page-type-ux-redesign</t>
+          <t>feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -3394,19 +3394,19 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
         <v>49</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr"/>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>feat-footer-logo-interactivity</t>
+          <t>feat-page-type-ux-redesign</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3443,18 +3443,18 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3464,11 +3464,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
-        </is>
-      </c>
+      <c r="L62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
@@ -3476,33 +3472,33 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>content-refresh-best-broadband-tv-deals-guide</t>
+          <t>feat-footer-logo-interactivity</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Research-led editorial refresh: Best Broadband and TV Deals guide</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
         <v>48</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -3512,7 +3508,11 @@
       </c>
       <c r="J63" s="3" t="inlineStr"/>
       <c r="K63" s="3" t="inlineStr"/>
-      <c r="L63" s="3" t="inlineStr"/>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -3520,29 +3520,29 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>audit-core-web-vitals-reporting</t>
+          <t>content-refresh-best-broadband-tv-deals-guide</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Research-led editorial refresh: Best Broadband and TV Deals guide</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
@@ -3564,38 +3564,38 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>ops-awin-publisher-api-integration</t>
+          <t>audit-core-web-vitals-reporting</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Direct Awin Publisher API access — programme status and link generation</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
         <v>47</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr"/>
@@ -3608,38 +3608,38 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>ops-awin-publisher-api-integration</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Direct Awin Publisher API access — programme status and link generation</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G66" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="G66" s="2" t="n">
-        <v>58</v>
-      </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -3652,33 +3652,33 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>audit-broken-links-redirects</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -3696,33 +3696,33 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-broken-links-redirects</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -3750,19 +3750,19 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -3794,19 +3794,19 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3822,8 +3822,52 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr"/>
+      <c r="K71" s="3" t="inlineStr"/>
+      <c r="L71" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L70"/>
+  <autoFilter ref="A1:L71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6575,7 +6619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7892,29 +7936,29 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Mobile and cross-device navigation overhaul</t>
+          <t>Deep rewrite: Cheapest Broadband Deals UK guide (2nd content-priority-analysis target)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>New scripts/analyze_mobile_ux.py scanned Uswitch, broadband.co.uk and choose.co.uk (MoneySavingExpert 403, reported not bypassed) with a mobile Safari user agent for markup/CSS signals: viewport meta and hamburger menu markers were universal but already correct on our own site; tel: click-to-call was absent everywhere (0/4, skipped); sticky bottom CTA (1/4) and apple-touch-icon (2/4) were too weak/incomplete to act on. The real gap was found by direct inspection, not the scan: the mobile nav was a small anchored dropdown of 10 flat links with ~36px touch targets, while the desktop nav beside it was a full mega-menu, and the header postcode checker was desktop-only so phone users had no quick postcode access outside the homepage/deals page. Replaced it with new components/MobileNav.tsx: a full-width slide-down panel reusing the desktop mega-menu's own icon/link data (exported from MainNav.tsx, so the two can't drift apart), every link at a 44px (min-h-11) touch target, and the postcode checker embedded at the top so it's reachable from any page. Added anchor ids to /guides category sections so the new mobile Guides menu jumps to a real target instead of an unread query param.</t>
+          <t>Second target from scripts/analyze_content_priority.py's ranked list: 130 real GSC AI-feature impressions at 481 words, and materially stale (last touched 2026-06-01, still citing NOW Broadband at a since-changed £17.99). Rewritten to 1,101 words, drawing on session-verified pricing across 11 providers rather than fresh research for most of them. Real correction made: NOW Broadband's usable Full Fibre 75 now starts at £23/mo, not the stale £17.99 the old copy cited -- no longer reliably the cheapest option, now similar to or pricier than Plusnet (£21.99) and EE (£22.99). Real new finding: Community Fibre's Essential 35 at £12.50/mo is the genuinely cheapest full-fibre deal on the market (London/Surrey/Sussex only). Verified current social tariff pricing (Virgin Media £12.50, BT Home Essentials £15-20, Sky Broadband Basics £20 existing-customers-only) plus a real, citable Ofcom stat: ~4.2 million eligible households, only ~532,000 actually claiming one. Caught the same JSX-vs-.ts apostrophe-escaping bug found on the previous guide (one instance this time, in the NOW Broadband paragraph) before shipping -- confirmed via the file's own reviewSources-style checked-date convention. 1,101 words sits just under this session's own 1,200-word guide depth floor; left as is rather than padding for its own sake, since the content is already comprehensive (2 real data tables, 5 FAQs, all newly sourced).</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -7923,12 +7967,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>components/MobileNav.tsx, components/MainNav.tsx, app/layout.tsx, app/guides/page.tsx</t>
+          <t>app/guides/[slug]/page.tsx (cheapest-broadband-uk), data/guides.ts</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ops-content-priority-analysis-tooling</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -7938,7 +7982,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7958,19 +8002,19 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Mobile and cross-device navigation overhaul</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
+          <t>New scripts/analyze_mobile_ux.py scanned Uswitch, broadband.co.uk and choose.co.uk (MoneySavingExpert 403, reported not bypassed) with a mobile Safari user agent for markup/CSS signals: viewport meta and hamburger menu markers were universal but already correct on our own site; tel: click-to-call was absent everywhere (0/4, skipped); sticky bottom CTA (1/4) and apple-touch-icon (2/4) were too weak/incomplete to act on. The real gap was found by direct inspection, not the scan: the mobile nav was a small anchored dropdown of 10 flat links with ~36px touch targets, while the desktop nav beside it was a full mega-menu, and the header postcode checker was desktop-only so phone users had no quick postcode access outside the homepage/deals page. Replaced it with new components/MobileNav.tsx: a full-width slide-down panel reusing the desktop mega-menu's own icon/link data (exported from MainNav.tsx, so the two can't drift apart), every link at a 44px (min-h-11) touch target, and the postcode checker embedded at the top so it's reachable from any page. Added anchor ids to /guides category sections so the new mobile Guides menu jumps to a real target instead of an unread query param.</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -7979,7 +8023,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>components/MainNav.tsx, app/layout.tsx</t>
+          <t>components/MobileNav.tsx, components/MainNav.tsx, app/layout.tsx, app/guides/page.tsx</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -8014,19 +8058,19 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Animated, interactive mobile menu with click-outside-to-close</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Direct UX/interaction-design request, not a scraping pass. Rewrote components/MobileNav.tsx from a native &lt;details&gt; element (no animation, no click-outside-to-close) to a controlled client component: hamburger icon morphs into an X on open; a blurred backdrop closes the menu on click or Escape; the panel and its sections slide/fade in with a staggered delay reusing the same transition idiom as components/ScrollReveal.tsx; Providers/Postcode/Guides/Tools became single-open accordions using a CSS-only grid-template-rows 0fr-&gt;1fr transition (no JS height measurement); the menu auto-closes on route change via usePathname(); background scroll is locked while open; focus moves into the panel on open and returns to the trigger on Escape. Global prefers-reduced-motion handling already in app/globals.css applies automatically. Not visually verified on a real device — no browser automation tool available this session, validated via build output, generated CSS and server-rendered markup only.</t>
+          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
         <v>50</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -8035,7 +8079,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>components/MobileNav.tsx</t>
+          <t>components/MainNav.tsx, app/layout.tsx</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8065,24 +8109,24 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Animated, interactive mobile menu with click-outside-to-close</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
+          <t>Direct UX/interaction-design request, not a scraping pass. Rewrote components/MobileNav.tsx from a native &lt;details&gt; element (no animation, no click-outside-to-close) to a controlled client component: hamburger icon morphs into an X on open; a blurred backdrop closes the menu on click or Escape; the panel and its sections slide/fade in with a staggered delay reusing the same transition idiom as components/ScrollReveal.tsx; Providers/Postcode/Guides/Tools became single-open accordions using a CSS-only grid-template-rows 0fr-&gt;1fr transition (no JS height measurement); the menu auto-closes on route change via usePathname(); background scroll is locked while open; focus moves into the panel on open and returns to the trigger on Escape. Global prefers-reduced-motion handling already in app/globals.css applies automatically. Not visually verified on a real device — no browser automation tool available this session, validated via build output, generated CSS and server-rendered markup only.</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -8091,22 +8135,22 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
+          <t>components/MobileNav.tsx</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>Email delivery provider</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8121,24 +8165,24 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
+          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
         <v>49</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -8147,22 +8191,22 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
+          <t>New subscription flow + data/provider-live-deals.json</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Email delivery provider</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>Growth playbook — Functionality pillar</t>
         </is>
       </c>
     </row>
@@ -8182,28 +8226,28 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
+          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>app/layout.tsx, components/Logo.tsx</t>
+          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -8228,38 +8272,38 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Research-led editorial refresh: Best Broadband and TV Deals guide</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>User-requested application of the same Stage 3/4/4a research process from the Awin content batches to a single existing guide page, /guides/best-broadband-and-tv-deals. Unlike the thin provider stubs rewritten in the Awin batches, this guide was already well-built (tables, methodology, 7 FAQs, real Ofcom citations, last checked 29 July 2026) -- not a stub needing a ground-up rewrite, so this was a verify-and-deepen pass grounded in fresh research rather than a full replacement. Scraped 2 top-ranking competitors (MoneySuperMarket, Uswitch) per Stage 3.0: found MoneySupermarket runs a 15-question FAQ (ours had 7) and leads with an expert-quoted bundling-savings statistic. Traced that claim to its actual primary source rather than citing the secondary restatement: Ofcom's own February 2026 research, savings of £26-£48/month from bundling and pay-TV averaging £12/month within a bundle (23% real-terms fall) -- a stronger, more current, primary-sourced figure than the competitor's 2023-dated stat, added as a new section. Also found and added two genuinely new, specific facts the page didn't have: Virgin Media's Max Volt bundle (real current pricing including its two scheduled rises to April 2028) as a concrete worked example, and Virgin Media's 'Most Reliable Broadband Provider' win at the 2026 Uswitch Telecoms Awards (Opensignal-verified, a genuine third-party measurement). Named the specific Sky bundle example (Sky Stream, Sky TV, Netflix + Full Fibre 300, £35/month) that the existing copy referenced only vaguely. Added 2 new FAQs tied to the new content. Fixed 2 pre-existing em dashes found during the pass (a legitimate en-dash numeric range, '50-100Mbps', was left alone -- not an AI-tell, different typographic use). Updated the page's stated fact-check date and guides.ts updatedDate to 2026-08-24.</t>
+          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
         <v>48</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>app/guides/[slug]/page.tsx (best-broadband-and-tv-deals), data/guides.ts</t>
+          <t>app/layout.tsx, components/Logo.tsx</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8274,7 +8318,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8284,29 +8328,29 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Research-led editorial refresh: Best Broadband and TV Deals guide</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
+          <t>User-requested application of the same Stage 3/4/4a research process from the Awin content batches to a single existing guide page, /guides/best-broadband-and-tv-deals. Unlike the thin provider stubs rewritten in the Awin batches, this guide was already well-built (tables, methodology, 7 FAQs, real Ofcom citations, last checked 29 July 2026) -- not a stub needing a ground-up rewrite, so this was a verify-and-deepen pass grounded in fresh research rather than a full replacement. Scraped 2 top-ranking competitors (MoneySuperMarket, Uswitch) per Stage 3.0: found MoneySupermarket runs a 15-question FAQ (ours had 7) and leads with an expert-quoted bundling-savings statistic. Traced that claim to its actual primary source rather than citing the secondary restatement: Ofcom's own February 2026 research, savings of £26-£48/month from bundling and pay-TV averaging £12/month within a bundle (23% real-terms fall) -- a stronger, more current, primary-sourced figure than the competitor's 2023-dated stat, added as a new section. Also found and added two genuinely new, specific facts the page didn't have: Virgin Media's Max Volt bundle (real current pricing including its two scheduled rises to April 2028) as a concrete worked example, and Virgin Media's 'Most Reliable Broadband Provider' win at the 2026 Uswitch Telecoms Awards (Opensignal-verified, a genuine third-party measurement). Named the specific Sky bundle example (Sky Stream, Sky TV, Netflix + Full Fibre 300, £35/month) that the existing copy referenced only vaguely. Added 2 new FAQs tied to the new content. Fixed 2 pre-existing em dashes found during the pass (a legitimate en-dash numeric range, '50-100Mbps', was left alone -- not an AI-tell, different typographic use). Updated the page's stated fact-check date and guides.ts updatedDate to 2026-08-24.</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
@@ -8315,22 +8359,22 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Sitewide template performance report</t>
+          <t>app/guides/[slug]/page.tsx (best-broadband-and-tv-deals), data/guides.ts</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>Field data or representative lab baselines</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8340,53 +8384,53 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Direct Awin Publisher API access — programme status and link generation</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>User asked to connect Claude to their Awin account and provided a real API token. There's no one-click connector for Awin (unlike Google Drive/Gmail), so this uses Awin's own Publisher API directly. First live run corrected two wrong assumptions from documentation research: 'programmedetails' requires a specific advertiserId (not a bulk listing endpoint) -- the actual bulk-status endpoint is GET /publishers/{id}/programmes?relationship=X, and 'any' is not a valid value for it (loops joined/pending/suspended/rejected instead; 'notjoined' returns the ~21k whole-platform catalogue so it's excluded from the default and only fetched on request). POST /publishers/{id}/linkbuilder/generate confirmed working, verified against TalkTalk (advertiser 3674). REAL FINDING from the first run, both surfaced to the user and worth acting on: only 4 programmes are joined (TalkTalk, Broadband Genie, Zzoomm, Highland Broadband), 7 pending (Sky ROI, Community Fibre, National Broadband, Trooli, Pine Media, Cuckoo, Zen Internet), and 9 REJECTED including BT (both consumer and business), Vodafone, Plusnet, EE, Virgin Media, Hyperoptic and toob. Cross-checked data/providers.ts: none of the currently-live affiliateUrl values (including TalkTalk, which IS approved) use Awin's awin1.com tracking format -- they're all plain provider URLs, so the site is very likely not earning commission on any current outbound click, joined or not, despite the on-page commercial disclosures implying it might.</t>
+          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
         <v>47</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>scripts/awin_sync.py</t>
+          <t>Sitewide template performance report</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>AWIN_API_TOKEN from the user's Awin account (user menu -&gt; API Credentials)</t>
+          <t>Field data or representative lab baselines</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -8396,53 +8440,53 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Direct Awin Publisher API access — programme status and link generation</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+          <t>User asked to connect Claude to their Awin account and provided a real API token. There's no one-click connector for Awin (unlike Google Drive/Gmail), so this uses Awin's own Publisher API directly. First live run corrected two wrong assumptions from documentation research: 'programmedetails' requires a specific advertiserId (not a bulk listing endpoint) -- the actual bulk-status endpoint is GET /publishers/{id}/programmes?relationship=X, and 'any' is not a valid value for it (loops joined/pending/suspended/rejected instead; 'notjoined' returns the ~21k whole-platform catalogue so it's excluded from the default and only fetched on request). POST /publishers/{id}/linkbuilder/generate confirmed working, verified against TalkTalk (advertiser 3674). REAL FINDING from the first run, both surfaced to the user and worth acting on: only 4 programmes are joined (TalkTalk, Broadband Genie, Zzoomm, Highland Broadband), 7 pending (Sky ROI, Community Fibre, National Broadband, Trooli, Pine Media, Cuckoo, Zen Internet), and 9 REJECTED including BT (both consumer and business), Vodafone, Plusnet, EE, Virgin Media, Hyperoptic and toob. Cross-checked data/providers.ts: none of the currently-live affiliateUrl values (including TalkTalk, which IS approved) use Awin's awin1.com tracking format -- they're all plain provider URLs, so the site is very likely not earning commission on any current outbound click, joined or not, despite the on-page commercial disclosures implying it might.</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G33" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>58</v>
-      </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>scripts/awin_sync.py</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>AWIN_API_TOKEN from the user's Awin account (user menu -&gt; API Credentials)</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8452,43 +8496,43 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
+          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Sitewide crawl and redirect report</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -8498,7 +8542,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -8508,43 +8552,43 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide crawl and redirect report</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
@@ -8554,7 +8598,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -8569,24 +8613,24 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -8595,12 +8639,12 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -8610,7 +8654,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -8625,53 +8669,109 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F37" s="3" t="n">
+      <c r="F38" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G37" s="3" t="n">
+      <c r="G38" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L37" s="3" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L37"/>
+  <autoFilter ref="A1:L38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8712,7 +8812,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>69 total (33 page builds, 36 feature/strategy builds); 55 already marked Done.</t>
+          <t>70 total (33 page builds, 37 feature/strategy builds); 56 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -176,8 +176,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L71" headerRowCount="1">
-  <autoFilter ref="A1:L71"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L72" headerRowCount="1">
+  <autoFilter ref="A1:L72"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -241,8 +241,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L38" headerRowCount="1">
-  <autoFilter ref="A1:L38"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L39" headerRowCount="1">
+  <autoFilter ref="A1:L39"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3384,29 +3384,29 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>feat-price-drop-alerts</t>
+          <t>content-refresh-best-business-broadband-guide</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Deep rewrite: Best Business Broadband Providers UK guide (3rd content-priority-analysis target)</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr"/>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>feat-page-type-ux-redesign</t>
+          <t>feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3438,19 +3438,19 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
         <v>49</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>feat-footer-logo-interactivity</t>
+          <t>feat-page-type-ux-redesign</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -3487,18 +3487,18 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -3508,11 +3508,7 @@
       </c>
       <c r="J63" s="3" t="inlineStr"/>
       <c r="K63" s="3" t="inlineStr"/>
-      <c r="L63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
-        </is>
-      </c>
+      <c r="L63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -3520,33 +3516,33 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>content-refresh-best-broadband-tv-deals-guide</t>
+          <t>feat-footer-logo-interactivity</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Research-led editorial refresh: Best Broadband and TV Deals guide</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
         <v>48</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3556,7 +3552,11 @@
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
@@ -3564,29 +3564,29 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>audit-core-web-vitals-reporting</t>
+          <t>content-refresh-best-broadband-tv-deals-guide</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Research-led editorial refresh: Best Broadband and TV Deals guide</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr"/>
@@ -3608,38 +3608,38 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>ops-awin-publisher-api-integration</t>
+          <t>audit-core-web-vitals-reporting</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Direct Awin Publisher API access — programme status and link generation</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
         <v>47</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -3652,38 +3652,38 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>ops-awin-publisher-api-integration</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Direct Awin Publisher API access — programme status and link generation</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G67" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="G67" s="3" t="n">
-        <v>58</v>
-      </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr"/>
@@ -3696,33 +3696,33 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>audit-broken-links-redirects</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3740,33 +3740,33 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-broken-links-redirects</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -3794,19 +3794,19 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -3838,19 +3838,19 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
@@ -3866,8 +3866,52 @@
       <c r="K71" s="3" t="inlineStr"/>
       <c r="L71" s="3" t="inlineStr"/>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L71"/>
+  <autoFilter ref="A1:L72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6619,7 +6663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8160,29 +8204,29 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Deep rewrite: Best Business Broadband Providers UK guide (3rd content-priority-analysis target)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
+          <t>Third target from scripts/analyze_content_priority.py's ranked list: 142 real GSC AI-feature impressions at 596 words. This page lives on a different template than the [slug]-based guides (app/guides/best-business-broadband-providers-uk/ is a standalone PrioritySeoPage route backed by data/priority-pages.ts), and had 2 pre-existing em dashes fixed as part of the pass. Rewritten to 1,050 words with real, specific per-provider data: Vodafone Business has the most competitive entry-level price (~£20-22/mo excl. VAT), Zen Business leads on satisfaction (Which? Recommended since 2021, 84% score) -- consistent with, and corroborating, the consumer Zen Internet findings from the Awin-rejected batch, Virgin Media Business has the fastest raw speed (442 Mbps average), and a genuinely useful, specific stat: out-of-contract business customers overpay 24.86% more per month on average. Added a real contended-vs-uncontended leased-line explainer with current pricing (from ~£69/mo entry-level). Also fixed a real bug in the analysis script itself found while validating this page: DATE_RE didn't recognise the PrioritySeoPage template's 'Last researched and reviewed:' phrasing (colon, different verb), so every page on that template was incorrectly scored as having no checked date -- fixed and confirmed it also corrected the score for /guides/satellite-broadband-uk on the same template.</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -8191,22 +8235,22 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
+          <t>data/priority-pages.ts (business), scripts/analyze_content_priority.py</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Email delivery provider</t>
+          <t>ops-content-priority-analysis-tooling</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8221,24 +8265,24 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
+          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
         <v>49</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
@@ -8247,22 +8291,22 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
+          <t>New subscription flow + data/provider-live-deals.json</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Email delivery provider</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>Growth playbook — Functionality pillar</t>
         </is>
       </c>
     </row>
@@ -8282,28 +8326,28 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
+          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>app/layout.tsx, components/Logo.tsx</t>
+          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8328,38 +8372,38 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Research-led editorial refresh: Best Broadband and TV Deals guide</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>User-requested application of the same Stage 3/4/4a research process from the Awin content batches to a single existing guide page, /guides/best-broadband-and-tv-deals. Unlike the thin provider stubs rewritten in the Awin batches, this guide was already well-built (tables, methodology, 7 FAQs, real Ofcom citations, last checked 29 July 2026) -- not a stub needing a ground-up rewrite, so this was a verify-and-deepen pass grounded in fresh research rather than a full replacement. Scraped 2 top-ranking competitors (MoneySuperMarket, Uswitch) per Stage 3.0: found MoneySupermarket runs a 15-question FAQ (ours had 7) and leads with an expert-quoted bundling-savings statistic. Traced that claim to its actual primary source rather than citing the secondary restatement: Ofcom's own February 2026 research, savings of £26-£48/month from bundling and pay-TV averaging £12/month within a bundle (23% real-terms fall) -- a stronger, more current, primary-sourced figure than the competitor's 2023-dated stat, added as a new section. Also found and added two genuinely new, specific facts the page didn't have: Virgin Media's Max Volt bundle (real current pricing including its two scheduled rises to April 2028) as a concrete worked example, and Virgin Media's 'Most Reliable Broadband Provider' win at the 2026 Uswitch Telecoms Awards (Opensignal-verified, a genuine third-party measurement). Named the specific Sky bundle example (Sky Stream, Sky TV, Netflix + Full Fibre 300, £35/month) that the existing copy referenced only vaguely. Added 2 new FAQs tied to the new content. Fixed 2 pre-existing em dashes found during the pass (a legitimate en-dash numeric range, '50-100Mbps', was left alone -- not an AI-tell, different typographic use). Updated the page's stated fact-check date and guides.ts updatedDate to 2026-08-24.</t>
+          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
         <v>48</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>app/guides/[slug]/page.tsx (best-broadband-and-tv-deals), data/guides.ts</t>
+          <t>app/layout.tsx, components/Logo.tsx</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -8374,7 +8418,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8384,29 +8428,29 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Research-led editorial refresh: Best Broadband and TV Deals guide</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
+          <t>User-requested application of the same Stage 3/4/4a research process from the Awin content batches to a single existing guide page, /guides/best-broadband-and-tv-deals. Unlike the thin provider stubs rewritten in the Awin batches, this guide was already well-built (tables, methodology, 7 FAQs, real Ofcom citations, last checked 29 July 2026) -- not a stub needing a ground-up rewrite, so this was a verify-and-deepen pass grounded in fresh research rather than a full replacement. Scraped 2 top-ranking competitors (MoneySuperMarket, Uswitch) per Stage 3.0: found MoneySupermarket runs a 15-question FAQ (ours had 7) and leads with an expert-quoted bundling-savings statistic. Traced that claim to its actual primary source rather than citing the secondary restatement: Ofcom's own February 2026 research, savings of £26-£48/month from bundling and pay-TV averaging £12/month within a bundle (23% real-terms fall) -- a stronger, more current, primary-sourced figure than the competitor's 2023-dated stat, added as a new section. Also found and added two genuinely new, specific facts the page didn't have: Virgin Media's Max Volt bundle (real current pricing including its two scheduled rises to April 2028) as a concrete worked example, and Virgin Media's 'Most Reliable Broadband Provider' win at the 2026 Uswitch Telecoms Awards (Opensignal-verified, a genuine third-party measurement). Named the specific Sky bundle example (Sky Stream, Sky TV, Netflix + Full Fibre 300, £35/month) that the existing copy referenced only vaguely. Added 2 new FAQs tied to the new content. Fixed 2 pre-existing em dashes found during the pass (a legitimate en-dash numeric range, '50-100Mbps', was left alone -- not an AI-tell, different typographic use). Updated the page's stated fact-check date and guides.ts updatedDate to 2026-08-24.</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -8415,22 +8459,22 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Sitewide template performance report</t>
+          <t>app/guides/[slug]/page.tsx (best-broadband-and-tv-deals), data/guides.ts</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Field data or representative lab baselines</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8440,53 +8484,53 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Direct Awin Publisher API access — programme status and link generation</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>User asked to connect Claude to their Awin account and provided a real API token. There's no one-click connector for Awin (unlike Google Drive/Gmail), so this uses Awin's own Publisher API directly. First live run corrected two wrong assumptions from documentation research: 'programmedetails' requires a specific advertiserId (not a bulk listing endpoint) -- the actual bulk-status endpoint is GET /publishers/{id}/programmes?relationship=X, and 'any' is not a valid value for it (loops joined/pending/suspended/rejected instead; 'notjoined' returns the ~21k whole-platform catalogue so it's excluded from the default and only fetched on request). POST /publishers/{id}/linkbuilder/generate confirmed working, verified against TalkTalk (advertiser 3674). REAL FINDING from the first run, both surfaced to the user and worth acting on: only 4 programmes are joined (TalkTalk, Broadband Genie, Zzoomm, Highland Broadband), 7 pending (Sky ROI, Community Fibre, National Broadband, Trooli, Pine Media, Cuckoo, Zen Internet), and 9 REJECTED including BT (both consumer and business), Vodafone, Plusnet, EE, Virgin Media, Hyperoptic and toob. Cross-checked data/providers.ts: none of the currently-live affiliateUrl values (including TalkTalk, which IS approved) use Awin's awin1.com tracking format -- they're all plain provider URLs, so the site is very likely not earning commission on any current outbound click, joined or not, despite the on-page commercial disclosures implying it might.</t>
+          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
         <v>47</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>scripts/awin_sync.py</t>
+          <t>Sitewide template performance report</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>AWIN_API_TOKEN from the user's Awin account (user menu -&gt; API Credentials)</t>
+          <t>Field data or representative lab baselines</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -8496,53 +8540,53 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Direct Awin Publisher API access — programme status and link generation</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+          <t>User asked to connect Claude to their Awin account and provided a real API token. There's no one-click connector for Awin (unlike Google Drive/Gmail), so this uses Awin's own Publisher API directly. First live run corrected two wrong assumptions from documentation research: 'programmedetails' requires a specific advertiserId (not a bulk listing endpoint) -- the actual bulk-status endpoint is GET /publishers/{id}/programmes?relationship=X, and 'any' is not a valid value for it (loops joined/pending/suspended/rejected instead; 'notjoined' returns the ~21k whole-platform catalogue so it's excluded from the default and only fetched on request). POST /publishers/{id}/linkbuilder/generate confirmed working, verified against TalkTalk (advertiser 3674). REAL FINDING from the first run, both surfaced to the user and worth acting on: only 4 programmes are joined (TalkTalk, Broadband Genie, Zzoomm, Highland Broadband), 7 pending (Sky ROI, Community Fibre, National Broadband, Trooli, Pine Media, Cuckoo, Zen Internet), and 9 REJECTED including BT (both consumer and business), Vodafone, Plusnet, EE, Virgin Media, Hyperoptic and toob. Cross-checked data/providers.ts: none of the currently-live affiliateUrl values (including TalkTalk, which IS approved) use Awin's awin1.com tracking format -- they're all plain provider URLs, so the site is very likely not earning commission on any current outbound click, joined or not, despite the on-page commercial disclosures implying it might.</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G34" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="G34" s="2" t="n">
-        <v>58</v>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>scripts/awin_sync.py</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>AWIN_API_TOKEN from the user's Awin account (user menu -&gt; API Credentials)</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8552,43 +8596,43 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
+          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Sitewide crawl and redirect report</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
@@ -8598,7 +8642,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -8608,43 +8652,43 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide crawl and redirect report</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -8654,7 +8698,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -8669,24 +8713,24 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
@@ -8695,12 +8739,12 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
@@ -8710,7 +8754,7 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -8725,53 +8769,109 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="F39" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="G39" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K39" s="3" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L39" s="3" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L38"/>
+  <autoFilter ref="A1:L39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8812,7 +8912,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>70 total (33 page builds, 37 feature/strategy builds); 56 already marked Done.</t>
+          <t>71 total (33 page builds, 38 feature/strategy builds); 57 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -176,8 +176,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L72" headerRowCount="1">
-  <autoFilter ref="A1:L72"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L73" headerRowCount="1">
+  <autoFilter ref="A1:L73"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -241,8 +241,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L39" headerRowCount="1">
-  <autoFilter ref="A1:L39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L40" headerRowCount="1">
+  <autoFilter ref="A1:L40"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3696,29 +3696,29 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>content-refresh-best-5g-home-broadband-guide</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Deep rewrite: Best 5G Home Broadband UK guide (4th content-priority-analysis target)</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
@@ -3740,33 +3740,33 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>audit-broken-links-redirects</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -3784,33 +3784,33 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-broken-links-redirects</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -3838,19 +3838,19 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -3882,19 +3882,19 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3910,8 +3910,52 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
     </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr"/>
+      <c r="K73" s="3" t="inlineStr"/>
+      <c r="L73" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L72"/>
+  <autoFilter ref="A1:L73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6663,7 +6707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8596,29 +8640,29 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Deep rewrite: Best 5G Home Broadband UK guide (4th content-priority-analysis target)</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+          <t>Fourth target from scripts/analyze_content_priority.py's ranked list: 30 real GSC AI-feature impressions at 601 words, and the old copy named no real providers or prices at all, just generic 5G-vs-fibre advice. Rewritten to 1,036 words with real current data for all 4 major UK 5G home broadband options: Three (best value, from GBP29/mo, ~150 Mbps), Vodafone GigaCube (cheapest fixed term at GBP21/mo, or a genuine GBP60/mo no-contract option), EE Smart 5G Hub (broadest UK 5G coverage, GBP30-50/mo), and National Broadband (already deeply covered in the Awin-pending batch) framed correctly here as a multi-network specialist rather than a single-network alternative -- it connects to whichever of the 4 UK networks is strongest at a given address, a genuinely different value proposition worth explaining rather than just listing as a fourth option. Found and included a real Trustpilot-vs-Ofcom divergence for Three specifically (4.5 Trustpilot, worst-quartile Ofcom complaints alongside EE and Vodafone) and linked to the full-fibre guide's deeper explanation of that pattern rather than repeating it in full.</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
@@ -8627,22 +8671,22 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>app/guides/[slug]/page.tsx (best-5g-home-broadband-uk), data/guides.ts</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>ops-content-priority-analysis-tooling</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8652,43 +8696,43 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
+          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Sitewide crawl and redirect report</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -8698,7 +8742,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -8708,43 +8752,43 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide crawl and redirect report</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
@@ -8754,7 +8798,7 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -8769,24 +8813,24 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -8795,12 +8839,12 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -8810,7 +8854,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -8825,53 +8869,109 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F39" s="3" t="n">
+      <c r="F40" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G39" s="3" t="n">
+      <c r="G40" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K39" s="3" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L39" s="3" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L39"/>
+  <autoFilter ref="A1:L40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8912,7 +9012,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>71 total (33 page builds, 38 feature/strategy builds); 57 already marked Done.</t>
+          <t>72 total (33 page builds, 39 feature/strategy builds); 58 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$74</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -176,8 +176,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L73" headerRowCount="1">
-  <autoFilter ref="A1:L73"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L74" headerRowCount="1">
+  <autoFilter ref="A1:L74"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -241,8 +241,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L40" headerRowCount="1">
-  <autoFilter ref="A1:L40"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L41" headerRowCount="1">
+  <autoFilter ref="A1:L41"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3784,38 +3784,38 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>audit-broken-links-redirects</t>
+          <t>content-refresh-best-phone-and-broadband-deals-guide</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Deep rewrite: Best Phone and Broadband Deals guide (5th content-priority-analysis target)</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G70" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="G70" s="2" t="n">
-        <v>48</v>
-      </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
@@ -3828,33 +3828,33 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-broken-links-redirects</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -3882,19 +3882,19 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -3926,19 +3926,19 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
@@ -3954,8 +3954,52 @@
       <c r="K73" s="3" t="inlineStr"/>
       <c r="L73" s="3" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L73"/>
+  <autoFilter ref="A1:L74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6707,7 +6751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8752,53 +8796,53 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Deep rewrite: Best Phone and Broadband Deals guide (5th content-priority-analysis target)</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
+          <t>Fifth target from scripts/analyze_content_priority.py's ranked list: the old copy was generic Digital Voice/line-rental advice with no dates, no stats and one pre-existing em dash, at 457 words. Rewritten with the real PSTN switch-off timeline: full shutdown now locked in for 31 January 2027 (moved from the original December 2025 target after Openreach confirmed the technical barriers were resolved), with PSTN customer numbers falling from 5.2 million (July 2024) to 3.2 million (July 2025). Added Ofcom's minimum one-hour battery backup requirement for emergency-services access during a power cut, and the industry PSTN Charter's commitment not to migrate telecare/vulnerable users without confirmed-compatible equipment. Added a real, specific call-plan cost example (TalkTalk's Anytime Calls add-on at GBP12/mo on top of base broadband) to replace the previous fully generic 'compare the whole contract' advice. FAQs expanded from 3 to 5. Fixed the pre-existing em dash in the dek field.</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G37" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>48</v>
-      </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Sitewide crawl and redirect report</t>
+          <t>data/priority-pages.ts (phone)</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ops-content-priority-analysis-tooling</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8808,43 +8852,43 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide crawl and redirect report</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -8854,7 +8898,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -8869,24 +8913,24 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
@@ -8895,12 +8939,12 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
@@ -8910,7 +8954,7 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -8925,53 +8969,109 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="n">
+      <c r="F41" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G41" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="K41" s="3" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="L41" s="3" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L40"/>
+  <autoFilter ref="A1:L41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9012,7 +9112,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>72 total (33 page builds, 39 feature/strategy builds); 58 already marked Done.</t>
+          <t>73 total (33 page builds, 40 feature/strategy builds); 59 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -176,8 +176,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L74" headerRowCount="1">
-  <autoFilter ref="A1:L74"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L75" headerRowCount="1">
+  <autoFilter ref="A1:L75"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -241,8 +241,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L41" headerRowCount="1">
-  <autoFilter ref="A1:L41"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L42" headerRowCount="1">
+  <autoFilter ref="A1:L42"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>page-guides/student-broadband-by-university-city</t>
+          <t>content-refresh-sky-provider-page</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1139,18 +1139,18 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Student broadband by university city: short-term and rolling deals</t>
+          <t>Deep rewrite: Sky provider page (6th content-priority-analysis target, first provider-type page)</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>65.90000000000001</v>
+        <v>66</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>36.2</v>
+        <v>60</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>page-postcode/edinburgh</t>
+          <t>page-guides/student-broadband-by-university-city</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1183,18 +1183,18 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Broadband providers in Edinburgh: coverage and best deals</t>
+          <t>Student broadband by university city: short-term and rolling deals</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>65.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>40</v>
+        <v>36.2</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>page-guides/small-office-broadband-setup-uk</t>
+          <t>page-postcode/edinburgh</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1227,14 +1227,14 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Small office broadband setup: routers, backup and support checklist</t>
+          <t>Broadband providers in Edinburgh: coverage and best deals</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
         <v>65.8</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>41.9</v>
+        <v>40</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>page-providers/compare/bt-vs-plusnet</t>
+          <t>page-guides/small-office-broadband-setup-uk</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1271,18 +1271,18 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>BT vs Plusnet broadband: which is better in 2026?</t>
+          <t>Small office broadband setup: routers, backup and support checklist</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>65.5</v>
+        <v>65.8</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>36.4</v>
+        <v>41.9</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>page-postcode/glasgow</t>
+          <t>page-providers/compare/bt-vs-plusnet</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1315,18 +1315,18 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Broadband providers in Glasgow: coverage and best deals</t>
+          <t>BT vs Plusnet broadband: which is better in 2026?</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
         <v>65.5</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>40.2</v>
+        <v>36.4</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>page-postcode/liverpool</t>
+          <t>page-postcode/glasgow</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1359,14 +1359,14 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Broadband providers in Liverpool: coverage and best deals</t>
+          <t>Broadband providers in Glasgow: coverage and best deals</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
         <v>65.5</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>page-guides/broadband-for-landlords-and-hmos-uk</t>
+          <t>page-postcode/liverpool</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1403,18 +1403,18 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Broadband for landlords and HMOs: what to set up and who pays</t>
+          <t>Broadband providers in Liverpool: coverage and best deals</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>65.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>36.6</v>
+        <v>40.1</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>page-postcode/leeds</t>
+          <t>page-guides/broadband-for-landlords-and-hmos-uk</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1447,18 +1447,18 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Broadband providers in Leeds: coverage and best deals</t>
+          <t>Broadband for landlords and HMOs: what to set up and who pays</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
         <v>65.09999999999999</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>40.3</v>
+        <v>36.6</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>page-providers/compare/ee-vs-talktalk</t>
+          <t>page-postcode/leeds</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1491,18 +1491,18 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>EE vs TalkTalk broadband: which is better in 2026?</t>
+          <t>Broadband providers in Leeds: coverage and best deals</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>65</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>36.4</v>
+        <v>40.3</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>page-postcode/bristol</t>
+          <t>page-providers/compare/ee-vs-talktalk</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1535,18 +1535,18 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Broadband providers in Bristol: coverage and best deals</t>
+          <t>EE vs TalkTalk broadband: which is better in 2026?</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>40.8</v>
+        <v>36.4</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>page-postcode/birmingham</t>
+          <t>page-postcode/bristol</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1579,14 +1579,14 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Broadband providers in Birmingham: coverage and best deals</t>
+          <t>Broadband providers in Bristol: coverage and best deals</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>64.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>41.1</v>
+        <v>40.8</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>page-postcode/manchester</t>
+          <t>page-postcode/birmingham</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1623,14 +1623,14 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Broadband providers in Manchester: coverage and best deals</t>
+          <t>Broadband providers in Birmingham: coverage and best deals</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>64.2</v>
+        <v>64.5</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>page-guides/leased-line-cost-uk-explained</t>
+          <t>page-postcode/manchester</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1667,14 +1667,14 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Leased line cost UK: what small businesses actually pay</t>
+          <t>Broadband providers in Manchester: coverage and best deals</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>63.3</v>
+        <v>64.2</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>58.6</v>
+        <v>41.2</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1696,33 +1696,33 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>ops-conversion-reporting-loop</t>
+          <t>page-guides/leased-line-cost-uk-explained</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Validate conversion events and establish the GSC/analytics reporting loop</t>
+          <t>Leased line cost UK: what small businesses actually pay</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>63</v>
+        <v>63.3</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>72</v>
+        <v>58.6</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1732,11 +1732,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr"/>
       <c r="K23" s="3" t="inlineStr"/>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>Shipped to Vercel production 2026-08-23: consent-aware GA4 events for postcode submits, speed-test starts/completions/failures, deal filter/sort use and outbound provider clicks, with session first-touch attribution and no full postcode sent. Measurement contract and weekly GSC/GA4 loop documented in docs/analytics-measurement-plan.md.</t>
-        </is>
-      </c>
+      <c r="L23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1744,33 +1740,33 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>page-guides/starlink-vs-fibre-broadband-uk</t>
+          <t>ops-conversion-reporting-loop</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Starlink vs fibre broadband: when satellite makes sense in the UK</t>
+          <t>Validate conversion events and establish the GSC/analytics reporting loop</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>62.9</v>
+        <v>63</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>35.4</v>
+        <v>72</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1780,7 +1776,11 @@
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Shipped to Vercel production 2026-08-23: consent-aware GA4 events for postcode submits, speed-test starts/completions/failures, deal filter/sort use and outbound provider clicks, with session first-touch attribution and no full postcode sent. Measurement contract and weekly GSC/GA4 loop documented in docs/analytics-measurement-plan.md.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>page-providers/compare/virgin-media-vs-sky</t>
+          <t>page-guides/starlink-vs-fibre-broadband-uk</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1803,14 +1803,14 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Virgin Media vs Sky broadband: which is better in 2026?</t>
+          <t>Starlink vs fibre broadband: when satellite makes sense in the UK</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>62.8</v>
+        <v>62.9</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>36.2</v>
+        <v>35.4</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>page-guides/january-broadband-deals-uk</t>
+          <t>page-providers/compare/virgin-media-vs-sky</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1847,14 +1847,14 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>January broadband deals UK: new-year switching guide</t>
+          <t>Virgin Media vs Sky broadband: which is better in 2026?</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>61.7</v>
+        <v>62.8</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>36.9</v>
+        <v>36.2</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1876,33 +1876,33 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket</t>
+          <t>page-guides/january-broadband-deals-uk</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Shortlist / compare-basket pattern</t>
+          <t>January broadband deals UK: new-year switching guide</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>61</v>
+        <v>61.7</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>64</v>
+        <v>36.9</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -1912,11 +1912,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr"/>
       <c r="K27" s="3" t="inlineStr"/>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>Shipped to Vercel production 2026-08-23: visitors can shortlist two or three providers on /compare, retain the shortlist in local storage, compare price, maximum speed, contract, setup fee, coverage and customer rating in responsive finalist cards, then continue to a provider review or tracked deal link. Includes accessible controls, a three-provider limit and GA4 shortlist/basket events.</t>
-        </is>
-      </c>
+      <c r="L27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1924,29 +1920,29 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>growth-awin-advertiser-outreach</t>
+          <t>feat-shortlist-compare-basket</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Partnerships</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Continue selective Awin advertiser outreach</t>
+          <t>Shortlist / compare-basket pattern</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1955,12 +1951,16 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Shipped to Vercel production 2026-08-23: visitors can shortlist two or three providers on /compare, retain the shortlist in local storage, compare price, maximum speed, contract, setup fee, coverage and customer rating in responsive finalist cards, then continue to a provider review or tracked deal link. Includes accessible controls, a three-provider limit and GA4 shortlist/basket events.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>content-awin-rejected-provider-deep-content</t>
+          <t>growth-awin-advertiser-outreach</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Partnerships</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Deep, researched content for Awin-rejected providers (BT, Virgin Media, EE, Vodafone, Plusnet, Hyperoptic, toob, giffgaff)</t>
+          <t>Continue selective Awin advertiser outreach</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
         <v>60</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr"/>
@@ -2012,33 +2012,33 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>page-tools/broadband-cost-calculator</t>
+          <t>content-awin-rejected-provider-deep-content</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Broadband cost calculator: true monthly and contract-length cost</t>
+          <t>Deep, researched content for Awin-rejected providers (BT, Virgin Media, EE, Vodafone, Plusnet, Hyperoptic, toob, giffgaff)</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>59.9</v>
+        <v>60</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>27.6</v>
+        <v>65</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2048,11 +2048,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>Live at /tools/broadband-cost-calculator, committed and deployed 2026-08-21.</t>
-        </is>
-      </c>
+      <c r="L30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -2060,7 +2056,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>page-providers/onestream</t>
+          <t>page-tools/broadband-cost-calculator</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2070,19 +2066,19 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Onestream — plans, coverage and Awin-tracked deals</t>
+          <t>Broadband cost calculator: true monthly and contract-length cost</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>59.4</v>
+        <v>59.9</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>28</v>
+        <v>27.6</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
@@ -2096,7 +2092,11 @@
       </c>
       <c r="J31" s="3" t="inlineStr"/>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Live at /tools/broadband-cost-calculator, committed and deployed 2026-08-21.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>page-guides/no-credit-check-broadband-uk</t>
+          <t>page-providers/onestream</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2119,18 +2119,18 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>No credit check broadband in the UK: options and what to expect</t>
+          <t>Onestream — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>34.8</v>
+        <v>28</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2148,38 +2148,38 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>feat-review-aggregation-module</t>
+          <t>page-guides/no-credit-check-broadband-uk</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Real review-aggregation trust module</t>
+          <t>No credit check broadband in the UK: options and what to expect</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>59</v>
+        <v>59.3</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>62</v>
+        <v>34.8</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr"/>
@@ -2192,38 +2192,38 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>page-providers/brsk</t>
+          <t>feat-review-aggregation-module</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Brsk — plans, coverage and Awin-tracked deals</t>
+          <t>Real review-aggregation trust module</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>59</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>28.5</v>
+        <v>62</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>page-guides/fttp-vs-fttc-explained</t>
+          <t>page-providers/brsk</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -2251,14 +2251,14 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>FTTP vs FTTC: what the difference means for your speed</t>
+          <t>Brsk — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>58.4</v>
+        <v>59</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>27.8</v>
+        <v>28.5</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>page-guides/best-mesh-wifi-for-your-broadband-router</t>
+          <t>page-guides/fttp-vs-fttc-explained</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2295,18 +2295,18 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
+          <t>FTTP vs FTTC: what the difference means for your speed</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
         <v>58.4</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>34</v>
+        <v>27.8</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>page-guides/broadband-help-if-you-claim-benefits-uk</t>
+          <t>page-guides/best-mesh-wifi-for-your-broadband-router</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2339,18 +2339,18 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
+          <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>58.2</v>
+        <v>58.4</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>27.5</v>
+        <v>34</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -2368,38 +2368,38 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ops-adsense-site-review</t>
+          <t>page-guides/broadband-help-if-you-claim-benefits-uk</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Complete AdSense site review and authorisation monitoring</t>
+          <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>58</v>
+        <v>58.2</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>55</v>
+        <v>27.5</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -2412,38 +2412,38 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>content-awin-approved-provider-deep-content</t>
+          <t>ops-adsense-site-review</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Deep, researched content for Awin-approved providers (TalkTalk, Zzoomm, Highland Broadband)</t>
+          <t>Complete AdSense site review and authorisation monitoring</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
         <v>58</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr"/>
@@ -2456,12 +2456,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>page-providers/gigaclear</t>
+          <t>content-awin-approved-provider-deep-content</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2471,18 +2471,18 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
+          <t>Deep, researched content for Awin-approved providers (TalkTalk, Zzoomm, Highland Broadband)</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>56.9</v>
+        <v>58</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>27.9</v>
+        <v>62</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>page-providers/youfibre</t>
+          <t>page-providers/gigaclear</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2515,14 +2515,14 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
+          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>56.6</v>
+        <v>56.9</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>28.7</v>
+        <v>27.9</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>page-providers/cuckoo</t>
+          <t>page-providers/youfibre</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
+          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>56.5</v>
+        <v>56.6</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>27.9</v>
+        <v>28.7</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2588,12 +2588,12 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>audit-city-hub-thinness</t>
+          <t>page-providers/cuckoo</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Content audit</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -2603,23 +2603,23 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Verify each new city hub has a genuinely local fact</t>
+          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>56</v>
+        <v>56.5</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>50</v>
+        <v>27.9</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr"/>
@@ -2632,12 +2632,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>ops-content-priority-analysis-tooling</t>
+          <t>audit-city-hub-thinness</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>Content audit</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2647,14 +2647,14 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Content priority analysis: real SEO + GEO signals, build vs. update on one list</t>
+          <t>Verify each new city hub has a genuinely local fact</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
         <v>56</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>page-guides/black-friday-broadband-deals-uk</t>
+          <t>ops-content-priority-analysis-tooling</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -2691,18 +2691,18 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
+          <t>Content priority analysis: real SEO + GEO signals, build vs. update on one list</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>55.8</v>
+        <v>56</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>page-providers/shell-energy</t>
+          <t>page-guides/black-friday-broadband-deals-uk</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2735,18 +2735,18 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
+          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>55.7</v>
+        <v>55.8</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>page-research/broadband-customer-service-rankings-uk</t>
+          <t>page-providers/shell-energy</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -2779,14 +2779,14 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
+          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>55.1</v>
+        <v>55.7</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
@@ -2808,33 +2808,33 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>feat-nav-header-footer-ia</t>
+          <t>page-research/broadband-customer-service-rankings-uk</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Navigation/header/footer IA improvements</t>
+          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>55</v>
+        <v>55.1</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>60</v>
+        <v>27.8</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2844,11 +2844,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>Shipped 2026-08-22: scripts/scrape_navigation_patterns.py scanned 5 best-in-class sites (broadband.co.uk stood out on sticky header + breadcrumbs + trust badge). Confirmed BroadbandPicker's sticky header and breadcrumbs already match best practice. Added Postcode to primary nav (desktop+mobile), restructured footer 4-&gt;6 columns adding Tools, Find Broadband by Area, and Research links to fix a crawl/link-equity gap for the 2,800+ postcode-district and tools pages. Deliberately did NOT fabricate a trust badge (no real Trustpilot/press presence yet) and did NOT widen the header postcode breakpoint (risk of stacking two unverified density changes without a browser check). See docs/navigation-ia-analysis.md.</t>
-        </is>
-      </c>
+      <c r="L48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
@@ -2856,7 +2852,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>feat-contact-form-email-delivery</t>
+          <t>feat-nav-header-footer-ia</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -2866,19 +2862,19 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Working contact form delivering to a real inbox, no third-party service</t>
+          <t>Navigation/header/footer IA improvements</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
         <v>55</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
@@ -2887,12 +2883,16 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr"/>
       <c r="K49" s="3" t="inlineStr"/>
-      <c r="L49" s="3" t="inlineStr"/>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-22: scripts/scrape_navigation_patterns.py scanned 5 best-in-class sites (broadband.co.uk stood out on sticky header + breadcrumbs + trust badge). Confirmed BroadbandPicker's sticky header and breadcrumbs already match best practice. Added Postcode to primary nav (desktop+mobile), restructured footer 4-&gt;6 columns adding Tools, Find Broadband by Area, and Research links to fix a crawl/link-equity gap for the 2,800+ postcode-district and tools pages. Deliberately did NOT fabricate a trust badge (no real Trustpilot/press presence yet) and did NOT widen the header postcode breakpoint (risk of stacking two unverified density changes without a browser check). See docs/navigation-ia-analysis.md.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -2900,38 +2900,38 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>content-awin-pending-provider-deep-content</t>
+          <t>feat-contact-form-email-delivery</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Deep, researched content for Awin-pending providers (Community Fibre, Cuckoo, Zen Internet, National Broadband, Trooli, Pine Media)</t>
+          <t>Working contact form delivering to a real inbox, no third-party service</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
         <v>55</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -2944,12 +2944,12 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
+          <t>content-awin-pending-provider-deep-content</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -2959,18 +2959,18 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Broadband complaints and the ombudsman: your UK rights</t>
+          <t>Deep, researched content for Awin-pending providers (Community Fibre, Cuckoo, Zen Internet, National Broadband, Trooli, Pine Media)</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>54.7</v>
+        <v>55</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>25.9</v>
+        <v>58</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>growth-original-research-outreach</t>
+          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3003,23 +3003,23 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Run original-research outreach and digital PR</t>
+          <t>Broadband complaints and the ombudsman: your UK rights</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>54</v>
+        <v>54.7</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>68</v>
+        <v>25.9</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -3032,29 +3032,29 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>content-refresh-best-full-fibre-guide</t>
+          <t>growth-original-research-outreach</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Deep rewrite: Best Full Fibre Broadband UK guide (top content-priority-analysis target)</t>
+          <t>Run original-research outreach and digital PR</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
         <v>54</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr"/>
@@ -3076,29 +3076,29 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>growth-quarterly-data-reprioritisation</t>
+          <t>content-refresh-best-full-fibre-guide</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
+          <t>Deep rewrite: Best Full Fibre Broadband UK guide (top content-priority-analysis target)</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -3120,29 +3120,29 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>feat-postcode-journey-personalisation</t>
+          <t>growth-quarterly-data-reprioritisation</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
         <v>53</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr"/>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>feat-homepage-visual-redesign</t>
+          <t>feat-postcode-journey-personalisation</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3179,11 +3179,11 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Homepage visual redesign: illustrations + interactivity</t>
+          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>55</v>
@@ -3208,22 +3208,22 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>content-refresh-cheapest-broadband-guide</t>
+          <t>feat-homepage-visual-redesign</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Deep rewrite: Cheapest Broadband Deals UK guide (2nd content-priority-analysis target)</t>
+          <t>Homepage visual redesign: illustrations + interactivity</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
@@ -3252,29 +3252,29 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>feat-mobile-cross-device-navigation</t>
+          <t>content-refresh-cheapest-broadband-guide</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Mobile and cross-device navigation overhaul</t>
+          <t>Deep rewrite: Cheapest Broadband Deals UK guide (2nd content-priority-analysis target)</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>feat-mega-menu-navigation</t>
+          <t>feat-mobile-cross-device-navigation</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -3311,14 +3311,14 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Mobile and cross-device navigation overhaul</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>feat-animated-interactive-mobile-menu</t>
+          <t>feat-mega-menu-navigation</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3355,14 +3355,14 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Animated, interactive mobile menu with click-outside-to-close</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
         <v>50</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3384,29 +3384,29 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>content-refresh-best-business-broadband-guide</t>
+          <t>feat-animated-interactive-mobile-menu</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Deep rewrite: Best Business Broadband Providers UK guide (3rd content-priority-analysis target)</t>
+          <t>Animated, interactive mobile menu with click-outside-to-close</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
@@ -3428,29 +3428,29 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>feat-price-drop-alerts</t>
+          <t>content-refresh-best-business-broadband-guide</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Deep rewrite: Best Business Broadband Providers UK guide (3rd content-priority-analysis target)</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>feat-page-type-ux-redesign</t>
+          <t>feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -3482,19 +3482,19 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
         <v>49</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr"/>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>feat-footer-logo-interactivity</t>
+          <t>feat-page-type-ux-redesign</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3531,18 +3531,18 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3552,11 +3552,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
-        </is>
-      </c>
+      <c r="L64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
@@ -3564,33 +3560,33 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>content-refresh-best-broadband-tv-deals-guide</t>
+          <t>feat-footer-logo-interactivity</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Research-led editorial refresh: Best Broadband and TV Deals guide</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
         <v>48</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -3600,7 +3596,11 @@
       </c>
       <c r="J65" s="3" t="inlineStr"/>
       <c r="K65" s="3" t="inlineStr"/>
-      <c r="L65" s="3" t="inlineStr"/>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -3608,29 +3608,29 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>audit-core-web-vitals-reporting</t>
+          <t>content-refresh-best-broadband-tv-deals-guide</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Research-led editorial refresh: Best Broadband and TV Deals guide</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -3652,38 +3652,38 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>ops-awin-publisher-api-integration</t>
+          <t>audit-core-web-vitals-reporting</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Direct Awin Publisher API access — programme status and link generation</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
         <v>47</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr"/>
@@ -3696,33 +3696,33 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>content-refresh-best-5g-home-broadband-guide</t>
+          <t>ops-awin-publisher-api-integration</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Deep rewrite: Best 5G Home Broadband UK guide (4th content-priority-analysis target)</t>
+          <t>Direct Awin Publisher API access — programme status and link generation</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
         <v>47</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3740,29 +3740,29 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>content-refresh-best-5g-home-broadband-guide</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Deep rewrite: Best 5G Home Broadband UK guide (4th content-priority-analysis target)</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr"/>
@@ -3784,29 +3784,29 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>content-refresh-best-phone-and-broadband-deals-guide</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Deep rewrite: Best Phone and Broadband Deals guide (5th content-priority-analysis target)</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
         <v>45</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
@@ -3828,38 +3828,38 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>audit-broken-links-redirects</t>
+          <t>content-refresh-best-phone-and-broadband-deals-guide</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Deep rewrite: Best Phone and Broadband Deals guide (5th content-priority-analysis target)</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G71" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="G71" s="3" t="n">
-        <v>48</v>
-      </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr"/>
@@ -3872,33 +3872,33 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-broken-links-redirects</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -3926,19 +3926,19 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3970,19 +3970,19 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3998,8 +3998,52 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
     </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr"/>
+      <c r="K75" s="3" t="inlineStr"/>
+      <c r="L75" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L74"/>
+  <autoFilter ref="A1:L75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6751,7 +6795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7116,29 +7160,29 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Validate conversion events and establish the GSC/analytics reporting loop</t>
+          <t>Deep rewrite: Sky provider page (6th content-priority-analysis target, first provider-type page)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Confirm postcode submits, speed-test completions, filter use, outbound provider clicks and assisted conversions are recorded reliably, then use query and engagement evidence to reprioritise future work.</t>
+          <t>Sixth target from scripts/analyze_content_priority.py's ranked list, and the first provider-page (not guide-page) target: /providers/sky carries the single highest mapped search volume of any page on the site (172,237/mo) but was only 387 words with no excerpt or contentSections at all -- the sky entry in data/providers.ts was missing those two fields entirely, unlike the already-rewritten bt and virgin-media entries. Rewritten to ~1,700 words with 6 contentSections (deals, Openreach network/speeds, the April 2026 flat GBP3 price rise -- Sky's first year using pounds-and-pence instead of a percentage, down from 6.2% in 2025 -- Sky Broadband Shield/TV bundles, a Trustpilot-vs-Ofcom section, and a final verdict), plus 4 FAQs and full reviewSources. Corrected 3 stale top-level fields that were actively wrong: trustpilotScore 3.8 -&gt; 2.7 (cross-checked against this site's own existing bt-vs-sky and sky-vs-vodafone comparison pages, which already used 2.7 as of 21 August 2026 -- caught and fixed a first-pass error of my own where a single WebFetch summary suggested 1.4, before corroborating against two independent sources and this site's own prior content), contractLengths [18] -&gt; [24] (Sky has not offered an 18-month contract for some time), and monthlyPriceFrom 25.00 -&gt; 23.00 to match the real current cheapest tier (Superfast, 67 Mbps).</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -7147,12 +7191,12 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>GSC, analytics and conversion reporting</t>
+          <t>data/providers.ts (sky)</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Sufficient live traffic and event data</t>
+          <t>ops-content-priority-analysis-tooling</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -7162,7 +7206,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Build Status / Technical SEO</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7172,29 +7216,29 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Shortlist / compare-basket pattern</t>
+          <t>Validate conversion events and establish the GSC/analytics reporting loop</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Let users tick 2–3 deals and see them side by side, matching Uswitch and broadband.co.uk. Current /compare is one full table — good for browsing, weaker for a final decision between finalists.</t>
+          <t>Confirm postcode submits, speed-test completions, filter use, outbound provider clicks and assisted conversions are recorded reliably, then use query and engagement evidence to reprioritise future work.</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -7203,12 +7247,12 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>app/compare</t>
+          <t>GSC, analytics and conversion reporting</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Sufficient live traffic and event data</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -7218,7 +7262,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Build Status / Technical SEO</t>
         </is>
       </c>
     </row>
@@ -7228,29 +7272,29 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Partnerships</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Continue selective Awin advertiser outreach</t>
+          <t>Shortlist / compare-basket pattern</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Apply to best-fit provider programmes with tailored pitches, relevant live URLs, audience evidence, promotional method and compliance controls; log decisions and feedback. Real status pulled from the Awin Publisher API 2026-08-23 (see ops-awin-publisher-api-integration): joined -- TalkTalk, Broadband Genie, Zzoomm, Highland Broadband. Pending -- Sky ROI, Community Fibre, National Broadband, Trooli, Pine Media, Cuckoo, Zen Internet. Rejected -- BT (consumer + business), Vodafone, Plusnet, EE, Virgin Media, Hyperoptic, toob, giffgaff. The 8 rejected mainstream providers are the priority re-application targets; Zzoomm and Highland Broadband are approved but not yet added as providers on the site at all.</t>
+          <t>Let users tick 2–3 deals and see them side by side, matching Uswitch and broadband.co.uk. Current /compare is one full table — good for browsing, weaker for a final decision between finalists.</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -7259,22 +7303,22 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Awin publisher 2942019 and partner application log</t>
+          <t>app/compare</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Current audience evidence and compliant commercial pages</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: 90 Day Roadmap</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -7284,53 +7328,53 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Partnerships</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Deep, researched content for Awin-rejected providers (BT, Virgin Media, EE, Vodafone, Plusnet, Hyperoptic, toob, giffgaff)</t>
+          <t>Continue selective Awin advertiser outreach</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Third and final batch in the Awin content series (after approved and pending), covering all 8 real providers rejected on Awin: BT (both consumer 3041 and business 3042 programmes), Virgin Media, EE, Vodafone, Plusnet, Hyperoptic, toob and giffgaff. All 7 existing entries were thin (no contentSections) and fully rewritten; giffgaff did not exist on the site at all and was added new. IMPORTANT CORRECTION made mid-batch: while researching BT's price rise, discovered Ofcom banned inflation-linked/percentage-based mid-contract price rise terms in all new contracts from 17 January 2025 (providers must now disclose a flat pounds-and-pence figure instead). This retroactively invalidated 5 sentences written in the two earlier Awin batches (Community Fibre, Zen Internet and Zzoomm entries in data/providers.ts, plus the Community Fibre vs Hyperoptic comparison) that described CPI-linked percentage rises as a current practice -- all 5 were corrected in this same batch before continuing, and this correction is itself the kind of thing worth surfacing: a fact later research revealed to be wrong wasn't left standing. Real findings surfaced across this batch: BT and EE both maintain two separate Trustpilot pages (a mobile/brand-dominated headline score and a much lower broadband-specific one, roughly 4.0 vs 1.5 for BT, 4.2 vs 1.3 for EE) -- the broadband-specific figure was used as the primary trustpilotScore field in both cases, with the discrepancy explained in the copy since it's a genuinely useful, non-obvious insight. Plusnet's low Trustpilot score sits alongside the *best* Ofcom complaints record of any major UK provider (4 per 100,000 in Q1 2026, against TalkTalk's 10, Vodafone's 8 and BT's 7) -- a real, evidenced gap between self-selected review-platform sentiment and regulatory complaint-volume data, explained rather than picking one source and ignoring the other. Virgin Media shows the same pattern in reverse: an extremely low Trustpilot score (~1.4) next to an Ofcom complaints record at or below the industry average. giffgaff is a genuinely new product (broadband launched September 2025 on Nexfibre, the Virgin Media O2 wholesale network, not Openreach) with no separate broadband Trustpilot page yet -- flagged honestly as thin evidence rather than borrowing giffgaff's much larger mobile-customer score uncritically. All affiliateUrl values stay as each provider's own plain site URL, since Awin rejected these applications outright (not merely pending) -- every reviewSources array states this explicitly. Three new comparison pages targeting genuine content gaps rather than one-per-provider completeness (this batch's providers already had extensive existing head-to-head coverage from earlier site work): bt-vs-hyperoptic (safe wide-coverage default vs better-value niche upgrade), plusnet-vs-ee (same BT Group parent, opposite ends of Ofcom's complaints table), toob-vs-giffgaff (two newer no-price-rise challenger brands on completely different networks). All copy hand-checked for zero em dashes and zero banned AI-tell vocabulary/phrases.</t>
+          <t>Apply to best-fit provider programmes with tailored pitches, relevant live URLs, audience evidence, promotional method and compliance controls; log decisions and feedback. Real status pulled from the Awin Publisher API 2026-08-23 (see ops-awin-publisher-api-integration): joined -- TalkTalk, Broadband Genie, Zzoomm, Highland Broadband. Pending -- Sky ROI, Community Fibre, National Broadband, Trooli, Pine Media, Cuckoo, Zen Internet. Rejected -- BT (consumer + business), Vodafone, Plusnet, EE, Virgin Media, Hyperoptic, toob, giffgaff. The 8 rejected mainstream providers are the priority re-application targets; Zzoomm and Highland Broadband are approved but not yet added as providers on the site at all.</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>60</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>data/providers.ts (bt, virgin-media, ee, vodafone, plusnet, hyperoptic, toob, giffgaff, plus corrections to community-fibre, zen-internet, zzoomm), data/provider-comparisons.ts (bt-vs-hyperoptic, plusnet-vs-ee, toob-vs-giffgaff, plus a correction to community-fibre-vs-hyperoptic), public/logos/giffgaff.svg</t>
+          <t>Awin publisher 2942019 and partner application log</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>ops-awin-publisher-api-integration, content-awin-approved-provider-deep-content, content-awin-pending-provider-deep-content</t>
+          <t>Current audience evidence and compliant commercial pages</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: 90 Day Roadmap</t>
         </is>
       </c>
     </row>
@@ -7340,53 +7384,53 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Real review-aggregation trust module</t>
+          <t>Deep, researched content for Awin-rejected providers (BT, Virgin Media, EE, Vodafone, Plusnet, Hyperoptic, toob, giffgaff)</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Blend the existing Ofcom-complaints research methodology with live Trustpilot scores into one visible trust module reused across provider and comparison pages, instead of a single quoted score per page.</t>
+          <t>Third and final batch in the Awin content series (after approved and pending), covering all 8 real providers rejected on Awin: BT (both consumer 3041 and business 3042 programmes), Virgin Media, EE, Vodafone, Plusnet, Hyperoptic, toob and giffgaff. All 7 existing entries were thin (no contentSections) and fully rewritten; giffgaff did not exist on the site at all and was added new. IMPORTANT CORRECTION made mid-batch: while researching BT's price rise, discovered Ofcom banned inflation-linked/percentage-based mid-contract price rise terms in all new contracts from 17 January 2025 (providers must now disclose a flat pounds-and-pence figure instead). This retroactively invalidated 5 sentences written in the two earlier Awin batches (Community Fibre, Zen Internet and Zzoomm entries in data/providers.ts, plus the Community Fibre vs Hyperoptic comparison) that described CPI-linked percentage rises as a current practice -- all 5 were corrected in this same batch before continuing, and this correction is itself the kind of thing worth surfacing: a fact later research revealed to be wrong wasn't left standing. Real findings surfaced across this batch: BT and EE both maintain two separate Trustpilot pages (a mobile/brand-dominated headline score and a much lower broadband-specific one, roughly 4.0 vs 1.5 for BT, 4.2 vs 1.3 for EE) -- the broadband-specific figure was used as the primary trustpilotScore field in both cases, with the discrepancy explained in the copy since it's a genuinely useful, non-obvious insight. Plusnet's low Trustpilot score sits alongside the *best* Ofcom complaints record of any major UK provider (4 per 100,000 in Q1 2026, against TalkTalk's 10, Vodafone's 8 and BT's 7) -- a real, evidenced gap between self-selected review-platform sentiment and regulatory complaint-volume data, explained rather than picking one source and ignoring the other. Virgin Media shows the same pattern in reverse: an extremely low Trustpilot score (~1.4) next to an Ofcom complaints record at or below the industry average. giffgaff is a genuinely new product (broadband launched September 2025 on Nexfibre, the Virgin Media O2 wholesale network, not Openreach) with no separate broadband Trustpilot page yet -- flagged honestly as thin evidence rather than borrowing giffgaff's much larger mobile-customer score uncritically. All affiliateUrl values stay as each provider's own plain site URL, since Awin rejected these applications outright (not merely pending) -- every reviewSources array states this explicitly. Three new comparison pages targeting genuine content gaps rather than one-per-provider completeness (this batch's providers already had extensive existing head-to-head coverage from earlier site work): bt-vs-hyperoptic (safe wide-coverage default vs better-value niche upgrade), plusnet-vs-ee (same BT Group parent, opposite ends of Ofcom's complaints table), toob-vs-giffgaff (two newer no-price-rise challenger brands on completely different networks). All copy hand-checked for zero em dashes and zero banned AI-tell vocabulary/phrases.</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>New shared component, used on provider + comparison pages</t>
+          <t>data/providers.ts (bt, virgin-media, ee, vodafone, plusnet, hyperoptic, toob, giffgaff, plus corrections to community-fibre, zen-internet, zzoomm), data/provider-comparisons.ts (bt-vs-hyperoptic, plusnet-vs-ee, toob-vs-giffgaff, plus a correction to community-fibre-vs-hyperoptic), public/logos/giffgaff.svg</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>ops-awin-publisher-api-integration, content-awin-approved-provider-deep-content, content-awin-pending-provider-deep-content</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7396,53 +7440,53 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Complete AdSense site review and authorisation monitoring</t>
+          <t>Real review-aggregation trust module</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Monitor the existing AdSense review, consent implementation and ads.txt authorisation; resolve any concrete policy or crawler issue reported by AdSense.</t>
+          <t>Blend the existing Ofcom-complaints research methodology with live Trustpilot scores into one visible trust module reused across provider and comparison pages, instead of a single quoted score per page.</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>AdSense status and /ads.txt</t>
+          <t>New shared component, used on provider + comparison pages</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Google site-review processing</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Build Status</t>
+          <t>Growth playbook — Functionality pillar</t>
         </is>
       </c>
     </row>
@@ -7452,53 +7496,53 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Deep, researched content for Awin-approved providers (TalkTalk, Zzoomm, Highland Broadband)</t>
+          <t>Complete AdSense site review and authorisation monitoring</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Following the Awin programme-status pull (ops-awin-publisher-api-integration), built full researched content for the 3 real providers among the 4 joined programmes (Broadband Genie is a comparison site, not an ISP, and was excluded). Per docs/page-build-pipeline-brief.md Stage 3/4/4a: for each provider, fetched the provider's own site for current pricing/speeds/contract terms, WebSearched Trustpilot and, where relevant, Ofcom's own complaints data, and wrote an 8-section contentSections block plus FAQs matching the site's deepest existing template (Gigaclear). All copy hand-checked for zero em dashes and zero banned AI-tell vocabulary/phrases per the Stage 4a list. TalkTalk's existing entry was materially stale (Trustpilot claimed 2.8, real current figure 1.5 from 50k+ reviews in Trustpilot's 'Bad' band; Ofcom's Q1 2026 report names TalkTalk the UK's most complained-about broadband provider for the third consecutive quarter; the old 'price-lock guarantee' highlight was false, two scheduled April 2027/2028 rises are now built into every contract) -- fully rewritten, not just extended. Zzoomm and Highland Broadband were brand-new Provider entries (real Awin tracking links, placeholder text-wordmark logos per the brief's guardrail against fabricating brand marks). In passing, corrected Plusnet's stale trustpilotScore field (3.9 -&gt; 2.0, the real current figure) since new comparison copy was about to cite it -- Plusnet's own deep content rewrite is out of scope (not an Awin-approved programme). Two new comparison pages: talktalk-vs-plusnet (a genuinely stark, well-evidenced contrast -- same price bracket, opposite ends of Ofcom's complaints table) and zzoomm-vs-hyperoptic (two symmetrical full-fibre altnets with almost non-overlapping coverage footprints). Internal linking relies on the existing 'How {provider} compares' module built earlier this session; both new comparisons are discoverable via /providers/compare and the sitemap even where they don't make a crowded provider's top-3 related slice.</t>
+          <t>Monitor the existing AdSense review, consent implementation and ads.txt authorisation; resolve any concrete policy or crawler issue reported by AdSense.</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
         <v>58</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>data/providers.ts (talktalk, zzoomm, highland-broadband, plusnet trustpilotScore), data/provider-comparisons.ts (talktalk-vs-plusnet, zzoomm-vs-hyperoptic), public/logos/zzoomm.svg, public/logos/highland-broadband.svg</t>
+          <t>AdSense status and /ads.txt</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>ops-awin-publisher-api-integration</t>
+          <t>Google site-review processing</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Build Status</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7552,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Content audit</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -7518,43 +7562,43 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Verify each new city hub has a genuinely local fact</t>
+          <t>Deep, researched content for Awin-approved providers (TalkTalk, Zzoomm, Highland Broadband)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8 new city hubs (Birmingham, Bristol, Edinburgh, Glasgow, Leeds, Liverpool, Manchester, Sheffield) plus 50 existing postcode-prefix pages is a lot of near-identical templates. Each needs at least one real local fact (a named local altnet, a real coverage figure) or it reads as duplicate content — audit before building the next batch of cities.</t>
+          <t>Following the Awin programme-status pull (ops-awin-publisher-api-integration), built full researched content for the 3 real providers among the 4 joined programmes (Broadband Genie is a comparison site, not an ISP, and was excluded). Per docs/page-build-pipeline-brief.md Stage 3/4/4a: for each provider, fetched the provider's own site for current pricing/speeds/contract terms, WebSearched Trustpilot and, where relevant, Ofcom's own complaints data, and wrote an 8-section contentSections block plus FAQs matching the site's deepest existing template (Gigaclear). All copy hand-checked for zero em dashes and zero banned AI-tell vocabulary/phrases per the Stage 4a list. TalkTalk's existing entry was materially stale (Trustpilot claimed 2.8, real current figure 1.5 from 50k+ reviews in Trustpilot's 'Bad' band; Ofcom's Q1 2026 report names TalkTalk the UK's most complained-about broadband provider for the third consecutive quarter; the old 'price-lock guarantee' highlight was false, two scheduled April 2027/2028 rises are now built into every contract) -- fully rewritten, not just extended. Zzoomm and Highland Broadband were brand-new Provider entries (real Awin tracking links, placeholder text-wordmark logos per the brief's guardrail against fabricating brand marks). In passing, corrected Plusnet's stale trustpilotScore field (3.9 -&gt; 2.0, the real current figure) since new comparison copy was about to cite it -- Plusnet's own deep content rewrite is out of scope (not an Awin-approved programme). Two new comparison pages: talktalk-vs-plusnet (a genuinely stark, well-evidenced contrast -- same price bracket, opposite ends of Ofcom's complaints table) and zzoomm-vs-hyperoptic (two symmetrical full-fibre altnets with almost non-overlapping coverage footprints). Internal linking relies on the existing 'How {provider} compares' module built earlier this session; both new comparisons are discoverable via /providers/compare and the sitemap even where they don't make a crowded provider's top-3 related slice.</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>data/priority-pages.ts city entries</t>
+          <t>data/providers.ts (talktalk, zzoomm, highland-broadband, plusnet trustpilotScore), data/provider-comparisons.ts (talktalk-vs-plusnet, zzoomm-vs-hyperoptic), public/logos/zzoomm.svg, public/logos/highland-broadband.svg</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ops-awin-publisher-api-integration</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7564,7 +7608,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>Content audit</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -7574,19 +7618,19 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Content priority analysis: real SEO + GEO signals, build vs. update on one list</t>
+          <t>Verify each new city hub has a genuinely local fact</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>User asked for a script that does detailed SEO analysis of the site's own data and prioritises what to build vs. update, weighting generative-AI/GEO reports specifically. Built scripts/analyze_content_priority.py: combines real mapped search volume already researched in docs/broadbandpicker-keyword-mapping.xlsx with a live crawl of every provider/comparison/guide page (word count against this session's own depth floors, FAQPage schema, a detectable answer-first paragraph, a parsed checked/reviewed date). Mid-build discovered the user's actual request: a real Google Search Console 'Performance on Search Generative AI Features' export had been dropped into data/GSC/, which is ground truth for AI Overview surfacing, not a proxy -- rebuilt the script to load and heavily weight it. Caught and fixed two real bugs before reporting any findings: word counts of 15k-17k+ caused by the React RSC hydration payload inside &lt;script&gt; tags being counted as visible text, and every page falsely flagging 'no answer-first paragraph' because the &lt;p&gt; search matched header mega-menu labels before reaching the main content -- both fixed by parsing with lxml, stripping script/style, and scoping to &lt;main&gt;. Real finding once the GSC data was wired in: /guides/best-full-fibre-broadband-uk earned 512 real AI-feature impressions in the last 28 days while sitting at 636 words, the clearest 'already working, just needs depth' signal on the site -- now the top-ranked refresh target, above even /providers/sky's 172,237 monthly search volume, since Sky currently earns almost no AI-feature traction (4 impressions) and represents a different kind of opportunity. Sky also does not appear in any of the 3 Awin relationship lists at all (joined/pending/rejected), confirmed via a direct re-check -- no record of ever applying. Every row in the Content Gap Roadmap is already marked built (33/33), so there are currently no new-page gaps on the existing curated keyword list. Findings written up in docs/content-priority-analysis.md.</t>
+          <t>8 new city hubs (Birmingham, Bristol, Edinburgh, Glasgow, Leeds, Liverpool, Manchester, Sheffield) plus 50 existing postcode-prefix pages is a lot of near-identical templates. Each needs at least one real local fact (a named local altnet, a real coverage figure) or it reads as duplicate content — audit before building the next batch of cities.</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
         <v>56</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -7595,22 +7639,22 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>scripts/analyze_content_priority.py</t>
+          <t>data/priority-pages.ts city entries</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>docs/broadbandpicker-keyword-mapping.xlsx (existing keyword research)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -7620,43 +7664,43 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Navigation/header/footer IA improvements</t>
+          <t>Content priority analysis: real SEO + GEO signals, build vs. update on one list</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Researched via scripts/scrape_navigation_patterns.py against 5 best-in-class sites. broadband.co.uk (closest single-vertical comparable) stood out on sticky header, breadcrumbs and a trust badge near the top; BroadbandPicker already matches on the first two. Header nav link count split cleanly into supersite (127-556 links) vs specialist (21 links) patterns, confirming the growth playbook's 'specialist, not supersite' positioning. Added Postcode to primary nav; restructured the footer from 4 to 6 columns (added Tools, Find Broadband by Area, Research) to fix a crawl/link-equity gap for the postcode-district and tools pages built this session.</t>
+          <t>User asked for a script that does detailed SEO analysis of the site's own data and prioritises what to build vs. update, weighting generative-AI/GEO reports specifically. Built scripts/analyze_content_priority.py: combines real mapped search volume already researched in docs/broadbandpicker-keyword-mapping.xlsx with a live crawl of every provider/comparison/guide page (word count against this session's own depth floors, FAQPage schema, a detectable answer-first paragraph, a parsed checked/reviewed date). Mid-build discovered the user's actual request: a real Google Search Console 'Performance on Search Generative AI Features' export had been dropped into data/GSC/, which is ground truth for AI Overview surfacing, not a proxy -- rebuilt the script to load and heavily weight it. Caught and fixed two real bugs before reporting any findings: word counts of 15k-17k+ caused by the React RSC hydration payload inside &lt;script&gt; tags being counted as visible text, and every page falsely flagging 'no answer-first paragraph' because the &lt;p&gt; search matched header mega-menu labels before reaching the main content -- both fixed by parsing with lxml, stripping script/style, and scoping to &lt;main&gt;. Real finding once the GSC data was wired in: /guides/best-full-fibre-broadband-uk earned 512 real AI-feature impressions in the last 28 days while sitting at 636 words, the clearest 'already working, just needs depth' signal on the site -- now the top-ranked refresh target, above even /providers/sky's 172,237 monthly search volume, since Sky currently earns almost no AI-feature traction (4 impressions) and represents a different kind of opportunity. Sky also does not appear in any of the 3 Awin relationship lists at all (joined/pending/rejected), confirmed via a direct re-check -- no record of ever applying. Every row in the Content Gap Roadmap is already marked built (33/33), so there are currently no new-page gaps on the existing curated keyword list. Findings written up in docs/content-priority-analysis.md.</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>60</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>app/layout.tsx</t>
+          <t>scripts/analyze_content_priority.py</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>docs/broadbandpicker-keyword-mapping.xlsx (existing keyword research)</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -7666,7 +7710,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-22 — researched before implementing per the Strategic Lens process</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7681,24 +7725,24 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Working contact form delivering to a real inbox, no third-party service</t>
+          <t>Navigation/header/footer IA improvements</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Previously /contact only offered mailto: links to unverified custom-domain addresses (editorial@/partnerships@/hello@broadbandpicker.co.uk). Built a real contact form (components/ContactForm.tsx) posting to a new app/api/contact route, which sends via Gmail SMTP using nodemailer — no Supabase, no database, no third-party form/CRM service, per explicit instruction. All submissions land in sayedsahil.elt@gmail.com (CONTACT_TO_EMAIL env var), sent from a Gmail account authenticated with an App Password (CONTACT_SMTP_USER / CONTACT_SMTP_PASS). Reply-To is set to the sender's own address so replying goes straight back to them. Spam mitigation without any external service: a hidden honeypot field (bots that fill every input get silently dropped) and a submit-time check rejecting anything sent under 1.5s after the form rendered. Server-side validates name/email/reason/message independently of the client. The original mailto: cards are kept underneath as a secondary direct-email option. Requires CONTACT_SMTP_USER/PASS to be set in Vercel — the API route fails gracefully with a friendly error and a server log line if they're absent, rather than silently dropping messages.</t>
+          <t>Researched via scripts/scrape_navigation_patterns.py against 5 best-in-class sites. broadband.co.uk (closest single-vertical comparable) stood out on sticky header, breadcrumbs and a trust badge near the top; BroadbandPicker already matches on the first two. Header nav link count split cleanly into supersite (127-556 links) vs specialist (21 links) patterns, confirming the growth playbook's 'specialist, not supersite' positioning. Added Postcode to primary nav; restructured the footer from 4 to 6 columns (added Tools, Find Broadband by Area, Research) to fix a crawl/link-equity gap for the postcode-district and tools pages built this session.</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
         <v>55</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -7707,22 +7751,22 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>app/api/contact/route.ts, components/ContactForm.tsx, app/contact/page.tsx</t>
+          <t>app/layout.tsx</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>CONTACT_SMTP_USER / CONTACT_SMTP_PASS Gmail App Password set in Vercel env vars</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>User request 2026-08-22 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7732,48 +7776,48 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Deep, researched content for Awin-pending providers (Community Fibre, Cuckoo, Zen Internet, National Broadband, Trooli, Pine Media)</t>
+          <t>Working contact form delivering to a real inbox, no third-party service</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Follow-up to content-awin-approved-provider-deep-content, extending the same research process to the 6 real UK-relevant advertisers pending Awin approval (Sky ROI excluded -- Republic of Ireland Sky, not UK, out of scope for a UK site, confirmed with the user). Community Fibre and Zen Internet were existing but thin entries, fully rewritten. Cuckoo was already deep and dated the previous day; verified rather than rewritten. National Broadband, Trooli and Pine Media were brand-new Provider entries. National Broadband is the site's first 4G/5G fixed-wireless provider (a genuinely new content category, not another fibre altnet); Pine Media is a hyperlocal single-city (Sheffield-only) provider with a two-tier product split (its own symmetrical GIG network vs an Openreach-based GLO product) that needed explaining clearly to avoid conflating the two. Key design decision: because these programmes are pending, not joined, affiliateUrl stays as each provider's own plain site URL rather than an Awin tracking link -- confirmed via a live API test that Awin's linkbuilder will generate a structurally valid tracking URL even for a pending programme, which would be misleading to publish since it likely would not earn commission (or could breach Awin's terms) before approval. Each reviewSources array carries an explicit 'pending, not yet approved' note on the Awin source, matching the existing Gigaclear convention. All copy hand-checked for zero em dashes and zero banned AI-tell vocabulary/phrases. Three new comparison pages, chosen for genuine evidentiary value over one-per-provider completeness: community-fibre-vs-hyperoptic (London's two biggest symmetrical altnets, direct competitors), trooli-vs-zzoomm (two multi-region altnets with near-zero coverage overlap and matching no-price-rise policies), and national-broadband-vs-highland-broadband (5G available now vs fibre still being built -- a genuine buy-now-or-wait decision for the same rural Scottish customer). Cuckoo, Zen Internet and Pine Media were deliberately left without a new comparison this round -- no natural, non-forced head-to-head partner existed for any of them without inventing artificial relevance.</t>
+          <t>Previously /contact only offered mailto: links to unverified custom-domain addresses (editorial@/partnerships@/hello@broadbandpicker.co.uk). Built a real contact form (components/ContactForm.tsx) posting to a new app/api/contact route, which sends via Gmail SMTP using nodemailer — no Supabase, no database, no third-party form/CRM service, per explicit instruction. All submissions land in sayedsahil.elt@gmail.com (CONTACT_TO_EMAIL env var), sent from a Gmail account authenticated with an App Password (CONTACT_SMTP_USER / CONTACT_SMTP_PASS). Reply-To is set to the sender's own address so replying goes straight back to them. Spam mitigation without any external service: a hidden honeypot field (bots that fill every input get silently dropped) and a submit-time check rejecting anything sent under 1.5s after the form rendered. Server-side validates name/email/reason/message independently of the client. The original mailto: cards are kept underneath as a secondary direct-email option. Requires CONTACT_SMTP_USER/PASS to be set in Vercel — the API route fails gracefully with a friendly error and a server log line if they're absent, rather than silently dropping messages.</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
         <v>55</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>data/providers.ts (community-fibre, cuckoo, zen-internet, national-broadband, trooli, pine-media), data/provider-comparisons.ts (community-fibre-vs-hyperoptic, trooli-vs-zzoomm, national-broadband-vs-highland-broadband), public/logos/national-broadband.svg, public/logos/trooli.svg, public/logos/pine-media.svg</t>
+          <t>app/api/contact/route.ts, components/ContactForm.tsx, app/contact/page.tsx</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>content-awin-approved-provider-deep-content, ops-awin-publisher-api-integration</t>
+          <t>CONTACT_SMTP_USER / CONTACT_SMTP_PASS Gmail App Password set in Vercel env vars</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -7788,7 +7832,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -7798,43 +7842,43 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Run original-research outreach and digital PR</t>
+          <t>Deep, researched content for Awin-pending providers (Community Fibre, Cuckoo, Zen Internet, National Broadband, Trooli, Pine Media)</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Build a relevant outreach list and earn citations and links to the live Ofcom-backed customer-satisfaction research.</t>
+          <t>Follow-up to content-awin-approved-provider-deep-content, extending the same research process to the 6 real UK-relevant advertisers pending Awin approval (Sky ROI excluded -- Republic of Ireland Sky, not UK, out of scope for a UK site, confirmed with the user). Community Fibre and Zen Internet were existing but thin entries, fully rewritten. Cuckoo was already deep and dated the previous day; verified rather than rewritten. National Broadband, Trooli and Pine Media were brand-new Provider entries. National Broadband is the site's first 4G/5G fixed-wireless provider (a genuinely new content category, not another fibre altnet); Pine Media is a hyperlocal single-city (Sheffield-only) provider with a two-tier product split (its own symmetrical GIG network vs an Openreach-based GLO product) that needed explaining clearly to avoid conflating the two. Key design decision: because these programmes are pending, not joined, affiliateUrl stays as each provider's own plain site URL rather than an Awin tracking link -- confirmed via a live API test that Awin's linkbuilder will generate a structurally valid tracking URL even for a pending programme, which would be misleading to publish since it likely would not earn commission (or could breach Awin's terms) before approval. Each reviewSources array carries an explicit 'pending, not yet approved' note on the Awin source, matching the existing Gigaclear convention. All copy hand-checked for zero em dashes and zero banned AI-tell vocabulary/phrases. Three new comparison pages, chosen for genuine evidentiary value over one-per-provider completeness: community-fibre-vs-hyperoptic (London's two biggest symmetrical altnets, direct competitors), trooli-vs-zzoomm (two multi-region altnets with near-zero coverage overlap and matching no-price-rise policies), and national-broadband-vs-highland-broadband (5G available now vs fibre still being built -- a genuine buy-now-or-wait decision for the same rural Scottish customer). Cuckoo, Zen Internet and Pine Media were deliberately left without a new comparison this round -- no natural, non-forced head-to-head partner existed for any of them without inventing artificial relevance.</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>/research/uk-broadband-customer-satisfaction</t>
+          <t>data/providers.ts (community-fibre, cuckoo, zen-internet, national-broadband, trooli, pine-media), data/provider-comparisons.ts (community-fibre-vs-hyperoptic, trooli-vs-zzoomm, national-broadband-vs-highland-broadband), public/logos/national-broadband.svg, public/logos/trooli.svg, public/logos/pine-media.svg</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Research page and source methodology are live</t>
+          <t>content-awin-approved-provider-deep-content, ops-awin-publisher-api-integration</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Build Status / 90 Day Roadmap</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7844,29 +7888,29 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Deep rewrite: Best Full Fibre Broadband UK guide (top content-priority-analysis target)</t>
+          <t>Run original-research outreach and digital PR</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Top-ranked target from scripts/analyze_content_priority.py's first real run: 512 AI-feature impressions in the last 28 days (real GSC data) at only 636 words. Fully rewritten to 1,596 words, drawing on already-verified provider facts from the three Awin content batches (BT, EE, Vodafone, Plusnet, Community Fibre, Hyperoptic, toob, Zen Internet) plus new research for Sky and a genuinely counter-intuitive finding worth surfacing on its own: every major national provider has a low Trustpilot score, but Ofcom's Q1 2026 complaints data separates them clearly (Plusnet best at 4/100k, TalkTalk worst at 10/100k) -- explained as two measures of different things, not a contradiction. Also verified and included Vodafone's real 2026 award wins (Expert Reviews Broadband Awards, Uswitch Most Popular Provider) alongside its poor Ofcom complaints position, rather than picking one narrative. Caught and fixed a real bug before shipping: wrote several apostrophes as literal backslash-escapes ( \' ) copying the .ts string-literal habit from data/providers.ts into JSX text content, where they would have rendered as a visible backslash -- fixed to the file's existing &amp;apos; convention and verified against the live rendered HTML, not just the build passing, before considering it done.</t>
+          <t>Build a relevant outreach list and earn citations and links to the live Ofcom-backed customer-satisfaction research.</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
         <v>54</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -7875,22 +7919,22 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>app/guides/[slug]/page.tsx (best-full-fibre-broadband-uk), data/guides.ts</t>
+          <t>/research/uk-broadband-customer-satisfaction</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>ops-content-priority-analysis-tooling</t>
+          <t>Research page and source methodology are live</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Build Status / 90 Day Roadmap</t>
         </is>
       </c>
     </row>
@@ -7900,29 +7944,29 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
+          <t>Deep rewrite: Best Full Fibre Broadband UK guide (top content-priority-analysis target)</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Review query/page performance, assisted conversions, Awin decisions and engagement data, then record the next-quarter build decisions.</t>
+          <t>Top-ranked target from scripts/analyze_content_priority.py's first real run: 512 AI-feature impressions in the last 28 days (real GSC data) at only 636 words. Fully rewritten to 1,596 words, drawing on already-verified provider facts from the three Awin content batches (BT, EE, Vodafone, Plusnet, Community Fibre, Hyperoptic, toob, Zen Internet) plus new research for Sky and a genuinely counter-intuitive finding worth surfacing on its own: every major national provider has a low Trustpilot score, but Ofcom's Q1 2026 complaints data separates them clearly (Plusnet best at 4/100k, TalkTalk worst at 10/100k) -- explained as two measures of different things, not a contradiction. Also verified and included Vodafone's real 2026 award wins (Expert Reviews Broadband Awards, Uswitch Most Popular Provider) alongside its poor Ofcom complaints position, rather than picking one narrative. Caught and fixed a real bug before shipping: wrote several apostrophes as literal backslash-escapes ( \' ) copying the .ts string-literal habit from data/providers.ts into JSX text content, where they would have rendered as a visible backslash -- fixed to the file's existing &amp;apos; convention and verified against the live rendered HTML, not just the build passing, before considering it done.</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -7931,22 +7975,22 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Next-quarter decision log</t>
+          <t>app/guides/[slug]/page.tsx (best-full-fibre-broadband-uk), data/guides.ts</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>ops-conversion-reporting-loop and sufficient observation period</t>
+          <t>ops-content-priority-analysis-tooling</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: 90 Day Roadmap</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -7956,29 +8000,29 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>User asked for a postcode -&gt; select-your-house-number address picker with customised content, and explicitly asked whether it could be built free. Researched live (WebSearch, 2026-08-23): full UK address-level lookup (the data behind 'pick your house from a list') is Royal Mail's licensed PAF data, not open -- getAddress.io, a popular free-tier provider, was shut down in Oct 2025 after a Royal Mail/IDDQD IP claim; Ideal Postcodes gives a 1-month/50-credit trial then pay-as-you-go; no provider offers a genuine unlimited free tier at real traffic. Separately, even a working address picker wouldn't improve accuracy without a paid per-address line-checker API (Openreach or provider-specific), which is a commercial relationship, not a script. Presented both findings and 3 options to the user via AskUserQuestion; they chose the free path: deepen personalisation using data already held, no new API, no new cost. Shipped: extended the existing components/PostcodeContextBar.tsx (previously only on deals/compare/provider pages) to guide pages and all 3 tool pages (speed test, broadband match, cost calculator) so a stored postcode follows the visitor through the full journey; new components/ProviderAvailabilityBadge.tsx shows a real yes/no ('BT is/isn't listed as available in {town}') on provider review pages, but only for the 51 postcode areas with real availableProviders data in data/postcodes.ts -- silently renders nothing outside that set rather than guessing; new components/ReturningVisitorBanner.tsx greets a returning visitor on the homepage with a direct link back to their own postcode's deals.</t>
+          <t>Review query/page performance, assisted conversions, Awin decisions and engagement data, then record the next-quarter build decisions.</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
         <v>53</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -7987,22 +8031,22 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>components/ProviderAvailabilityBadge.tsx, components/ReturningVisitorBanner.tsx, components/PostcodeContextBar.tsx, app/page.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/speed-test/page.tsx, app/tools/broadband-match/page.tsx, app/tools/broadband-cost-calculator/page.tsx</t>
+          <t>Next-quarter decision log</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>None -- deliberately built on data already held, no new API/cost</t>
+          <t>ops-conversion-reporting-loop and sufficient observation period</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: 90 Day Roadmap</t>
         </is>
       </c>
     </row>
@@ -8022,16 +8066,16 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Homepage visual redesign: illustrations + interactivity</t>
+          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Researched via scripts/analyze_homepage_visual_design.py against 5 UK broadband comparison homepages: none uses stock-photo hero banners; the dominant visual language is heavy inline SVG (Uswitch ships 195) and provider logos, no carousel/animation library detected anywhere. Generated 7 original on-brand SVG illustrations (scripts/generate_homepage_illustrations.py: hero network graphic, 3 colour-filled step icons, 2 gradient blobs, a quiz illustration) rather than stock photography, matching what's actually proven in this vertical. Added a scroll-reveal component, hover interactions, and restructured the Broadband Match promo to a two-column illustrated layout. Content/copy unchanged, visual/UX only.</t>
+          <t>User asked for a postcode -&gt; select-your-house-number address picker with customised content, and explicitly asked whether it could be built free. Researched live (WebSearch, 2026-08-23): full UK address-level lookup (the data behind 'pick your house from a list') is Royal Mail's licensed PAF data, not open -- getAddress.io, a popular free-tier provider, was shut down in Oct 2025 after a Royal Mail/IDDQD IP claim; Ideal Postcodes gives a 1-month/50-credit trial then pay-as-you-go; no provider offers a genuine unlimited free tier at real traffic. Separately, even a working address picker wouldn't improve accuracy without a paid per-address line-checker API (Openreach or provider-specific), which is a commercial relationship, not a script. Presented both findings and 3 options to the user via AskUserQuestion; they chose the free path: deepen personalisation using data already held, no new API, no new cost. Shipped: extended the existing components/PostcodeContextBar.tsx (previously only on deals/compare/provider pages) to guide pages and all 3 tool pages (speed test, broadband match, cost calculator) so a stored postcode follows the visitor through the full journey; new components/ProviderAvailabilityBadge.tsx shows a real yes/no ('BT is/isn't listed as available in {town}') on provider review pages, but only for the 51 postcode areas with real availableProviders data in data/postcodes.ts -- silently renders nothing outside that set rather than guessing; new components/ReturningVisitorBanner.tsx greets a returning visitor on the homepage with a direct link back to their own postcode's deals.</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>55</v>
@@ -8043,12 +8087,12 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>app/page.tsx, components/ScrollReveal.tsx, public/illustrations/</t>
+          <t>components/ProviderAvailabilityBadge.tsx, components/ReturningVisitorBanner.tsx, components/PostcodeContextBar.tsx, app/page.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/speed-test/page.tsx, app/tools/broadband-match/page.tsx, app/tools/broadband-cost-calculator/page.tsx</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None -- deliberately built on data already held, no new API/cost</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -8068,22 +8112,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Deep rewrite: Cheapest Broadband Deals UK guide (2nd content-priority-analysis target)</t>
+          <t>Homepage visual redesign: illustrations + interactivity</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Second target from scripts/analyze_content_priority.py's ranked list: 130 real GSC AI-feature impressions at 481 words, and materially stale (last touched 2026-06-01, still citing NOW Broadband at a since-changed £17.99). Rewritten to 1,101 words, drawing on session-verified pricing across 11 providers rather than fresh research for most of them. Real correction made: NOW Broadband's usable Full Fibre 75 now starts at £23/mo, not the stale £17.99 the old copy cited -- no longer reliably the cheapest option, now similar to or pricier than Plusnet (£21.99) and EE (£22.99). Real new finding: Community Fibre's Essential 35 at £12.50/mo is the genuinely cheapest full-fibre deal on the market (London/Surrey/Sussex only). Verified current social tariff pricing (Virgin Media £12.50, BT Home Essentials £15-20, Sky Broadband Basics £20 existing-customers-only) plus a real, citable Ofcom stat: ~4.2 million eligible households, only ~532,000 actually claiming one. Caught the same JSX-vs-.ts apostrophe-escaping bug found on the previous guide (one instance this time, in the NOW Broadband paragraph) before shipping -- confirmed via the file's own reviewSources-style checked-date convention. 1,101 words sits just under this session's own 1,200-word guide depth floor; left as is rather than padding for its own sake, since the content is already comprehensive (2 real data tables, 5 FAQs, all newly sourced).</t>
+          <t>Researched via scripts/analyze_homepage_visual_design.py against 5 UK broadband comparison homepages: none uses stock-photo hero banners; the dominant visual language is heavy inline SVG (Uswitch ships 195) and provider logos, no carousel/animation library detected anywhere. Generated 7 original on-brand SVG illustrations (scripts/generate_homepage_illustrations.py: hero network graphic, 3 colour-filled step icons, 2 gradient blobs, a quiz illustration) rather than stock photography, matching what's actually proven in this vertical. Added a scroll-reveal component, hover interactions, and restructured the Broadband Match promo to a two-column illustrated layout. Content/copy unchanged, visual/UX only.</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -8099,12 +8143,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>app/guides/[slug]/page.tsx (cheapest-broadband-uk), data/guides.ts</t>
+          <t>app/page.tsx, components/ScrollReveal.tsx, public/illustrations/</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>ops-content-priority-analysis-tooling</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -8114,7 +8158,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8124,29 +8168,29 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Mobile and cross-device navigation overhaul</t>
+          <t>Deep rewrite: Cheapest Broadband Deals UK guide (2nd content-priority-analysis target)</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>New scripts/analyze_mobile_ux.py scanned Uswitch, broadband.co.uk and choose.co.uk (MoneySavingExpert 403, reported not bypassed) with a mobile Safari user agent for markup/CSS signals: viewport meta and hamburger menu markers were universal but already correct on our own site; tel: click-to-call was absent everywhere (0/4, skipped); sticky bottom CTA (1/4) and apple-touch-icon (2/4) were too weak/incomplete to act on. The real gap was found by direct inspection, not the scan: the mobile nav was a small anchored dropdown of 10 flat links with ~36px touch targets, while the desktop nav beside it was a full mega-menu, and the header postcode checker was desktop-only so phone users had no quick postcode access outside the homepage/deals page. Replaced it with new components/MobileNav.tsx: a full-width slide-down panel reusing the desktop mega-menu's own icon/link data (exported from MainNav.tsx, so the two can't drift apart), every link at a 44px (min-h-11) touch target, and the postcode checker embedded at the top so it's reachable from any page. Added anchor ids to /guides category sections so the new mobile Guides menu jumps to a real target instead of an unread query param.</t>
+          <t>Second target from scripts/analyze_content_priority.py's ranked list: 130 real GSC AI-feature impressions at 481 words, and materially stale (last touched 2026-06-01, still citing NOW Broadband at a since-changed £17.99). Rewritten to 1,101 words, drawing on session-verified pricing across 11 providers rather than fresh research for most of them. Real correction made: NOW Broadband's usable Full Fibre 75 now starts at £23/mo, not the stale £17.99 the old copy cited -- no longer reliably the cheapest option, now similar to or pricier than Plusnet (£21.99) and EE (£22.99). Real new finding: Community Fibre's Essential 35 at £12.50/mo is the genuinely cheapest full-fibre deal on the market (London/Surrey/Sussex only). Verified current social tariff pricing (Virgin Media £12.50, BT Home Essentials £15-20, Sky Broadband Basics £20 existing-customers-only) plus a real, citable Ofcom stat: ~4.2 million eligible households, only ~532,000 actually claiming one. Caught the same JSX-vs-.ts apostrophe-escaping bug found on the previous guide (one instance this time, in the NOW Broadband paragraph) before shipping -- confirmed via the file's own reviewSources-style checked-date convention. 1,101 words sits just under this session's own 1,200-word guide depth floor; left as is rather than padding for its own sake, since the content is already comprehensive (2 real data tables, 5 FAQs, all newly sourced).</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -8155,12 +8199,12 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>components/MobileNav.tsx, components/MainNav.tsx, app/layout.tsx, app/guides/page.tsx</t>
+          <t>app/guides/[slug]/page.tsx (cheapest-broadband-uk), data/guides.ts</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ops-content-priority-analysis-tooling</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -8170,7 +8214,7 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8190,19 +8234,19 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Mobile and cross-device navigation overhaul</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
+          <t>New scripts/analyze_mobile_ux.py scanned Uswitch, broadband.co.uk and choose.co.uk (MoneySavingExpert 403, reported not bypassed) with a mobile Safari user agent for markup/CSS signals: viewport meta and hamburger menu markers were universal but already correct on our own site; tel: click-to-call was absent everywhere (0/4, skipped); sticky bottom CTA (1/4) and apple-touch-icon (2/4) were too weak/incomplete to act on. The real gap was found by direct inspection, not the scan: the mobile nav was a small anchored dropdown of 10 flat links with ~36px touch targets, while the desktop nav beside it was a full mega-menu, and the header postcode checker was desktop-only so phone users had no quick postcode access outside the homepage/deals page. Replaced it with new components/MobileNav.tsx: a full-width slide-down panel reusing the desktop mega-menu's own icon/link data (exported from MainNav.tsx, so the two can't drift apart), every link at a 44px (min-h-11) touch target, and the postcode checker embedded at the top so it's reachable from any page. Added anchor ids to /guides category sections so the new mobile Guides menu jumps to a real target instead of an unread query param.</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -8211,7 +8255,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>components/MainNav.tsx, app/layout.tsx</t>
+          <t>components/MobileNav.tsx, components/MainNav.tsx, app/layout.tsx, app/guides/page.tsx</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8246,19 +8290,19 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Animated, interactive mobile menu with click-outside-to-close</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Direct UX/interaction-design request, not a scraping pass. Rewrote components/MobileNav.tsx from a native &lt;details&gt; element (no animation, no click-outside-to-close) to a controlled client component: hamburger icon morphs into an X on open; a blurred backdrop closes the menu on click or Escape; the panel and its sections slide/fade in with a staggered delay reusing the same transition idiom as components/ScrollReveal.tsx; Providers/Postcode/Guides/Tools became single-open accordions using a CSS-only grid-template-rows 0fr-&gt;1fr transition (no JS height measurement); the menu auto-closes on route change via usePathname(); background scroll is locked while open; focus moves into the panel on open and returns to the trigger on Escape. Global prefers-reduced-motion handling already in app/globals.css applies automatically. Not visually verified on a real device — no browser automation tool available this session, validated via build output, generated CSS and server-rendered markup only.</t>
+          <t>Extended scripts/scrape_navigation_patterns.py with mega-menu structural detection (top-level item count, icons-in-dropdown, descriptive subtext, nesting depth). Found Uswitch uses icons in dropdown items and broadband.co.uk uses one-line descriptions under category groups — both implemented. Built components/MainNav.tsx: Providers, Postcode, Guides and Tools are now dropdowns with icons and descriptions; Compare and Deals stay direct links as primary single-destination actions. The Guides dropdown is a real mega-menu pulling the site's actual 6 guide categories and their real guides live from data/guides.ts — stays correct as the pipeline adds guides, no hardcoding. CSS-only (group-hover/group-focus-within), keyboard-reachable via Tab, no JS dependency.</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -8267,7 +8311,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>components/MobileNav.tsx</t>
+          <t>components/MainNav.tsx, app/layout.tsx</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -8292,29 +8336,29 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Deep rewrite: Best Business Broadband Providers UK guide (3rd content-priority-analysis target)</t>
+          <t>Animated, interactive mobile menu with click-outside-to-close</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Third target from scripts/analyze_content_priority.py's ranked list: 142 real GSC AI-feature impressions at 596 words. This page lives on a different template than the [slug]-based guides (app/guides/best-business-broadband-providers-uk/ is a standalone PrioritySeoPage route backed by data/priority-pages.ts), and had 2 pre-existing em dashes fixed as part of the pass. Rewritten to 1,050 words with real, specific per-provider data: Vodafone Business has the most competitive entry-level price (~£20-22/mo excl. VAT), Zen Business leads on satisfaction (Which? Recommended since 2021, 84% score) -- consistent with, and corroborating, the consumer Zen Internet findings from the Awin-rejected batch, Virgin Media Business has the fastest raw speed (442 Mbps average), and a genuinely useful, specific stat: out-of-contract business customers overpay 24.86% more per month on average. Added a real contended-vs-uncontended leased-line explainer with current pricing (from ~£69/mo entry-level). Also fixed a real bug in the analysis script itself found while validating this page: DATE_RE didn't recognise the PrioritySeoPage template's 'Last researched and reviewed:' phrasing (colon, different verb), so every page on that template was incorrectly scored as having no checked date -- fixed and confirmed it also corrected the score for /guides/satellite-broadband-uk on the same template.</t>
+          <t>Direct UX/interaction-design request, not a scraping pass. Rewrote components/MobileNav.tsx from a native &lt;details&gt; element (no animation, no click-outside-to-close) to a controlled client component: hamburger icon morphs into an X on open; a blurred backdrop closes the menu on click or Escape; the panel and its sections slide/fade in with a staggered delay reusing the same transition idiom as components/ScrollReveal.tsx; Providers/Postcode/Guides/Tools became single-open accordions using a CSS-only grid-template-rows 0fr-&gt;1fr transition (no JS height measurement); the menu auto-closes on route change via usePathname(); background scroll is locked while open; focus moves into the panel on open and returns to the trigger on Escape. Global prefers-reduced-motion handling already in app/globals.css applies automatically. Not visually verified on a real device — no browser automation tool available this session, validated via build output, generated CSS and server-rendered markup only.</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
         <v>50</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -8323,12 +8367,12 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>data/priority-pages.ts (business), scripts/analyze_content_priority.py</t>
+          <t>components/MobileNav.tsx</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>ops-content-priority-analysis-tooling</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -8338,7 +8382,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8348,29 +8392,29 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Deep rewrite: Best Business Broadband Providers UK guide (3rd content-priority-analysis target)</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
+          <t>Third target from scripts/analyze_content_priority.py's ranked list: 142 real GSC AI-feature impressions at 596 words. This page lives on a different template than the [slug]-based guides (app/guides/best-business-broadband-providers-uk/ is a standalone PrioritySeoPage route backed by data/priority-pages.ts), and had 2 pre-existing em dashes fixed as part of the pass. Rewritten to 1,050 words with real, specific per-provider data: Vodafone Business has the most competitive entry-level price (~£20-22/mo excl. VAT), Zen Business leads on satisfaction (Which? Recommended since 2021, 84% score) -- consistent with, and corroborating, the consumer Zen Internet findings from the Awin-rejected batch, Virgin Media Business has the fastest raw speed (442 Mbps average), and a genuinely useful, specific stat: out-of-contract business customers overpay 24.86% more per month on average. Added a real contended-vs-uncontended leased-line explainer with current pricing (from ~£69/mo entry-level). Also fixed a real bug in the analysis script itself found while validating this page: DATE_RE didn't recognise the PrioritySeoPage template's 'Last researched and reviewed:' phrasing (colon, different verb), so every page on that template was incorrectly scored as having no checked date -- fixed and confirmed it also corrected the score for /guides/satellite-broadband-uk on the same template.</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
@@ -8379,22 +8423,22 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
+          <t>data/priority-pages.ts (business), scripts/analyze_content_priority.py</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>Email delivery provider</t>
+          <t>ops-content-priority-analysis-tooling</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8409,24 +8453,24 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
+          <t>data/provider-live-deals.json already tracks live pricing. An email/notification layer on top ("tell me if broadband in my postcode drops below £X") is mostly wiring, and it's a retention mechanic none of the readable competitors emphasised as much as their comparison tables.</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
         <v>49</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -8435,22 +8479,22 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
+          <t>New subscription flow + data/provider-live-deals.json</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Email delivery provider</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>Growth playbook — Functionality pillar</t>
         </is>
       </c>
     </row>
@@ -8470,28 +8514,28 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
+          <t>New scripts/analyze_page_type_ux.py scans competitor pages by theme (deals listing, provider review, guide article, postcode/checker hub) rather than homepage-only, against Uswitch, broadband.co.uk, choose.co.uk and MoneySavingExpert (403, reported not bypassed). Confirmed signals: comparison checkboxes near-universal; badge/chip labels on deals listings + review index; TOC on the guide article + one deals listing; pros/cons on provider review + deals; related-content on provider review + deals; rating widget on one deals listing. No dedicated postcode-hub competitor page exists in this vertical. Shipped strictly against confirmed signals: computed Best Value/Fastest/Editor's Pick badges in components/DealTable.tsx; new components/RatingStars.tsx replacing plain-text Trustpilot scores plus a 'How {provider} compares' related-comparisons module on provider pages; a jump-to-section table of contents on guide pages via new lib/extractHeadings.tsx (JSX-tree heading-ID injection, avoids hand-editing 40 existing guide definitions), gated behind 3+ headings; and the same cheapest/fastest badges plus rating stars carried onto postcode-hub provider cards since deals and hub serve the same comparison job.</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>app/layout.tsx, components/Logo.tsx</t>
+          <t>components/DealTable.tsx, components/RatingStars.tsx, lib/extractHeadings.tsx, app/providers/[slug]/page.tsx, app/guides/[slug]/page.tsx, app/postcode/[area]/page.tsx</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -8516,38 +8560,38 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Research-led editorial refresh: Best Broadband and TV Deals guide</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>User-requested application of the same Stage 3/4/4a research process from the Awin content batches to a single existing guide page, /guides/best-broadband-and-tv-deals. Unlike the thin provider stubs rewritten in the Awin batches, this guide was already well-built (tables, methodology, 7 FAQs, real Ofcom citations, last checked 29 July 2026) -- not a stub needing a ground-up rewrite, so this was a verify-and-deepen pass grounded in fresh research rather than a full replacement. Scraped 2 top-ranking competitors (MoneySuperMarket, Uswitch) per Stage 3.0: found MoneySupermarket runs a 15-question FAQ (ours had 7) and leads with an expert-quoted bundling-savings statistic. Traced that claim to its actual primary source rather than citing the secondary restatement: Ofcom's own February 2026 research, savings of £26-£48/month from bundling and pay-TV averaging £12/month within a bundle (23% real-terms fall) -- a stronger, more current, primary-sourced figure than the competitor's 2023-dated stat, added as a new section. Also found and added two genuinely new, specific facts the page didn't have: Virgin Media's Max Volt bundle (real current pricing including its two scheduled rises to April 2028) as a concrete worked example, and Virgin Media's 'Most Reliable Broadband Provider' win at the 2026 Uswitch Telecoms Awards (Opensignal-verified, a genuine third-party measurement). Named the specific Sky bundle example (Sky Stream, Sky TV, Netflix + Full Fibre 300, £35/month) that the existing copy referenced only vaguely. Added 2 new FAQs tied to the new content. Fixed 2 pre-existing em dashes found during the pass (a legitimate en-dash numeric range, '50-100Mbps', was left alone -- not an AI-tell, different typographic use). Updated the page's stated fact-check date and guides.ts updatedDate to 2026-08-24.</t>
+          <t>Extended scripts/analyze_homepage_visual_design.py with footer-specific detection (logo, social icons, accordion/back-to-top, hover density). Confirmed directly in app/layout.tsx (not just inferred from the scan) that the footer had no logo at all. Added components/Logo.tsx (extracted from the header, reused larger in the footer with a tagline), made the 6 footer link columns &lt;details open&gt; elements with a mobile-only collapse toggle (desktop behaves exactly as static headings did, via lg:pointer-events-none, so nothing is at risk of accidental collapse), upgraded the social link to a hover-interactive pill button, and added a 'Back to top' link using the existing global smooth-scroll behaviour.</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
         <v>48</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>app/guides/[slug]/page.tsx (best-broadband-and-tv-deals), data/guides.ts</t>
+          <t>app/layout.tsx, components/Logo.tsx</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8562,7 +8606,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8572,29 +8616,29 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Research-led editorial refresh: Best Broadband and TV Deals guide</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
+          <t>User-requested application of the same Stage 3/4/4a research process from the Awin content batches to a single existing guide page, /guides/best-broadband-and-tv-deals. Unlike the thin provider stubs rewritten in the Awin batches, this guide was already well-built (tables, methodology, 7 FAQs, real Ofcom citations, last checked 29 July 2026) -- not a stub needing a ground-up rewrite, so this was a verify-and-deepen pass grounded in fresh research rather than a full replacement. Scraped 2 top-ranking competitors (MoneySuperMarket, Uswitch) per Stage 3.0: found MoneySupermarket runs a 15-question FAQ (ours had 7) and leads with an expert-quoted bundling-savings statistic. Traced that claim to its actual primary source rather than citing the secondary restatement: Ofcom's own February 2026 research, savings of £26-£48/month from bundling and pay-TV averaging £12/month within a bundle (23% real-terms fall) -- a stronger, more current, primary-sourced figure than the competitor's 2023-dated stat, added as a new section. Also found and added two genuinely new, specific facts the page didn't have: Virgin Media's Max Volt bundle (real current pricing including its two scheduled rises to April 2028) as a concrete worked example, and Virgin Media's 'Most Reliable Broadband Provider' win at the 2026 Uswitch Telecoms Awards (Opensignal-verified, a genuine third-party measurement). Named the specific Sky bundle example (Sky Stream, Sky TV, Netflix + Full Fibre 300, £35/month) that the existing copy referenced only vaguely. Added 2 new FAQs tied to the new content. Fixed 2 pre-existing em dashes found during the pass (a legitimate en-dash numeric range, '50-100Mbps', was left alone -- not an AI-tell, different typographic use). Updated the page's stated fact-check date and guides.ts updatedDate to 2026-08-24.</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
@@ -8603,22 +8647,22 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Sitewide template performance report</t>
+          <t>app/guides/[slug]/page.tsx (best-broadband-and-tv-deals), data/guides.ts</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>Field data or representative lab baselines</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8628,53 +8672,53 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Direct Awin Publisher API access — programme status and link generation</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>User asked to connect Claude to their Awin account and provided a real API token. There's no one-click connector for Awin (unlike Google Drive/Gmail), so this uses Awin's own Publisher API directly. First live run corrected two wrong assumptions from documentation research: 'programmedetails' requires a specific advertiserId (not a bulk listing endpoint) -- the actual bulk-status endpoint is GET /publishers/{id}/programmes?relationship=X, and 'any' is not a valid value for it (loops joined/pending/suspended/rejected instead; 'notjoined' returns the ~21k whole-platform catalogue so it's excluded from the default and only fetched on request). POST /publishers/{id}/linkbuilder/generate confirmed working, verified against TalkTalk (advertiser 3674). REAL FINDING from the first run, both surfaced to the user and worth acting on: only 4 programmes are joined (TalkTalk, Broadband Genie, Zzoomm, Highland Broadband), 7 pending (Sky ROI, Community Fibre, National Broadband, Trooli, Pine Media, Cuckoo, Zen Internet), and 9 REJECTED including BT (both consumer and business), Vodafone, Plusnet, EE, Virgin Media, Hyperoptic and toob. Cross-checked data/providers.ts: none of the currently-live affiliateUrl values (including TalkTalk, which IS approved) use Awin's awin1.com tracking format -- they're all plain provider URLs, so the site is very likely not earning commission on any current outbound click, joined or not, despite the on-page commercial disclosures implying it might.</t>
+          <t>Track LCP, INP and CLS by page template and prioritise JS or image-weight fixes from evidence.</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>47</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>scripts/awin_sync.py</t>
+          <t>Sitewide template performance report</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>AWIN_API_TOKEN from the user's Awin account (user menu -&gt; API Credentials)</t>
+          <t>Field data or representative lab baselines</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -8684,43 +8728,43 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Deep rewrite: Best 5G Home Broadband UK guide (4th content-priority-analysis target)</t>
+          <t>Direct Awin Publisher API access — programme status and link generation</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Fourth target from scripts/analyze_content_priority.py's ranked list: 30 real GSC AI-feature impressions at 601 words, and the old copy named no real providers or prices at all, just generic 5G-vs-fibre advice. Rewritten to 1,036 words with real current data for all 4 major UK 5G home broadband options: Three (best value, from GBP29/mo, ~150 Mbps), Vodafone GigaCube (cheapest fixed term at GBP21/mo, or a genuine GBP60/mo no-contract option), EE Smart 5G Hub (broadest UK 5G coverage, GBP30-50/mo), and National Broadband (already deeply covered in the Awin-pending batch) framed correctly here as a multi-network specialist rather than a single-network alternative -- it connects to whichever of the 4 UK networks is strongest at a given address, a genuinely different value proposition worth explaining rather than just listing as a fourth option. Found and included a real Trustpilot-vs-Ofcom divergence for Three specifically (4.5 Trustpilot, worst-quartile Ofcom complaints alongside EE and Vodafone) and linked to the full-fibre guide's deeper explanation of that pattern rather than repeating it in full.</t>
+          <t>User asked to connect Claude to their Awin account and provided a real API token. There's no one-click connector for Awin (unlike Google Drive/Gmail), so this uses Awin's own Publisher API directly. First live run corrected two wrong assumptions from documentation research: 'programmedetails' requires a specific advertiserId (not a bulk listing endpoint) -- the actual bulk-status endpoint is GET /publishers/{id}/programmes?relationship=X, and 'any' is not a valid value for it (loops joined/pending/suspended/rejected instead; 'notjoined' returns the ~21k whole-platform catalogue so it's excluded from the default and only fetched on request). POST /publishers/{id}/linkbuilder/generate confirmed working, verified against TalkTalk (advertiser 3674). REAL FINDING from the first run, both surfaced to the user and worth acting on: only 4 programmes are joined (TalkTalk, Broadband Genie, Zzoomm, Highland Broadband), 7 pending (Sky ROI, Community Fibre, National Broadband, Trooli, Pine Media, Cuckoo, Zen Internet), and 9 REJECTED including BT (both consumer and business), Vodafone, Plusnet, EE, Virgin Media, Hyperoptic and toob. Cross-checked data/providers.ts: none of the currently-live affiliateUrl values (including TalkTalk, which IS approved) use Awin's awin1.com tracking format -- they're all plain provider URLs, so the site is very likely not earning commission on any current outbound click, joined or not, despite the on-page commercial disclosures implying it might.</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
         <v>47</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>app/guides/[slug]/page.tsx (best-5g-home-broadband-uk), data/guides.ts</t>
+          <t>scripts/awin_sync.py</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>ops-content-priority-analysis-tooling</t>
+          <t>AWIN_API_TOKEN from the user's Awin account (user menu -&gt; API Credentials)</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
@@ -8730,7 +8774,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
+          <t>User request 2026-08-23 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8740,29 +8784,29 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Deep rewrite: Best 5G Home Broadband UK guide (4th content-priority-analysis target)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
+          <t>Fourth target from scripts/analyze_content_priority.py's ranked list: 30 real GSC AI-feature impressions at 601 words, and the old copy named no real providers or prices at all, just generic 5G-vs-fibre advice. Rewritten to 1,036 words with real current data for all 4 major UK 5G home broadband options: Three (best value, from GBP29/mo, ~150 Mbps), Vodafone GigaCube (cheapest fixed term at GBP21/mo, or a genuine GBP60/mo no-contract option), EE Smart 5G Hub (broadest UK 5G coverage, GBP30-50/mo), and National Broadband (already deeply covered in the Awin-pending batch) framed correctly here as a multi-network specialist rather than a single-network alternative -- it connects to whichever of the 4 UK networks is strongest at a given address, a genuinely different value proposition worth explaining rather than just listing as a fourth option. Found and included a real Trustpilot-vs-Ofcom divergence for Three specifically (4.5 Trustpilot, worst-quartile Ofcom complaints alongside EE and Vodafone) and linked to the full-fibre guide's deeper explanation of that pattern rather than repeating it in full.</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -8771,22 +8815,22 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Sitewide mobile layout</t>
+          <t>app/guides/[slug]/page.tsx (best-5g-home-broadband-uk), data/guides.ts</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Mobile analytics/drop-off data</t>
+          <t>ops-content-priority-analysis-tooling</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — UX pillar</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8796,29 +8840,29 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Deep rewrite: Best Phone and Broadband Deals guide (5th content-priority-analysis target)</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Fifth target from scripts/analyze_content_priority.py's ranked list: the old copy was generic Digital Voice/line-rental advice with no dates, no stats and one pre-existing em dash, at 457 words. Rewritten with the real PSTN switch-off timeline: full shutdown now locked in for 31 January 2027 (moved from the original December 2025 target after Openreach confirmed the technical barriers were resolved), with PSTN customer numbers falling from 5.2 million (July 2024) to 3.2 million (July 2025). Added Ofcom's minimum one-hour battery backup requirement for emergency-services access during a power cut, and the industry PSTN Charter's commitment not to migrate telecare/vulnerable users without confirmed-compatible equipment. Added a real, specific call-plan cost example (TalkTalk's Anytime Calls add-on at GBP12/mo on top of base broadband) to replace the previous fully generic 'compare the whole contract' advice. FAQs expanded from 3 to 5. Fixed the pre-existing em dash in the dek field.</t>
+          <t>The competitor evidence (15k–23k word desktop hubs) is desktop-shaped. On mobile that content needs a different information architecture — sticky summary bar, collapsed sections, thumb-reachable CTAs. Worth a dedicated pass once analytics show where mobile users drop off.</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
         <v>45</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
@@ -8827,22 +8871,22 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>data/priority-pages.ts (phone)</t>
+          <t>Sitewide mobile layout</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>ops-content-priority-analysis-tooling</t>
+          <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
+          <t>Growth playbook — UX pillar</t>
         </is>
       </c>
     </row>
@@ -8852,53 +8896,53 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Deep rewrite: Best Phone and Broadband Deals guide (5th content-priority-analysis target)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
+          <t>Fifth target from scripts/analyze_content_priority.py's ranked list: the old copy was generic Digital Voice/line-rental advice with no dates, no stats and one pre-existing em dash, at 457 words. Rewritten with the real PSTN switch-off timeline: full shutdown now locked in for 31 January 2027 (moved from the original December 2025 target after Openreach confirmed the technical barriers were resolved), with PSTN customer numbers falling from 5.2 million (July 2024) to 3.2 million (July 2025). Added Ofcom's minimum one-hour battery backup requirement for emergency-services access during a power cut, and the industry PSTN Charter's commitment not to migrate telecare/vulnerable users without confirmed-compatible equipment. Added a real, specific call-plan cost example (TalkTalk's Anytime Calls add-on at GBP12/mo on top of base broadband) to replace the previous fully generic 'compare the whole contract' advice. FAQs expanded from 3 to 5. Fixed the pre-existing em dash in the dek field.</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G38" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="G38" s="2" t="n">
-        <v>48</v>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Sitewide crawl and redirect report</t>
+          <t>data/priority-pages.ts (phone)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ops-content-priority-analysis-tooling</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -8908,43 +8952,43 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Crawlability</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>Monitor broken inbound and internal URLs and maintain relevant one-hop redirects.</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>Sitewide crawl and redirect report</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
@@ -8954,7 +8998,7 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>BroadbandPicker SEO &amp; Content Plan — Live: Technical SEO</t>
         </is>
       </c>
     </row>
@@ -8969,24 +9013,24 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -8995,12 +9039,12 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -9010,7 +9054,7 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -9025,53 +9069,109 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F41" s="3" t="n">
+      <c r="F42" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G41" s="3" t="n">
+      <c r="G42" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K41" s="3" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L41" s="3" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L41"/>
+  <autoFilter ref="A1:L42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9112,7 +9212,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>73 total (33 page builds, 40 feature/strategy builds); 59 already marked Done.</t>
+          <t>74 total (33 page builds, 41 feature/strategy builds); 60 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -176,8 +176,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L75" headerRowCount="1">
-  <autoFilter ref="A1:L75"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L76" headerRowCount="1">
+  <autoFilter ref="A1:L76"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -241,8 +241,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L42" headerRowCount="1">
-  <autoFilter ref="A1:L42"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L43" headerRowCount="1">
+  <autoFilter ref="A1:L43"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:L76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>content-refresh-now-broadband-provider-page</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -3931,23 +3931,23 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Deep rewrite: NOW Broadband provider page (7th content-priority-analysis target)</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr"/>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3970,19 +3970,19 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -4014,19 +4014,19 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
@@ -4042,8 +4042,52 @@
       <c r="K75" s="3" t="inlineStr"/>
       <c r="L75" s="3" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L75"/>
+  <autoFilter ref="A1:L76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6795,7 +6839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9008,7 +9052,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -9018,43 +9062,43 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Deep rewrite: NOW Broadband provider page (7th content-priority-analysis target)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>Seventh target from scripts/analyze_content_priority.py's ranked list: /providers/now-broadband was 386 words with no excerpt or contentSections, and its top-level fields were stale on two counts that research corrected -- contractLengths was still [12] (NOW dropped its flexible 12-month contracts; every current package is now a standard 24-month term, per thinkbroadband's dedicated news item on the change) and monthlyPriceFrom was a stale GBP17.99 against a real current cheapest tier of GBP23 (Full Fibre 100). Rewritten to ~1,450 words with 5 contentSections. The genuinely distinctive finding here, different from every other Trustpilot-vs-Ofcom section written this session: NOW is a real exception to the usual pattern, scoring poorly on BOTH Trustpilot (1.2/5, corrected from a stale 3.2) AND Ofcom's Q4 2025 complaints data (11 per 100k vs the 8 industry average), noticeably worse than sister brand Sky on the same underlying Openreach network -- written up as a genuine data point about support quality diverging from infrastructure quality within the same corporate group, not just review-platform noise. Also corrected trustpilotScore 3.2 -&gt; 1.2.</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>data/providers.ts (now-broadband)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>ops-content-priority-analysis-tooling</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -9069,24 +9113,24 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
@@ -9095,12 +9139,12 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
@@ -9110,7 +9154,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -9125,53 +9169,109 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="F43" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G43" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="I43" s="3" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="K43" s="3" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="L43" s="3" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L42"/>
+  <autoFilter ref="A1:L43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9212,7 +9312,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>74 total (33 page builds, 41 feature/strategy builds); 60 already marked Done.</t>
+          <t>75 total (33 page builds, 42 feature/strategy builds); 61 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -176,8 +176,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L76" headerRowCount="1">
-  <autoFilter ref="A1:L76"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L77" headerRowCount="1">
+  <autoFilter ref="A1:L77"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -241,8 +241,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L43" headerRowCount="1">
-  <autoFilter ref="A1:L43"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L44" headerRowCount="1">
+  <autoFilter ref="A1:L44"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3960,12 +3960,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>content-refresh-youfibre-provider-page</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3975,23 +3975,23 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Deep rewrite: YouFibre provider page (8th content-priority-analysis target)</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -4014,19 +4014,19 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4058,19 +4058,19 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -4086,8 +4086,52 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
     </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr"/>
+      <c r="K77" s="3" t="inlineStr"/>
+      <c r="L77" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L76"/>
+  <autoFilter ref="A1:L77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6839,7 +6883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9108,7 +9152,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -9118,43 +9162,43 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Deep rewrite: YouFibre provider page (8th content-priority-analysis target)</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>Eighth target from scripts/analyze_content_priority.py's ranked list: /providers/youfibre was 397 words with no excerpt or contentSections. Rewritten to ~1,575 words with 6 contentSections. The standout finding, verified against a primary Virgin Media O2 press release after a first-pass WebSearch AI summary over-stated it as a done deal: YouFibre's parent company, Substantial Group (Netomnia), is being acquired for GBP2bn by nexfibre (a joint venture of InfraVia, Liberty Global and Telefonica), which then plans to resell the YouFibre/Brsk retail brands to Virgin Media O2 for GBP150m -- announced Feb 2026, referred to the CMA for a Phase 2 investigation on 1 July 2026, and NOT yet completed (expected ~Q3 2026 at the earliest). Also wrote up the real, documented fallout from the March 2026 Brsk-to-YouFibre customer migration (billing errors, login/password-reset failures, reported speed drops, overwhelmed support chat), sourced from ISPreview rather than the vague pre-existing 'Trustpilot sentiment has been mixed' line. Updated the speeds array to the real current tiers (200/1000/2000/8000 Mbps symmetrical, replacing stale 200/900/1800) and contractLengths from [1,12,24] to [1,24] to match the two options confirmed by current pricing research.</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>data/providers.ts (youfibre)</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>ops-content-priority-analysis-tooling</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -9169,24 +9213,24 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -9195,12 +9239,12 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -9210,7 +9254,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -9225,53 +9269,109 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F43" s="3" t="n">
+      <c r="F44" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G43" s="3" t="n">
+      <c r="G44" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K43" s="3" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L43" s="3" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L43"/>
+  <autoFilter ref="A1:L44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9312,7 +9412,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>75 total (33 page builds, 42 feature/strategy builds); 61 already marked Done.</t>
+          <t>76 total (33 page builds, 43 feature/strategy builds); 62 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -176,8 +176,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L77" headerRowCount="1">
-  <autoFilter ref="A1:L77"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L78" headerRowCount="1">
+  <autoFilter ref="A1:L78"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -241,8 +241,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L44" headerRowCount="1">
-  <autoFilter ref="A1:L44"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L45" headerRowCount="1">
+  <autoFilter ref="A1:L45"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:L78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4004,12 +4004,12 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>content-refresh-best-broadband-providers-uk-guide</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -4019,23 +4019,23 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Deep rewrite: Best Broadband Providers UK ranking guide (9th content-priority-analysis target)</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr"/>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>bet-annual-research-report</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4058,19 +4058,19 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -4102,19 +4102,19 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
@@ -4130,8 +4130,52 @@
       <c r="K77" s="3" t="inlineStr"/>
       <c r="L77" s="3" t="inlineStr"/>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L77"/>
+  <autoFilter ref="A1:L78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6883,7 +6927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9208,7 +9252,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -9218,43 +9262,43 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Deep rewrite: Best Broadband Providers UK ranking guide (9th content-priority-analysis target)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
+          <t>Ninth target from scripts/analyze_content_priority.py's ranked list. This ranking page's data was badly stale: it cited Q4 2025 Ofcom complaints figures and June-2026 Trustpilot scores that had already been superseded by this site's own freshly-researched provider pages (Sky, NOW Broadband, BT, Virgin Media, EE, Plusnet, Vodafone, TalkTalk from earlier this session). Rather than re-researching each provider from scratch, cross-referenced this page's ranking table against data/providers.ts's own already-vetted current fields (price, Trustpilot, reviewedDate) and fetched a fresh single-source Ofcom Q1 2026 complaints table (published 23 July 2026, record-low industry average of 6 per 100k) to replace the mixed-quarter data. Corrected several materially wrong claims: TalkTalk was still framed as 'budget only' at GBP19.99 when it is now GBP25 and no longer the cheapest big-name option; Community Fibre was described as 'London-only' when coverage has expanded into Surrey and Sussex; EE's 'best for reliability' halo no longer holds under Q1 2026 data (6 per 100k, tied with Virgin Media, not uniquely best). Added a new section contrasting sister brands Sky (5 per 100k) and NOW Broadband (11 per 100k, different quarter, footnoted) on the identical Openreach network, a genuine support-quality data point. Word count 872 -&gt; 1,333.</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>New annual research page + methodology extension</t>
+          <t>app/guides/[slug]/page.tsx (best-broadband-providers-uk), data/guides.ts</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
+          <t>ops-content-priority-analysis-tooling</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Content pillar</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -9269,24 +9313,24 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>No competitor scanned publishes original research. Built on the existing /research page's methodology, an annual report is a natural press/backlink asset a comparison-table page can never be.</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
@@ -9295,12 +9339,12 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>New annual research page + methodology extension</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
@@ -9310,7 +9354,7 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
@@ -9325,53 +9369,109 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="n">
+      <c r="F45" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G45" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="K45" s="3" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="L45" s="3" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L44"/>
+  <autoFilter ref="A1:L45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9412,7 +9512,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>76 total (33 page builds, 43 feature/strategy builds); 62 already marked Done.</t>
+          <t>77 total (33 page builds, 44 feature/strategy builds); 63 already marked Done.</t>
         </is>
       </c>
     </row>

--- a/docs/master-build-tracker.xlsx
+++ b/docs/master-build-tracker.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Tracker'!$A$1:$L$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pending Build Priority'!$A$1:$N$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Page Builds'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Feature &amp; Strategy Builds'!$A$1:$L$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -176,8 +176,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L78" headerRowCount="1">
-  <autoFilter ref="A1:L78"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MasterTrackerTable" displayName="MasterTrackerTable" ref="A1:L79" headerRowCount="1">
+  <autoFilter ref="A1:L79"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -241,8 +241,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L45" headerRowCount="1">
-  <autoFilter ref="A1:L45"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeatureStrategyBuildTable" displayName="FeatureStrategyBuildTable" ref="A1:L46" headerRowCount="1">
+  <autoFilter ref="A1:L46"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Type"/>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L78"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4092,38 +4092,38 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>content-refresh-broadband-without-phone-line-guide</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Deep rewrite: Broadband Without a Phone Line guide (10th content-priority-analysis target)</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr"/>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4146,19 +4146,19 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -4174,8 +4174,52 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
     </row>
+    <row r="79">
+      <c r="A79" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr"/>
+      <c r="K79" s="3" t="inlineStr"/>
+      <c r="L79" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L78"/>
+  <autoFilter ref="A1:L79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6927,7 +6971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9364,53 +9408,53 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Deep rewrite: Broadband Without a Phone Line guide (10th content-priority-analysis target)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+          <t>Tenth target from scripts/analyze_content_priority.py's ranked list: 770 words, stale pricing table (every one of 8 providers priced against months-old figures already corrected on this site's own provider pages), and a wrong PSTN switch-off date ('by the end of 2027' -- the real, now-locked-in date is 31 January 2027). Rewrote using the same PSTN research gathered for the best-phone-and-broadband-deals refresh earlier this session (5.2m -&gt; 3.2m migration stat, Ofcom's 1-hour power-cut battery backup minimum, the PSTN Charter's telecare protections), added a genuinely missing section -- 'What happens to a home phone during a power cut?' -- since the old version covered whether a line is needed at all but never addressed the actual practical question once Digital Voice is the default. Refreshed all 8 provider prices against data/providers.ts's own current fields, updated Virgin Media coverage 52% (was 53%) and added Ofcom's Spring 2026 Connected Nations split (89% gigabit-capable, 82% full fibre, 93% urban vs 66% rural). Word count 770 -&gt; 1,196; left just under the self-imposed 1,200-word floor rather than pad.</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>components/</t>
+          <t>app/guides/[slug]/page.tsx (broadband-without-phone-line), data/guides.ts</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+          <t>ops-content-priority-analysis-tooling</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Growth playbook — Functionality pillar</t>
+          <t>User request 2026-08-24 — researched before implementing per the Strategic Lens process</t>
         </is>
       </c>
     </row>
@@ -9425,53 +9469,109 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>PostcodeChecker, SpeedTest, StickyFilterBar and SocialProofCounter already exist as separate components. As the shortlist and price-alert features land, adopt accessible primitives (Radix-style) underneath rather than hand-rolling focus/keyboard behaviour again each time.</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Growth playbook — Functionality pillar</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Every guide lives as a hand-written object in data/guides.ts plus matching JSX in app/guides/[slug]/page.tsx. Fine at 30 guides; at 100+ it becomes the bottleneck. Plan a move to MDX-per-guide or a lightweight headless CMS before volume forces it.</t>
         </is>
       </c>
-      <c r="F45" s="3" t="n">
+      <c r="F46" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G45" s="3" t="n">
+      <c r="G46" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="J45" s="3" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="K45" s="3" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L45" s="3" t="inlineStr">
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>Growth playbook — Content pillar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <